--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -629,6 +629,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="17">
       <c r="A4" s="38" t="inlineStr">
         <is>
@@ -717,7 +718,7 @@
       </c>
       <c r="B11" s="40" t="inlineStr">
         <is>
-          <t>Written by the runner: raw model JSON per record.</t>
+          <t>Written by the runner: raw model JSON per record (and usage_json when the API returns token usage).</t>
         </is>
       </c>
     </row>
@@ -741,7 +742,7 @@
       </c>
       <c r="B13" s="42" t="inlineStr">
         <is>
-          <t>Written by the runner: run metadata.</t>
+          <t>Written by the runner: run metadata (includes token totals when the API returns usage).</t>
         </is>
       </c>
     </row>

--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -13,10 +13,15 @@
     <sheet name="Labels" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Records" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Lists" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="output_Results" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="output_Raw" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="output_Summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="output_Run_info" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="output_nimble_Results" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="output_nimble_Raw" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="output_nimble_Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="output_nimble_Run_info" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="output_jev_Results" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="output_jev_Raw" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="output_jev_Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="output_jev_Run_info" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="output_compare" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -28,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -129,6 +134,15 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -199,7 +213,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -326,6 +340,8 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,272 +624,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="22" customWidth="1" style="16" min="1" max="1"/>
-    <col width="90" customWidth="1" style="16" min="2" max="2"/>
+    <col width="28" customWidth="1" style="16" min="1" max="1"/>
+    <col width="110" customWidth="1" style="16" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="17">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Nimble batch classifier - control workbook</t>
+      <c r="A1" s="46" t="inlineStr">
+        <is>
+          <t>Nimble / Jev batch classifier - control workbook</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="17">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>Define questions, labels and records here. A program reads this file, sends each record to Nimble (Ollama /v1/systemone), clears any existing output_* sheets, then writes fresh output_* sheets back into this same workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Define questions, labels and records here. Run with --engine nimble or --engine jev. Each engine writes its own output_&lt;engine&gt;_* sheets and does not clear the other. When both Results sheets exist, output_compare is refreshed.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="15" customHeight="1" s="17">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>SHEETS</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="17">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>Settings: model, URL, timeout, default review threshold, test-run size.</t>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Settings: engine (nimble|jev), timeouts, review threshold, test-run size. Engine preset overrides model/base_url/endpoint.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="17">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>One row per question. Type is choice (pick one label), noul (yes/no) or score (place on a scale). Leave equipment_type blank to ask the question of every record.</t>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>One row per question. Type is choice, noul (yes/no) or score. Leave equipment_type blank to ask every record.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="17">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Labels</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>One row per answer option, for choice and score questions only. noul questions take no labels. For score questions, 'order' is the position on the scale, lowest first.</t>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Answer options for choice and score only. For score, order is scale position (lowest first).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="17">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>One row per statement to classify. Optional expected_&lt;question_id&gt; columns hold the known correct answer, so the program can measure accuracy.</t>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Statements to classify. Optional expected_&lt;question_id&gt; columns for accuracy.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="17">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Lists</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>Dropdown values (equipment types). Add new equipment types here.</t>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Dropdown values (equipment types).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="17">
-      <c r="A10" s="41" t="inlineStr">
-        <is>
-          <t>output_Results</t>
-        </is>
-      </c>
-      <c r="B10" s="42" t="inlineStr">
-        <is>
-          <t>Written by the runner: answers, confidence, review flags. Cleared at the start of each run, rewritten when the run finishes.</t>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>output_nimble_*</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Written by --engine nimble: Results, Raw, Summary, Run_info.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="17">
-      <c r="A11" s="39" t="inlineStr">
-        <is>
-          <t>output_Raw</t>
-        </is>
-      </c>
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>Written by the runner: raw model JSON per record (and usage_json when the API returns token usage).</t>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>output_jev_*</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Written by --engine jev: Results, Raw, Summary, Run_info.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="17">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>output_Summary</t>
-        </is>
-      </c>
-      <c r="B12" s="40" t="inlineStr">
-        <is>
-          <t>Written by the runner: accuracy / confidence stats (accuracy needs expected_* columns).</t>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>output_compare</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Side-by-side Nimble vs Jev answers when both Results sheets exist. Diffs highlighted.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="17">
-      <c r="A13" s="41" t="inlineStr">
-        <is>
-          <t>output_Run_info</t>
-        </is>
-      </c>
-      <c r="B13" s="42" t="inlineStr">
-        <is>
-          <t>Written by the runner: run metadata (includes token totals when the API returns usage).</t>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>COLOURS</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1" s="17">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>COLOURS</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Blue text</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Cells you edit.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="17">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>Blue text</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>Cells you edit.</t>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Black text, grey fill</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Formulas. Do not edit.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="17">
-      <c r="A16" s="39" t="inlineStr">
-        <is>
-          <t>Black text, grey fill</t>
-        </is>
-      </c>
-      <c r="B16" s="40" t="inlineStr">
-        <is>
-          <t>Formulas. Do not edit. The 'check' columns turn red when a row has a problem.</t>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Yellow row</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Flagged for review (low confidence).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="17">
-      <c r="A17" s="44" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Orange row (compare)</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Nimble and Jev answers disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="17">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>RULES</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="17">
-      <c r="A18" s="39" t="inlineStr">
+    </row>
+    <row r="19" ht="30" customHeight="1" s="17">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Use Config engine or CLI --engine. Jev needs TYPESAFE_API_KEY. Nimble needs local Ollama &gt;= 0.35.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="17">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>IDs</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
-        <is>
-          <t>question_id and label values are sent to the model as keys. Use short lowercase words with underscores, no spaces or quotes (e.g. tube_leak). question_id must be unique across the whole workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="17">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>question_id and label: short lowercase with underscores, no spaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1" s="17">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Always add 'other'</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t>Nimble can only pick from the labels you give it. Include an 'other' label on every choice question so vague records are not forced into a wrong category.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="17">
-      <c r="A20" s="41" t="inlineStr">
-        <is>
-          <t>One idea per question</t>
-        </is>
-      </c>
-      <c r="B20" s="42" t="inlineStr">
-        <is>
-          <t>Ask about what the text says, not what only an engineer would infer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1" s="17">
-      <c r="A21" s="39" t="inlineStr">
-        <is>
-          <t>Equipment type</t>
-        </is>
-      </c>
-      <c r="B21" s="40" t="inlineStr">
-        <is>
-          <t>A record is asked every question whose equipment_type matches its own, plus every question with a blank equipment_type.</t>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Include other on every choice question.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Expected values</t>
         </is>
       </c>
-      <c r="B22" s="40" t="inlineStr">
-        <is>
-          <t>For choice questions, use a label from the Labels sheet. For noul questions, use true or false. Leave blank if unknown.</t>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>choice: a Labels value; noul: true or false.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>Thresholds</t>
-        </is>
-      </c>
-      <c r="B23" s="40" t="inlineStr">
-        <is>
-          <t>review_below is the confidence under which a row is flagged for a person to review. The default of 0.6 on Config is a placeholder: tune it using records with known answers.</t>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>EXAMPLES</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
-        <is>
-          <t>EXAMPLES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Example rows</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
-        <is>
-          <t>The rows filled in on every sheet are illustrative examples for pumps, heat exchangers and distillation columns. The expected values are examples, not validated data. Replace or delete them.</t>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Illustrative pumps / exchangers / columns. Replace with your plant data.</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="17" min="1" max="1"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="B2" s="35" t="inlineStr">
         <is>
-          <t>20260930_112907</t>
+          <t>20260930_142141</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
     <row r="4">
       <c r="A4" s="35" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="B4" s="35" t="inlineStr">
@@ -951,109 +951,2536 @@
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>ollama_version</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>0.35.0</t>
+          <t>nimble</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>questions_hash</t>
+          <t>base_url</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>f73a405167a3</t>
+          <t>http://localhost:11434</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>records_in_run</t>
+          <t>endpoint_info</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.35.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>records_completed</t>
+          <t>questions_hash</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>f73a405167a3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>failed_records</t>
+          <t>api_key_configured</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>review_threshold_default</t>
+          <t>records_in_run</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>elapsed_seconds</t>
+          <t>records_completed</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>checkpoint</t>
+          <t>failed_records</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_20260930_112907.jsonl</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
+          <t>review_threshold_default</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>elapsed_seconds</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_142141.jsonl</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>6698</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>6722</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>records_with_usage</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
           <t>output_sheets</t>
         </is>
       </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>output_nimble_Results, output_nimble_Raw, output_nimble_Summary, output_nimble_Run_info</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="17" min="1" max="1"/>
+    <col width="12" customWidth="1" style="17" min="2" max="2"/>
+    <col width="12" customWidth="1" style="17" min="3" max="3"/>
+    <col width="60" customWidth="1" style="17" min="4" max="4"/>
+    <col width="16" customWidth="1" style="17" min="5" max="5"/>
+    <col width="12" customWidth="1" style="17" min="6" max="6"/>
+    <col width="10" customWidth="1" style="17" min="7" max="7"/>
+    <col width="16" customWidth="1" style="17" min="8" max="8"/>
+    <col width="12" customWidth="1" style="17" min="9" max="9"/>
+    <col width="10" customWidth="1" style="17" min="10" max="10"/>
+    <col width="16" customWidth="1" style="17" min="11" max="11"/>
+    <col width="12" customWidth="1" style="17" min="12" max="12"/>
+    <col width="10" customWidth="1" style="17" min="13" max="13"/>
+    <col width="16" customWidth="1" style="17" min="14" max="14"/>
+    <col width="12" customWidth="1" style="17" min="15" max="15"/>
+    <col width="10" customWidth="1" style="17" min="16" max="16"/>
+    <col width="16" customWidth="1" style="17" min="17" max="17"/>
+    <col width="12" customWidth="1" style="17" min="18" max="18"/>
+    <col width="10" customWidth="1" style="17" min="19" max="19"/>
+    <col width="16" customWidth="1" style="17" min="20" max="20"/>
+    <col width="12" customWidth="1" style="17" min="21" max="21"/>
+    <col width="10" customWidth="1" style="17" min="22" max="22"/>
+    <col width="16" customWidth="1" style="17" min="23" max="23"/>
+    <col width="12" customWidth="1" style="17" min="24" max="24"/>
+    <col width="10" customWidth="1" style="17" min="25" max="25"/>
+    <col width="16" customWidth="1" style="17" min="26" max="26"/>
+    <col width="12" customWidth="1" style="17" min="27" max="27"/>
+    <col width="10" customWidth="1" style="17" min="28" max="28"/>
+    <col width="16" customWidth="1" style="17" min="29" max="29"/>
+    <col width="12" customWidth="1" style="17" min="30" max="30"/>
+    <col width="10" customWidth="1" style="17" min="31" max="31"/>
+    <col width="12" customWidth="1" style="17" min="32" max="32"/>
+    <col width="45" customWidth="1" style="17" min="33" max="33"/>
+    <col width="30" customWidth="1" style="17" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>record_id</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>equipment_type</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>pump_failure_mode__answer</t>
+        </is>
+      </c>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>pump_failure_mode__confidence</t>
+        </is>
+      </c>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>pump_failure_mode__value</t>
+        </is>
+      </c>
+      <c r="H1" s="31" t="inlineStr">
+        <is>
+          <t>pump_containment__answer</t>
+        </is>
+      </c>
+      <c r="I1" s="31" t="inlineStr">
+        <is>
+          <t>pump_containment__confidence</t>
+        </is>
+      </c>
+      <c r="J1" s="31" t="inlineStr">
+        <is>
+          <t>pump_containment__value</t>
+        </is>
+      </c>
+      <c r="K1" s="31" t="inlineStr">
+        <is>
+          <t>pump_urgency__answer</t>
+        </is>
+      </c>
+      <c r="L1" s="31" t="inlineStr">
+        <is>
+          <t>pump_urgency__confidence</t>
+        </is>
+      </c>
+      <c r="M1" s="31" t="inlineStr">
+        <is>
+          <t>pump_urgency__value</t>
+        </is>
+      </c>
+      <c r="N1" s="31" t="inlineStr">
+        <is>
+          <t>hx_problem__answer</t>
+        </is>
+      </c>
+      <c r="O1" s="31" t="inlineStr">
+        <is>
+          <t>hx_problem__confidence</t>
+        </is>
+      </c>
+      <c r="P1" s="31" t="inlineStr">
+        <is>
+          <t>hx_problem__value</t>
+        </is>
+      </c>
+      <c r="Q1" s="31" t="inlineStr">
+        <is>
+          <t>hx_crosscontam__answer</t>
+        </is>
+      </c>
+      <c r="R1" s="31" t="inlineStr">
+        <is>
+          <t>hx_crosscontam__confidence</t>
+        </is>
+      </c>
+      <c r="S1" s="31" t="inlineStr">
+        <is>
+          <t>hx_crosscontam__value</t>
+        </is>
+      </c>
+      <c r="T1" s="31" t="inlineStr">
+        <is>
+          <t>hx_impact__answer</t>
+        </is>
+      </c>
+      <c r="U1" s="31" t="inlineStr">
+        <is>
+          <t>hx_impact__confidence</t>
+        </is>
+      </c>
+      <c r="V1" s="31" t="inlineStr">
+        <is>
+          <t>hx_impact__value</t>
+        </is>
+      </c>
+      <c r="W1" s="31" t="inlineStr">
+        <is>
+          <t>col_symptom__answer</t>
+        </is>
+      </c>
+      <c r="X1" s="31" t="inlineStr">
+        <is>
+          <t>col_symptom__confidence</t>
+        </is>
+      </c>
+      <c r="Y1" s="31" t="inlineStr">
+        <is>
+          <t>col_symptom__value</t>
+        </is>
+      </c>
+      <c r="Z1" s="31" t="inlineStr">
+        <is>
+          <t>col_offspec__answer</t>
+        </is>
+      </c>
+      <c r="AA1" s="31" t="inlineStr">
+        <is>
+          <t>col_offspec__confidence</t>
+        </is>
+      </c>
+      <c r="AB1" s="31" t="inlineStr">
+        <is>
+          <t>col_offspec__value</t>
+        </is>
+      </c>
+      <c r="AC1" s="31" t="inlineStr">
+        <is>
+          <t>col_stability__answer</t>
+        </is>
+      </c>
+      <c r="AD1" s="31" t="inlineStr">
+        <is>
+          <t>col_stability__confidence</t>
+        </is>
+      </c>
+      <c r="AE1" s="31" t="inlineStr">
+        <is>
+          <t>col_stability__value</t>
+        </is>
+      </c>
+      <c r="AF1" s="31" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="AG1" s="31" t="inlineStr">
+        <is>
+          <t>review_reasons</t>
+        </is>
+      </c>
+      <c r="AH1" s="31" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>P-101A</t>
+        </is>
+      </c>
+      <c r="D2" s="36" t="inlineStr">
+        <is>
+          <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
+        </is>
+      </c>
+      <c r="E2" s="35" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="F2" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I2" s="37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J2" s="37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K2" s="35" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="L2" s="37" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M2" s="37" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="N2" s="35" t="inlineStr"/>
+      <c r="O2" s="35" t="inlineStr"/>
+      <c r="P2" s="35" t="inlineStr"/>
+      <c r="Q2" s="35" t="inlineStr"/>
+      <c r="R2" s="35" t="inlineStr"/>
+      <c r="S2" s="35" t="inlineStr"/>
+      <c r="T2" s="35" t="inlineStr"/>
+      <c r="U2" s="35" t="inlineStr"/>
+      <c r="V2" s="35" t="inlineStr"/>
+      <c r="W2" s="35" t="inlineStr"/>
+      <c r="X2" s="35" t="inlineStr"/>
+      <c r="Y2" s="35" t="inlineStr"/>
+      <c r="Z2" s="35" t="inlineStr"/>
+      <c r="AA2" s="35" t="inlineStr"/>
+      <c r="AB2" s="35" t="inlineStr"/>
+      <c r="AC2" s="35" t="inlineStr"/>
+      <c r="AD2" s="35" t="inlineStr"/>
+      <c r="AE2" s="35" t="inlineStr"/>
+      <c r="AF2" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="35" t="inlineStr"/>
+      <c r="AH2" s="35" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>P-114</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="inlineStr">
+        <is>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="F3" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I3" s="37" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J3" s="37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="35" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="L3" s="37" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M3" s="37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N3" s="35" t="inlineStr"/>
+      <c r="O3" s="35" t="inlineStr"/>
+      <c r="P3" s="35" t="inlineStr"/>
+      <c r="Q3" s="35" t="inlineStr"/>
+      <c r="R3" s="35" t="inlineStr"/>
+      <c r="S3" s="35" t="inlineStr"/>
+      <c r="T3" s="35" t="inlineStr"/>
+      <c r="U3" s="35" t="inlineStr"/>
+      <c r="V3" s="35" t="inlineStr"/>
+      <c r="W3" s="35" t="inlineStr"/>
+      <c r="X3" s="35" t="inlineStr"/>
+      <c r="Y3" s="35" t="inlineStr"/>
+      <c r="Z3" s="35" t="inlineStr"/>
+      <c r="AA3" s="35" t="inlineStr"/>
+      <c r="AB3" s="35" t="inlineStr"/>
+      <c r="AC3" s="35" t="inlineStr"/>
+      <c r="AD3" s="35" t="inlineStr"/>
+      <c r="AE3" s="35" t="inlineStr"/>
+      <c r="AF3" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="35" t="inlineStr"/>
+      <c r="AH3" s="35" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>E-205</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr"/>
+      <c r="F4" s="35" t="inlineStr"/>
+      <c r="G4" s="35" t="inlineStr"/>
+      <c r="H4" s="35" t="inlineStr"/>
+      <c r="I4" s="35" t="inlineStr"/>
+      <c r="J4" s="35" t="inlineStr"/>
+      <c r="K4" s="35" t="inlineStr"/>
+      <c r="L4" s="35" t="inlineStr"/>
+      <c r="M4" s="35" t="inlineStr"/>
+      <c r="N4" s="35" t="inlineStr">
+        <is>
+          <t>fouling</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R4" s="37" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="S4" s="37" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T4" s="35" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="U4" s="37" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="V4" s="37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W4" s="35" t="inlineStr"/>
+      <c r="X4" s="35" t="inlineStr"/>
+      <c r="Y4" s="35" t="inlineStr"/>
+      <c r="Z4" s="35" t="inlineStr"/>
+      <c r="AA4" s="35" t="inlineStr"/>
+      <c r="AB4" s="35" t="inlineStr"/>
+      <c r="AC4" s="35" t="inlineStr"/>
+      <c r="AD4" s="35" t="inlineStr"/>
+      <c r="AE4" s="35" t="inlineStr"/>
+      <c r="AF4" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="35" t="inlineStr"/>
+      <c r="AH4" s="35" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr"/>
+      <c r="F5" s="32" t="inlineStr"/>
+      <c r="G5" s="32" t="inlineStr"/>
+      <c r="H5" s="32" t="inlineStr"/>
+      <c r="I5" s="32" t="inlineStr"/>
+      <c r="J5" s="32" t="inlineStr"/>
+      <c r="K5" s="32" t="inlineStr"/>
+      <c r="L5" s="32" t="inlineStr"/>
+      <c r="M5" s="32" t="inlineStr"/>
+      <c r="N5" s="32" t="inlineStr">
+        <is>
+          <t>tube_leak</t>
+        </is>
+      </c>
+      <c r="O5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R5" s="34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S5" s="34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T5" s="32" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="U5" s="34" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="V5" s="34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W5" s="32" t="inlineStr"/>
+      <c r="X5" s="32" t="inlineStr"/>
+      <c r="Y5" s="32" t="inlineStr"/>
+      <c r="Z5" s="32" t="inlineStr"/>
+      <c r="AA5" s="32" t="inlineStr"/>
+      <c r="AB5" s="32" t="inlineStr"/>
+      <c r="AC5" s="32" t="inlineStr"/>
+      <c r="AD5" s="32" t="inlineStr"/>
+      <c r="AE5" s="32" t="inlineStr"/>
+      <c r="AF5" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="32" t="inlineStr">
+        <is>
+          <t>hx_impact: low confidence (0.49)</t>
+        </is>
+      </c>
+      <c r="AH5" s="32" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr"/>
+      <c r="F6" s="35" t="inlineStr"/>
+      <c r="G6" s="35" t="inlineStr"/>
+      <c r="H6" s="35" t="inlineStr"/>
+      <c r="I6" s="35" t="inlineStr"/>
+      <c r="J6" s="35" t="inlineStr"/>
+      <c r="K6" s="35" t="inlineStr"/>
+      <c r="L6" s="35" t="inlineStr"/>
+      <c r="M6" s="35" t="inlineStr"/>
+      <c r="N6" s="35" t="inlineStr"/>
+      <c r="O6" s="35" t="inlineStr"/>
+      <c r="P6" s="35" t="inlineStr"/>
+      <c r="Q6" s="35" t="inlineStr"/>
+      <c r="R6" s="35" t="inlineStr"/>
+      <c r="S6" s="35" t="inlineStr"/>
+      <c r="T6" s="35" t="inlineStr"/>
+      <c r="U6" s="35" t="inlineStr"/>
+      <c r="V6" s="35" t="inlineStr"/>
+      <c r="W6" s="35" t="inlineStr">
+        <is>
+          <t>flooding</t>
+        </is>
+      </c>
+      <c r="X6" s="37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Y6" s="37" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Z6" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="AA6" s="37" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AB6" s="37" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AC6" s="35" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="AD6" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="35" t="inlineStr"/>
+      <c r="AH6" s="35" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr"/>
+      <c r="F7" s="35" t="inlineStr"/>
+      <c r="G7" s="35" t="inlineStr"/>
+      <c r="H7" s="35" t="inlineStr"/>
+      <c r="I7" s="35" t="inlineStr"/>
+      <c r="J7" s="35" t="inlineStr"/>
+      <c r="K7" s="35" t="inlineStr"/>
+      <c r="L7" s="35" t="inlineStr"/>
+      <c r="M7" s="35" t="inlineStr"/>
+      <c r="N7" s="35" t="inlineStr"/>
+      <c r="O7" s="35" t="inlineStr"/>
+      <c r="P7" s="35" t="inlineStr"/>
+      <c r="Q7" s="35" t="inlineStr"/>
+      <c r="R7" s="35" t="inlineStr"/>
+      <c r="S7" s="35" t="inlineStr"/>
+      <c r="T7" s="35" t="inlineStr"/>
+      <c r="U7" s="35" t="inlineStr"/>
+      <c r="V7" s="35" t="inlineStr"/>
+      <c r="W7" s="35" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="X7" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AA7" s="37" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AB7" s="37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AC7" s="35" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AD7" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="35" t="inlineStr"/>
+      <c r="AH7" s="35" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="17" min="1" max="1"/>
+    <col width="40" customWidth="1" style="17" min="2" max="2"/>
+    <col width="120" customWidth="1" style="17" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>record_id</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>usage_json</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>raw_answers_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 465, "output_tokens": 92}</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "bearing": 0.0, "instrument": 0.0, "seal": 1.0, "other": 0.0}}, "pump_containment": {"type": "noul", "noul": 0.9}, "pump_urgency": {"type": "score", "score": 1.99, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 464, "output_tokens": 92}</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"instrument": 0.0, "other": 0.0, "cavitation": 0.0, "seal": 0.0, "bearing": 1.0}}, "pump_containment": {"type": "noul", "noul": 0.01}, "pump_urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.99, "1": 0.01, "2": 0.0}}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 484, "output_tokens": 102}</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"tube_leak": 0.0, "other": 0.0, "flow_maldistribution": 0.0, "control_valve": 0.0, "fouling": 1.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.13}, "hx_impact": {"type": "score", "score": 1.09, "confidence": 0.86, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.91, "2": 0.09}}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 487, "output_tokens": 102}</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"other": 0.0, "fouling": 0.0, "flow_maldistribution": 0.0, "tube_leak": 1.0, "control_valve": 0.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.9}, "hx_impact": {"type": "score", "score": 1.27, "confidence": 0.49, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.04, "1": 0.66, "2": 0.3}}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 514, "output_tokens": 117}</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "confidence": 0.81, "probabilities": {"flooding": 0.84, "foaming": 0.08, "fouling": 0.01, "weeping": 0.0, "instrument": 0.04, "other": 0.03, "reboiler_condenser": 0.0}}, "col_offspec": {"type": "noul", "noul": 0.99}, "col_stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 512, "output_tokens": 115}</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>{"col_symptom": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"weeping": 0.0, "instrument": 0.0, "foaming": 0.0, "flooding": 0.0, "reboiler_condenser": 0.0, "fouling": 0.0, "other": 1.0}}, "col_offspec": {"type": "noul", "noul": 0.01}, "col_stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="17" min="1" max="1"/>
+    <col width="10" customWidth="1" style="17" min="2" max="2"/>
+    <col width="8" customWidth="1" style="17" min="3" max="3"/>
+    <col width="10" customWidth="1" style="17" min="4" max="4"/>
+    <col width="18" customWidth="1" style="17" min="5" max="5"/>
+    <col width="16" customWidth="1" style="17" min="6" max="6"/>
+    <col width="14" customWidth="1" style="17" min="7" max="7"/>
+    <col width="9" customWidth="1" style="17" min="8" max="8"/>
+    <col width="10" customWidth="1" style="17" min="9" max="9"/>
+    <col width="20" customWidth="1" style="17" min="10" max="10"/>
+    <col width="20" customWidth="1" style="17" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>asked</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>answered</t>
+        </is>
+      </c>
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>flagged_for_review</t>
+        </is>
+      </c>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>mean_confidence</t>
+        </is>
+      </c>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>with_expected</t>
+        </is>
+      </c>
+      <c r="H1" s="31" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="I1" s="31" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="J1" s="31" t="inlineStr">
+        <is>
+          <t>mean_conf_when_correct</t>
+        </is>
+      </c>
+      <c r="K1" s="31" t="inlineStr">
+        <is>
+          <t>mean_conf_when_wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>pump_failure_mode</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="35" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>pump_containment</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>noul</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="35" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="G3" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="35" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="K3" s="35" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>pump_urgency</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G4" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K4" s="35" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>hx_problem</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="35" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>hx_crosscontam</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>noul</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="35" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="G6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="35" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="K6" s="35" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>hx_impact</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K7" s="35" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>col_symptom</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="35" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="G8" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K8" s="35" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>col_offspec</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>noul</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K9" s="35" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>col_stability</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="35" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" style="17" min="1" max="1"/>
+    <col width="70" customWidth="1" style="17" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>run_started</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>20260930_142230</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>engine</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>jev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>jev-1.13.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>base_url</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>https://api.typesafe.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>endpoint_info</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>remote:https://api.typesafe.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>questions_hash</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>f73a405167a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>api_key_configured</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>records_in_run</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>records_completed</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>failed_records</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>review_threshold_default</t>
+        </is>
+      </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>output_Results, output_Raw, output_Summary, output_Run_info</t>
-        </is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>elapsed_seconds</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_jev_20260930_142230.jsonl</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>records_with_usage</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>output_sheets</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>output_jev_Results, output_jev_Raw, output_jev_Summary, output_jev_Run_info</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="17" min="1" max="1"/>
+    <col width="22" customWidth="1" style="17" min="2" max="2"/>
+    <col width="14" customWidth="1" style="17" min="3" max="3"/>
+    <col width="14" customWidth="1" style="17" min="4" max="4"/>
+    <col width="8" customWidth="1" style="17" min="5" max="5"/>
+    <col width="14" customWidth="1" style="17" min="6" max="6"/>
+    <col width="14" customWidth="1" style="17" min="7" max="7"/>
+    <col width="12" customWidth="1" style="17" min="8" max="8"/>
+    <col width="12" customWidth="1" style="17" min="9" max="9"/>
+    <col width="12" customWidth="1" style="17" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>record_id</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>nimble_answer</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>jev_answer</t>
+        </is>
+      </c>
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>agree</t>
+        </is>
+      </c>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>nimble_confidence</t>
+        </is>
+      </c>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>jev_confidence</t>
+        </is>
+      </c>
+      <c r="H1" s="31" t="inlineStr">
+        <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="I1" s="31" t="inlineStr">
+        <is>
+          <t>nimble_correct</t>
+        </is>
+      </c>
+      <c r="J1" s="31" t="inlineStr">
+        <is>
+          <t>jev_correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>pump_containment</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D2" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E2" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="35" t="n">
+        <v>0.9347743692709441</v>
+      </c>
+      <c r="G2" s="35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I2" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>pump_failure_mode</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="35" t="n">
+        <v>0.886096743401824</v>
+      </c>
+      <c r="G3" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="35" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="I3" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>pump_urgency</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="35" t="n">
+        <v>0.5139963542213443</v>
+      </c>
+      <c r="G4" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H4" s="35" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="I4" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>pump_containment</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>0.9908501157291482</v>
+      </c>
+      <c r="G5" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I5" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>pump_failure_mode</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="35" t="n">
+        <v>0.971844626140937</v>
+      </c>
+      <c r="G6" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="35" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="I6" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>pump_urgency</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>0.942439470709464</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="I7" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>hx_crosscontam</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="35" t="n">
+        <v>0.9778307138401591</v>
+      </c>
+      <c r="G8" s="35" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I8" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>hx_impact</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>0.1302623881325073</v>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="I9" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>hx_problem</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>fouling</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>fouling</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="35" t="n">
+        <v>0.8436129076949702</v>
+      </c>
+      <c r="G10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>fouling</t>
+        </is>
+      </c>
+      <c r="I10" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>hx_crosscontam</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>0.9973633152102099</v>
+      </c>
+      <c r="G11" s="35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I11" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>hx_impact</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>0.5160678099489566</v>
+      </c>
+      <c r="G12" s="35" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H12" s="35" t="inlineStr">
+        <is>
+          <t>severe</t>
+        </is>
+      </c>
+      <c r="I12" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>hx_problem</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>tube_leak</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>tube_leak</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>0.9809344898041918</v>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="35" t="inlineStr">
+        <is>
+          <t>tube_leak</t>
+        </is>
+      </c>
+      <c r="I13" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>col_offspec</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="35" t="n">
+        <v>0.9990587441403763</v>
+      </c>
+      <c r="G14" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H14" s="35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I14" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>col_stability</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>0.6363997745790606</v>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="35" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="I15" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>col_symptom</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>flooding</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>flooding</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>0.5761713560101278</v>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>flooding</t>
+        </is>
+      </c>
+      <c r="I16" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>col_offspec</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>0.9979530469785511</v>
+      </c>
+      <c r="G17" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H17" s="35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I17" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>col_stability</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="35" t="n">
+        <v>0.980965088363793</v>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="35" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="I18" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>col_symptom</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>0.9310185171064398</v>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="35" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I19" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="35" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1067,173 +3494,203 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="26" customWidth="1" style="16" min="1" max="1"/>
-    <col width="34" customWidth="1" style="16" min="2" max="2"/>
-    <col width="80" customWidth="1" style="16" min="3" max="3"/>
+    <col width="22" customWidth="1" style="16" min="1" max="1"/>
+    <col width="28" customWidth="1" style="16" min="2" max="2"/>
+    <col width="90" customWidth="1" style="16" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="47" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="17">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>engine</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>nimble</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>nimble (local Ollama) or jev (TypeSafe). CLI --engine overrides this. Preset sets model/base_url/endpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="17">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>nimble</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
-        <is>
-          <t>Ollama model name. Must be pulled first (ollama pull nimble). Requires Ollama 0.35 or later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="17">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Overridden by engine preset at runtime (nimble or jev-1.13.0). Kept for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="17">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>base_url</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>http://localhost:11434</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t>Ollama server address.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="17">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Overridden by engine preset (localhost:11434 or https://api.typesafe.ai).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="17">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>/v1/systemone</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
-        <is>
-          <t>Decision-model endpoint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="17">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Decision-model endpoint (same for both engines).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="17">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>timeout_seconds</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B6" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Per-request timeout.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="17">
-      <c r="A6" s="26" t="inlineStr">
+    <row r="7" ht="23.85" customHeight="1" s="17">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>retries</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Retries per record after a failed request.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="23.85" customHeight="1" s="17">
-      <c r="A7" s="26" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="17">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>default_review_below</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B8" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Placeholder threshold. Rows with confidence below this are flagged for review. Tune on records with known answers.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="17">
-      <c r="A8" s="26" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="17">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>test_first_n</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B9" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Number of records processed in test mode. Set to blank or 0 to disable.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="17">
-      <c r="A9" s="26" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="17">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>record_text_column</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Name of the Records column that holds the statement.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="17">
-      <c r="A10" s="26" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>output_prefix</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>nimble_results</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>Legacy. Checkpoints are named &lt;workbook_stem&gt;_&lt;timestamp&gt;.jsonl beside the workbook. Excel results use output_* sheets.</t>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Legacy. Results use output_&lt;engine&gt;_* sheets; checkpoints are &lt;workbook&gt;_&lt;engine&gt;_&lt;timestamp&gt;.jsonl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>api_key</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr"/>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Leave blank. Prefer export TYPESAFE_API_KEY=... for Jev (never commit a key).</t>
         </is>
       </c>
     </row>
@@ -16014,10 +18471,10 @@
         </is>
       </c>
       <c r="F2" s="34" t="n">
-        <v>0.8845493270621723</v>
+        <v>0.886096743401824</v>
       </c>
       <c r="G2" s="34" t="n">
-        <v>0.9656847333764127</v>
+        <v>0.9662224910900805</v>
       </c>
       <c r="H2" s="32" t="inlineStr">
         <is>
@@ -16025,10 +18482,10 @@
         </is>
       </c>
       <c r="I2" s="34" t="n">
-        <v>0.9344222768578154</v>
+        <v>0.9347743692709441</v>
       </c>
       <c r="J2" s="34" t="n">
-        <v>0.9344222768578154</v>
+        <v>0.9347743692709441</v>
       </c>
       <c r="K2" s="32" t="inlineStr">
         <is>
@@ -16036,10 +18493,10 @@
         </is>
       </c>
       <c r="L2" s="34" t="n">
-        <v>0.5092630137668384</v>
+        <v>0.5139963542213443</v>
       </c>
       <c r="M2" s="34" t="n">
-        <v>1.792500181836202</v>
+        <v>1.795605456964634</v>
       </c>
       <c r="N2" s="32" t="inlineStr"/>
       <c r="O2" s="32" t="inlineStr"/>
@@ -16096,10 +18553,10 @@
         </is>
       </c>
       <c r="F3" s="37" t="n">
-        <v>0.9714843129418362</v>
+        <v>0.971844626140937</v>
       </c>
       <c r="G3" s="37" t="n">
-        <v>0.9934575546721711</v>
+        <v>0.9935691479963884</v>
       </c>
       <c r="H3" s="35" t="inlineStr">
         <is>
@@ -16107,10 +18564,10 @@
         </is>
       </c>
       <c r="I3" s="37" t="n">
-        <v>0.9911026645183536</v>
+        <v>0.9908501157291482</v>
       </c>
       <c r="J3" s="37" t="n">
-        <v>0.008897335481646413</v>
+        <v>0.009149884270851874</v>
       </c>
       <c r="K3" s="35" t="inlineStr">
         <is>
@@ -16118,10 +18575,10 @@
         </is>
       </c>
       <c r="L3" s="37" t="n">
-        <v>0.9435743291549853</v>
+        <v>0.942439470709464</v>
       </c>
       <c r="M3" s="37" t="n">
-        <v>0.01215235614936457</v>
+        <v>0.01254440492998592</v>
       </c>
       <c r="N3" s="35" t="inlineStr"/>
       <c r="O3" s="35" t="inlineStr"/>
@@ -16183,10 +18640,10 @@
         </is>
       </c>
       <c r="O4" s="34" t="n">
-        <v>0.8435687329991992</v>
+        <v>0.8436129076949702</v>
       </c>
       <c r="P4" s="34" t="n">
-        <v>0.9478850419472986</v>
+        <v>0.9479736032978536</v>
       </c>
       <c r="Q4" s="32" t="inlineStr">
         <is>
@@ -16194,10 +18651,10 @@
         </is>
       </c>
       <c r="R4" s="34" t="n">
-        <v>0.9770510463918108</v>
+        <v>0.9778307138401591</v>
       </c>
       <c r="S4" s="34" t="n">
-        <v>0.02294895360818915</v>
+        <v>0.02216928615984095</v>
       </c>
       <c r="T4" s="32" t="inlineStr">
         <is>
@@ -16205,10 +18662,10 @@
         </is>
       </c>
       <c r="U4" s="34" t="n">
-        <v>0.1334007415612771</v>
+        <v>0.1302623881325073</v>
       </c>
       <c r="V4" s="34" t="n">
-        <v>1.315495834073972</v>
+        <v>1.300448838097414</v>
       </c>
       <c r="W4" s="32" t="inlineStr"/>
       <c r="X4" s="32" t="inlineStr"/>
@@ -16265,10 +18722,10 @@
         </is>
       </c>
       <c r="O5" s="34" t="n">
-        <v>0.9811052724756711</v>
+        <v>0.9809344898041918</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>0.9959796555651736</v>
+        <v>0.9959396543190018</v>
       </c>
       <c r="Q5" s="32" t="inlineStr">
         <is>
@@ -16276,10 +18733,10 @@
         </is>
       </c>
       <c r="R5" s="34" t="n">
-        <v>0.9972773611314817</v>
+        <v>0.9973633152102099</v>
       </c>
       <c r="S5" s="34" t="n">
-        <v>0.9972773611314817</v>
+        <v>0.9973633152102099</v>
       </c>
       <c r="T5" s="32" t="inlineStr">
         <is>
@@ -16287,10 +18744,10 @@
         </is>
       </c>
       <c r="U5" s="34" t="n">
-        <v>0.5167403657884981</v>
+        <v>0.5160678099489566</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>1.011186618395636</v>
+        <v>1.01263221363486</v>
       </c>
       <c r="W5" s="32" t="inlineStr"/>
       <c r="X5" s="32" t="inlineStr"/>
@@ -16356,10 +18813,10 @@
         </is>
       </c>
       <c r="X6" s="34" t="n">
-        <v>0.575229541784642</v>
+        <v>0.5761713560101278</v>
       </c>
       <c r="Y6" s="34" t="n">
-        <v>0.5175961061389851</v>
+        <v>0.5213366239870925</v>
       </c>
       <c r="Z6" s="32" t="inlineStr">
         <is>
@@ -16367,10 +18824,10 @@
         </is>
       </c>
       <c r="AA6" s="34" t="n">
-        <v>0.9990573225259095</v>
+        <v>0.9990587441403763</v>
       </c>
       <c r="AB6" s="34" t="n">
-        <v>0.9990573225259095</v>
+        <v>0.9990587441403763</v>
       </c>
       <c r="AC6" s="32" t="inlineStr">
         <is>
@@ -16378,10 +18835,10 @@
         </is>
       </c>
       <c r="AD6" s="34" t="n">
-        <v>0.6360617217354828</v>
+        <v>0.6363997745790606</v>
       </c>
       <c r="AE6" s="34" t="n">
-        <v>1.81944012506878</v>
+        <v>1.819090602596957</v>
       </c>
       <c r="AF6" s="32" t="b">
         <v>1</v>
@@ -16438,10 +18895,10 @@
         </is>
       </c>
       <c r="X7" s="37" t="n">
-        <v>0.9294495624188652</v>
+        <v>0.9310185171064398</v>
       </c>
       <c r="Y7" s="37" t="n">
-        <v>0.9729023573239992</v>
+        <v>0.9736380706169232</v>
       </c>
       <c r="Z7" s="35" t="inlineStr">
         <is>
@@ -16449,10 +18906,10 @@
         </is>
       </c>
       <c r="AA7" s="37" t="n">
-        <v>0.9980349345556877</v>
+        <v>0.9979530469785511</v>
       </c>
       <c r="AB7" s="37" t="n">
-        <v>0.001965065444312336</v>
+        <v>0.002046953021448908</v>
       </c>
       <c r="AC7" s="35" t="inlineStr">
         <is>
@@ -16460,10 +18917,10 @@
         </is>
       </c>
       <c r="AD7" s="37" t="n">
-        <v>0.9805633856279246</v>
+        <v>0.980965088363793</v>
       </c>
       <c r="AE7" s="37" t="n">
-        <v>0.004745121587660906</v>
+        <v>0.004613240175433055</v>
       </c>
       <c r="AF7" s="35" t="b">
         <v>0</v>
@@ -16482,11 +18939,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
-    <col width="120" customWidth="1" style="17" min="2" max="2"/>
+    <col width="40" customWidth="1" style="17" min="2" max="2"/>
+    <col width="120" customWidth="1" style="17" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16497,6 +18955,11 @@
       </c>
       <c r="B1" s="31" t="inlineStr">
         <is>
+          <t>usage_json</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
           <t>raw_answers_json</t>
         </is>
       </c>
@@ -16509,7 +18972,12 @@
       </c>
       <c r="B2" s="35" t="inlineStr">
         <is>
-          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9656847333764127, "bearing": 0.012815798358892808, "cavitation": 0.01719299268622746, "instrument": 0.0018161557694942427, "other": 0.0024903198089730396}, "confidence": 0.8845493270621723}, "pump_containment": {"type": "noul", "noul": 0.9344222768578154}, "pump_urgency": {"type": "score", "score": 1.7925001818362023, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.045530782702412724, "1": 0.11643825275897222, "2": 0.838030964538615}, "confidence": 0.5092630137668384}}</t>
+          <t>{"input_tokens": 1063, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9662224910900805, "bearing": 0.012618353313619128, "cavitation": 0.01697751866187461, "instrument": 0.0017525858181681566, "other": 0.0024290511162574644}, "confidence": 0.886096743401824}, "pump_containment": {"type": "noul", "noul": 0.9347743692709441}, "pump_urgency": {"type": "score", "score": 1.7956054569646345, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.04461471259079198, "1": 0.11516511785378156, "2": 0.8402201695554264}, "confidence": 0.5139963542213443}}</t>
         </is>
       </c>
     </row>
@@ -16521,7 +18989,12 @@
       </c>
       <c r="B3" s="35" t="inlineStr">
         <is>
-          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.0043512978021535585, "bearing": 0.9934575546721711, "cavitation": 0.000905819088747979, "instrument": 0.0004185861337592025, "other": 0.0008667423031681805}, "confidence": 0.9714843129418362}, "pump_containment": {"type": "noul", "noul": 0.008897335481646413}, "pump_urgency": {"type": "score", "score": 0.012152356149364569, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9897726497601865, "1": 0.008302344330262468, "2": 0.0019250059095510502}, "confidence": 0.9435743291549853}}</t>
+          <t>{"input_tokens": 1066, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.004210403841587444, "bearing": 0.9935691479963884, "cavitation": 0.0009314177515951069, "instrument": 0.000396133117015098, "other": 0.0008928972934135872}, "confidence": 0.971844626140937}, "pump_containment": {"type": "noul", "noul": 0.009149884270851874}, "pump_urgency": {"type": "score", "score": 0.01254440492998592, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9895670238896596, "1": 0.008321547290695114, "2": 0.0021114288196454035}, "confidence": 0.942439470709464}}</t>
         </is>
       </c>
     </row>
@@ -16533,7 +19006,12 @@
       </c>
       <c r="B4" s="35" t="inlineStr">
         <is>
-          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9478850419472986, "tube_leak": 0.028015671752445407, "flow_maldistribution": 0.021038713019720476, "control_valve": 0.0009826808054082873, "other": 0.0020778924751272197}, "confidence": 0.8435687329991992}, "hx_crosscontam": {"type": "noul", "noul": 0.02294895360818915}, "hx_impact": {"type": "score", "score": 1.3154958340739715, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.10341257644438336, "1": 0.4776790130372617, "2": 0.41890841051835487}, "confidence": 0.13340074156127713}}</t>
+          <t>{"input_tokens": 1104, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9479736032978536, "tube_leak": 0.028153284493628594, "flow_maldistribution": 0.020678156580426196, "control_valve": 0.0009853402904680163, "other": 0.0022096153376235015}, "confidence": 0.8436129076949702}, "hx_crosscontam": {"type": "noul", "noul": 0.022169286159840953}, "hx_impact": {"type": "score", "score": 1.300448838097414, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.10685025101872331, "1": 0.48585065986513976, "2": 0.40729908911613705}, "confidence": 0.13026238813250735}}</t>
         </is>
       </c>
     </row>
@@ -16545,7 +19023,12 @@
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0007413265006967869, "tube_leak": 0.9959796555651736, "flow_maldistribution": 0.00043550090530919514, "control_valve": 0.00032655607260840267, "other": 0.0025169609562122087}, "confidence": 0.9811052724756711}, "hx_crosscontam": {"type": "noul", "noul": 0.9972773611314817}, "hx_impact": {"type": "score", "score": 1.011186618395636, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.07036651965596523, "1": 0.8480803422924331, "2": 0.08155313805160146}, "confidence": 0.5167403657884981}}</t>
+          <t>{"input_tokens": 1101, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0007495941289747238, "tube_leak": 0.9959396543190018, "flow_maldistribution": 0.00044349003446748496, "control_valve": 0.00033230586104586267, "other": 0.0025349556565101997}, "confidence": 0.9809344898041918}, "hx_crosscontam": {"type": "noul", "noul": 0.9973633152102099}, "hx_impact": {"type": "score", "score": 1.0126322136348604, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.06982021992433367, "1": 0.8477273465164722, "2": 0.08245243355919417}, "confidence": 0.5160678099489566}}</t>
         </is>
       </c>
     </row>
@@ -16557,7 +19040,12 @@
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.5175961061389851, "weeping": 0.012200956102939394, "foaming": 0.4556040469819839, "fouling": 0.001680899310385979, "reboiler_condenser": 0.0013599361901990839, "instrument": 0.010907201436286347, "other": 0.0006508538392200906}, "confidence": 0.575229541784642}, "col_offspec": {"type": "noul", "noul": 0.9990573225259095}, "col_stability": {"type": "score", "score": 1.8194401250687795, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.07519103740662722, "1": 0.030177800117966076, "2": 0.8946311624754067}, "confidence": 0.6360617217354828}}</t>
+          <t>{"input_tokens": 1185, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.5213366239870925, "weeping": 0.011961306768748318, "foaming": 0.45219931941914193, "fouling": 0.0016842474743738354, "reboiler_condenser": 0.001308984041366691, "instrument": 0.010858531272865853, "other": 0.0006509870364110156}, "confidence": 0.5761713560101278}, "col_offspec": {"type": "noul", "noul": 0.9990587441403763}, "col_stability": {"type": "score", "score": 1.8190906025969573, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.07555197936212335, "1": 0.029805438678796, "2": 0.8946425819590806}, "confidence": 0.6363997745790606}}</t>
         </is>
       </c>
     </row>
@@ -16569,7 +19057,12 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>{"col_symptom": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.024242860849536994, "weeping": 0.0010585059610439293, "foaming": 0.0006364711561126581, "fouling": 0.0009836821928156953, "reboiler_condenser": 0.00011520558342775971, "instrument": 6.0916933063774306e-05, "other": 0.9729023573239992}, "confidence": 0.9294495624188652}, "col_offspec": {"type": "noul", "noul": 0.0019650654443123363}, "col_stability": {"type": "score", "score": 0.004745121587660906, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.997151610266207, "1": 0.0009516578799251958, "2": 0.001896731853867855}, "confidence": 0.9805633856279246}}</t>
+          <t>{"input_tokens": 1179, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>{"col_symptom": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.023605525638543064, "weeping": 0.001033789006631328, "foaming": 0.0006111553689247979, "fouling": 0.0009357907207663385, "reboiler_condenser": 0.00011554811428608701, "instrument": 6.012053392512738e-05, "other": 0.9736380706169232}, "confidence": 0.9310185171064398}, "col_offspec": {"type": "noul", "noul": 0.002046953021448908}, "col_stability": {"type": "score", "score": 0.004613240175433055, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.9972211021457282, "1": 0.0009445555331100775, "2": 0.0018343423211614886}, "confidence": 0.980965088363793}}</t>
         </is>
       </c>
     </row>
@@ -16678,7 +19171,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="35" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G2" s="35" t="n">
         <v>2</v>
@@ -16690,7 +19183,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="35" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="K2" s="35" t="inlineStr"/>
     </row>
@@ -16752,7 +19245,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>0.726</v>
+        <v>0.728</v>
       </c>
       <c r="G4" s="35" t="n">
         <v>2</v>
@@ -16764,7 +19257,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="35" t="n">
-        <v>0.726</v>
+        <v>0.728</v>
       </c>
       <c r="K4" s="35" t="inlineStr"/>
     </row>
@@ -16826,7 +19319,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
       <c r="G6" s="35" t="n">
         <v>2</v>
@@ -16838,7 +19331,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="35" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
       <c r="K6" s="35" t="inlineStr"/>
     </row>
@@ -16863,7 +19356,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>0.325</v>
+        <v>0.323</v>
       </c>
       <c r="G7" s="35" t="n">
         <v>2</v>
@@ -16875,10 +19368,10 @@
         <v>0.5</v>
       </c>
       <c r="J7" s="35" t="n">
-        <v>0.133</v>
+        <v>0.13</v>
       </c>
       <c r="K7" s="35" t="n">
-        <v>0.517</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="8">
@@ -16902,7 +19395,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="35" t="n">
-        <v>0.752</v>
+        <v>0.754</v>
       </c>
       <c r="G8" s="35" t="n">
         <v>2</v>
@@ -16914,7 +19407,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="35" t="n">
-        <v>0.752</v>
+        <v>0.754</v>
       </c>
       <c r="K8" s="35" t="inlineStr"/>
     </row>
@@ -16976,7 +19469,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="35" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G10" s="35" t="n">
         <v>2</v>
@@ -16988,7 +19481,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="35" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K10" s="35" t="inlineStr"/>
     </row>

--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="B2" s="35" t="inlineStr">
         <is>
-          <t>20260930_142141</t>
+          <t>20260930_142515</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>5.1</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_142141.jsonl</t>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_142515.jsonl</t>
         </is>
       </c>
     </row>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="I2" s="37" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="J2" s="37" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="K2" s="35" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="R4" s="37" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="S4" s="37" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="T4" s="35" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="U4" s="37" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="V4" s="37" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W4" s="35" t="inlineStr"/>
       <c r="X4" s="35" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
         <v>0.49</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W5" s="32" t="inlineStr"/>
       <c r="X5" s="32" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="X6" s="37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="Y6" s="37" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="Z6" s="35" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "bearing": 0.0, "instrument": 0.0, "seal": 1.0, "other": 0.0}}, "pump_containment": {"type": "noul", "noul": 0.9}, "pump_urgency": {"type": "score", "score": 1.99, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}}</t>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "bearing": 0.0, "instrument": 0.0, "seal": 1.0, "other": 0.0}}, "pump_containment": {"type": "noul", "noul": 0.89}, "pump_urgency": {"type": "score", "score": 1.99, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}}</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C3" s="35" t="inlineStr">
         <is>
-          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"instrument": 0.0, "other": 0.0, "cavitation": 0.0, "seal": 0.0, "bearing": 1.0}}, "pump_containment": {"type": "noul", "noul": 0.01}, "pump_urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.99, "1": 0.01, "2": 0.0}}}</t>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"other": 0.0, "seal": 0.0, "cavitation": 0.0, "bearing": 1.0, "instrument": 0.0}}, "pump_containment": {"type": "noul", "noul": 0.01}, "pump_urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"tube_leak": 0.0, "other": 0.0, "flow_maldistribution": 0.0, "control_valve": 0.0, "fouling": 1.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.13}, "hx_impact": {"type": "score", "score": 1.09, "confidence": 0.86, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.91, "2": 0.09}}}</t>
+          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "tube_leak": 0.0, "other": 0.0, "flow_maldistribution": 0.0, "fouling": 1.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.14}, "hx_impact": {"type": "score", "score": 1.1, "confidence": 0.84, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.9, "2": 0.1}}}</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"other": 0.0, "fouling": 0.0, "flow_maldistribution": 0.0, "tube_leak": 1.0, "control_valve": 0.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.9}, "hx_impact": {"type": "score", "score": 1.27, "confidence": 0.49, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.04, "1": 0.66, "2": 0.3}}}</t>
+          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "tube_leak": 1.0, "fouling": 0.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.9}, "hx_impact": {"type": "score", "score": 1.25, "confidence": 0.49, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.05, "1": 0.65, "2": 0.3}}}</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "confidence": 0.81, "probabilities": {"flooding": 0.84, "foaming": 0.08, "fouling": 0.01, "weeping": 0.0, "instrument": 0.04, "other": 0.03, "reboiler_condenser": 0.0}}, "col_offspec": {"type": "noul", "noul": 0.99}, "col_stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}}</t>
+          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "confidence": 0.84, "probabilities": {"instrument": 0.02, "flooding": 0.87, "other": 0.02, "reboiler_condenser": 0.0, "weeping": 0.0, "foaming": 0.09, "fouling": 0.0}}, "col_offspec": {"type": "noul", "noul": 0.99}, "col_stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}}</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>{"col_symptom": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"weeping": 0.0, "instrument": 0.0, "foaming": 0.0, "flooding": 0.0, "reboiler_condenser": 0.0, "fouling": 0.0, "other": 1.0}}, "col_offspec": {"type": "noul", "noul": 0.01}, "col_stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
+          <t>{"col_symptom": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"fouling": 0.0, "weeping": 0.0, "other": 1.0, "flooding": 0.0, "foaming": 0.0, "reboiler_condenser": 0.0, "instrument": 0.0}}, "col_offspec": {"type": "noul", "noul": 0.01}, "col_stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>0.945</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G3" s="35" t="n">
         <v>2</v>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="35" t="n">
-        <v>0.945</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K3" s="35" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>0.885</v>
+        <v>0.88</v>
       </c>
       <c r="G6" s="35" t="n">
         <v>2</v>
@@ -2237,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="35" t="n">
-        <v>0.885</v>
+        <v>0.88</v>
       </c>
       <c r="K6" s="35" t="inlineStr"/>
     </row>
@@ -2262,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>0.675</v>
+        <v>0.665</v>
       </c>
       <c r="G7" s="35" t="n">
         <v>2</v>
@@ -2274,7 +2274,7 @@
         <v>0.5</v>
       </c>
       <c r="J7" s="35" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="K7" s="35" t="n">
         <v>0.49</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="35" t="n">
-        <v>0.905</v>
+        <v>0.92</v>
       </c>
       <c r="G8" s="35" t="n">
         <v>2</v>
@@ -2313,7 +2313,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="35" t="n">
-        <v>0.905</v>
+        <v>0.92</v>
       </c>
       <c r="K8" s="35" t="inlineStr"/>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="B2" s="35" t="inlineStr">
         <is>
-          <t>20260930_142230</t>
+          <t>20260930_142521</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_jev_20260930_142230.jsonl</t>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_jev_20260930_142521.jsonl</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
         <v>0.9347743692709441</v>
       </c>
       <c r="G2" s="35" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="H2" s="35" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>0.9778307138401591</v>
       </c>
       <c r="G8" s="35" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H8" s="35" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>0.1302623881325073</v>
       </c>
       <c r="G9" s="35" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="H9" s="35" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>0.5761713560101278</v>
       </c>
       <c r="G16" s="35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="H16" s="35" t="inlineStr">
         <is>

--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="16" min="1" max="1"/>
@@ -634,246 +634,269 @@
     <row r="1" ht="17.35" customHeight="1" s="17">
       <c r="A1" s="46" t="inlineStr">
         <is>
-          <t>Nimble / Jev batch classifier - control workbook</t>
+          <t>Nimble / Jev batch classifier — control workbook (v1.0-dev)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="17">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Define questions, labels and records here. Run with --engine nimble or --engine jev. Each engine writes its own output_&lt;engine&gt;_* sheets and does not clear the other. When both Results sheets exist, output_compare is refreshed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="17">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Edit questions, labels, and records here. Run: python nimble_runner.py &lt;this file&gt; --engine nimble|jev. Each engine writes output_&lt;engine&gt;_* only and does not clear the other. When both Results sheets exist, output_compare is refreshed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Docs: repo README.md (quick start); docs/functional-spec.md (as-built spec + UML).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="17"/>
+    <row r="5" ht="15" customHeight="1" s="17">
+      <c r="A5" t="inlineStr">
         <is>
           <t>SHEETS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="17">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="6" ht="30" customHeight="1" s="17">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Settings: engine (nimble|jev), timeouts, review threshold, test-run size. Engine preset overrides model/base_url/endpoint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="17">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>engine (nimble|jev), timeouts, review threshold, test_first_n. Runtime preset overrides model/base_url/endpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="17">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Questions</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>One row per question. Type is choice, noul (yes/no) or score. Leave equipment_type blank to ask every record.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="17">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>One row per question: choice, noul (yes/no), or score. Blank equipment_type = all records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="17">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Labels</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Answer options for choice and score only. For score, order is scale position (lowest first).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="17">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Options for choice and score only. For score, order is scale position (lowest first).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="17">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>Statements to classify. Optional expected_&lt;question_id&gt; columns for accuracy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="17">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Text to classify. Optional expected_&lt;question_id&gt; for accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="17">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Lists</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Dropdown values (equipment types).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="17">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Equipment-type dropdown values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="17">
+      <c r="A11" t="inlineStr">
         <is>
           <t>output_nimble_*</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Written by --engine nimble: Results, Raw, Summary, Run_info.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="17">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Results / Raw / Summary / Run_info from --engine nimble.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="17">
+      <c r="A12" t="inlineStr">
         <is>
           <t>output_jev_*</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Written by --engine jev: Results, Raw, Summary, Run_info.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="17">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Results / Raw / Summary / Run_info from --engine jev.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="17">
+      <c r="A13" t="inlineStr">
         <is>
           <t>output_compare</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Side-by-side Nimble vs Jev answers when both Results sheets exist. Diffs highlighted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="17">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nimble vs Jev answers when both Results exist. Diffs highlighted orange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1" s="17"/>
+    <row r="15" ht="30" customHeight="1" s="17">
+      <c r="A15" t="inlineStr">
         <is>
           <t>COLOURS</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1" s="17">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="17">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Blue text</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Cells you edit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="17">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Black text, grey fill</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Formulas. Do not edit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="17">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Editable cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Grey fill / formulas</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Do not edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="17">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Yellow row</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Flagged for review (low confidence).</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="17">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Orange row (compare)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Nimble and Jev answers disagree.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="17">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Engines disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="17"/>
+    <row r="21" ht="45" customHeight="1" s="17">
+      <c r="A21" t="inlineStr">
         <is>
           <t>RULES</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="17">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Use Config engine or CLI --engine. Jev needs TYPESAFE_API_KEY. Nimble needs local Ollama &gt;= 0.35.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="17">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Config engine or CLI --engine. Nimble: Ollama &gt;= 0.35. Jev: export TYPESAFE_API_KEY (leave Config api_key blank).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>IDs</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>question_id and label: short lowercase with underscores, no spaces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1" s="17">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>question_id and label: letters, digits, _ or -; no spaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Always add 'other'</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Include other on every choice question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>On every choice question so vague text is not forced into a wrong label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Expected values</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>choice: a Labels value; noul: true or false.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Close workbook</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unlock/close this file in Excel/LibreOffice before running the classifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>EXAMPLES</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Example rows</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Illustrative pumps / exchangers / columns. Replace with your plant data.</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Illustrative pumps / exchangers / columns — replace with plant data.</t>
         </is>
       </c>
     </row>

--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="16" min="1" max="1"/>
@@ -634,269 +634,296 @@
     <row r="1" ht="17.35" customHeight="1" s="17">
       <c r="A1" s="46" t="inlineStr">
         <is>
-          <t>Nimble / Jev batch classifier — control workbook (v1.0-dev)</t>
+          <t>Nimble and Jev — control workbook</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="17">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Edit questions, labels, and records here. Run: python nimble_runner.py &lt;this file&gt; --engine nimble|jev. Each engine writes output_&lt;engine&gt;_* only and does not clear the other. When both Results sheets exist, output_compare is refreshed.</t>
+          <t>This one workbook works with BOTH engines: Nimble (local Ollama) and Jev (TypeSafe cloud).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Docs: repo README.md (quick start); docs/functional-spec.md (as-built spec + UML).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="17"/>
-    <row r="5" ht="15" customHeight="1" s="17">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SHEETS</t>
-        </is>
-      </c>
-    </row>
+          <t>Edit questions and records here. Run from the terminal (see the repo README.md). Use --engine nimble or --engine jev.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="17">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Each engine writes its own output_&lt;engine&gt;_* sheets and does not clear the other. When both Results exist, output_compare is filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="17"/>
     <row r="6" ht="30" customHeight="1" s="17">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>engine (nimble|jev), timeouts, review threshold, test_first_n. Runtime preset overrides model/base_url/endpoint.</t>
+          <t>SHEETS YOU EDIT</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="17">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>One row per question: choice, noul (yes/no), or score. Blank equipment_type = all records.</t>
+          <t>Default engine, timeouts, review threshold, test size. Runtime preset still sets model/URL for the chosen engine.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="17">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Labels</t>
+          <t>Questions</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Options for choice and score only. For score, order is scale position (lowest first).</t>
+          <t>One row per question: choice, noul (yes/no), or score. Blank equipment_type = ask every record.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="17">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Records</t>
+          <t>Labels</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Text to classify. Optional expected_&lt;question_id&gt; for accuracy.</t>
+          <t>Options for choice and score only. For score, order is the scale (lowest first).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="17">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>Records</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equipment-type dropdown values.</t>
+          <t>Text to classify. Optional expected_&lt;question_id&gt; for accuracy checks.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="17">
       <c r="A11" t="inlineStr">
         <is>
-          <t>output_nimble_*</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Results / Raw / Summary / Run_info from --engine nimble.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="17">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>output_jev_*</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Results / Raw / Summary / Run_info from --engine jev.</t>
-        </is>
-      </c>
-    </row>
+          <t>Equipment-type dropdown values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="17"/>
     <row r="13" ht="15" customHeight="1" s="17">
       <c r="A13" t="inlineStr">
         <is>
-          <t>output_compare</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nimble vs Jev answers when both Results exist. Diffs highlighted orange.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1" s="17"/>
+          <t>SHEETS THE RUNNER WRITES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1" s="17">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>output_nimble_*</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Results / Raw / Summary / Run_info from a Nimble run.</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="30" customHeight="1" s="17">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COLOURS</t>
+          <t>output_jev_*</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Results / Raw / Summary / Run_info from a Jev run.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="17">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Blue text</t>
+          <t>output_compare</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Editable cells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Grey fill / formulas</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Do not edit.</t>
-        </is>
-      </c>
-    </row>
+          <t>Side-by-side Nimble vs Jev when both Results sheets exist. Diffs highlighted orange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="17"/>
     <row r="18" ht="30" customHeight="1" s="17">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Yellow row</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Flagged for review (low confidence).</t>
+          <t>COLOURS</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="17">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Orange row (compare)</t>
+          <t>Blue text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Engines disagree.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="17"/>
+          <t>Editable cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="17">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Grey fill / formulas</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Do not edit.</t>
+        </is>
+      </c>
+    </row>
     <row r="21" ht="45" customHeight="1" s="17">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>Yellow row</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Flagged for review (low confidence).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engine</t>
+          <t>Orange row (compare)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Config engine or CLI --engine. Nimble: Ollama &gt;= 0.35. Jev: export TYPESAFE_API_KEY (leave Config api_key blank).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>IDs</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_id and label: letters, digits, _ or -; no spaces.</t>
-        </is>
-      </c>
-    </row>
+          <t>Nimble and Jev disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Always add 'other'</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>On every choice question so vague text is not forced into a wrong label.</t>
+          <t>RULES</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Expected values</t>
+          <t>How to run</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>choice: a Labels value; noul: true or false.</t>
+          <t>Commands are in the repo README.md — not inside this spreadsheet.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Close workbook</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Unlock/close this file in Excel/LibreOffice before running the classifier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
+          <t>Config engine or CLI --engine. Nimble needs Ollama &gt;= 0.35. Jev needs TYPESAFE_API_KEY in the environment (leave Config api_key blank).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IDs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>question_id and label: letters, digits, _ or -; no spaces.</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EXAMPLES</t>
+          <t>Always add 'other'</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>On every choice question so vague text is not forced into a wrong label.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Expected values</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>choice: a Labels value; noul: true or false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Close workbook</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Close this file in Excel/LibreOffice before running the classifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EXAMPLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Example rows</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Illustrative pumps / exchangers / columns — replace with plant data.</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Illustrative pumps / exchangers / columns — replace with your plant data.</t>
         </is>
       </c>
     </row>

--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -13,14 +13,14 @@
     <sheet name="Labels" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Records" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Lists" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="output_jev_Results" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="output_jev_Raw" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="output_jev_Summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="output_jev_Run_info" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="output_nimble_Results" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="output_nimble_Raw" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="output_nimble_Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="output_nimble_Run_info" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="output_nimble_Results" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="output_nimble_Raw" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="output_nimble_Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="output_nimble_Run_info" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="output_jev_Results" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="output_jev_Raw" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="output_jev_Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="output_jev_Run_info" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="output_compare" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
@@ -33,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -113,6 +113,11 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -184,7 +189,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -295,6 +300,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,12 +388,12 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Leave blank to ask this question of every record.</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Optional. Overrides Config default_review_below for this question. Leave blank to use the default.</t>
       </text>
@@ -577,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="18" min="1" max="1"/>
@@ -585,273 +591,196 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="19">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Nimble / Jev batch classifier — control workbook (v1.0-dev)</t>
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>Nimble and Jev — control workbook</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="19">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>Edit questions, labels, and records here. Run: python nimble_runner.py &lt;this file&gt; --engine nimble|jev. Each engine writes output_&lt;engine&gt;_* only and does not clear the other. When both Results sheets exist, output_compare is refreshed.</t>
+          <t>Questions are scoped by equipment_type: a Pump question is never used for a Heat Exchanger or Column.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="19">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>Docs: repo README.md (quick start); docs/functional-spec.md (as-built spec + UML).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="19"/>
-    <row r="5" ht="15" customHeight="1" s="19">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>SHEETS</t>
-        </is>
-      </c>
-    </row>
+          <t>Edit here; run from the terminal (repo README.md) with --engine nimble or --engine jev.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="19">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Results are long-format: one row per answer for that asset only. title = short human label; question_id = unique key per equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="19"/>
     <row r="6" ht="30" customHeight="1" s="19">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>engine (nimble|jev), timeouts, review threshold, test_first_n. Runtime preset overrides model/base_url/endpoint.</t>
+          <t>SHEETS YOU EDIT</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="19">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>One row per question: choice, noul (yes/no), or score. Blank equipment_type = all records.</t>
+          <t>Default engine, timeouts, review threshold, test size.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="19">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Labels</t>
+          <t>Questions</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Options for choice and score only. For score, order is scale position (lowest first).</t>
+          <t>question_id, title, equipment_type, type, instructions, active.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="19">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>Records</t>
+          <t>Labels</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Text to classify. Optional expected_&lt;question_id&gt; for accuracy.</t>
+          <t>Options for choice and score only.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="19">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>Records</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Equipment-type dropdown values.</t>
+          <t>Text to classify. Optional expected_&lt;question_id&gt;.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="19">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>output_nimble_*</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Results / Raw / Summary / Run_info from --engine nimble.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="19">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>output_jev_*</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Results / Raw / Summary / Run_info from --engine jev.</t>
-        </is>
-      </c>
-    </row>
+          <t>Equipment-type dropdown values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="19"/>
     <row r="13" ht="15" customHeight="1" s="19">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>output_compare</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Nimble vs Jev answers when both Results exist. Diffs highlighted orange.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1" s="19"/>
+          <t>SHEETS THE RUNNER WRITES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1" s="19">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>output_nimble_* / output_jev_*</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Results (long), Raw, Summary, Run_info.</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="30" customHeight="1" s="19">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>COLOURS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="19">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>Blue text</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Editable cells.</t>
-        </is>
-      </c>
-    </row>
+          <t>output_compare</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Nimble vs Jev when both Results exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="19"/>
     <row r="17" ht="30" customHeight="1" s="19">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>Grey fill / formulas</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Do not edit.</t>
+          <t>RULES</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="19">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>Yellow row</t>
+          <t>Equipment scoping</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Flagged for review (low confidence).</t>
+          <t>Never reuse a pump question_id for other equipment (or the reverse).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Orange row (compare)</t>
+          <t>How to run</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Engines disagree.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="19"/>
+          <t>See repo README.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="19">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Jev key</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>export TYPESAFE_API_KEY=... ; leave Config api_key blank.</t>
+        </is>
+      </c>
+    </row>
     <row r="21" ht="45" customHeight="1" s="19">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>RULES</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="19">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Engine</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Config engine or CLI --engine. Nimble: Ollama &gt;= 0.35. Jev: export TYPESAFE_API_KEY (leave Config api_key blank).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="19">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>IDs</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>question_id and label: letters, digits, _ or -; no spaces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="19">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>Always add 'other'</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>On every choice question so vague text is not forced into a wrong label.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="19">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Expected values</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>choice: a Labels value; noul: true or false.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="19">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
           <t>Close workbook</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>Unlock/close this file in Excel/LibreOffice before running the classifier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="19">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>EXAMPLES</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="19">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Example rows</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>Illustrative pumps / exchangers / columns — replace with plant data.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Close Excel/LibreOffice before running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="19"/>
+    <row r="23" ht="15" customHeight="1" s="19"/>
+    <row r="24" ht="15" customHeight="1" s="19"/>
+    <row r="25" ht="15" customHeight="1" s="19"/>
+    <row r="26" ht="15" customHeight="1" s="19"/>
+    <row r="28" ht="15" customHeight="1" s="19"/>
+    <row r="29" ht="15" customHeight="1" s="19"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
@@ -864,261 +793,67 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="18" min="1" max="1"/>
-    <col width="70" customWidth="1" style="18" min="2" max="2"/>
+    <col width="26" customWidth="1" style="19" min="1" max="1"/>
+    <col width="70" customWidth="1" style="19" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="19">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="19">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>run_started</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>20260930_142521</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="19">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>workbook</t>
-        </is>
-      </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="19">
-      <c r="A4" s="27" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>engine</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>jev</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="19">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>jev-1.13.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="19">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>base_url</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>https://api.typesafe.ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="19">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>endpoint_info</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>remote:https://api.typesafe.ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="19">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>questions_hash</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>f73a405167a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="19">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>api_key_configured</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="19">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>records_in_run</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="19">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>records_completed</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="19">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>failed_records</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="19">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>review_threshold_default</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="19">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>elapsed_seconds</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="19">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>checkpoint</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_jev_20260930_142521.jsonl</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="19">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>input_tokens</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>2926</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="19">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="19">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>total_tokens</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>3546</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>records_with_usage</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="19">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>output_sheets</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>output_jev_Results, output_jev_Raw, output_jev_Summary, output_jev_Run_info</t>
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>nimble</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>rebuilt_from</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>output_nimble_Raw</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>long-format rebuild without new API calls</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1235,7 +970,7 @@
       </c>
       <c r="F2" s="34" t="inlineStr">
         <is>
-          <t>pump_failure_mode</t>
+          <t>Failure mode</t>
         </is>
       </c>
       <c r="G2" s="34" t="inlineStr">
@@ -1244,10 +979,10 @@
         </is>
       </c>
       <c r="H2" s="36" t="n">
-        <v>0.8845493270621723</v>
+        <v>1</v>
       </c>
       <c r="I2" s="36" t="n">
-        <v>0.9656847333764127</v>
+        <v>1</v>
       </c>
       <c r="J2" s="34" t="b">
         <v>0</v>
@@ -1283,7 +1018,7 @@
       </c>
       <c r="F3" s="34" t="inlineStr">
         <is>
-          <t>pump_containment</t>
+          <t>Containment</t>
         </is>
       </c>
       <c r="G3" s="34" t="inlineStr">
@@ -1292,10 +1027,10 @@
         </is>
       </c>
       <c r="H3" s="36" t="n">
-        <v>0.9344222768578154</v>
+        <v>0.89</v>
       </c>
       <c r="I3" s="36" t="n">
-        <v>0.9344222768578154</v>
+        <v>0.89</v>
       </c>
       <c r="J3" s="34" t="b">
         <v>0</v>
@@ -1304,56 +1039,52 @@
       <c r="L3" s="34" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>pump_urgency</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
-        <is>
-          <t>pump_urgency</t>
-        </is>
-      </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>immediate</t>
         </is>
       </c>
-      <c r="H4" s="39" t="n">
-        <v>0.5092630137668384</v>
-      </c>
-      <c r="I4" s="39" t="n">
-        <v>1.792500181836202</v>
-      </c>
-      <c r="J4" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="37" t="inlineStr">
-        <is>
-          <t>pump_urgency: low confidence (0.51)</t>
-        </is>
-      </c>
-      <c r="L4" s="37" t="inlineStr"/>
+      <c r="H4" s="36" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I4" s="36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J4" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="34" t="inlineStr"/>
+      <c r="L4" s="34" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
@@ -1383,7 +1114,7 @@
       </c>
       <c r="F5" s="34" t="inlineStr">
         <is>
-          <t>pump_failure_mode</t>
+          <t>Failure mode</t>
         </is>
       </c>
       <c r="G5" s="34" t="inlineStr">
@@ -1392,10 +1123,10 @@
         </is>
       </c>
       <c r="H5" s="36" t="n">
-        <v>0.9714843129418362</v>
+        <v>1</v>
       </c>
       <c r="I5" s="36" t="n">
-        <v>0.9934575546721711</v>
+        <v>1</v>
       </c>
       <c r="J5" s="34" t="b">
         <v>0</v>
@@ -1431,7 +1162,7 @@
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
-          <t>pump_containment</t>
+          <t>Containment</t>
         </is>
       </c>
       <c r="G6" s="34" t="inlineStr">
@@ -1440,10 +1171,10 @@
         </is>
       </c>
       <c r="H6" s="36" t="n">
-        <v>0.9911026645183536</v>
+        <v>0.99</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>0.008897335481646413</v>
+        <v>0.01</v>
       </c>
       <c r="J6" s="34" t="b">
         <v>0</v>
@@ -1479,7 +1210,7 @@
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>pump_urgency</t>
+          <t>Urgency</t>
         </is>
       </c>
       <c r="G7" s="34" t="inlineStr">
@@ -1488,10 +1219,10 @@
         </is>
       </c>
       <c r="H7" s="36" t="n">
-        <v>0.9435743291549853</v>
+        <v>0.99</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>0.01215235614936457</v>
+        <v>0.01</v>
       </c>
       <c r="J7" s="34" t="b">
         <v>0</v>
@@ -1527,7 +1258,7 @@
       </c>
       <c r="F8" s="34" t="inlineStr">
         <is>
-          <t>hx_problem</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="G8" s="34" t="inlineStr">
@@ -1536,10 +1267,10 @@
         </is>
       </c>
       <c r="H8" s="36" t="n">
-        <v>0.8435687329991992</v>
+        <v>1</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>0.9478850419472986</v>
+        <v>1</v>
       </c>
       <c r="J8" s="34" t="b">
         <v>0</v>
@@ -1575,7 +1306,7 @@
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>hx_crosscontam</t>
+          <t>Cross-contamination</t>
         </is>
       </c>
       <c r="G9" s="34" t="inlineStr">
@@ -1584,10 +1315,10 @@
         </is>
       </c>
       <c r="H9" s="36" t="n">
-        <v>0.9770510463918108</v>
+        <v>0.86</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>0.02294895360818915</v>
+        <v>0.14</v>
       </c>
       <c r="J9" s="34" t="b">
         <v>0</v>
@@ -1596,56 +1327,52 @@
       <c r="L9" s="34" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>E-205</t>
         </is>
       </c>
-      <c r="D10" s="38" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>hx_impact</t>
         </is>
       </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>hx_impact</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="H10" s="39" t="n">
-        <v>0.1334007415612771</v>
-      </c>
-      <c r="I10" s="39" t="n">
-        <v>1.315495834073972</v>
-      </c>
-      <c r="J10" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="37" t="inlineStr">
-        <is>
-          <t>hx_impact: low confidence (0.13)</t>
-        </is>
-      </c>
-      <c r="L10" s="37" t="inlineStr"/>
+      <c r="H10" s="36" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I10" s="36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J10" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="34" t="inlineStr"/>
+      <c r="L10" s="34" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
@@ -1675,7 +1402,7 @@
       </c>
       <c r="F11" s="34" t="inlineStr">
         <is>
-          <t>hx_problem</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="G11" s="34" t="inlineStr">
@@ -1684,10 +1411,10 @@
         </is>
       </c>
       <c r="H11" s="36" t="n">
-        <v>0.9811052724756711</v>
+        <v>1</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>0.9959796555651736</v>
+        <v>1</v>
       </c>
       <c r="J11" s="34" t="b">
         <v>0</v>
@@ -1723,7 +1450,7 @@
       </c>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>hx_crosscontam</t>
+          <t>Cross-contamination</t>
         </is>
       </c>
       <c r="G12" s="34" t="inlineStr">
@@ -1732,10 +1459,10 @@
         </is>
       </c>
       <c r="H12" s="36" t="n">
-        <v>0.9972773611314817</v>
+        <v>0.9</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>0.9972773611314817</v>
+        <v>0.9</v>
       </c>
       <c r="J12" s="34" t="b">
         <v>0</v>
@@ -1771,7 +1498,7 @@
       </c>
       <c r="F13" s="37" t="inlineStr">
         <is>
-          <t>hx_impact</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="G13" s="37" t="inlineStr">
@@ -1780,72 +1507,68 @@
         </is>
       </c>
       <c r="H13" s="39" t="n">
-        <v>0.5167403657884981</v>
+        <v>0.49</v>
       </c>
       <c r="I13" s="39" t="n">
-        <v>1.011186618395636</v>
+        <v>1.25</v>
       </c>
       <c r="J13" s="37" t="b">
         <v>1</v>
       </c>
       <c r="K13" s="37" t="inlineStr">
         <is>
-          <t>hx_impact: low confidence (0.52)</t>
+          <t>hx_impact: low confidence (0.49)</t>
         </is>
       </c>
       <c r="L13" s="37" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E14" s="37" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>col_symptom</t>
         </is>
       </c>
-      <c r="F14" s="37" t="inlineStr">
-        <is>
-          <t>col_symptom</t>
-        </is>
-      </c>
-      <c r="G14" s="37" t="inlineStr">
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>flooding</t>
         </is>
       </c>
-      <c r="H14" s="39" t="n">
-        <v>0.575229541784642</v>
-      </c>
-      <c r="I14" s="39" t="n">
-        <v>0.5175961061389851</v>
-      </c>
-      <c r="J14" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="37" t="inlineStr">
-        <is>
-          <t>col_symptom: low confidence (0.58)</t>
-        </is>
-      </c>
-      <c r="L14" s="37" t="inlineStr"/>
+      <c r="H14" s="36" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I14" s="36" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J14" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="34" t="inlineStr"/>
+      <c r="L14" s="34" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
@@ -1875,7 +1598,7 @@
       </c>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>col_offspec</t>
+          <t>Off-spec</t>
         </is>
       </c>
       <c r="G15" s="34" t="inlineStr">
@@ -1884,10 +1607,10 @@
         </is>
       </c>
       <c r="H15" s="36" t="n">
-        <v>0.9990573225259095</v>
+        <v>0.99</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>0.9990573225259095</v>
+        <v>0.99</v>
       </c>
       <c r="J15" s="34" t="b">
         <v>0</v>
@@ -1923,7 +1646,7 @@
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>col_stability</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="G16" s="34" t="inlineStr">
@@ -1932,10 +1655,10 @@
         </is>
       </c>
       <c r="H16" s="36" t="n">
-        <v>0.6360617217354828</v>
+        <v>1</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>1.81944012506878</v>
+        <v>2</v>
       </c>
       <c r="J16" s="34" t="b">
         <v>0</v>
@@ -1971,7 +1694,7 @@
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>col_symptom</t>
+          <t>Symptom</t>
         </is>
       </c>
       <c r="G17" s="34" t="inlineStr">
@@ -1980,10 +1703,10 @@
         </is>
       </c>
       <c r="H17" s="36" t="n">
-        <v>0.9294495624188652</v>
+        <v>1</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>0.9729023573239992</v>
+        <v>1</v>
       </c>
       <c r="J17" s="34" t="b">
         <v>0</v>
@@ -2019,7 +1742,7 @@
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>col_offspec</t>
+          <t>Off-spec</t>
         </is>
       </c>
       <c r="G18" s="34" t="inlineStr">
@@ -2028,10 +1751,10 @@
         </is>
       </c>
       <c r="H18" s="36" t="n">
-        <v>0.9980349345556877</v>
+        <v>0.99</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>0.001965065444312336</v>
+        <v>0.01</v>
       </c>
       <c r="J18" s="34" t="b">
         <v>0</v>
@@ -2067,7 +1790,7 @@
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>col_stability</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="G19" s="34" t="inlineStr">
@@ -2076,10 +1799,10 @@
         </is>
       </c>
       <c r="H19" s="36" t="n">
-        <v>0.9805633856279246</v>
+        <v>1</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>0.004745121587660906</v>
+        <v>0</v>
       </c>
       <c r="J19" s="34" t="b">
         <v>0</v>
@@ -2131,12 +1854,12 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>{"input_tokens": 1063, "output_tokens": 4}</t>
+          <t>{"input_tokens": 465, "output_tokens": 92}</t>
         </is>
       </c>
       <c r="C2" s="34" t="inlineStr">
         <is>
-          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9656847333764127, "bearing": 0.012815798358892808, "cavitation": 0.01719299268622746, "instrument": 0.0018161557694942427, "other": 0.0024903198089730396}, "confidence": 0.8845493270621723}, "pump_containment": {"type": "noul", "noul": 0.9344222768578154}, "pump_urgency": {"type": "score", "score": 1.7925001818362023, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.045530782702412724, "1": 0.11643825275897222, "2": 0.838030964538615}, "confidence": 0.5092630137668384}}</t>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "bearing": 0.0, "instrument": 0.0, "seal": 1.0, "other": 0.0}}, "pump_containment": {"type": "noul", "noul": 0.89}, "pump_urgency": {"type": "score", "score": 1.99, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}}</t>
         </is>
       </c>
     </row>
@@ -2148,12 +1871,12 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>{"input_tokens": 1066, "output_tokens": 4}</t>
+          <t>{"input_tokens": 464, "output_tokens": 92}</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.0043512978021535585, "bearing": 0.9934575546721711, "cavitation": 0.000905819088747979, "instrument": 0.0004185861337592025, "other": 0.0008667423031681805}, "confidence": 0.9714843129418362}, "pump_containment": {"type": "noul", "noul": 0.008897335481646413}, "pump_urgency": {"type": "score", "score": 0.012152356149364569, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9897726497601865, "1": 0.008302344330262468, "2": 0.0019250059095510502}, "confidence": 0.9435743291549853}}</t>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"other": 0.0, "seal": 0.0, "cavitation": 0.0, "bearing": 1.0, "instrument": 0.0}}, "pump_containment": {"type": "noul", "noul": 0.01}, "pump_urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -2165,12 +1888,12 @@
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>{"input_tokens": 1104, "output_tokens": 4}</t>
+          <t>{"input_tokens": 484, "output_tokens": 102}</t>
         </is>
       </c>
       <c r="C4" s="34" t="inlineStr">
         <is>
-          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9478850419472986, "tube_leak": 0.028015671752445407, "flow_maldistribution": 0.021038713019720476, "control_valve": 0.0009826808054082873, "other": 0.0020778924751272197}, "confidence": 0.8435687329991992}, "hx_crosscontam": {"type": "noul", "noul": 0.02294895360818915}, "hx_impact": {"type": "score", "score": 1.3154958340739715, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.10341257644438336, "1": 0.4776790130372617, "2": 0.41890841051835487}, "confidence": 0.13340074156127713}}</t>
+          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "tube_leak": 0.0, "other": 0.0, "flow_maldistribution": 0.0, "fouling": 1.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.14}, "hx_impact": {"type": "score", "score": 1.1, "confidence": 0.84, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.9, "2": 0.1}}}</t>
         </is>
       </c>
     </row>
@@ -2182,12 +1905,12 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>{"input_tokens": 1101, "output_tokens": 4}</t>
+          <t>{"input_tokens": 487, "output_tokens": 102}</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0007413265006967869, "tube_leak": 0.9959796555651736, "flow_maldistribution": 0.00043550090530919514, "control_valve": 0.00032655607260840267, "other": 0.0025169609562122087}, "confidence": 0.9811052724756711}, "hx_crosscontam": {"type": "noul", "noul": 0.9972773611314817}, "hx_impact": {"type": "score", "score": 1.011186618395636, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.07036651965596523, "1": 0.8480803422924331, "2": 0.08155313805160146}, "confidence": 0.5167403657884981}}</t>
+          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "tube_leak": 1.0, "fouling": 0.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.9}, "hx_impact": {"type": "score", "score": 1.25, "confidence": 0.49, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.05, "1": 0.65, "2": 0.3}}}</t>
         </is>
       </c>
     </row>
@@ -2199,12 +1922,12 @@
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>{"input_tokens": 1185, "output_tokens": 4}</t>
+          <t>{"input_tokens": 514, "output_tokens": 117}</t>
         </is>
       </c>
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.5175961061389851, "weeping": 0.012200956102939394, "foaming": 0.4556040469819839, "fouling": 0.001680899310385979, "reboiler_condenser": 0.0013599361901990839, "instrument": 0.010907201436286347, "other": 0.0006508538392200906}, "confidence": 0.575229541784642}, "col_offspec": {"type": "noul", "noul": 0.9990573225259095}, "col_stability": {"type": "score", "score": 1.8194401250687795, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.07519103740662722, "1": 0.030177800117966076, "2": 0.8946311624754067}, "confidence": 0.6360617217354828}}</t>
+          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "confidence": 0.84, "probabilities": {"instrument": 0.02, "flooding": 0.87, "other": 0.02, "reboiler_condenser": 0.0, "weeping": 0.0, "foaming": 0.09, "fouling": 0.0}}, "col_offspec": {"type": "noul", "noul": 0.99}, "col_stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}}</t>
         </is>
       </c>
     </row>
@@ -2216,12 +1939,12 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>{"input_tokens": 1179, "output_tokens": 4}</t>
+          <t>{"input_tokens": 512, "output_tokens": 115}</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>{"col_symptom": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.024242860849536994, "weeping": 0.0010585059610439293, "foaming": 0.0006364711561126581, "fouling": 0.0009836821928156953, "reboiler_condenser": 0.00011520558342775971, "instrument": 6.0916933063774306e-05, "other": 0.9729023573239992}, "confidence": 0.9294495624188652}, "col_offspec": {"type": "noul", "noul": 0.0019650654443123363}, "col_stability": {"type": "score", "score": 0.004745121587660906, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.997151610266207, "1": 0.0009516578799251958, "2": 0.001896731853867855}, "confidence": 0.9805633856279246}}</t>
+          <t>{"col_symptom": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"fouling": 0.0, "weeping": 0.0, "other": 1.0, "flooding": 0.0, "foaming": 0.0, "reboiler_condenser": 0.0, "instrument": 0.0}}, "col_offspec": {"type": "noul", "noul": 0.01}, "col_stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2046,7 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>pump_failure_mode</t>
+          <t>Failure mode</t>
         </is>
       </c>
       <c r="C2" s="34" t="inlineStr">
@@ -2341,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="34" t="n">
-        <v>0.928</v>
+        <v>1</v>
       </c>
       <c r="H2" s="34" t="n">
         <v>2</v>
@@ -2353,7 +2076,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="34" t="n">
-        <v>0.928</v>
+        <v>1</v>
       </c>
       <c r="L2" s="34" t="inlineStr"/>
     </row>
@@ -2365,7 +2088,7 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>pump_containment</t>
+          <t>Containment</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
@@ -2383,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="34" t="n">
-        <v>0.963</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H3" s="34" t="n">
         <v>2</v>
@@ -2395,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="34" t="n">
-        <v>0.963</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L3" s="34" t="inlineStr"/>
     </row>
@@ -2407,7 +2130,7 @@
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>pump_urgency</t>
+          <t>Urgency</t>
         </is>
       </c>
       <c r="C4" s="34" t="inlineStr">
@@ -2422,10 +2145,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>0.726</v>
+        <v>0.99</v>
       </c>
       <c r="H4" s="34" t="n">
         <v>2</v>
@@ -2437,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="34" t="n">
-        <v>0.726</v>
+        <v>0.99</v>
       </c>
       <c r="L4" s="34" t="inlineStr"/>
     </row>
@@ -2449,7 +2172,7 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>hx_problem</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
@@ -2467,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>0.912</v>
+        <v>1</v>
       </c>
       <c r="H5" s="34" t="n">
         <v>2</v>
@@ -2479,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>0.912</v>
+        <v>1</v>
       </c>
       <c r="L5" s="34" t="inlineStr"/>
     </row>
@@ -2491,7 +2214,7 @@
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>hx_crosscontam</t>
+          <t>Cross-contamination</t>
         </is>
       </c>
       <c r="C6" s="34" t="inlineStr">
@@ -2509,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>0.987</v>
+        <v>0.88</v>
       </c>
       <c r="H6" s="34" t="n">
         <v>2</v>
@@ -2521,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>0.987</v>
+        <v>0.88</v>
       </c>
       <c r="L6" s="34" t="inlineStr"/>
     </row>
@@ -2533,7 +2256,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>hx_impact</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
@@ -2548,10 +2271,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="34" t="n">
-        <v>0.325</v>
+        <v>0.665</v>
       </c>
       <c r="H7" s="34" t="n">
         <v>2</v>
@@ -2563,10 +2286,10 @@
         <v>0.5</v>
       </c>
       <c r="K7" s="34" t="n">
-        <v>0.133</v>
+        <v>0.84</v>
       </c>
       <c r="L7" s="34" t="n">
-        <v>0.517</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="8">
@@ -2577,7 +2300,7 @@
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>col_symptom</t>
+          <t>Symptom</t>
         </is>
       </c>
       <c r="C8" s="34" t="inlineStr">
@@ -2592,10 +2315,10 @@
         <v>2</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>0.752</v>
+        <v>0.92</v>
       </c>
       <c r="H8" s="34" t="n">
         <v>2</v>
@@ -2607,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="34" t="n">
-        <v>0.752</v>
+        <v>0.92</v>
       </c>
       <c r="L8" s="34" t="inlineStr"/>
     </row>
@@ -2619,7 +2342,7 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>col_offspec</t>
+          <t>Off-spec</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
@@ -2637,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
       <c r="H9" s="34" t="n">
         <v>2</v>
@@ -2649,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="34" t="n">
-        <v>0.999</v>
+        <v>0.99</v>
       </c>
       <c r="L9" s="34" t="inlineStr"/>
     </row>
@@ -2661,7 +2384,7 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>col_stability</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
@@ -2679,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>0.8080000000000001</v>
+        <v>1</v>
       </c>
       <c r="H10" s="34" t="n">
         <v>2</v>
@@ -2691,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="34" t="n">
-        <v>0.8080000000000001</v>
+        <v>1</v>
       </c>
       <c r="L10" s="34" t="inlineStr"/>
     </row>
@@ -2706,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="19" min="1" max="1"/>
@@ -2728,228 +2451,36 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>run_started</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>20260930_163356</t>
+          <t>jev</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>rebuilt_from</t>
         </is>
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook.xlsx</t>
+          <t>output_jev_Raw</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>nimble</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>nimble</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>base_url</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>http://localhost:11434</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>endpoint_info</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>0.35.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>questions_hash</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>cddf93bf9d63</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>api_key_configured</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>records_in_run</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>records_completed</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>failed_records</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>review_threshold_default</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>elapsed_seconds</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>checkpoint</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_163356.jsonl</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>input_tokens</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>6698</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>total_tokens</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="inlineStr">
-        <is>
-          <t>6722</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>records_with_usage</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="34" t="inlineStr">
-        <is>
-          <t>output_sheets</t>
-        </is>
-      </c>
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>output_nimble_Results, output_nimble_Raw, output_nimble_Summary, output_nimble_Run_info</t>
+          <t>long-format rebuild without new API calls</t>
         </is>
       </c>
     </row>
@@ -4010,7 +3541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="18" min="1" max="1"/>
@@ -4029,37 +3560,42 @@
           <t>question_id</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>equipment_type</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="E1" s="22" t="inlineStr">
         <is>
           <t>instructions</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="F1" s="22" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="F1" s="22" t="inlineStr">
+      <c r="G1" s="22" t="inlineStr">
         <is>
           <t>review_below</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>label_count</t>
         </is>
       </c>
-      <c r="H1" s="22" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>check</t>
         </is>
@@ -4071,33 +3607,38 @@
           <t>pump_failure_mode</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>choice</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>What is the primary failure mode described?</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F2" s="24" t="n"/>
-      <c r="G2" s="25">
+      <c r="G2" s="24" t="n"/>
+      <c r="H2" s="25">
         <f>IF(A2="","",COUNTIF(Labels!$A$2:$A$300,A2))</f>
         <v/>
       </c>
-      <c r="H2" s="25">
-        <f>IF(A2="","",IF(COUNTIF($A$2:$A$60,A2)&gt;1,"Duplicate question_id",IF(D2="","Missing instructions",IF(C2="noul",IF(G2=0,"OK","noul takes no labels"),IF(OR(C2="choice",C2="score"),IF(G2&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I2" s="25">
+        <f>IF(A2="","",IF(COUNTIF($A$2:$A$60,A2)&gt;1,"Duplicate question_id",IF(E2="","Missing instructions",IF(D2="noul",IF(H2=0,"OK","noul takes no labels"),IF(OR(D2="choice",D2="score"),IF(H2&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -4107,33 +3648,38 @@
           <t>pump_containment</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>noul</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>Does the text describe process fluid leaking out of the equipment?</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F3" s="24" t="n"/>
-      <c r="G3" s="25">
+      <c r="G3" s="24" t="n"/>
+      <c r="H3" s="25">
         <f>IF(A3="","",COUNTIF(Labels!$A$2:$A$300,A3))</f>
         <v/>
       </c>
-      <c r="H3" s="25">
-        <f>IF(A3="","",IF(COUNTIF($A$2:$A$60,A3)&gt;1,"Duplicate question_id",IF(D3="","Missing instructions",IF(C3="noul",IF(G3=0,"OK","noul takes no labels"),IF(OR(C3="choice",C3="score"),IF(G3&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I3" s="25">
+        <f>IF(A3="","",IF(COUNTIF($A$2:$A$60,A3)&gt;1,"Duplicate question_id",IF(E3="","Missing instructions",IF(D3="noul",IF(H3=0,"OK","noul takes no labels"),IF(OR(D3="choice",D3="score"),IF(H3&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -4143,35 +3689,40 @@
           <t>pump_urgency</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>How urgent is follow-up?</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F4" s="24" t="n">
+      <c r="G4" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="G4" s="25">
+      <c r="H4" s="25">
         <f>IF(A4="","",COUNTIF(Labels!$A$2:$A$300,A4))</f>
         <v/>
       </c>
-      <c r="H4" s="25">
-        <f>IF(A4="","",IF(COUNTIF($A$2:$A$60,A4)&gt;1,"Duplicate question_id",IF(D4="","Missing instructions",IF(C4="noul",IF(G4=0,"OK","noul takes no labels"),IF(OR(C4="choice",C4="score"),IF(G4&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I4" s="25">
+        <f>IF(A4="","",IF(COUNTIF($A$2:$A$60,A4)&gt;1,"Duplicate question_id",IF(E4="","Missing instructions",IF(D4="noul",IF(H4=0,"OK","noul takes no labels"),IF(OR(D4="choice",D4="score"),IF(H4&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -4181,33 +3732,38 @@
           <t>hx_problem</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>choice</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>What is the primary problem described?</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="25">
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="25">
         <f>IF(A5="","",COUNTIF(Labels!$A$2:$A$300,A5))</f>
         <v/>
       </c>
-      <c r="H5" s="25">
-        <f>IF(A5="","",IF(COUNTIF($A$2:$A$60,A5)&gt;1,"Duplicate question_id",IF(D5="","Missing instructions",IF(C5="noul",IF(G5=0,"OK","noul takes no labels"),IF(OR(C5="choice",C5="score"),IF(G5&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I5" s="25">
+        <f>IF(A5="","",IF(COUNTIF($A$2:$A$60,A5)&gt;1,"Duplicate question_id",IF(E5="","Missing instructions",IF(D5="noul",IF(H5=0,"OK","noul takes no labels"),IF(OR(D5="choice",D5="score"),IF(H5&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -4217,33 +3773,38 @@
           <t>hx_crosscontam</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Cross-contamination</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>noul</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Does the text suggest mixing of shell-side and tube-side fluids?</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="25">
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="25">
         <f>IF(A6="","",COUNTIF(Labels!$A$2:$A$300,A6))</f>
         <v/>
       </c>
-      <c r="H6" s="25">
-        <f>IF(A6="","",IF(COUNTIF($A$2:$A$60,A6)&gt;1,"Duplicate question_id",IF(D6="","Missing instructions",IF(C6="noul",IF(G6=0,"OK","noul takes no labels"),IF(OR(C6="choice",C6="score"),IF(G6&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I6" s="25">
+        <f>IF(A6="","",IF(COUNTIF($A$2:$A$60,A6)&gt;1,"Duplicate question_id",IF(E6="","Missing instructions",IF(D6="noul",IF(H6=0,"OK","noul takes no labels"),IF(OR(D6="choice",D6="score"),IF(H6&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -4253,33 +3814,38 @@
           <t>hx_impact</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>How severe is the performance impact?</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="25">
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="25">
         <f>IF(A7="","",COUNTIF(Labels!$A$2:$A$300,A7))</f>
         <v/>
       </c>
-      <c r="H7" s="25">
-        <f>IF(A7="","",IF(COUNTIF($A$2:$A$60,A7)&gt;1,"Duplicate question_id",IF(D7="","Missing instructions",IF(C7="noul",IF(G7=0,"OK","noul takes no labels"),IF(OR(C7="choice",C7="score"),IF(G7&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I7" s="25">
+        <f>IF(A7="","",IF(COUNTIF($A$2:$A$60,A7)&gt;1,"Duplicate question_id",IF(E7="","Missing instructions",IF(D7="noul",IF(H7=0,"OK","noul takes no labels"),IF(OR(D7="choice",D7="score"),IF(H7&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -4289,33 +3855,38 @@
           <t>col_symptom</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>choice</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Which operating symptom is described?</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="25">
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="25">
         <f>IF(A8="","",COUNTIF(Labels!$A$2:$A$300,A8))</f>
         <v/>
       </c>
-      <c r="H8" s="25">
-        <f>IF(A8="","",IF(COUNTIF($A$2:$A$60,A8)&gt;1,"Duplicate question_id",IF(D8="","Missing instructions",IF(C8="noul",IF(G8=0,"OK","noul takes no labels"),IF(OR(C8="choice",C8="score"),IF(G8&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I8" s="25">
+        <f>IF(A8="","",IF(COUNTIF($A$2:$A$60,A8)&gt;1,"Duplicate question_id",IF(E8="","Missing instructions",IF(D8="noul",IF(H8=0,"OK","noul takes no labels"),IF(OR(D8="choice",D8="score"),IF(H8&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -4325,33 +3896,38 @@
           <t>col_offspec</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>noul</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Does the text mention off-spec product?</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="25">
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="25">
         <f>IF(A9="","",COUNTIF(Labels!$A$2:$A$300,A9))</f>
         <v/>
       </c>
-      <c r="H9" s="25">
-        <f>IF(A9="","",IF(COUNTIF($A$2:$A$60,A9)&gt;1,"Duplicate question_id",IF(D9="","Missing instructions",IF(C9="noul",IF(G9=0,"OK","noul takes no labels"),IF(OR(C9="choice",C9="score"),IF(G9&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I9" s="25">
+        <f>IF(A9="","",IF(COUNTIF($A$2:$A$60,A9)&gt;1,"Duplicate question_id",IF(E9="","Missing instructions",IF(D9="noul",IF(H9=0,"OK","noul takes no labels"),IF(OR(D9="choice",D9="score"),IF(H9&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -4361,833 +3937,838 @@
           <t>col_stability</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>How stable is column operation?</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="25">
+      <c r="G10" s="24" t="n"/>
+      <c r="H10" s="25">
         <f>IF(A10="","",COUNTIF(Labels!$A$2:$A$300,A10))</f>
         <v/>
       </c>
-      <c r="H10" s="25">
-        <f>IF(A10="","",IF(COUNTIF($A$2:$A$60,A10)&gt;1,"Duplicate question_id",IF(D10="","Missing instructions",IF(C10="noul",IF(G10=0,"OK","noul takes no labels"),IF(OR(C10="choice",C10="score"),IF(G10&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I10" s="25">
+        <f>IF(A10="","",IF(COUNTIF($A$2:$A$60,A10)&gt;1,"Duplicate question_id",IF(E10="","Missing instructions",IF(D10="noul",IF(H10=0,"OK","noul takes no labels"),IF(OR(D10="choice",D10="score"),IF(H10&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="19">
       <c r="A11" s="23" t="n"/>
-      <c r="B11" s="23" t="n"/>
       <c r="C11" s="23" t="n"/>
       <c r="D11" s="23" t="n"/>
       <c r="E11" s="23" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="25">
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="25">
         <f>IF(A11="","",COUNTIF(Labels!$A$2:$A$300,A11))</f>
         <v/>
       </c>
-      <c r="H11" s="25">
-        <f>IF(A11="","",IF(COUNTIF($A$2:$A$60,A11)&gt;1,"Duplicate question_id",IF(D11="","Missing instructions",IF(C11="noul",IF(G11=0,"OK","noul takes no labels"),IF(OR(C11="choice",C11="score"),IF(G11&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I11" s="25">
+        <f>IF(A11="","",IF(COUNTIF($A$2:$A$60,A11)&gt;1,"Duplicate question_id",IF(E11="","Missing instructions",IF(D11="noul",IF(H11=0,"OK","noul takes no labels"),IF(OR(D11="choice",D11="score"),IF(H11&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="19">
       <c r="A12" s="23" t="n"/>
-      <c r="B12" s="23" t="n"/>
       <c r="C12" s="23" t="n"/>
       <c r="D12" s="23" t="n"/>
       <c r="E12" s="23" t="n"/>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="25">
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="25">
         <f>IF(A12="","",COUNTIF(Labels!$A$2:$A$300,A12))</f>
         <v/>
       </c>
-      <c r="H12" s="25">
-        <f>IF(A12="","",IF(COUNTIF($A$2:$A$60,A12)&gt;1,"Duplicate question_id",IF(D12="","Missing instructions",IF(C12="noul",IF(G12=0,"OK","noul takes no labels"),IF(OR(C12="choice",C12="score"),IF(G12&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I12" s="25">
+        <f>IF(A12="","",IF(COUNTIF($A$2:$A$60,A12)&gt;1,"Duplicate question_id",IF(E12="","Missing instructions",IF(D12="noul",IF(H12=0,"OK","noul takes no labels"),IF(OR(D12="choice",D12="score"),IF(H12&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="19">
       <c r="A13" s="23" t="n"/>
-      <c r="B13" s="23" t="n"/>
       <c r="C13" s="23" t="n"/>
       <c r="D13" s="23" t="n"/>
       <c r="E13" s="23" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="25">
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="25">
         <f>IF(A13="","",COUNTIF(Labels!$A$2:$A$300,A13))</f>
         <v/>
       </c>
-      <c r="H13" s="25">
-        <f>IF(A13="","",IF(COUNTIF($A$2:$A$60,A13)&gt;1,"Duplicate question_id",IF(D13="","Missing instructions",IF(C13="noul",IF(G13=0,"OK","noul takes no labels"),IF(OR(C13="choice",C13="score"),IF(G13&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I13" s="25">
+        <f>IF(A13="","",IF(COUNTIF($A$2:$A$60,A13)&gt;1,"Duplicate question_id",IF(E13="","Missing instructions",IF(D13="noul",IF(H13=0,"OK","noul takes no labels"),IF(OR(D13="choice",D13="score"),IF(H13&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="19">
       <c r="A14" s="23" t="n"/>
-      <c r="B14" s="23" t="n"/>
       <c r="C14" s="23" t="n"/>
       <c r="D14" s="23" t="n"/>
       <c r="E14" s="23" t="n"/>
-      <c r="F14" s="24" t="n"/>
-      <c r="G14" s="25">
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="25">
         <f>IF(A14="","",COUNTIF(Labels!$A$2:$A$300,A14))</f>
         <v/>
       </c>
-      <c r="H14" s="25">
-        <f>IF(A14="","",IF(COUNTIF($A$2:$A$60,A14)&gt;1,"Duplicate question_id",IF(D14="","Missing instructions",IF(C14="noul",IF(G14=0,"OK","noul takes no labels"),IF(OR(C14="choice",C14="score"),IF(G14&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I14" s="25">
+        <f>IF(A14="","",IF(COUNTIF($A$2:$A$60,A14)&gt;1,"Duplicate question_id",IF(E14="","Missing instructions",IF(D14="noul",IF(H14=0,"OK","noul takes no labels"),IF(OR(D14="choice",D14="score"),IF(H14&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="19">
       <c r="A15" s="23" t="n"/>
-      <c r="B15" s="23" t="n"/>
       <c r="C15" s="23" t="n"/>
       <c r="D15" s="23" t="n"/>
       <c r="E15" s="23" t="n"/>
-      <c r="F15" s="24" t="n"/>
-      <c r="G15" s="25">
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="25">
         <f>IF(A15="","",COUNTIF(Labels!$A$2:$A$300,A15))</f>
         <v/>
       </c>
-      <c r="H15" s="25">
-        <f>IF(A15="","",IF(COUNTIF($A$2:$A$60,A15)&gt;1,"Duplicate question_id",IF(D15="","Missing instructions",IF(C15="noul",IF(G15=0,"OK","noul takes no labels"),IF(OR(C15="choice",C15="score"),IF(G15&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I15" s="25">
+        <f>IF(A15="","",IF(COUNTIF($A$2:$A$60,A15)&gt;1,"Duplicate question_id",IF(E15="","Missing instructions",IF(D15="noul",IF(H15=0,"OK","noul takes no labels"),IF(OR(D15="choice",D15="score"),IF(H15&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="19">
       <c r="A16" s="23" t="n"/>
-      <c r="B16" s="23" t="n"/>
       <c r="C16" s="23" t="n"/>
       <c r="D16" s="23" t="n"/>
       <c r="E16" s="23" t="n"/>
-      <c r="F16" s="24" t="n"/>
-      <c r="G16" s="25">
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="24" t="n"/>
+      <c r="H16" s="25">
         <f>IF(A16="","",COUNTIF(Labels!$A$2:$A$300,A16))</f>
         <v/>
       </c>
-      <c r="H16" s="25">
-        <f>IF(A16="","",IF(COUNTIF($A$2:$A$60,A16)&gt;1,"Duplicate question_id",IF(D16="","Missing instructions",IF(C16="noul",IF(G16=0,"OK","noul takes no labels"),IF(OR(C16="choice",C16="score"),IF(G16&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I16" s="25">
+        <f>IF(A16="","",IF(COUNTIF($A$2:$A$60,A16)&gt;1,"Duplicate question_id",IF(E16="","Missing instructions",IF(D16="noul",IF(H16=0,"OK","noul takes no labels"),IF(OR(D16="choice",D16="score"),IF(H16&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="19">
       <c r="A17" s="23" t="n"/>
-      <c r="B17" s="23" t="n"/>
       <c r="C17" s="23" t="n"/>
       <c r="D17" s="23" t="n"/>
       <c r="E17" s="23" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="25">
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="25">
         <f>IF(A17="","",COUNTIF(Labels!$A$2:$A$300,A17))</f>
         <v/>
       </c>
-      <c r="H17" s="25">
-        <f>IF(A17="","",IF(COUNTIF($A$2:$A$60,A17)&gt;1,"Duplicate question_id",IF(D17="","Missing instructions",IF(C17="noul",IF(G17=0,"OK","noul takes no labels"),IF(OR(C17="choice",C17="score"),IF(G17&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I17" s="25">
+        <f>IF(A17="","",IF(COUNTIF($A$2:$A$60,A17)&gt;1,"Duplicate question_id",IF(E17="","Missing instructions",IF(D17="noul",IF(H17=0,"OK","noul takes no labels"),IF(OR(D17="choice",D17="score"),IF(H17&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="19">
       <c r="A18" s="23" t="n"/>
-      <c r="B18" s="23" t="n"/>
       <c r="C18" s="23" t="n"/>
       <c r="D18" s="23" t="n"/>
       <c r="E18" s="23" t="n"/>
-      <c r="F18" s="24" t="n"/>
-      <c r="G18" s="25">
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="25">
         <f>IF(A18="","",COUNTIF(Labels!$A$2:$A$300,A18))</f>
         <v/>
       </c>
-      <c r="H18" s="25">
-        <f>IF(A18="","",IF(COUNTIF($A$2:$A$60,A18)&gt;1,"Duplicate question_id",IF(D18="","Missing instructions",IF(C18="noul",IF(G18=0,"OK","noul takes no labels"),IF(OR(C18="choice",C18="score"),IF(G18&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I18" s="25">
+        <f>IF(A18="","",IF(COUNTIF($A$2:$A$60,A18)&gt;1,"Duplicate question_id",IF(E18="","Missing instructions",IF(D18="noul",IF(H18=0,"OK","noul takes no labels"),IF(OR(D18="choice",D18="score"),IF(H18&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="19">
       <c r="A19" s="23" t="n"/>
-      <c r="B19" s="23" t="n"/>
       <c r="C19" s="23" t="n"/>
       <c r="D19" s="23" t="n"/>
       <c r="E19" s="23" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="25">
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="25">
         <f>IF(A19="","",COUNTIF(Labels!$A$2:$A$300,A19))</f>
         <v/>
       </c>
-      <c r="H19" s="25">
-        <f>IF(A19="","",IF(COUNTIF($A$2:$A$60,A19)&gt;1,"Duplicate question_id",IF(D19="","Missing instructions",IF(C19="noul",IF(G19=0,"OK","noul takes no labels"),IF(OR(C19="choice",C19="score"),IF(G19&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I19" s="25">
+        <f>IF(A19="","",IF(COUNTIF($A$2:$A$60,A19)&gt;1,"Duplicate question_id",IF(E19="","Missing instructions",IF(D19="noul",IF(H19=0,"OK","noul takes no labels"),IF(OR(D19="choice",D19="score"),IF(H19&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="19">
       <c r="A20" s="23" t="n"/>
-      <c r="B20" s="23" t="n"/>
       <c r="C20" s="23" t="n"/>
       <c r="D20" s="23" t="n"/>
       <c r="E20" s="23" t="n"/>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="25">
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="24" t="n"/>
+      <c r="H20" s="25">
         <f>IF(A20="","",COUNTIF(Labels!$A$2:$A$300,A20))</f>
         <v/>
       </c>
-      <c r="H20" s="25">
-        <f>IF(A20="","",IF(COUNTIF($A$2:$A$60,A20)&gt;1,"Duplicate question_id",IF(D20="","Missing instructions",IF(C20="noul",IF(G20=0,"OK","noul takes no labels"),IF(OR(C20="choice",C20="score"),IF(G20&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I20" s="25">
+        <f>IF(A20="","",IF(COUNTIF($A$2:$A$60,A20)&gt;1,"Duplicate question_id",IF(E20="","Missing instructions",IF(D20="noul",IF(H20=0,"OK","noul takes no labels"),IF(OR(D20="choice",D20="score"),IF(H20&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="19">
       <c r="A21" s="23" t="n"/>
-      <c r="B21" s="23" t="n"/>
       <c r="C21" s="23" t="n"/>
       <c r="D21" s="23" t="n"/>
       <c r="E21" s="23" t="n"/>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="25">
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="25">
         <f>IF(A21="","",COUNTIF(Labels!$A$2:$A$300,A21))</f>
         <v/>
       </c>
-      <c r="H21" s="25">
-        <f>IF(A21="","",IF(COUNTIF($A$2:$A$60,A21)&gt;1,"Duplicate question_id",IF(D21="","Missing instructions",IF(C21="noul",IF(G21=0,"OK","noul takes no labels"),IF(OR(C21="choice",C21="score"),IF(G21&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I21" s="25">
+        <f>IF(A21="","",IF(COUNTIF($A$2:$A$60,A21)&gt;1,"Duplicate question_id",IF(E21="","Missing instructions",IF(D21="noul",IF(H21=0,"OK","noul takes no labels"),IF(OR(D21="choice",D21="score"),IF(H21&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="19">
       <c r="A22" s="23" t="n"/>
-      <c r="B22" s="23" t="n"/>
       <c r="C22" s="23" t="n"/>
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="23" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="25">
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="25">
         <f>IF(A22="","",COUNTIF(Labels!$A$2:$A$300,A22))</f>
         <v/>
       </c>
-      <c r="H22" s="25">
-        <f>IF(A22="","",IF(COUNTIF($A$2:$A$60,A22)&gt;1,"Duplicate question_id",IF(D22="","Missing instructions",IF(C22="noul",IF(G22=0,"OK","noul takes no labels"),IF(OR(C22="choice",C22="score"),IF(G22&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I22" s="25">
+        <f>IF(A22="","",IF(COUNTIF($A$2:$A$60,A22)&gt;1,"Duplicate question_id",IF(E22="","Missing instructions",IF(D22="noul",IF(H22=0,"OK","noul takes no labels"),IF(OR(D22="choice",D22="score"),IF(H22&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="19">
       <c r="A23" s="23" t="n"/>
-      <c r="B23" s="23" t="n"/>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="23" t="n"/>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="25">
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="25">
         <f>IF(A23="","",COUNTIF(Labels!$A$2:$A$300,A23))</f>
         <v/>
       </c>
-      <c r="H23" s="25">
-        <f>IF(A23="","",IF(COUNTIF($A$2:$A$60,A23)&gt;1,"Duplicate question_id",IF(D23="","Missing instructions",IF(C23="noul",IF(G23=0,"OK","noul takes no labels"),IF(OR(C23="choice",C23="score"),IF(G23&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I23" s="25">
+        <f>IF(A23="","",IF(COUNTIF($A$2:$A$60,A23)&gt;1,"Duplicate question_id",IF(E23="","Missing instructions",IF(D23="noul",IF(H23=0,"OK","noul takes no labels"),IF(OR(D23="choice",D23="score"),IF(H23&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="19">
       <c r="A24" s="23" t="n"/>
-      <c r="B24" s="23" t="n"/>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="23" t="n"/>
-      <c r="F24" s="24" t="n"/>
-      <c r="G24" s="25">
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="25">
         <f>IF(A24="","",COUNTIF(Labels!$A$2:$A$300,A24))</f>
         <v/>
       </c>
-      <c r="H24" s="25">
-        <f>IF(A24="","",IF(COUNTIF($A$2:$A$60,A24)&gt;1,"Duplicate question_id",IF(D24="","Missing instructions",IF(C24="noul",IF(G24=0,"OK","noul takes no labels"),IF(OR(C24="choice",C24="score"),IF(G24&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I24" s="25">
+        <f>IF(A24="","",IF(COUNTIF($A$2:$A$60,A24)&gt;1,"Duplicate question_id",IF(E24="","Missing instructions",IF(D24="noul",IF(H24=0,"OK","noul takes no labels"),IF(OR(D24="choice",D24="score"),IF(H24&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="19">
       <c r="A25" s="23" t="n"/>
-      <c r="B25" s="23" t="n"/>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="23" t="n"/>
-      <c r="F25" s="24" t="n"/>
-      <c r="G25" s="25">
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="25">
         <f>IF(A25="","",COUNTIF(Labels!$A$2:$A$300,A25))</f>
         <v/>
       </c>
-      <c r="H25" s="25">
-        <f>IF(A25="","",IF(COUNTIF($A$2:$A$60,A25)&gt;1,"Duplicate question_id",IF(D25="","Missing instructions",IF(C25="noul",IF(G25=0,"OK","noul takes no labels"),IF(OR(C25="choice",C25="score"),IF(G25&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I25" s="25">
+        <f>IF(A25="","",IF(COUNTIF($A$2:$A$60,A25)&gt;1,"Duplicate question_id",IF(E25="","Missing instructions",IF(D25="noul",IF(H25=0,"OK","noul takes no labels"),IF(OR(D25="choice",D25="score"),IF(H25&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="19">
       <c r="A26" s="23" t="n"/>
-      <c r="B26" s="23" t="n"/>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="23" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="25">
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="25">
         <f>IF(A26="","",COUNTIF(Labels!$A$2:$A$300,A26))</f>
         <v/>
       </c>
-      <c r="H26" s="25">
-        <f>IF(A26="","",IF(COUNTIF($A$2:$A$60,A26)&gt;1,"Duplicate question_id",IF(D26="","Missing instructions",IF(C26="noul",IF(G26=0,"OK","noul takes no labels"),IF(OR(C26="choice",C26="score"),IF(G26&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I26" s="25">
+        <f>IF(A26="","",IF(COUNTIF($A$2:$A$60,A26)&gt;1,"Duplicate question_id",IF(E26="","Missing instructions",IF(D26="noul",IF(H26=0,"OK","noul takes no labels"),IF(OR(D26="choice",D26="score"),IF(H26&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="19">
       <c r="A27" s="23" t="n"/>
-      <c r="B27" s="23" t="n"/>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="23" t="n"/>
       <c r="E27" s="23" t="n"/>
-      <c r="F27" s="24" t="n"/>
-      <c r="G27" s="25">
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="25">
         <f>IF(A27="","",COUNTIF(Labels!$A$2:$A$300,A27))</f>
         <v/>
       </c>
-      <c r="H27" s="25">
-        <f>IF(A27="","",IF(COUNTIF($A$2:$A$60,A27)&gt;1,"Duplicate question_id",IF(D27="","Missing instructions",IF(C27="noul",IF(G27=0,"OK","noul takes no labels"),IF(OR(C27="choice",C27="score"),IF(G27&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I27" s="25">
+        <f>IF(A27="","",IF(COUNTIF($A$2:$A$60,A27)&gt;1,"Duplicate question_id",IF(E27="","Missing instructions",IF(D27="noul",IF(H27=0,"OK","noul takes no labels"),IF(OR(D27="choice",D27="score"),IF(H27&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="19">
       <c r="A28" s="23" t="n"/>
-      <c r="B28" s="23" t="n"/>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="23" t="n"/>
       <c r="E28" s="23" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="25">
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="25">
         <f>IF(A28="","",COUNTIF(Labels!$A$2:$A$300,A28))</f>
         <v/>
       </c>
-      <c r="H28" s="25">
-        <f>IF(A28="","",IF(COUNTIF($A$2:$A$60,A28)&gt;1,"Duplicate question_id",IF(D28="","Missing instructions",IF(C28="noul",IF(G28=0,"OK","noul takes no labels"),IF(OR(C28="choice",C28="score"),IF(G28&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I28" s="25">
+        <f>IF(A28="","",IF(COUNTIF($A$2:$A$60,A28)&gt;1,"Duplicate question_id",IF(E28="","Missing instructions",IF(D28="noul",IF(H28=0,"OK","noul takes no labels"),IF(OR(D28="choice",D28="score"),IF(H28&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="19">
       <c r="A29" s="23" t="n"/>
-      <c r="B29" s="23" t="n"/>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="23" t="n"/>
       <c r="E29" s="23" t="n"/>
-      <c r="F29" s="24" t="n"/>
-      <c r="G29" s="25">
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="25">
         <f>IF(A29="","",COUNTIF(Labels!$A$2:$A$300,A29))</f>
         <v/>
       </c>
-      <c r="H29" s="25">
-        <f>IF(A29="","",IF(COUNTIF($A$2:$A$60,A29)&gt;1,"Duplicate question_id",IF(D29="","Missing instructions",IF(C29="noul",IF(G29=0,"OK","noul takes no labels"),IF(OR(C29="choice",C29="score"),IF(G29&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I29" s="25">
+        <f>IF(A29="","",IF(COUNTIF($A$2:$A$60,A29)&gt;1,"Duplicate question_id",IF(E29="","Missing instructions",IF(D29="noul",IF(H29=0,"OK","noul takes no labels"),IF(OR(D29="choice",D29="score"),IF(H29&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="19">
       <c r="A30" s="23" t="n"/>
-      <c r="B30" s="23" t="n"/>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="23" t="n"/>
       <c r="E30" s="23" t="n"/>
-      <c r="F30" s="24" t="n"/>
-      <c r="G30" s="25">
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="25">
         <f>IF(A30="","",COUNTIF(Labels!$A$2:$A$300,A30))</f>
         <v/>
       </c>
-      <c r="H30" s="25">
-        <f>IF(A30="","",IF(COUNTIF($A$2:$A$60,A30)&gt;1,"Duplicate question_id",IF(D30="","Missing instructions",IF(C30="noul",IF(G30=0,"OK","noul takes no labels"),IF(OR(C30="choice",C30="score"),IF(G30&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I30" s="25">
+        <f>IF(A30="","",IF(COUNTIF($A$2:$A$60,A30)&gt;1,"Duplicate question_id",IF(E30="","Missing instructions",IF(D30="noul",IF(H30=0,"OK","noul takes no labels"),IF(OR(D30="choice",D30="score"),IF(H30&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="19">
       <c r="A31" s="23" t="n"/>
-      <c r="B31" s="23" t="n"/>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="23" t="n"/>
       <c r="E31" s="23" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="25">
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="25">
         <f>IF(A31="","",COUNTIF(Labels!$A$2:$A$300,A31))</f>
         <v/>
       </c>
-      <c r="H31" s="25">
-        <f>IF(A31="","",IF(COUNTIF($A$2:$A$60,A31)&gt;1,"Duplicate question_id",IF(D31="","Missing instructions",IF(C31="noul",IF(G31=0,"OK","noul takes no labels"),IF(OR(C31="choice",C31="score"),IF(G31&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I31" s="25">
+        <f>IF(A31="","",IF(COUNTIF($A$2:$A$60,A31)&gt;1,"Duplicate question_id",IF(E31="","Missing instructions",IF(D31="noul",IF(H31=0,"OK","noul takes no labels"),IF(OR(D31="choice",D31="score"),IF(H31&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="19">
       <c r="A32" s="23" t="n"/>
-      <c r="B32" s="23" t="n"/>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="23" t="n"/>
       <c r="E32" s="23" t="n"/>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="25">
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="25">
         <f>IF(A32="","",COUNTIF(Labels!$A$2:$A$300,A32))</f>
         <v/>
       </c>
-      <c r="H32" s="25">
-        <f>IF(A32="","",IF(COUNTIF($A$2:$A$60,A32)&gt;1,"Duplicate question_id",IF(D32="","Missing instructions",IF(C32="noul",IF(G32=0,"OK","noul takes no labels"),IF(OR(C32="choice",C32="score"),IF(G32&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I32" s="25">
+        <f>IF(A32="","",IF(COUNTIF($A$2:$A$60,A32)&gt;1,"Duplicate question_id",IF(E32="","Missing instructions",IF(D32="noul",IF(H32=0,"OK","noul takes no labels"),IF(OR(D32="choice",D32="score"),IF(H32&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="19">
       <c r="A33" s="23" t="n"/>
-      <c r="B33" s="23" t="n"/>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="23" t="n"/>
       <c r="E33" s="23" t="n"/>
-      <c r="F33" s="24" t="n"/>
-      <c r="G33" s="25">
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="25">
         <f>IF(A33="","",COUNTIF(Labels!$A$2:$A$300,A33))</f>
         <v/>
       </c>
-      <c r="H33" s="25">
-        <f>IF(A33="","",IF(COUNTIF($A$2:$A$60,A33)&gt;1,"Duplicate question_id",IF(D33="","Missing instructions",IF(C33="noul",IF(G33=0,"OK","noul takes no labels"),IF(OR(C33="choice",C33="score"),IF(G33&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I33" s="25">
+        <f>IF(A33="","",IF(COUNTIF($A$2:$A$60,A33)&gt;1,"Duplicate question_id",IF(E33="","Missing instructions",IF(D33="noul",IF(H33=0,"OK","noul takes no labels"),IF(OR(D33="choice",D33="score"),IF(H33&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="19">
       <c r="A34" s="23" t="n"/>
-      <c r="B34" s="23" t="n"/>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="23" t="n"/>
-      <c r="F34" s="24" t="n"/>
-      <c r="G34" s="25">
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="25">
         <f>IF(A34="","",COUNTIF(Labels!$A$2:$A$300,A34))</f>
         <v/>
       </c>
-      <c r="H34" s="25">
-        <f>IF(A34="","",IF(COUNTIF($A$2:$A$60,A34)&gt;1,"Duplicate question_id",IF(D34="","Missing instructions",IF(C34="noul",IF(G34=0,"OK","noul takes no labels"),IF(OR(C34="choice",C34="score"),IF(G34&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I34" s="25">
+        <f>IF(A34="","",IF(COUNTIF($A$2:$A$60,A34)&gt;1,"Duplicate question_id",IF(E34="","Missing instructions",IF(D34="noul",IF(H34=0,"OK","noul takes no labels"),IF(OR(D34="choice",D34="score"),IF(H34&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="19">
       <c r="A35" s="23" t="n"/>
-      <c r="B35" s="23" t="n"/>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="23" t="n"/>
-      <c r="F35" s="24" t="n"/>
-      <c r="G35" s="25">
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="25">
         <f>IF(A35="","",COUNTIF(Labels!$A$2:$A$300,A35))</f>
         <v/>
       </c>
-      <c r="H35" s="25">
-        <f>IF(A35="","",IF(COUNTIF($A$2:$A$60,A35)&gt;1,"Duplicate question_id",IF(D35="","Missing instructions",IF(C35="noul",IF(G35=0,"OK","noul takes no labels"),IF(OR(C35="choice",C35="score"),IF(G35&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I35" s="25">
+        <f>IF(A35="","",IF(COUNTIF($A$2:$A$60,A35)&gt;1,"Duplicate question_id",IF(E35="","Missing instructions",IF(D35="noul",IF(H35=0,"OK","noul takes no labels"),IF(OR(D35="choice",D35="score"),IF(H35&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="19">
       <c r="A36" s="23" t="n"/>
-      <c r="B36" s="23" t="n"/>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="23" t="n"/>
-      <c r="F36" s="24" t="n"/>
-      <c r="G36" s="25">
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="25">
         <f>IF(A36="","",COUNTIF(Labels!$A$2:$A$300,A36))</f>
         <v/>
       </c>
-      <c r="H36" s="25">
-        <f>IF(A36="","",IF(COUNTIF($A$2:$A$60,A36)&gt;1,"Duplicate question_id",IF(D36="","Missing instructions",IF(C36="noul",IF(G36=0,"OK","noul takes no labels"),IF(OR(C36="choice",C36="score"),IF(G36&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I36" s="25">
+        <f>IF(A36="","",IF(COUNTIF($A$2:$A$60,A36)&gt;1,"Duplicate question_id",IF(E36="","Missing instructions",IF(D36="noul",IF(H36=0,"OK","noul takes no labels"),IF(OR(D36="choice",D36="score"),IF(H36&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="19">
       <c r="A37" s="23" t="n"/>
-      <c r="B37" s="23" t="n"/>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="23" t="n"/>
-      <c r="F37" s="24" t="n"/>
-      <c r="G37" s="25">
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="24" t="n"/>
+      <c r="H37" s="25">
         <f>IF(A37="","",COUNTIF(Labels!$A$2:$A$300,A37))</f>
         <v/>
       </c>
-      <c r="H37" s="25">
-        <f>IF(A37="","",IF(COUNTIF($A$2:$A$60,A37)&gt;1,"Duplicate question_id",IF(D37="","Missing instructions",IF(C37="noul",IF(G37=0,"OK","noul takes no labels"),IF(OR(C37="choice",C37="score"),IF(G37&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I37" s="25">
+        <f>IF(A37="","",IF(COUNTIF($A$2:$A$60,A37)&gt;1,"Duplicate question_id",IF(E37="","Missing instructions",IF(D37="noul",IF(H37=0,"OK","noul takes no labels"),IF(OR(D37="choice",D37="score"),IF(H37&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="19">
       <c r="A38" s="23" t="n"/>
-      <c r="B38" s="23" t="n"/>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="23" t="n"/>
-      <c r="F38" s="24" t="n"/>
-      <c r="G38" s="25">
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="24" t="n"/>
+      <c r="H38" s="25">
         <f>IF(A38="","",COUNTIF(Labels!$A$2:$A$300,A38))</f>
         <v/>
       </c>
-      <c r="H38" s="25">
-        <f>IF(A38="","",IF(COUNTIF($A$2:$A$60,A38)&gt;1,"Duplicate question_id",IF(D38="","Missing instructions",IF(C38="noul",IF(G38=0,"OK","noul takes no labels"),IF(OR(C38="choice",C38="score"),IF(G38&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I38" s="25">
+        <f>IF(A38="","",IF(COUNTIF($A$2:$A$60,A38)&gt;1,"Duplicate question_id",IF(E38="","Missing instructions",IF(D38="noul",IF(H38=0,"OK","noul takes no labels"),IF(OR(D38="choice",D38="score"),IF(H38&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="19">
       <c r="A39" s="23" t="n"/>
-      <c r="B39" s="23" t="n"/>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="23" t="n"/>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="25">
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="25">
         <f>IF(A39="","",COUNTIF(Labels!$A$2:$A$300,A39))</f>
         <v/>
       </c>
-      <c r="H39" s="25">
-        <f>IF(A39="","",IF(COUNTIF($A$2:$A$60,A39)&gt;1,"Duplicate question_id",IF(D39="","Missing instructions",IF(C39="noul",IF(G39=0,"OK","noul takes no labels"),IF(OR(C39="choice",C39="score"),IF(G39&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I39" s="25">
+        <f>IF(A39="","",IF(COUNTIF($A$2:$A$60,A39)&gt;1,"Duplicate question_id",IF(E39="","Missing instructions",IF(D39="noul",IF(H39=0,"OK","noul takes no labels"),IF(OR(D39="choice",D39="score"),IF(H39&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="19">
       <c r="A40" s="23" t="n"/>
-      <c r="B40" s="23" t="n"/>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="23" t="n"/>
-      <c r="F40" s="24" t="n"/>
-      <c r="G40" s="25">
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="24" t="n"/>
+      <c r="H40" s="25">
         <f>IF(A40="","",COUNTIF(Labels!$A$2:$A$300,A40))</f>
         <v/>
       </c>
-      <c r="H40" s="25">
-        <f>IF(A40="","",IF(COUNTIF($A$2:$A$60,A40)&gt;1,"Duplicate question_id",IF(D40="","Missing instructions",IF(C40="noul",IF(G40=0,"OK","noul takes no labels"),IF(OR(C40="choice",C40="score"),IF(G40&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I40" s="25">
+        <f>IF(A40="","",IF(COUNTIF($A$2:$A$60,A40)&gt;1,"Duplicate question_id",IF(E40="","Missing instructions",IF(D40="noul",IF(H40=0,"OK","noul takes no labels"),IF(OR(D40="choice",D40="score"),IF(H40&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="19">
       <c r="A41" s="23" t="n"/>
-      <c r="B41" s="23" t="n"/>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="23" t="n"/>
-      <c r="F41" s="24" t="n"/>
-      <c r="G41" s="25">
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="24" t="n"/>
+      <c r="H41" s="25">
         <f>IF(A41="","",COUNTIF(Labels!$A$2:$A$300,A41))</f>
         <v/>
       </c>
-      <c r="H41" s="25">
-        <f>IF(A41="","",IF(COUNTIF($A$2:$A$60,A41)&gt;1,"Duplicate question_id",IF(D41="","Missing instructions",IF(C41="noul",IF(G41=0,"OK","noul takes no labels"),IF(OR(C41="choice",C41="score"),IF(G41&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I41" s="25">
+        <f>IF(A41="","",IF(COUNTIF($A$2:$A$60,A41)&gt;1,"Duplicate question_id",IF(E41="","Missing instructions",IF(D41="noul",IF(H41=0,"OK","noul takes no labels"),IF(OR(D41="choice",D41="score"),IF(H41&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="19">
       <c r="A42" s="23" t="n"/>
-      <c r="B42" s="23" t="n"/>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="23" t="n"/>
       <c r="E42" s="23" t="n"/>
-      <c r="F42" s="24" t="n"/>
-      <c r="G42" s="25">
+      <c r="F42" s="23" t="n"/>
+      <c r="G42" s="24" t="n"/>
+      <c r="H42" s="25">
         <f>IF(A42="","",COUNTIF(Labels!$A$2:$A$300,A42))</f>
         <v/>
       </c>
-      <c r="H42" s="25">
-        <f>IF(A42="","",IF(COUNTIF($A$2:$A$60,A42)&gt;1,"Duplicate question_id",IF(D42="","Missing instructions",IF(C42="noul",IF(G42=0,"OK","noul takes no labels"),IF(OR(C42="choice",C42="score"),IF(G42&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I42" s="25">
+        <f>IF(A42="","",IF(COUNTIF($A$2:$A$60,A42)&gt;1,"Duplicate question_id",IF(E42="","Missing instructions",IF(D42="noul",IF(H42=0,"OK","noul takes no labels"),IF(OR(D42="choice",D42="score"),IF(H42&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="19">
       <c r="A43" s="23" t="n"/>
-      <c r="B43" s="23" t="n"/>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="23" t="n"/>
       <c r="E43" s="23" t="n"/>
-      <c r="F43" s="24" t="n"/>
-      <c r="G43" s="25">
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="24" t="n"/>
+      <c r="H43" s="25">
         <f>IF(A43="","",COUNTIF(Labels!$A$2:$A$300,A43))</f>
         <v/>
       </c>
-      <c r="H43" s="25">
-        <f>IF(A43="","",IF(COUNTIF($A$2:$A$60,A43)&gt;1,"Duplicate question_id",IF(D43="","Missing instructions",IF(C43="noul",IF(G43=0,"OK","noul takes no labels"),IF(OR(C43="choice",C43="score"),IF(G43&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I43" s="25">
+        <f>IF(A43="","",IF(COUNTIF($A$2:$A$60,A43)&gt;1,"Duplicate question_id",IF(E43="","Missing instructions",IF(D43="noul",IF(H43=0,"OK","noul takes no labels"),IF(OR(D43="choice",D43="score"),IF(H43&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="19">
       <c r="A44" s="23" t="n"/>
-      <c r="B44" s="23" t="n"/>
       <c r="C44" s="23" t="n"/>
       <c r="D44" s="23" t="n"/>
       <c r="E44" s="23" t="n"/>
-      <c r="F44" s="24" t="n"/>
-      <c r="G44" s="25">
+      <c r="F44" s="23" t="n"/>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="25">
         <f>IF(A44="","",COUNTIF(Labels!$A$2:$A$300,A44))</f>
         <v/>
       </c>
-      <c r="H44" s="25">
-        <f>IF(A44="","",IF(COUNTIF($A$2:$A$60,A44)&gt;1,"Duplicate question_id",IF(D44="","Missing instructions",IF(C44="noul",IF(G44=0,"OK","noul takes no labels"),IF(OR(C44="choice",C44="score"),IF(G44&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I44" s="25">
+        <f>IF(A44="","",IF(COUNTIF($A$2:$A$60,A44)&gt;1,"Duplicate question_id",IF(E44="","Missing instructions",IF(D44="noul",IF(H44=0,"OK","noul takes no labels"),IF(OR(D44="choice",D44="score"),IF(H44&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="19">
       <c r="A45" s="23" t="n"/>
-      <c r="B45" s="23" t="n"/>
       <c r="C45" s="23" t="n"/>
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="23" t="n"/>
-      <c r="F45" s="24" t="n"/>
-      <c r="G45" s="25">
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="25">
         <f>IF(A45="","",COUNTIF(Labels!$A$2:$A$300,A45))</f>
         <v/>
       </c>
-      <c r="H45" s="25">
-        <f>IF(A45="","",IF(COUNTIF($A$2:$A$60,A45)&gt;1,"Duplicate question_id",IF(D45="","Missing instructions",IF(C45="noul",IF(G45=0,"OK","noul takes no labels"),IF(OR(C45="choice",C45="score"),IF(G45&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I45" s="25">
+        <f>IF(A45="","",IF(COUNTIF($A$2:$A$60,A45)&gt;1,"Duplicate question_id",IF(E45="","Missing instructions",IF(D45="noul",IF(H45=0,"OK","noul takes no labels"),IF(OR(D45="choice",D45="score"),IF(H45&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="19">
       <c r="A46" s="23" t="n"/>
-      <c r="B46" s="23" t="n"/>
       <c r="C46" s="23" t="n"/>
       <c r="D46" s="23" t="n"/>
       <c r="E46" s="23" t="n"/>
-      <c r="F46" s="24" t="n"/>
-      <c r="G46" s="25">
+      <c r="F46" s="23" t="n"/>
+      <c r="G46" s="24" t="n"/>
+      <c r="H46" s="25">
         <f>IF(A46="","",COUNTIF(Labels!$A$2:$A$300,A46))</f>
         <v/>
       </c>
-      <c r="H46" s="25">
-        <f>IF(A46="","",IF(COUNTIF($A$2:$A$60,A46)&gt;1,"Duplicate question_id",IF(D46="","Missing instructions",IF(C46="noul",IF(G46=0,"OK","noul takes no labels"),IF(OR(C46="choice",C46="score"),IF(G46&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I46" s="25">
+        <f>IF(A46="","",IF(COUNTIF($A$2:$A$60,A46)&gt;1,"Duplicate question_id",IF(E46="","Missing instructions",IF(D46="noul",IF(H46=0,"OK","noul takes no labels"),IF(OR(D46="choice",D46="score"),IF(H46&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="19">
       <c r="A47" s="23" t="n"/>
-      <c r="B47" s="23" t="n"/>
       <c r="C47" s="23" t="n"/>
       <c r="D47" s="23" t="n"/>
       <c r="E47" s="23" t="n"/>
-      <c r="F47" s="24" t="n"/>
-      <c r="G47" s="25">
+      <c r="F47" s="23" t="n"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="25">
         <f>IF(A47="","",COUNTIF(Labels!$A$2:$A$300,A47))</f>
         <v/>
       </c>
-      <c r="H47" s="25">
-        <f>IF(A47="","",IF(COUNTIF($A$2:$A$60,A47)&gt;1,"Duplicate question_id",IF(D47="","Missing instructions",IF(C47="noul",IF(G47=0,"OK","noul takes no labels"),IF(OR(C47="choice",C47="score"),IF(G47&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I47" s="25">
+        <f>IF(A47="","",IF(COUNTIF($A$2:$A$60,A47)&gt;1,"Duplicate question_id",IF(E47="","Missing instructions",IF(D47="noul",IF(H47=0,"OK","noul takes no labels"),IF(OR(D47="choice",D47="score"),IF(H47&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="19">
       <c r="A48" s="23" t="n"/>
-      <c r="B48" s="23" t="n"/>
       <c r="C48" s="23" t="n"/>
       <c r="D48" s="23" t="n"/>
       <c r="E48" s="23" t="n"/>
-      <c r="F48" s="24" t="n"/>
-      <c r="G48" s="25">
+      <c r="F48" s="23" t="n"/>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="25">
         <f>IF(A48="","",COUNTIF(Labels!$A$2:$A$300,A48))</f>
         <v/>
       </c>
-      <c r="H48" s="25">
-        <f>IF(A48="","",IF(COUNTIF($A$2:$A$60,A48)&gt;1,"Duplicate question_id",IF(D48="","Missing instructions",IF(C48="noul",IF(G48=0,"OK","noul takes no labels"),IF(OR(C48="choice",C48="score"),IF(G48&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I48" s="25">
+        <f>IF(A48="","",IF(COUNTIF($A$2:$A$60,A48)&gt;1,"Duplicate question_id",IF(E48="","Missing instructions",IF(D48="noul",IF(H48=0,"OK","noul takes no labels"),IF(OR(D48="choice",D48="score"),IF(H48&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="19">
       <c r="A49" s="23" t="n"/>
-      <c r="B49" s="23" t="n"/>
       <c r="C49" s="23" t="n"/>
       <c r="D49" s="23" t="n"/>
       <c r="E49" s="23" t="n"/>
-      <c r="F49" s="24" t="n"/>
-      <c r="G49" s="25">
+      <c r="F49" s="23" t="n"/>
+      <c r="G49" s="24" t="n"/>
+      <c r="H49" s="25">
         <f>IF(A49="","",COUNTIF(Labels!$A$2:$A$300,A49))</f>
         <v/>
       </c>
-      <c r="H49" s="25">
-        <f>IF(A49="","",IF(COUNTIF($A$2:$A$60,A49)&gt;1,"Duplicate question_id",IF(D49="","Missing instructions",IF(C49="noul",IF(G49=0,"OK","noul takes no labels"),IF(OR(C49="choice",C49="score"),IF(G49&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I49" s="25">
+        <f>IF(A49="","",IF(COUNTIF($A$2:$A$60,A49)&gt;1,"Duplicate question_id",IF(E49="","Missing instructions",IF(D49="noul",IF(H49=0,"OK","noul takes no labels"),IF(OR(D49="choice",D49="score"),IF(H49&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="19">
       <c r="A50" s="23" t="n"/>
-      <c r="B50" s="23" t="n"/>
       <c r="C50" s="23" t="n"/>
       <c r="D50" s="23" t="n"/>
       <c r="E50" s="23" t="n"/>
-      <c r="F50" s="24" t="n"/>
-      <c r="G50" s="25">
+      <c r="F50" s="23" t="n"/>
+      <c r="G50" s="24" t="n"/>
+      <c r="H50" s="25">
         <f>IF(A50="","",COUNTIF(Labels!$A$2:$A$300,A50))</f>
         <v/>
       </c>
-      <c r="H50" s="25">
-        <f>IF(A50="","",IF(COUNTIF($A$2:$A$60,A50)&gt;1,"Duplicate question_id",IF(D50="","Missing instructions",IF(C50="noul",IF(G50=0,"OK","noul takes no labels"),IF(OR(C50="choice",C50="score"),IF(G50&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I50" s="25">
+        <f>IF(A50="","",IF(COUNTIF($A$2:$A$60,A50)&gt;1,"Duplicate question_id",IF(E50="","Missing instructions",IF(D50="noul",IF(H50=0,"OK","noul takes no labels"),IF(OR(D50="choice",D50="score"),IF(H50&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="19">
       <c r="A51" s="23" t="n"/>
-      <c r="B51" s="23" t="n"/>
       <c r="C51" s="23" t="n"/>
       <c r="D51" s="23" t="n"/>
       <c r="E51" s="23" t="n"/>
-      <c r="F51" s="24" t="n"/>
-      <c r="G51" s="25">
+      <c r="F51" s="23" t="n"/>
+      <c r="G51" s="24" t="n"/>
+      <c r="H51" s="25">
         <f>IF(A51="","",COUNTIF(Labels!$A$2:$A$300,A51))</f>
         <v/>
       </c>
-      <c r="H51" s="25">
-        <f>IF(A51="","",IF(COUNTIF($A$2:$A$60,A51)&gt;1,"Duplicate question_id",IF(D51="","Missing instructions",IF(C51="noul",IF(G51=0,"OK","noul takes no labels"),IF(OR(C51="choice",C51="score"),IF(G51&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I51" s="25">
+        <f>IF(A51="","",IF(COUNTIF($A$2:$A$60,A51)&gt;1,"Duplicate question_id",IF(E51="","Missing instructions",IF(D51="noul",IF(H51=0,"OK","noul takes no labels"),IF(OR(D51="choice",D51="score"),IF(H51&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="19">
       <c r="A52" s="23" t="n"/>
-      <c r="B52" s="23" t="n"/>
       <c r="C52" s="23" t="n"/>
       <c r="D52" s="23" t="n"/>
       <c r="E52" s="23" t="n"/>
-      <c r="F52" s="24" t="n"/>
-      <c r="G52" s="25">
+      <c r="F52" s="23" t="n"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="25">
         <f>IF(A52="","",COUNTIF(Labels!$A$2:$A$300,A52))</f>
         <v/>
       </c>
-      <c r="H52" s="25">
-        <f>IF(A52="","",IF(COUNTIF($A$2:$A$60,A52)&gt;1,"Duplicate question_id",IF(D52="","Missing instructions",IF(C52="noul",IF(G52=0,"OK","noul takes no labels"),IF(OR(C52="choice",C52="score"),IF(G52&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I52" s="25">
+        <f>IF(A52="","",IF(COUNTIF($A$2:$A$60,A52)&gt;1,"Duplicate question_id",IF(E52="","Missing instructions",IF(D52="noul",IF(H52=0,"OK","noul takes no labels"),IF(OR(D52="choice",D52="score"),IF(H52&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="19">
       <c r="A53" s="23" t="n"/>
-      <c r="B53" s="23" t="n"/>
       <c r="C53" s="23" t="n"/>
       <c r="D53" s="23" t="n"/>
       <c r="E53" s="23" t="n"/>
-      <c r="F53" s="24" t="n"/>
-      <c r="G53" s="25">
+      <c r="F53" s="23" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="25">
         <f>IF(A53="","",COUNTIF(Labels!$A$2:$A$300,A53))</f>
         <v/>
       </c>
-      <c r="H53" s="25">
-        <f>IF(A53="","",IF(COUNTIF($A$2:$A$60,A53)&gt;1,"Duplicate question_id",IF(D53="","Missing instructions",IF(C53="noul",IF(G53=0,"OK","noul takes no labels"),IF(OR(C53="choice",C53="score"),IF(G53&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I53" s="25">
+        <f>IF(A53="","",IF(COUNTIF($A$2:$A$60,A53)&gt;1,"Duplicate question_id",IF(E53="","Missing instructions",IF(D53="noul",IF(H53=0,"OK","noul takes no labels"),IF(OR(D53="choice",D53="score"),IF(H53&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="19">
       <c r="A54" s="23" t="n"/>
-      <c r="B54" s="23" t="n"/>
       <c r="C54" s="23" t="n"/>
       <c r="D54" s="23" t="n"/>
       <c r="E54" s="23" t="n"/>
-      <c r="F54" s="24" t="n"/>
-      <c r="G54" s="25">
+      <c r="F54" s="23" t="n"/>
+      <c r="G54" s="24" t="n"/>
+      <c r="H54" s="25">
         <f>IF(A54="","",COUNTIF(Labels!$A$2:$A$300,A54))</f>
         <v/>
       </c>
-      <c r="H54" s="25">
-        <f>IF(A54="","",IF(COUNTIF($A$2:$A$60,A54)&gt;1,"Duplicate question_id",IF(D54="","Missing instructions",IF(C54="noul",IF(G54=0,"OK","noul takes no labels"),IF(OR(C54="choice",C54="score"),IF(G54&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I54" s="25">
+        <f>IF(A54="","",IF(COUNTIF($A$2:$A$60,A54)&gt;1,"Duplicate question_id",IF(E54="","Missing instructions",IF(D54="noul",IF(H54=0,"OK","noul takes no labels"),IF(OR(D54="choice",D54="score"),IF(H54&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="19">
       <c r="A55" s="23" t="n"/>
-      <c r="B55" s="23" t="n"/>
       <c r="C55" s="23" t="n"/>
       <c r="D55" s="23" t="n"/>
       <c r="E55" s="23" t="n"/>
-      <c r="F55" s="24" t="n"/>
-      <c r="G55" s="25">
+      <c r="F55" s="23" t="n"/>
+      <c r="G55" s="24" t="n"/>
+      <c r="H55" s="25">
         <f>IF(A55="","",COUNTIF(Labels!$A$2:$A$300,A55))</f>
         <v/>
       </c>
-      <c r="H55" s="25">
-        <f>IF(A55="","",IF(COUNTIF($A$2:$A$60,A55)&gt;1,"Duplicate question_id",IF(D55="","Missing instructions",IF(C55="noul",IF(G55=0,"OK","noul takes no labels"),IF(OR(C55="choice",C55="score"),IF(G55&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I55" s="25">
+        <f>IF(A55="","",IF(COUNTIF($A$2:$A$60,A55)&gt;1,"Duplicate question_id",IF(E55="","Missing instructions",IF(D55="noul",IF(H55=0,"OK","noul takes no labels"),IF(OR(D55="choice",D55="score"),IF(H55&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="19">
       <c r="A56" s="23" t="n"/>
-      <c r="B56" s="23" t="n"/>
       <c r="C56" s="23" t="n"/>
       <c r="D56" s="23" t="n"/>
       <c r="E56" s="23" t="n"/>
-      <c r="F56" s="24" t="n"/>
-      <c r="G56" s="25">
+      <c r="F56" s="23" t="n"/>
+      <c r="G56" s="24" t="n"/>
+      <c r="H56" s="25">
         <f>IF(A56="","",COUNTIF(Labels!$A$2:$A$300,A56))</f>
         <v/>
       </c>
-      <c r="H56" s="25">
-        <f>IF(A56="","",IF(COUNTIF($A$2:$A$60,A56)&gt;1,"Duplicate question_id",IF(D56="","Missing instructions",IF(C56="noul",IF(G56=0,"OK","noul takes no labels"),IF(OR(C56="choice",C56="score"),IF(G56&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I56" s="25">
+        <f>IF(A56="","",IF(COUNTIF($A$2:$A$60,A56)&gt;1,"Duplicate question_id",IF(E56="","Missing instructions",IF(D56="noul",IF(H56=0,"OK","noul takes no labels"),IF(OR(D56="choice",D56="score"),IF(H56&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="19">
       <c r="A57" s="23" t="n"/>
-      <c r="B57" s="23" t="n"/>
       <c r="C57" s="23" t="n"/>
       <c r="D57" s="23" t="n"/>
       <c r="E57" s="23" t="n"/>
-      <c r="F57" s="24" t="n"/>
-      <c r="G57" s="25">
+      <c r="F57" s="23" t="n"/>
+      <c r="G57" s="24" t="n"/>
+      <c r="H57" s="25">
         <f>IF(A57="","",COUNTIF(Labels!$A$2:$A$300,A57))</f>
         <v/>
       </c>
-      <c r="H57" s="25">
-        <f>IF(A57="","",IF(COUNTIF($A$2:$A$60,A57)&gt;1,"Duplicate question_id",IF(D57="","Missing instructions",IF(C57="noul",IF(G57=0,"OK","noul takes no labels"),IF(OR(C57="choice",C57="score"),IF(G57&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I57" s="25">
+        <f>IF(A57="","",IF(COUNTIF($A$2:$A$60,A57)&gt;1,"Duplicate question_id",IF(E57="","Missing instructions",IF(D57="noul",IF(H57=0,"OK","noul takes no labels"),IF(OR(D57="choice",D57="score"),IF(H57&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="19">
       <c r="A58" s="23" t="n"/>
-      <c r="B58" s="23" t="n"/>
       <c r="C58" s="23" t="n"/>
       <c r="D58" s="23" t="n"/>
       <c r="E58" s="23" t="n"/>
-      <c r="F58" s="24" t="n"/>
-      <c r="G58" s="25">
+      <c r="F58" s="23" t="n"/>
+      <c r="G58" s="24" t="n"/>
+      <c r="H58" s="25">
         <f>IF(A58="","",COUNTIF(Labels!$A$2:$A$300,A58))</f>
         <v/>
       </c>
-      <c r="H58" s="25">
-        <f>IF(A58="","",IF(COUNTIF($A$2:$A$60,A58)&gt;1,"Duplicate question_id",IF(D58="","Missing instructions",IF(C58="noul",IF(G58=0,"OK","noul takes no labels"),IF(OR(C58="choice",C58="score"),IF(G58&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I58" s="25">
+        <f>IF(A58="","",IF(COUNTIF($A$2:$A$60,A58)&gt;1,"Duplicate question_id",IF(E58="","Missing instructions",IF(D58="noul",IF(H58=0,"OK","noul takes no labels"),IF(OR(D58="choice",D58="score"),IF(H58&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="19">
       <c r="A59" s="23" t="n"/>
-      <c r="B59" s="23" t="n"/>
       <c r="C59" s="23" t="n"/>
       <c r="D59" s="23" t="n"/>
       <c r="E59" s="23" t="n"/>
-      <c r="F59" s="24" t="n"/>
-      <c r="G59" s="25">
+      <c r="F59" s="23" t="n"/>
+      <c r="G59" s="24" t="n"/>
+      <c r="H59" s="25">
         <f>IF(A59="","",COUNTIF(Labels!$A$2:$A$300,A59))</f>
         <v/>
       </c>
-      <c r="H59" s="25">
-        <f>IF(A59="","",IF(COUNTIF($A$2:$A$60,A59)&gt;1,"Duplicate question_id",IF(D59="","Missing instructions",IF(C59="noul",IF(G59=0,"OK","noul takes no labels"),IF(OR(C59="choice",C59="score"),IF(G59&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I59" s="25">
+        <f>IF(A59="","",IF(COUNTIF($A$2:$A$60,A59)&gt;1,"Duplicate question_id",IF(E59="","Missing instructions",IF(D59="noul",IF(H59=0,"OK","noul takes no labels"),IF(OR(D59="choice",D59="score"),IF(H59&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="19">
       <c r="A60" s="23" t="n"/>
-      <c r="B60" s="23" t="n"/>
       <c r="C60" s="23" t="n"/>
       <c r="D60" s="23" t="n"/>
       <c r="E60" s="23" t="n"/>
-      <c r="F60" s="24" t="n"/>
-      <c r="G60" s="25">
+      <c r="F60" s="23" t="n"/>
+      <c r="G60" s="24" t="n"/>
+      <c r="H60" s="25">
         <f>IF(A60="","",COUNTIF(Labels!$A$2:$A$300,A60))</f>
         <v/>
       </c>
-      <c r="H60" s="25">
-        <f>IF(A60="","",IF(COUNTIF($A$2:$A$60,A60)&gt;1,"Duplicate question_id",IF(D60="","Missing instructions",IF(C60="noul",IF(G60=0,"OK","noul takes no labels"),IF(OR(C60="choice",C60="score"),IF(G60&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+      <c r="I60" s="25">
+        <f>IF(A60="","",IF(COUNTIF($A$2:$A$60,A60)&gt;1,"Duplicate question_id",IF(E60="","Missing instructions",IF(D60="noul",IF(H60=0,"OK","noul takes no labels"),IF(OR(D60="choice",D60="score"),IF(H60&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
         <v/>
       </c>
     </row>
@@ -18532,1260 +18113,1578 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="18" min="1" max="3"/>
-    <col width="60" customWidth="1" style="18" min="4" max="4"/>
-    <col width="16" customWidth="1" style="18" min="5" max="5"/>
-    <col width="12" customWidth="1" style="18" min="6" max="6"/>
-    <col width="10" customWidth="1" style="18" min="7" max="7"/>
-    <col width="16" customWidth="1" style="18" min="8" max="8"/>
-    <col width="12" customWidth="1" style="18" min="9" max="9"/>
-    <col width="10" customWidth="1" style="18" min="10" max="10"/>
-    <col width="16" customWidth="1" style="18" min="11" max="11"/>
-    <col width="12" customWidth="1" style="18" min="12" max="12"/>
-    <col width="10" customWidth="1" style="18" min="13" max="13"/>
-    <col width="16" customWidth="1" style="18" min="14" max="14"/>
-    <col width="12" customWidth="1" style="18" min="15" max="15"/>
-    <col width="10" customWidth="1" style="18" min="16" max="16"/>
-    <col width="16" customWidth="1" style="18" min="17" max="17"/>
-    <col width="12" customWidth="1" style="18" min="18" max="18"/>
-    <col width="10" customWidth="1" style="18" min="19" max="19"/>
-    <col width="16" customWidth="1" style="18" min="20" max="20"/>
-    <col width="12" customWidth="1" style="18" min="21" max="21"/>
-    <col width="10" customWidth="1" style="18" min="22" max="22"/>
-    <col width="16" customWidth="1" style="18" min="23" max="23"/>
-    <col width="12" customWidth="1" style="18" min="24" max="24"/>
-    <col width="10" customWidth="1" style="18" min="25" max="25"/>
-    <col width="16" customWidth="1" style="18" min="26" max="26"/>
-    <col width="12" customWidth="1" style="18" min="27" max="27"/>
-    <col width="10" customWidth="1" style="18" min="28" max="28"/>
-    <col width="16" customWidth="1" style="18" min="29" max="29"/>
-    <col width="12" customWidth="1" style="18" min="30" max="30"/>
-    <col width="10" customWidth="1" style="18" min="31" max="31"/>
-    <col width="12" customWidth="1" style="18" min="32" max="32"/>
-    <col width="45" customWidth="1" style="18" min="33" max="33"/>
-    <col width="30" customWidth="1" style="18" min="34" max="34"/>
+    <col width="12" customWidth="1" style="19" min="1" max="1"/>
+    <col width="12" customWidth="1" style="19" min="2" max="2"/>
+    <col width="12" customWidth="1" style="19" min="3" max="3"/>
+    <col width="50" customWidth="1" style="19" min="4" max="4"/>
+    <col width="22" customWidth="1" style="19" min="5" max="5"/>
+    <col width="20" customWidth="1" style="19" min="6" max="6"/>
+    <col width="14" customWidth="1" style="19" min="7" max="7"/>
+    <col width="12" customWidth="1" style="19" min="8" max="8"/>
+    <col width="10" customWidth="1" style="19" min="9" max="9"/>
+    <col width="12" customWidth="1" style="19" min="10" max="10"/>
+    <col width="40" customWidth="1" style="19" min="11" max="11"/>
+    <col width="30" customWidth="1" style="19" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.05" customHeight="1" s="19">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>record_id</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>equipment_type</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
-        <is>
-          <t>pump_failure_mode__answer</t>
-        </is>
-      </c>
-      <c r="F1" s="26" t="inlineStr">
-        <is>
-          <t>pump_failure_mode__confidence</t>
-        </is>
-      </c>
-      <c r="G1" s="26" t="inlineStr">
-        <is>
-          <t>pump_failure_mode__value</t>
-        </is>
-      </c>
-      <c r="H1" s="26" t="inlineStr">
-        <is>
-          <t>pump_containment__answer</t>
-        </is>
-      </c>
-      <c r="I1" s="26" t="inlineStr">
-        <is>
-          <t>pump_containment__confidence</t>
-        </is>
-      </c>
-      <c r="J1" s="26" t="inlineStr">
-        <is>
-          <t>pump_containment__value</t>
-        </is>
-      </c>
-      <c r="K1" s="26" t="inlineStr">
-        <is>
-          <t>pump_urgency__answer</t>
-        </is>
-      </c>
-      <c r="L1" s="26" t="inlineStr">
-        <is>
-          <t>pump_urgency__confidence</t>
-        </is>
-      </c>
-      <c r="M1" s="26" t="inlineStr">
-        <is>
-          <t>pump_urgency__value</t>
-        </is>
-      </c>
-      <c r="N1" s="26" t="inlineStr">
-        <is>
-          <t>hx_problem__answer</t>
-        </is>
-      </c>
-      <c r="O1" s="26" t="inlineStr">
-        <is>
-          <t>hx_problem__confidence</t>
-        </is>
-      </c>
-      <c r="P1" s="26" t="inlineStr">
-        <is>
-          <t>hx_problem__value</t>
-        </is>
-      </c>
-      <c r="Q1" s="26" t="inlineStr">
-        <is>
-          <t>hx_crosscontam__answer</t>
-        </is>
-      </c>
-      <c r="R1" s="26" t="inlineStr">
-        <is>
-          <t>hx_crosscontam__confidence</t>
-        </is>
-      </c>
-      <c r="S1" s="26" t="inlineStr">
-        <is>
-          <t>hx_crosscontam__value</t>
-        </is>
-      </c>
-      <c r="T1" s="26" t="inlineStr">
-        <is>
-          <t>hx_impact__answer</t>
-        </is>
-      </c>
-      <c r="U1" s="26" t="inlineStr">
-        <is>
-          <t>hx_impact__confidence</t>
-        </is>
-      </c>
-      <c r="V1" s="26" t="inlineStr">
-        <is>
-          <t>hx_impact__value</t>
-        </is>
-      </c>
-      <c r="W1" s="26" t="inlineStr">
-        <is>
-          <t>col_symptom__answer</t>
-        </is>
-      </c>
-      <c r="X1" s="26" t="inlineStr">
-        <is>
-          <t>col_symptom__confidence</t>
-        </is>
-      </c>
-      <c r="Y1" s="26" t="inlineStr">
-        <is>
-          <t>col_symptom__value</t>
-        </is>
-      </c>
-      <c r="Z1" s="26" t="inlineStr">
-        <is>
-          <t>col_offspec__answer</t>
-        </is>
-      </c>
-      <c r="AA1" s="26" t="inlineStr">
-        <is>
-          <t>col_offspec__confidence</t>
-        </is>
-      </c>
-      <c r="AB1" s="26" t="inlineStr">
-        <is>
-          <t>col_offspec__value</t>
-        </is>
-      </c>
-      <c r="AC1" s="26" t="inlineStr">
-        <is>
-          <t>col_stability__answer</t>
-        </is>
-      </c>
-      <c r="AD1" s="26" t="inlineStr">
-        <is>
-          <t>col_stability__confidence</t>
-        </is>
-      </c>
-      <c r="AE1" s="26" t="inlineStr">
-        <is>
-          <t>col_stability__value</t>
-        </is>
-      </c>
-      <c r="AF1" s="26" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
+      <c r="F1" s="33" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="G1" s="33" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="H1" s="33" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="I1" s="33" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="J1" s="33" t="inlineStr">
         <is>
           <t>needs_review</t>
         </is>
       </c>
-      <c r="AG1" s="26" t="inlineStr">
+      <c r="K1" s="33" t="inlineStr">
         <is>
           <t>review_reasons</t>
         </is>
       </c>
-      <c r="AH1" s="26" t="inlineStr">
+      <c r="L1" s="33" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="23.85" customHeight="1" s="19">
-      <c r="A2" s="27" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="35" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr">
+      <c r="E2" s="34" t="inlineStr">
+        <is>
+          <t>pump_failure_mode</t>
+        </is>
+      </c>
+      <c r="F2" s="34" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="G2" s="34" t="inlineStr">
         <is>
           <t>seal</t>
         </is>
       </c>
-      <c r="F2" s="29" t="n">
+      <c r="H2" s="36" t="n">
+        <v>0.8845493270621723</v>
+      </c>
+      <c r="I2" s="36" t="n">
+        <v>0.9656847333764127</v>
+      </c>
+      <c r="J2" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="34" t="inlineStr"/>
+      <c r="L2" s="34" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>P-101A</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="inlineStr">
+        <is>
+          <t>pump_containment</t>
+        </is>
+      </c>
+      <c r="F3" s="34" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="G3" s="34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H3" s="36" t="n">
+        <v>0.9344222768578154</v>
+      </c>
+      <c r="I3" s="36" t="n">
+        <v>0.9344222768578154</v>
+      </c>
+      <c r="J3" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="34" t="inlineStr"/>
+      <c r="L3" s="34" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>P-101A</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>pump_urgency</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="H4" s="39" t="n">
+        <v>0.5092630137668384</v>
+      </c>
+      <c r="I4" s="39" t="n">
+        <v>1.792500181836202</v>
+      </c>
+      <c r="J4" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="29" t="n">
+      <c r="K4" s="37" t="inlineStr">
+        <is>
+          <t>pump_urgency: low confidence (0.51)</t>
+        </is>
+      </c>
+      <c r="L4" s="37" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>P-114</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>pump_failure_mode</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="H5" s="36" t="n">
+        <v>0.9714843129418362</v>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>0.9934575546721711</v>
+      </c>
+      <c r="J5" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="34" t="inlineStr"/>
+      <c r="L5" s="34" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>P-114</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>pump_containment</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="G6" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H6" s="36" t="n">
+        <v>0.9911026645183536</v>
+      </c>
+      <c r="I6" s="36" t="n">
+        <v>0.008897335481646413</v>
+      </c>
+      <c r="J6" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="34" t="inlineStr"/>
+      <c r="L6" s="34" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>P-114</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>pump_urgency</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G7" s="34" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>0.9435743291549853</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>0.01215235614936457</v>
+      </c>
+      <c r="J7" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="34" t="inlineStr"/>
+      <c r="L7" s="34" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>E-205</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="inlineStr">
+        <is>
+          <t>hx_problem</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>fouling</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>0.8435687329991992</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>0.9478850419472986</v>
+      </c>
+      <c r="J8" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="34" t="inlineStr"/>
+      <c r="L8" s="34" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>E-205</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>hx_crosscontam</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>Cross-contamination</t>
+        </is>
+      </c>
+      <c r="G9" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H9" s="36" t="n">
+        <v>0.9770510463918108</v>
+      </c>
+      <c r="I9" s="36" t="n">
+        <v>0.02294895360818915</v>
+      </c>
+      <c r="J9" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="34" t="inlineStr"/>
+      <c r="L9" s="34" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>E-205</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="inlineStr">
+        <is>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>hx_impact</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="H10" s="39" t="n">
+        <v>0.1334007415612771</v>
+      </c>
+      <c r="I10" s="39" t="n">
+        <v>1.315495834073972</v>
+      </c>
+      <c r="J10" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="27" t="inlineStr">
+      <c r="K10" s="37" t="inlineStr">
+        <is>
+          <t>hx_impact: low confidence (0.13)</t>
+        </is>
+      </c>
+      <c r="L10" s="37" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>hx_problem</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="G11" s="34" t="inlineStr">
+        <is>
+          <t>tube_leak</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="n">
+        <v>0.9811052724756711</v>
+      </c>
+      <c r="I11" s="36" t="n">
+        <v>0.9959796555651736</v>
+      </c>
+      <c r="J11" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="34" t="inlineStr"/>
+      <c r="L11" s="34" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t>hx_crosscontam</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>Cross-contamination</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="I2" s="29" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J2" s="29" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="K2" s="27" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
-      <c r="L2" s="29" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="M2" s="29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="N2" s="27" t="n"/>
-      <c r="O2" s="27" t="n"/>
-      <c r="P2" s="27" t="n"/>
-      <c r="Q2" s="27" t="n"/>
-      <c r="R2" s="27" t="n"/>
-      <c r="S2" s="27" t="n"/>
-      <c r="T2" s="27" t="n"/>
-      <c r="U2" s="27" t="n"/>
-      <c r="V2" s="27" t="n"/>
-      <c r="W2" s="27" t="n"/>
-      <c r="X2" s="27" t="n"/>
-      <c r="Y2" s="27" t="n"/>
-      <c r="Z2" s="27" t="n"/>
-      <c r="AA2" s="27" t="n"/>
-      <c r="AB2" s="27" t="n"/>
-      <c r="AC2" s="27" t="n"/>
-      <c r="AD2" s="27" t="n"/>
-      <c r="AE2" s="27" t="n"/>
-      <c r="AF2" s="27">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="AG2" s="27" t="n"/>
-      <c r="AH2" s="27" t="n"/>
-    </row>
-    <row r="3" ht="23.85" customHeight="1" s="19">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>Pump</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>P-114</t>
-        </is>
-      </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
-        </is>
-      </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="F3" s="29" t="n">
+      <c r="H12" s="36" t="n">
+        <v>0.9972773611314817</v>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>0.9972773611314817</v>
+      </c>
+      <c r="J12" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="34" t="inlineStr"/>
+      <c r="L12" s="34" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D13" s="38" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>hx_impact</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="H13" s="39" t="n">
+        <v>0.5167403657884981</v>
+      </c>
+      <c r="I13" s="39" t="n">
+        <v>1.011186618395636</v>
+      </c>
+      <c r="J13" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="29" t="n">
+      <c r="K13" s="37" t="inlineStr">
+        <is>
+          <t>hx_impact: low confidence (0.52)</t>
+        </is>
+      </c>
+      <c r="L13" s="37" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>col_symptom</t>
+        </is>
+      </c>
+      <c r="F14" s="37" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G14" s="37" t="inlineStr">
+        <is>
+          <t>flooding</t>
+        </is>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>0.575229541784642</v>
+      </c>
+      <c r="I14" s="39" t="n">
+        <v>0.5175961061389851</v>
+      </c>
+      <c r="J14" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="K14" s="37" t="inlineStr">
+        <is>
+          <t>col_symptom: low confidence (0.58)</t>
+        </is>
+      </c>
+      <c r="L14" s="37" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>col_offspec</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="G15" s="34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H15" s="36" t="n">
+        <v>0.9990573225259095</v>
+      </c>
+      <c r="I15" s="36" t="n">
+        <v>0.9990573225259095</v>
+      </c>
+      <c r="J15" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="34" t="inlineStr"/>
+      <c r="L15" s="34" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>col_stability</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="G16" s="34" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="H16" s="36" t="n">
+        <v>0.6360617217354828</v>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>1.81944012506878</v>
+      </c>
+      <c r="J16" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="34" t="inlineStr"/>
+      <c r="L16" s="34" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>col_symptom</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="H17" s="36" t="n">
+        <v>0.9294495624188652</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>0.9729023573239992</v>
+      </c>
+      <c r="J17" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="34" t="inlineStr"/>
+      <c r="L17" s="34" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>col_offspec</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="29" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J3" s="29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K3" s="27" t="inlineStr">
-        <is>
-          <t>routine</t>
-        </is>
-      </c>
-      <c r="L3" s="29" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="M3" s="29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N3" s="27" t="n"/>
-      <c r="O3" s="27" t="n"/>
-      <c r="P3" s="27" t="n"/>
-      <c r="Q3" s="27" t="n"/>
-      <c r="R3" s="27" t="n"/>
-      <c r="S3" s="27" t="n"/>
-      <c r="T3" s="27" t="n"/>
-      <c r="U3" s="27" t="n"/>
-      <c r="V3" s="27" t="n"/>
-      <c r="W3" s="27" t="n"/>
-      <c r="X3" s="27" t="n"/>
-      <c r="Y3" s="27" t="n"/>
-      <c r="Z3" s="27" t="n"/>
-      <c r="AA3" s="27" t="n"/>
-      <c r="AB3" s="27" t="n"/>
-      <c r="AC3" s="27" t="n"/>
-      <c r="AD3" s="27" t="n"/>
-      <c r="AE3" s="27" t="n"/>
-      <c r="AF3" s="27">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="AG3" s="27" t="n"/>
-      <c r="AH3" s="27" t="n"/>
-    </row>
-    <row r="4" ht="23.85" customHeight="1" s="19">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>E-205</t>
-        </is>
-      </c>
-      <c r="D4" s="28" t="inlineStr">
-        <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
-        </is>
-      </c>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="27" t="n"/>
-      <c r="K4" s="27" t="n"/>
-      <c r="L4" s="27" t="n"/>
-      <c r="M4" s="27" t="n"/>
-      <c r="N4" s="27" t="inlineStr">
-        <is>
-          <t>fouling</t>
-        </is>
-      </c>
-      <c r="O4" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="27" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="R4" s="29" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="S4" s="29" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="T4" s="27" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="U4" s="29" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="V4" s="29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W4" s="27" t="n"/>
-      <c r="X4" s="27" t="n"/>
-      <c r="Y4" s="27" t="n"/>
-      <c r="Z4" s="27" t="n"/>
-      <c r="AA4" s="27" t="n"/>
-      <c r="AB4" s="27" t="n"/>
-      <c r="AC4" s="27" t="n"/>
-      <c r="AD4" s="27" t="n"/>
-      <c r="AE4" s="27" t="n"/>
-      <c r="AF4" s="27">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="AG4" s="27" t="n"/>
-      <c r="AH4" s="27" t="n"/>
-    </row>
-    <row r="5" ht="23.85" customHeight="1" s="19">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>E-310</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
-        </is>
-      </c>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="inlineStr">
-        <is>
-          <t>tube_leak</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="30" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="R5" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S5" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T5" s="30" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="U5" s="32" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="V5" s="32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W5" s="30" t="n"/>
-      <c r="X5" s="30" t="n"/>
-      <c r="Y5" s="30" t="n"/>
-      <c r="Z5" s="30" t="n"/>
-      <c r="AA5" s="30" t="n"/>
-      <c r="AB5" s="30" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="30" t="n"/>
-      <c r="AE5" s="30" t="n"/>
-      <c r="AF5" s="30">
-        <f>TRUE()</f>
-        <v/>
-      </c>
-      <c r="AG5" s="30" t="inlineStr">
-        <is>
-          <t>hx_impact: low confidence (0.49)</t>
-        </is>
-      </c>
-      <c r="AH5" s="30" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="19">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="H18" s="36" t="n">
+        <v>0.9980349345556877</v>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>0.001965065444312336</v>
+      </c>
+      <c r="J18" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="34" t="inlineStr"/>
+      <c r="L18" s="34" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>C-301</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="inlineStr">
-        <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
-        </is>
-      </c>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="27" t="n"/>
-      <c r="J6" s="27" t="n"/>
-      <c r="K6" s="27" t="n"/>
-      <c r="L6" s="27" t="n"/>
-      <c r="M6" s="27" t="n"/>
-      <c r="N6" s="27" t="n"/>
-      <c r="O6" s="27" t="n"/>
-      <c r="P6" s="27" t="n"/>
-      <c r="Q6" s="27" t="n"/>
-      <c r="R6" s="27" t="n"/>
-      <c r="S6" s="27" t="n"/>
-      <c r="T6" s="27" t="n"/>
-      <c r="U6" s="27" t="n"/>
-      <c r="V6" s="27" t="n"/>
-      <c r="W6" s="27" t="inlineStr">
-        <is>
-          <t>flooding</t>
-        </is>
-      </c>
-      <c r="X6" s="29" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="Y6" s="29" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="Z6" s="27" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="AA6" s="29" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AB6" s="29" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AC6" s="27" t="inlineStr">
-        <is>
-          <t>upset</t>
-        </is>
-      </c>
-      <c r="AD6" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" s="27">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="AG6" s="27" t="n"/>
-      <c r="AH6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="23.85" customHeight="1" s="19">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>C-402</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
         </is>
       </c>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-      <c r="Q7" s="27" t="n"/>
-      <c r="R7" s="27" t="n"/>
-      <c r="S7" s="27" t="n"/>
-      <c r="T7" s="27" t="n"/>
-      <c r="U7" s="27" t="n"/>
-      <c r="V7" s="27" t="n"/>
-      <c r="W7" s="27" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="X7" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="27" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AA7" s="29" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AB7" s="29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AC7" s="27" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>col_stability</t>
+        </is>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="G19" s="34" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="AD7" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="29" t="n">
+      <c r="H19" s="36" t="n">
+        <v>0.9805633856279246</v>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>0.004745121587660906</v>
+      </c>
+      <c r="J19" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" s="27">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="AG7" s="27" t="n"/>
-      <c r="AH7" s="27" t="n"/>
+      <c r="K19" s="34" t="inlineStr"/>
+      <c r="L19" s="34" t="inlineStr"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="18" min="1" max="1"/>
-    <col width="40" customWidth="1" style="18" min="2" max="2"/>
-    <col width="120" customWidth="1" style="18" min="3" max="3"/>
+    <col width="12" customWidth="1" style="19" min="1" max="1"/>
+    <col width="40" customWidth="1" style="19" min="2" max="2"/>
+    <col width="120" customWidth="1" style="19" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="19">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>record_id</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>usage_json</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>raw_answers_json</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="19">
-      <c r="A2" s="27" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>{"input_tokens": 465, "output_tokens": 92}</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "bearing": 0.0, "instrument": 0.0, "seal": 1.0, "other": 0.0}}, "pump_containment": {"type": "noul", "noul": 0.89}, "pump_urgency": {"type": "score", "score": 1.99, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="19">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 1063, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C2" s="34" t="inlineStr">
+        <is>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9656847333764127, "bearing": 0.012815798358892808, "cavitation": 0.01719299268622746, "instrument": 0.0018161557694942427, "other": 0.0024903198089730396}, "confidence": 0.8845493270621723}, "pump_containment": {"type": "noul", "noul": 0.9344222768578154}, "pump_urgency": {"type": "score", "score": 1.7925001818362023, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.045530782702412724, "1": 0.11643825275897222, "2": 0.838030964538615}, "confidence": 0.5092630137668384}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
-        <is>
-          <t>{"input_tokens": 464, "output_tokens": 92}</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"other": 0.0, "seal": 0.0, "cavitation": 0.0, "bearing": 1.0, "instrument": 0.0}}, "pump_containment": {"type": "noul", "noul": 0.01}, "pump_urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="19">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 1066, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>{"pump_failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.0043512978021535585, "bearing": 0.9934575546721711, "cavitation": 0.000905819088747979, "instrument": 0.0004185861337592025, "other": 0.0008667423031681805}, "confidence": 0.9714843129418362}, "pump_containment": {"type": "noul", "noul": 0.008897335481646413}, "pump_urgency": {"type": "score", "score": 0.012152356149364569, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9897726497601865, "1": 0.008302344330262468, "2": 0.0019250059095510502}, "confidence": 0.9435743291549853}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>{"input_tokens": 484, "output_tokens": 102}</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "tube_leak": 0.0, "other": 0.0, "flow_maldistribution": 0.0, "fouling": 1.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.14}, "hx_impact": {"type": "score", "score": 1.1, "confidence": 0.84, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.9, "2": 0.1}}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="19">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 1104, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>{"hx_problem": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9478850419472986, "tube_leak": 0.028015671752445407, "flow_maldistribution": 0.021038713019720476, "control_valve": 0.0009826808054082873, "other": 0.0020778924751272197}, "confidence": 0.8435687329991992}, "hx_crosscontam": {"type": "noul", "noul": 0.02294895360818915}, "hx_impact": {"type": "score", "score": 1.3154958340739715, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.10341257644438336, "1": 0.4776790130372617, "2": 0.41890841051835487}, "confidence": 0.13340074156127713}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>{"input_tokens": 487, "output_tokens": 102}</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "tube_leak": 1.0, "fouling": 0.0}}, "hx_crosscontam": {"type": "noul", "noul": 0.9}, "hx_impact": {"type": "score", "score": 1.25, "confidence": 0.49, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.05, "1": 0.65, "2": 0.3}}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="19">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 1101, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>{"hx_problem": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0007413265006967869, "tube_leak": 0.9959796555651736, "flow_maldistribution": 0.00043550090530919514, "control_valve": 0.00032655607260840267, "other": 0.0025169609562122087}, "confidence": 0.9811052724756711}, "hx_crosscontam": {"type": "noul", "noul": 0.9972773611314817}, "hx_impact": {"type": "score", "score": 1.011186618395636, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.07036651965596523, "1": 0.8480803422924331, "2": 0.08155313805160146}, "confidence": 0.5167403657884981}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>{"input_tokens": 514, "output_tokens": 117}</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "confidence": 0.84, "probabilities": {"instrument": 0.02, "flooding": 0.87, "other": 0.02, "reboiler_condenser": 0.0, "weeping": 0.0, "foaming": 0.09, "fouling": 0.0}}, "col_offspec": {"type": "noul", "noul": 0.99}, "col_stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="19">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 1185, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>{"col_symptom": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.5175961061389851, "weeping": 0.012200956102939394, "foaming": 0.4556040469819839, "fouling": 0.001680899310385979, "reboiler_condenser": 0.0013599361901990839, "instrument": 0.010907201436286347, "other": 0.0006508538392200906}, "confidence": 0.575229541784642}, "col_offspec": {"type": "noul", "noul": 0.9990573225259095}, "col_stability": {"type": "score", "score": 1.8194401250687795, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.07519103740662722, "1": 0.030177800117966076, "2": 0.8946311624754067}, "confidence": 0.6360617217354828}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>{"input_tokens": 512, "output_tokens": 115}</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>{"col_symptom": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"fouling": 0.0, "weeping": 0.0, "other": 1.0, "flooding": 0.0, "foaming": 0.0, "reboiler_condenser": 0.0, "instrument": 0.0}}, "col_offspec": {"type": "noul", "noul": 0.01}, "col_stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>{"input_tokens": 1179, "output_tokens": 4}</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>{"col_symptom": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.024242860849536994, "weeping": 0.0010585059610439293, "foaming": 0.0006364711561126581, "fouling": 0.0009836821928156953, "reboiler_condenser": 0.00011520558342775971, "instrument": 6.0916933063774306e-05, "other": 0.9729023573239992}, "confidence": 0.9294495624188652}, "col_offspec": {"type": "noul", "noul": 0.0019650654443123363}, "col_stability": {"type": "score", "score": 0.004745121587660906, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.997151610266207, "1": 0.0009516578799251958, "2": 0.001896731853867855}, "confidence": 0.9805633856279246}}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="18" min="1" max="1"/>
-    <col width="10" customWidth="1" style="18" min="2" max="2"/>
-    <col width="8" customWidth="1" style="18" min="3" max="3"/>
-    <col width="10" customWidth="1" style="18" min="4" max="4"/>
-    <col width="18" customWidth="1" style="18" min="5" max="5"/>
-    <col width="16" customWidth="1" style="18" min="6" max="6"/>
-    <col width="14" customWidth="1" style="18" min="7" max="7"/>
-    <col width="9" customWidth="1" style="18" min="8" max="8"/>
-    <col width="10" customWidth="1" style="18" min="9" max="9"/>
-    <col width="20" customWidth="1" style="18" min="10" max="11"/>
+    <col width="24" customWidth="1" style="19" min="1" max="1"/>
+    <col width="20" customWidth="1" style="19" min="2" max="2"/>
+    <col width="10" customWidth="1" style="19" min="3" max="3"/>
+    <col width="8" customWidth="1" style="19" min="4" max="4"/>
+    <col width="10" customWidth="1" style="19" min="5" max="5"/>
+    <col width="18" customWidth="1" style="19" min="6" max="6"/>
+    <col width="16" customWidth="1" style="19" min="7" max="7"/>
+    <col width="14" customWidth="1" style="19" min="8" max="8"/>
+    <col width="9" customWidth="1" style="19" min="9" max="9"/>
+    <col width="10" customWidth="1" style="19" min="10" max="10"/>
+    <col width="20" customWidth="1" style="19" min="11" max="11"/>
+    <col width="20" customWidth="1" style="19" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.85" customHeight="1" s="19">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>question_id</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>asked</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>answered</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>flagged_for_review</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="G1" s="33" t="inlineStr">
         <is>
           <t>mean_confidence</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="H1" s="33" t="inlineStr">
         <is>
           <t>with_expected</t>
         </is>
       </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="I1" s="33" t="inlineStr">
         <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="I1" s="26" t="inlineStr">
+      <c r="J1" s="33" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="J1" s="26" t="inlineStr">
+      <c r="K1" s="33" t="inlineStr">
         <is>
           <t>mean_conf_when_correct</t>
         </is>
       </c>
-      <c r="K1" s="26" t="inlineStr">
+      <c r="L1" s="33" t="inlineStr">
         <is>
           <t>mean_conf_when_wrong</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="19">
-      <c r="A2" s="27" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>pump_failure_mode</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>choice</t>
         </is>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="D2" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="27" t="n">
+      <c r="E2" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="27" t="n">
+      <c r="F2" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="27" t="n">
+      <c r="G2" s="34" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="H2" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="27" t="n">
+      <c r="K2" s="34" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="L2" s="34" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>pump_containment</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>noul</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="27" t="n">
+      <c r="E3" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="27" t="n">
+      <c r="F3" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="34" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="H3" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="27" t="n">
+      <c r="K3" s="34" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L3" s="34" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>pump_urgency</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="27" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="19">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>pump_containment</t>
-        </is>
-      </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="G4" s="34" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="34" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="L4" s="34" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>hx_problem</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="34" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="L5" s="34" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>hx_crosscontam</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>Cross-contamination</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>noul</t>
         </is>
       </c>
-      <c r="C3" s="27" t="n">
+      <c r="D6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="27" t="n">
+      <c r="E6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="27" t="n">
+      <c r="F6" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="27" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="G3" s="27" t="n">
+      <c r="G6" s="34" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="H6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="27" t="n">
+      <c r="I6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="27" t="n">
+      <c r="J6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="27" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="K3" s="27" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="19">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>pump_urgency</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="K6" s="34" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="L6" s="34" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>hx_impact</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="D7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="27" t="n">
+      <c r="E7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="F7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="34" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="L7" s="34" t="n">
+        <v>0.517</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>col_symptom</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="H8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="34" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="L8" s="34" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>col_offspec</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>noul</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="27" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="G4" s="27" t="n">
+      <c r="G9" s="34" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="H9" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="27" t="n">
+      <c r="I9" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="27" t="n">
+      <c r="J9" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="27" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="K4" s="27" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="19">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>hx_problem</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="n">
+      <c r="K9" s="34" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L9" s="34" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>col_stability</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="E10" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="F10" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="G10" s="34" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="27" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="19">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>hx_crosscontam</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>noul</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="19">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>hx_impact</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="19">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>col_symptom</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="K8" s="27" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="19">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>col_offspec</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>noul</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="K9" s="27" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="19">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>col_stability</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="27" t="n"/>
+      <c r="K10" s="34" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="L10" s="34" t="inlineStr"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -13,14 +13,14 @@
     <sheet name="Labels" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Records" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Lists" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="output_nimble_Results" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="output_nimble_Raw" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="output_nimble_Summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="output_nimble_Run_info" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="output_jev_Results" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="output_jev_Raw" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="output_jev_Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="output_jev_Run_info" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="output_jev_Results" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="output_jev_Raw" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="output_jev_Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="output_jev_Run_info" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="output_nimble_Results" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="output_nimble_Raw" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="output_nimble_Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="output_nimble_Run_info" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="output_compare" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
@@ -563,10 +563,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="28" customWidth="1" style="19" min="1" max="1"/>
+    <col width="22" customWidth="1" style="19" min="1" max="1"/>
     <col width="110" customWidth="1" style="19" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -580,48 +580,63 @@
     <row r="2" ht="30" customHeight="1" s="20">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Reliability concepts (Failure mode, Containment, Urgency, Impact) are common across equipment. Leave Questions.equipment_type blank for those.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="20">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>Answer choices differ by asset class via Labels.equipment_type (pump seal/bearing vs exchanger fouling/tube_leak under the same failure_mode question).</t>
-        </is>
-      </c>
-    </row>
+          <t>Classify plant statements with Nimble (local) or Jev (cloud). Edit this file; run from the terminal (see repo README).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="20"/>
     <row r="4" ht="15" customHeight="1" s="20">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>Asset-specific only: Cross-contamination (exchangers), Off-spec and Stability (columns).</t>
+          <t>SIMPLE MODEL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="20">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>Run from the terminal — repo README.md (--engine nimble|jev). Results are one row per answer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="20"/>
+          <t>Statements</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Records.text is the statement to classify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="20">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Common questions</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Blank equipment_type = asked for every asset (failure mode, containment, load, urgency, impact, potential impact).</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="30" customHeight="1" s="20">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>SHEETS</t>
+          <t>Unit-op questions</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Set equipment_type = only for that class (e.g. cross-contamination for heat exchangers; off-spec / stability for columns).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="20">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Answer types</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Shared concepts: blank equipment_type. Specific phenomena: set equipment_type.</t>
+          <t>Only three: choice (pick a label), noul (yes/no), score (ordered scale from Labels).</t>
         </is>
       </c>
     </row>
@@ -633,43 +648,110 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Optional equipment_type filters which choices are sent for that asset.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="20">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>Records</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>expected_&lt;question_id&gt; uses shared ids (expected_failure_mode, …).</t>
-        </is>
-      </c>
-    </row>
+          <t>For score/choice: list options. Optional Labels.equipment_type so choices differ by class (e.g. failure_mode).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="20"/>
     <row r="11" ht="15" customHeight="1" s="20">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>output_*_Results</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>Long format: question_id + title + answer for questions that apply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="20"/>
-    <row r="13" ht="15" customHeight="1" s="20"/>
-    <row r="14" ht="45" customHeight="1" s="20"/>
-    <row r="15" ht="30" customHeight="1" s="20"/>
+          <t>SHEETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="20">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Engine default, timeouts, test size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="20">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Questions / Labels / Records / Lists</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>As above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1" s="20">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>output_nimble_* / output_jev_*</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Results (one row per answer), Raw, Summary, Run_info.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="20">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>output_compare</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Nimble vs Jev when both have been run.</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="15" customHeight="1" s="20"/>
-    <row r="17" ht="30" customHeight="1" s="20"/>
-    <row r="18" ht="30" customHeight="1" s="20"/>
-    <row r="19" ht="30" customHeight="1" s="20"/>
-    <row r="20" ht="15" customHeight="1" s="20"/>
+    <row r="17" ht="30" customHeight="1" s="20">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="20">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Score range</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Not 1–10 by default. Levels are the Labels rows in order (usually 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="20">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>API key</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>For Jev: export TYPESAFE_API_KEY=... Leave Config api_key blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Close file</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Close Excel/LibreOffice before running the classifier.</t>
+        </is>
+      </c>
+    </row>
     <row r="21" ht="45" customHeight="1" s="20"/>
     <row r="22" ht="15" customHeight="1" s="20"/>
     <row r="23" ht="15" customHeight="1" s="20"/>
@@ -694,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -716,228 +798,24 @@
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
-          <t>run_started</t>
+          <t>engine</t>
         </is>
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>20260930_185940</t>
+          <t>jev</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="33" t="inlineStr">
-        <is>
-          <t>engine</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="inlineStr">
-        <is>
-          <t>nimble</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="33" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>nimble</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>base_url</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>http://localhost:11434</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>endpoint_info</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>0.35.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="33" t="inlineStr">
-        <is>
-          <t>questions_hash</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>445e6752b889</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>api_key_configured</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>records_in_run</t>
-        </is>
-      </c>
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>records_completed</t>
-        </is>
-      </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>failed_records</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>review_threshold_default</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>elapsed_seconds</t>
-        </is>
-      </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>checkpoint</t>
-        </is>
-      </c>
-      <c r="B15" s="33" t="inlineStr">
-        <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_185940.jsonl</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>input_tokens</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>15337</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="33" t="inlineStr">
-        <is>
-          <t>total_tokens</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>15373</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>records_with_usage</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>output_sheets</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>output_nimble_Results, output_nimble_Raw, output_nimble_Summary, output_nimble_Run_info</t>
+          <t>remapped to shared ids</t>
         </is>
       </c>
     </row>
@@ -952,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="20" min="1" max="1"/>
@@ -1068,10 +946,10 @@
         </is>
       </c>
       <c r="H2" s="35" t="n">
-        <v>1</v>
+        <v>0.8195945775641966</v>
       </c>
       <c r="I2" s="35" t="n">
-        <v>1</v>
+        <v>0.9403764383354369</v>
       </c>
       <c r="J2" s="33" t="b">
         <v>0</v>
@@ -1116,10 +994,10 @@
         </is>
       </c>
       <c r="H3" s="35" t="n">
-        <v>0.89</v>
+        <v>0.7691154479779605</v>
       </c>
       <c r="I3" s="35" t="n">
-        <v>0.89</v>
+        <v>0.7691154479779605</v>
       </c>
       <c r="J3" s="33" t="b">
         <v>0</v>
@@ -1128,52 +1006,56 @@
       <c r="L3" s="33" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="F4" s="33" t="inlineStr">
-        <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="G4" s="33" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
-      <c r="H4" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I4" s="35" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="J4" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="33" t="inlineStr"/>
-      <c r="L4" s="33" t="inlineStr"/>
+      <c r="E4" s="36" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="F4" s="36" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G4" s="36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H4" s="38" t="n">
+        <v>0.5252066897339631</v>
+      </c>
+      <c r="I4" s="38" t="n">
+        <v>1.101685927779176</v>
+      </c>
+      <c r="J4" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="36" t="inlineStr">
+        <is>
+          <t>load: low confidence (0.53)</t>
+        </is>
+      </c>
+      <c r="L4" s="36" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
@@ -1198,122 +1080,138 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="H5" s="38" t="n">
+        <v>0.4356639754842947</v>
+      </c>
+      <c r="I5" s="38" t="n">
+        <v>1.744118329531175</v>
+      </c>
+      <c r="J5" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="36" t="inlineStr">
+        <is>
+          <t>urgency: low confidence (0.44)</t>
+        </is>
+      </c>
+      <c r="L5" s="36" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>P-101A</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr"/>
-      <c r="H5" s="36" t="n"/>
-      <c r="I5" s="36" t="n"/>
-      <c r="J5" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L5" s="36" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>0.2861003836327028</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>1.099536415201052</v>
+      </c>
+      <c r="J6" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="36" t="inlineStr">
+        <is>
+          <t>impact: low confidence (0.29)</t>
+        </is>
+      </c>
+      <c r="L6" s="36" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>P-114</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t>failure_mode</t>
-        </is>
-      </c>
-      <c r="F6" s="33" t="inlineStr">
-        <is>
-          <t>Failure mode</t>
-        </is>
-      </c>
-      <c r="G6" s="33" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="H6" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="33" t="inlineStr"/>
-      <c r="L6" s="33" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>Pump</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>P-114</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>containment</t>
-        </is>
-      </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>Containment</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I7" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J7" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="33" t="inlineStr"/>
-      <c r="L7" s="33" t="inlineStr"/>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>P-101A</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H7" s="38" t="n">
+        <v>0.2688926828193108</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <v>1.58153004084961</v>
+      </c>
+      <c r="J7" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.27)</t>
+        </is>
+      </c>
+      <c r="L7" s="36" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
@@ -1338,24 +1236,24 @@
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>failure_mode</t>
         </is>
       </c>
       <c r="F8" s="33" t="inlineStr">
         <is>
-          <t>Urgency</t>
+          <t>Failure mode</t>
         </is>
       </c>
       <c r="G8" s="33" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="H8" s="35" t="n">
-        <v>0.99</v>
+        <v>0.9707274126385984</v>
       </c>
       <c r="I8" s="35" t="n">
-        <v>0.01</v>
+        <v>0.99356430421049</v>
       </c>
       <c r="J8" s="33" t="b">
         <v>0</v>
@@ -1364,90 +1262,94 @@
       <c r="L8" s="33" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>P-114</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="F9" s="36" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="G9" s="36" t="inlineStr"/>
-      <c r="H9" s="36" t="n"/>
-      <c r="I9" s="36" t="n"/>
-      <c r="J9" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L9" s="36" t="inlineStr"/>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>0.9858959050293358</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>0.01410409497066424</v>
+      </c>
+      <c r="J9" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="33" t="inlineStr"/>
+      <c r="L9" s="33" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>Heat Exchanger</t>
+          <t>Pump</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>E-205</t>
+          <t>P-114</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
         </is>
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
-          <t>failure_mode</t>
+          <t>load</t>
         </is>
       </c>
       <c r="F10" s="33" t="inlineStr">
         <is>
-          <t>Failure mode</t>
+          <t>Load</t>
         </is>
       </c>
       <c r="G10" s="33" t="inlineStr">
         <is>
-          <t>fouling</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="H10" s="35" t="n">
-        <v>1</v>
+        <v>0.8107506949544721</v>
       </c>
       <c r="I10" s="35" t="n">
-        <v>1</v>
+        <v>0.9830735117434298</v>
       </c>
       <c r="J10" s="33" t="b">
         <v>0</v>
@@ -1456,134 +1358,142 @@
       <c r="L10" s="33" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>E-205</t>
-        </is>
-      </c>
-      <c r="D11" s="37" t="inlineStr">
-        <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>containment</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>Containment</t>
-        </is>
-      </c>
-      <c r="G11" s="36" t="inlineStr"/>
-      <c r="H11" s="36" t="n"/>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L11" s="36" t="inlineStr"/>
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>P-114</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>0.9057681604539835</v>
+      </c>
+      <c r="I11" s="35" t="n">
+        <v>0.02394660660151229</v>
+      </c>
+      <c r="J11" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="33" t="inlineStr"/>
+      <c r="L11" s="33" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>E-205</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="inlineStr">
-        <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="inlineStr"/>
-      <c r="H12" s="36" t="n"/>
-      <c r="I12" s="36" t="n"/>
-      <c r="J12" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L12" s="36" t="inlineStr"/>
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>P-114</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G12" s="33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>0.8060517778980076</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>0.05461874556361802</v>
+      </c>
+      <c r="J12" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="33" t="inlineStr"/>
+      <c r="L12" s="33" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>Heat Exchanger</t>
+          <t>Pump</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>E-205</t>
+          <t>P-114</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>potential_impact</t>
         </is>
       </c>
       <c r="F13" s="33" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Potential impact</t>
         </is>
       </c>
       <c r="G13" s="33" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="H13" s="35" t="n">
-        <v>0.84</v>
+        <v>0.6617906884831326</v>
       </c>
       <c r="I13" s="35" t="n">
-        <v>1.1</v>
+        <v>0.9272016948488913</v>
       </c>
       <c r="J13" s="33" t="b">
         <v>0</v>
@@ -1614,24 +1524,24 @@
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
-          <t>cross_contamination</t>
+          <t>failure_mode</t>
         </is>
       </c>
       <c r="F14" s="33" t="inlineStr">
         <is>
-          <t>Cross-contamination</t>
+          <t>Failure mode</t>
         </is>
       </c>
       <c r="G14" s="33" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>fouling</t>
         </is>
       </c>
       <c r="H14" s="35" t="n">
-        <v>0.86</v>
+        <v>0.8964189370932257</v>
       </c>
       <c r="I14" s="35" t="n">
-        <v>0.14</v>
+        <v>0.9680451306120793</v>
       </c>
       <c r="J14" s="33" t="b">
         <v>0</v>
@@ -1642,7 +1552,7 @@
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
@@ -1652,34 +1562,34 @@
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>E-310</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
-          <t>failure_mode</t>
+          <t>containment</t>
         </is>
       </c>
       <c r="F15" s="33" t="inlineStr">
         <is>
-          <t>Failure mode</t>
+          <t>Containment</t>
         </is>
       </c>
       <c r="G15" s="33" t="inlineStr">
         <is>
-          <t>tube_leak</t>
+          <t>false</t>
         </is>
       </c>
       <c r="H15" s="35" t="n">
-        <v>1</v>
+        <v>0.9810367320377763</v>
       </c>
       <c r="I15" s="35" t="n">
-        <v>1</v>
+        <v>0.01896326796222373</v>
       </c>
       <c r="J15" s="33" t="b">
         <v>0</v>
@@ -1690,7 +1600,7 @@
     <row r="16">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B16" s="36" t="inlineStr">
@@ -1700,33 +1610,41 @@
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>E-310</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D16" s="37" t="inlineStr">
         <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E16" s="36" t="inlineStr">
         <is>
-          <t>containment</t>
+          <t>load</t>
         </is>
       </c>
       <c r="F16" s="36" t="inlineStr">
         <is>
-          <t>Containment</t>
-        </is>
-      </c>
-      <c r="G16" s="36" t="inlineStr"/>
-      <c r="H16" s="36" t="n"/>
-      <c r="I16" s="36" t="n"/>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G16" s="36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>0.5793208854661729</v>
+      </c>
+      <c r="I16" s="38" t="n">
+        <v>0.9234640502322689</v>
+      </c>
       <c r="J16" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
-          <t>no answer</t>
+          <t>load: low confidence (0.58)</t>
         </is>
       </c>
       <c r="L16" s="36" t="inlineStr"/>
@@ -1734,7 +1652,7 @@
     <row r="17">
       <c r="A17" s="36" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B17" s="36" t="inlineStr">
@@ -1744,12 +1662,12 @@
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>E-310</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D17" s="37" t="inlineStr">
         <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E17" s="36" t="inlineStr">
@@ -1762,15 +1680,23 @@
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G17" s="36" t="inlineStr"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
+      <c r="G17" s="36" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="H17" s="38" t="n">
+        <v>0.4559468789770235</v>
+      </c>
+      <c r="I17" s="38" t="n">
+        <v>0.2398700214389179</v>
+      </c>
       <c r="J17" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
-          <t>no answer</t>
+          <t>urgency: low confidence (0.46)</t>
         </is>
       </c>
       <c r="L17" s="36" t="inlineStr"/>
@@ -1778,7 +1704,7 @@
     <row r="18">
       <c r="A18" s="36" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B18" s="36" t="inlineStr">
@@ -1788,12 +1714,12 @@
       </c>
       <c r="C18" s="36" t="inlineStr">
         <is>
-          <t>E-310</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D18" s="37" t="inlineStr">
         <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E18" s="36" t="inlineStr">
@@ -1812,110 +1738,114 @@
         </is>
       </c>
       <c r="H18" s="38" t="n">
-        <v>0.49</v>
+        <v>0.3072345881491388</v>
       </c>
       <c r="I18" s="38" t="n">
-        <v>1.25</v>
+        <v>0.7770780189312785</v>
       </c>
       <c r="J18" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.49)</t>
+          <t>impact: low confidence (0.31)</t>
         </is>
       </c>
       <c r="L18" s="36" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C19" s="33" t="inlineStr">
-        <is>
-          <t>E-310</t>
-        </is>
-      </c>
-      <c r="D19" s="34" t="inlineStr">
-        <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
-        </is>
-      </c>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>cross_contamination</t>
-        </is>
-      </c>
-      <c r="F19" s="33" t="inlineStr">
-        <is>
-          <t>Cross-contamination</t>
-        </is>
-      </c>
-      <c r="G19" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I19" s="35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J19" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="33" t="inlineStr"/>
-      <c r="L19" s="33" t="inlineStr"/>
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>E-205</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F19" s="36" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H19" s="38" t="n">
+        <v>0.2703462680038269</v>
+      </c>
+      <c r="I19" s="38" t="n">
+        <v>0.4875360292089463</v>
+      </c>
+      <c r="J19" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.27)</t>
+        </is>
+      </c>
+      <c r="L19" s="36" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="33" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>Distillation Column</t>
+          <t>Heat Exchanger</t>
         </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>C-301</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
-          <t>failure_mode</t>
+          <t>cross_contamination</t>
         </is>
       </c>
       <c r="F20" s="33" t="inlineStr">
         <is>
-          <t>Failure mode</t>
+          <t>Cross-contamination</t>
         </is>
       </c>
       <c r="G20" s="33" t="inlineStr">
         <is>
-          <t>flooding</t>
+          <t>false</t>
         </is>
       </c>
       <c r="H20" s="35" t="n">
-        <v>0.84</v>
+        <v>0.9600284507335518</v>
       </c>
       <c r="I20" s="35" t="n">
-        <v>0.87</v>
+        <v>0.0399715492664482</v>
       </c>
       <c r="J20" s="33" t="b">
         <v>0</v>
@@ -1924,465 +1854,505 @@
       <c r="L20" s="33" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>failure_mode</t>
+        </is>
+      </c>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="inlineStr">
+        <is>
+          <t>tube_leak</t>
+        </is>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>0.980827621350109</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>0.9960106591003453</v>
+      </c>
+      <c r="J21" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="33" t="inlineStr"/>
+      <c r="L21" s="33" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>0.8231185626412096</v>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>0.1768814373587904</v>
+      </c>
+      <c r="J22" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="33" t="inlineStr"/>
+      <c r="L22" s="33" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G23" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>0.7082652363052141</v>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>1.023989710490751</v>
+      </c>
+      <c r="J23" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="33" t="inlineStr"/>
+      <c r="L23" s="33" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="F24" s="36" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G24" s="36" t="inlineStr">
+        <is>
+          <t>soon</t>
+        </is>
+      </c>
+      <c r="H24" s="38" t="n">
+        <v>0.3004673764848859</v>
+      </c>
+      <c r="I24" s="38" t="n">
+        <v>1.331217847775203</v>
+      </c>
+      <c r="J24" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" s="36" t="inlineStr">
+        <is>
+          <t>urgency: low confidence (0.30)</t>
+        </is>
+      </c>
+      <c r="L24" s="36" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E25" s="36" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="F25" s="36" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="H25" s="38" t="n">
+        <v>0.3120997517953533</v>
+      </c>
+      <c r="I25" s="38" t="n">
+        <v>1.139766134713401</v>
+      </c>
+      <c r="J25" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" s="36" t="inlineStr">
+        <is>
+          <t>impact: low confidence (0.31)</t>
+        </is>
+      </c>
+      <c r="L25" s="36" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E26" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F26" s="36" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G26" s="36" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="H26" s="38" t="n">
+        <v>0.2893414605806364</v>
+      </c>
+      <c r="I26" s="38" t="n">
+        <v>1.342348590487079</v>
+      </c>
+      <c r="J26" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.29)</t>
+        </is>
+      </c>
+      <c r="L26" s="36" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>cross_contamination</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>Cross-contamination</t>
+        </is>
+      </c>
+      <c r="G27" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>0.993523868071281</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>0.993523868071281</v>
+      </c>
+      <c r="J27" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="33" t="inlineStr"/>
+      <c r="L27" s="33" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D21" s="37" t="inlineStr">
+      <c r="D28" s="34" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
+        <is>
+          <t>failure_mode</t>
+        </is>
+      </c>
+      <c r="F28" s="33" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="G28" s="33" t="inlineStr">
+        <is>
+          <t>flooding</t>
+        </is>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>0.6803313388383841</v>
+      </c>
+      <c r="I28" s="35" t="n">
+        <v>0.7658952561283315</v>
+      </c>
+      <c r="J28" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" s="33" t="inlineStr"/>
+      <c r="L28" s="33" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="F21" s="36" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>Containment</t>
         </is>
       </c>
-      <c r="G21" s="36" t="inlineStr"/>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L21" s="36" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>0.9852695044791884</v>
+      </c>
+      <c r="I29" s="35" t="n">
+        <v>0.01473049552081164</v>
+      </c>
+      <c r="J29" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" s="33" t="inlineStr"/>
+      <c r="L29" s="33" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C22" s="36" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D22" s="37" t="inlineStr">
+      <c r="D30" s="37" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E22" s="36" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="F22" s="36" t="inlineStr">
-        <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="G22" s="36" t="inlineStr"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L22" s="36" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="36" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="inlineStr">
-        <is>
-          <t>C-301</t>
-        </is>
-      </c>
-      <c r="D23" s="37" t="inlineStr">
-        <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
-        </is>
-      </c>
-      <c r="E23" s="36" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="F23" s="36" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="G23" s="36" t="inlineStr"/>
-      <c r="H23" s="36" t="n"/>
-      <c r="I23" s="36" t="n"/>
-      <c r="J23" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L23" s="36" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="inlineStr">
-        <is>
-          <t>C-301</t>
-        </is>
-      </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>off_spec</t>
-        </is>
-      </c>
-      <c r="F24" s="33" t="inlineStr">
-        <is>
-          <t>Off-spec</t>
-        </is>
-      </c>
-      <c r="G24" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I24" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J24" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" s="33" t="inlineStr"/>
-      <c r="L24" s="33" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>C-301</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
-        </is>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>stability</t>
-        </is>
-      </c>
-      <c r="F25" s="33" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="G25" s="33" t="inlineStr">
-        <is>
-          <t>upset</t>
-        </is>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" s="33" t="inlineStr"/>
-      <c r="L25" s="33" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C26" s="33" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E26" s="33" t="inlineStr">
-        <is>
-          <t>failure_mode</t>
-        </is>
-      </c>
-      <c r="F26" s="33" t="inlineStr">
-        <is>
-          <t>Failure mode</t>
-        </is>
-      </c>
-      <c r="G26" s="33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" s="33" t="inlineStr"/>
-      <c r="L26" s="33" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="36" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B27" s="36" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C27" s="36" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D27" s="37" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E27" s="36" t="inlineStr">
-        <is>
-          <t>containment</t>
-        </is>
-      </c>
-      <c r="F27" s="36" t="inlineStr">
-        <is>
-          <t>Containment</t>
-        </is>
-      </c>
-      <c r="G27" s="36" t="inlineStr"/>
-      <c r="H27" s="36" t="n"/>
-      <c r="I27" s="36" t="n"/>
-      <c r="J27" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L27" s="36" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D28" s="37" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E28" s="36" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="F28" s="36" t="inlineStr">
-        <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="G28" s="36" t="inlineStr"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L28" s="36" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="36" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B29" s="36" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D29" s="37" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E29" s="36" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="F29" s="36" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="G29" s="36" t="inlineStr"/>
-      <c r="H29" s="36" t="n"/>
-      <c r="I29" s="36" t="n"/>
-      <c r="J29" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L29" s="36" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E30" s="33" t="inlineStr">
-        <is>
-          <t>off_spec</t>
-        </is>
-      </c>
-      <c r="F30" s="33" t="inlineStr">
-        <is>
-          <t>Off-spec</t>
-        </is>
-      </c>
-      <c r="G30" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H30" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I30" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J30" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" s="33" t="inlineStr"/>
-      <c r="L30" s="33" t="inlineStr"/>
+      <c r="E30" s="36" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="F30" s="36" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H30" s="38" t="n">
+        <v>0.188075872547421</v>
+      </c>
+      <c r="I30" s="38" t="n">
+        <v>1.299708878369453</v>
+      </c>
+      <c r="J30" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" s="36" t="inlineStr">
+        <is>
+          <t>load: low confidence (0.19)</t>
+        </is>
+      </c>
+      <c r="L30" s="36" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="B31" s="33" t="inlineStr">
@@ -2392,40 +2362,624 @@
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>C-402</t>
+          <t>C-301</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
       <c r="E31" s="33" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>urgency</t>
         </is>
       </c>
       <c r="F31" s="33" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Urgency</t>
         </is>
       </c>
       <c r="G31" s="33" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>immediate</t>
         </is>
       </c>
       <c r="H31" s="35" t="n">
-        <v>1</v>
+        <v>0.8091260652766668</v>
       </c>
       <c r="I31" s="35" t="n">
-        <v>0</v>
+        <v>1.937812200817456</v>
       </c>
       <c r="J31" s="33" t="b">
         <v>0</v>
       </c>
       <c r="K31" s="33" t="inlineStr"/>
       <c r="L31" s="33" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="36" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C32" s="36" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D32" s="37" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E32" s="36" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="F32" s="36" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G32" s="36" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="H32" s="38" t="n">
+        <v>0.1934498910234053</v>
+      </c>
+      <c r="I32" s="38" t="n">
+        <v>1.417932638835096</v>
+      </c>
+      <c r="J32" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" s="36" t="inlineStr">
+        <is>
+          <t>impact: low confidence (0.19)</t>
+        </is>
+      </c>
+      <c r="L32" s="36" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D33" s="37" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E33" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F33" s="36" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G33" s="36" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="H33" s="38" t="n">
+        <v>0.1714265267610506</v>
+      </c>
+      <c r="I33" s="38" t="n">
+        <v>1.337527379063873</v>
+      </c>
+      <c r="J33" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.17)</t>
+        </is>
+      </c>
+      <c r="L33" s="36" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="F34" s="33" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="G34" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H34" s="35" t="n">
+        <v>0.9972499411450706</v>
+      </c>
+      <c r="I34" s="35" t="n">
+        <v>0.9972499411450706</v>
+      </c>
+      <c r="J34" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" s="33" t="inlineStr"/>
+      <c r="L34" s="33" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E35" s="33" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="F35" s="33" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="G35" s="33" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="H35" s="35" t="n">
+        <v>0.8431627582980868</v>
+      </c>
+      <c r="I35" s="35" t="n">
+        <v>1.943775069671376</v>
+      </c>
+      <c r="J35" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" s="33" t="inlineStr"/>
+      <c r="L35" s="33" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E36" s="33" t="inlineStr">
+        <is>
+          <t>failure_mode</t>
+        </is>
+      </c>
+      <c r="F36" s="33" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="G36" s="33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>0.9363398600629796</v>
+      </c>
+      <c r="I36" s="35" t="n">
+        <v>0.9784069191734092</v>
+      </c>
+      <c r="J36" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" s="33" t="inlineStr"/>
+      <c r="L36" s="33" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="F37" s="33" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="G37" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H37" s="35" t="n">
+        <v>0.9957133755759788</v>
+      </c>
+      <c r="I37" s="35" t="n">
+        <v>0.004286624424021187</v>
+      </c>
+      <c r="J37" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="33" t="inlineStr"/>
+      <c r="L37" s="33" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G38" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H38" s="35" t="n">
+        <v>0.9348095470889991</v>
+      </c>
+      <c r="I38" s="35" t="n">
+        <v>0.9944437539675687</v>
+      </c>
+      <c r="J38" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" s="33" t="inlineStr"/>
+      <c r="L38" s="33" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G39" s="33" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>0.9150701099900012</v>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>0.02285845930706045</v>
+      </c>
+      <c r="J39" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" s="33" t="inlineStr"/>
+      <c r="L39" s="33" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E40" s="33" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="F40" s="33" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G40" s="33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>0.954014606183754</v>
+      </c>
+      <c r="I40" s="35" t="n">
+        <v>0.009865682566864381</v>
+      </c>
+      <c r="J40" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" s="33" t="inlineStr"/>
+      <c r="L40" s="33" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E41" s="33" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F41" s="33" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G41" s="33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>0.9293340218130992</v>
+      </c>
+      <c r="I41" s="35" t="n">
+        <v>0.01860644816057358</v>
+      </c>
+      <c r="J41" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" s="33" t="inlineStr"/>
+      <c r="L41" s="33" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E42" s="33" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="F42" s="33" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="G42" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H42" s="35" t="n">
+        <v>0.9947682918870171</v>
+      </c>
+      <c r="I42" s="35" t="n">
+        <v>0.00523170811298286</v>
+      </c>
+      <c r="J42" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" s="33" t="inlineStr"/>
+      <c r="L42" s="33" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E43" s="33" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="F43" s="33" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="G43" s="33" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="H43" s="35" t="n">
+        <v>0.9531418933138464</v>
+      </c>
+      <c r="I43" s="35" t="n">
+        <v>0.01156392735957413</v>
+      </c>
+      <c r="J43" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" s="33" t="inlineStr"/>
+      <c r="L43" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2471,12 +3025,12 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 465, "output_tokens": 92}</t>
+          <t>{"input_tokens": 3431, "output_tokens": 7}</t>
         </is>
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "bearing": 0.0, "instrument": 0.0, "seal": 1.0, "other": 0.0}}, "containment": {"type": "noul", "noul": 0.89}, "urgency": {"type": "score", "score": 1.99, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9403764383354369, "bearing": 0.023752584592859, "cavitation": 0.02777636530316554, "instrument": 0.002736962400376868, "other": 0.005357649368161494}, "confidence": 0.8195945775641966}, "containment": {"type": "noul", "noul": 0.7691154479779605}, "load": {"type": "score", "score": 1.1016859277791764, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.03030890919098518, "1": 0.8376962538388533, "2": 0.13199483697016162}, "confidence": 0.5252066897339631}, "urgency": {"type": "score", "score": 1.7441183295311746, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.025617318730848933, "1": 0.20464703300712783, "2": 0.7697356482620233}, "confidence": 0.4356639754842947}, "impact": {"type": "score", "score": 1.0995364152010518, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.09479898270390513, "1": 0.7108656193911379, "2": 0.19433539790495694}, "confidence": 0.28610038363270285}, "potential_impact": {"type": "score", "score": 1.5815300408496102, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.04895136691935876, "1": 0.3205672253116721, "2": 0.6304814077689691}, "confidence": 0.2688926828193108}}</t>
         </is>
       </c>
     </row>
@@ -2488,12 +3042,12 @@
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 464, "output_tokens": 92}</t>
+          <t>{"input_tokens": 3437, "output_tokens": 7}</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"other": 0.0, "seal": 0.0, "cavitation": 0.0, "bearing": 1.0, "instrument": 0.0}}, "containment": {"type": "noul", "noul": 0.01}, "urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.00271844877009735, "bearing": 0.99356430421049, "cavitation": 0.0014845156733352789, "instrument": 0.0006423127261355957, "other": 0.0015904186199419271}, "confidence": 0.9707274126385984}, "containment": {"type": "noul", "noul": 0.01410409497066424}, "load": {"type": "score", "score": 0.9830735117434298, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.03050219630445108, "1": 0.9559220956476682, "2": 0.013575708047880834}, "confidence": 0.810750694954472}, "urgency": {"type": "score", "score": 0.023946606601512287, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.981450571740185, "1": 0.013152249918117795, "2": 0.005397178341697247}, "confidence": 0.9057681604539835}, "impact": {"type": "score", "score": 0.054618745563618024, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.9509405327056056, "1": 0.043500189025170735, "2": 0.005559278269223646}, "confidence": 0.8060517778980076}, "potential_impact": {"type": "score", "score": 0.9272016948488913, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.08743343556647779, "1": 0.897931434018153, "2": 0.01463513041536913}, "confidence": 0.6617906884831326}}</t>
         </is>
       </c>
     </row>
@@ -2505,12 +3059,12 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 484, "output_tokens": 102}</t>
+          <t>{"input_tokens": 4529, "output_tokens": 8}</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "tube_leak": 0.0, "other": 0.0, "flow_maldistribution": 0.0, "fouling": 1.0}}, "cross_contamination": {"type": "noul", "noul": 0.14}, "impact": {"type": "score", "score": 1.1, "confidence": 0.84, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.9, "2": 0.1}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9680451306120793, "tube_leak": 0.023515279230748413, "flow_maldistribution": 0.005935079187159576, "control_valve": 0.0009338859656491551, "other": 0.001570625004363632}, "confidence": 0.8964189370932257}, "containment": {"type": "noul", "noul": 0.018963267962223727}, "load": {"type": "score", "score": 0.9234640502322689, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.10501361956542159, "1": 0.8665087106368881, "2": 0.028477669797690393}, "confidence": 0.5793208854661729}, "urgency": {"type": "score", "score": 0.2398700214389179, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.8066961046405768, "1": 0.14673776927992832, "2": 0.04656612607949479}, "confidence": 0.45594687897702346}, "impact": {"type": "score", "score": 0.7770780189312785, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.27090379744411325, "1": 0.681114386180495, "2": 0.04798181637539171}, "confidence": 0.30723458814913884}, "potential_impact": {"type": "score", "score": 0.48753602920894634, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.5430191923742405, "1": 0.4264255860425726, "2": 0.03055522158318688}, "confidence": 0.2703462680038269}, "cross_contamination": {"type": "noul", "noul": 0.0399715492664482}}</t>
         </is>
       </c>
     </row>
@@ -2522,12 +3076,12 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 487, "output_tokens": 102}</t>
+          <t>{"input_tokens": 4522, "output_tokens": 8}</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "tube_leak": 1.0, "fouling": 0.0}}, "cross_contamination": {"type": "noul", "noul": 0.9}, "impact": {"type": "score", "score": 1.25, "confidence": 0.49, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.05, "1": 0.65, "2": 0.3}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0012215421919611676, "tube_leak": 0.9960106591003453, "flow_maldistribution": 0.001772688409883248, "control_valve": 0.00026080847162997516, "other": 0.0007343018261804486}, "confidence": 0.980827621350109}, "containment": {"type": "noul", "noul": 0.17688143735879036}, "load": {"type": "score", "score": 1.0239897104907512, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.026435554656885116, "1": 0.9231391801954787, "2": 0.05042526514763627}, "confidence": 0.7082652363052141}, "urgency": {"type": "score", "score": 1.3312178477752035, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.028142554477525075, "1": 0.6124970432697464, "2": 0.3593604022527285}, "confidence": 0.30046737648488586}, "impact": {"type": "score", "score": 1.1397661347134012, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.07158432231093885, "1": 0.7170652206647211, "2": 0.21135045702434}, "confidence": 0.3120997517953533}, "potential_impact": {"type": "score", "score": 1.3423485904870789, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.03001426440708731, "1": 0.5976228806987464, "2": 0.37236285489416626}, "confidence": 0.28934146058063637}, "cross_contamination": {"type": "noul", "noul": 0.993523868071281}}</t>
         </is>
       </c>
     </row>
@@ -2539,12 +3093,12 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 514, "output_tokens": 117}</t>
+          <t>{"input_tokens": 5871, "output_tokens": 9}</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "flooding", "confidence": 0.84, "probabilities": {"instrument": 0.02, "flooding": 0.87, "other": 0.02, "reboiler_condenser": 0.0, "weeping": 0.0, "foaming": 0.09, "fouling": 0.0}}, "off_spec": {"type": "noul", "noul": 0.99}, "stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.7658952561283315, "weeping": 0.008919577166532836, "foaming": 0.21745773872133595, "fouling": 0.0013342903862147107, "reboiler_condenser": 0.0005000774452204862, "instrument": 0.005652697246225303, "other": 0.0002403629061388724}, "confidence": 0.6803313388383841}, "containment": {"type": "noul", "noul": 0.014730495520811644}, "load": {"type": "score", "score": 1.2997088783694535, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.07551032772657393, "1": 0.5492704661773986, "2": 0.37521920609602744}, "confidence": 0.18807587254742097}, "urgency": {"type": "score", "score": 1.937812200817456, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.018368378254247305, "1": 0.02545104267404942, "2": 0.9561805790717033}, "confidence": 0.8091260652766668}, "impact": {"type": "score", "score": 1.4179326388350961, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.06393700472216769, "1": 0.45419335172056846, "2": 0.4818696435572638}, "confidence": 0.19344989102340526}, "potential_impact": {"type": "score", "score": 1.3375273790638733, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.07889131789555637, "1": 0.5046899851450138, "2": 0.41641869695942973}, "confidence": 0.17142652676105063}, "off_spec": {"type": "noul", "noul": 0.9972499411450706}, "stability": {"type": "score", "score": 1.943775069671376, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.021825125227392647, "1": 0.01257467987383881, "2": 0.9656001948987686}, "confidence": 0.8431627582980868}}</t>
         </is>
       </c>
     </row>
@@ -2556,12 +3110,12 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 512, "output_tokens": 115}</t>
+          <t>{"input_tokens": 5855, "output_tokens": 9}</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"fouling": 0.0, "weeping": 0.0, "other": 1.0, "flooding": 0.0, "foaming": 0.0, "reboiler_condenser": 0.0, "instrument": 0.0}}, "off_spec": {"type": "noul", "noul": 0.01}, "stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.015310150196454458, "weeping": 0.003729595689138417, "foaming": 0.0009179110234264862, "fouling": 0.001424967860907713, "reboiler_condenser": 0.00012948811605478457, "instrument": 8.09679406090723e-05, "other": 0.9784069191734092}, "confidence": 0.9363398600629796}, "containment": {"type": "noul", "noul": 0.004286624424021187}, "load": {"type": "score", "score": 0.9944437539675687, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.008743324738875088, "1": 0.988069596554681, "2": 0.003187078706443858}, "confidence": 0.9348095470889991}, "urgency": {"type": "score", "score": 0.02285845930706045, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9839212234793119, "1": 0.009299093734315722, "2": 0.006779682786372365}, "confidence": 0.9150701099900012}, "impact": {"type": "score", "score": 0.00986568256686438, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.992105930482838, "1": 0.005922456467459379, "2": 0.001971613049702501}, "confidence": 0.954014606183754}, "potential_impact": {"type": "score", "score": 0.01860644816057358, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.9871339026939872, "1": 0.0071257464514525295, "2": 0.005740350854560525}, "confidence": 0.9293340218130992}, "off_spec": {"type": "noul", "noul": 0.00523170811298286}, "stability": {"type": "score", "score": 0.011563927359574127, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.9921165372801404, "1": 0.004202998080145225, "2": 0.003680464639714451}, "confidence": 0.9531418933138464}}</t>
         </is>
       </c>
     </row>
@@ -2576,7 +3130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="20" min="1" max="1"/>
@@ -2681,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>0.973</v>
+        <v>0.881</v>
       </c>
       <c r="H2" s="33" t="n">
         <v>6</v>
@@ -2693,7 +3247,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>0.973</v>
+        <v>0.881</v>
       </c>
       <c r="L2" s="33" t="inlineStr"/>
     </row>
@@ -2717,13 +3271,13 @@
         <v>6</v>
       </c>
       <c r="E3" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.923</v>
       </c>
       <c r="H3" s="33" t="n">
         <v>2</v>
@@ -2735,19 +3289,19 @@
         <v>1</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.878</v>
       </c>
       <c r="L3" s="33" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="33" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>load</t>
         </is>
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>Urgency</t>
+          <t>Load</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
@@ -2759,37 +3313,33 @@
         <v>6</v>
       </c>
       <c r="E4" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>0.99</v>
+        <v>0.624</v>
       </c>
       <c r="H4" s="33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="33" t="n">
-        <v>0.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J4" s="33" t="inlineStr"/>
+      <c r="K4" s="33" t="inlineStr"/>
       <c r="L4" s="33" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>urgency</t>
         </is>
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Urgency</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
@@ -2801,128 +3351,124 @@
         <v>6</v>
       </c>
       <c r="E5" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>0.665</v>
+        <v>0.637</v>
       </c>
       <c r="H5" s="33" t="n">
         <v>2</v>
       </c>
       <c r="I5" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L5" s="33" t="n">
-        <v>0.49</v>
-      </c>
+        <v>0.671</v>
+      </c>
+      <c r="L5" s="33" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
         <is>
-          <t>cross_contamination</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>Cross-contamination</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>noul</t>
+          <t>score</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0.88</v>
+        <v>0.476</v>
       </c>
       <c r="H6" s="33" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="33" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L6" s="33" t="inlineStr"/>
+        <v>0.307</v>
+      </c>
+      <c r="L6" s="33" t="n">
+        <v>0.312</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
         <is>
-          <t>off_spec</t>
+          <t>potential_impact</t>
         </is>
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>Off-spec</t>
+          <t>Potential impact</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>noul</t>
+          <t>score</t>
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F7" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="H7" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>2</v>
-      </c>
       <c r="I7" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="33" t="n">
-        <v>0.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J7" s="33" t="inlineStr"/>
+      <c r="K7" s="33" t="inlineStr"/>
       <c r="L7" s="33" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>cross_contamination</t>
         </is>
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Cross-contamination</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>noul</t>
         </is>
       </c>
       <c r="D8" s="33" t="n">
@@ -2935,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="H8" s="33" t="n">
         <v>2</v>
@@ -2947,9 +3493,93 @@
         <v>1</v>
       </c>
       <c r="K8" s="33" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="L8" s="33" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>noul</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="33" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="33" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2962,7 +3592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -2984,24 +3614,228 @@
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>run_started</t>
         </is>
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>jev</t>
+          <t>20260930_192034</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>remapped to shared ids</t>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>engine</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>nimble</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>nimble</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>base_url</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>http://localhost:11434</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>endpoint_info</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>0.35.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>questions_hash</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>c6060602276b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>api_key_configured</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>records_in_run</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>records_completed</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>failed_records</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>review_threshold_default</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>elapsed_seconds</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_192034.jsonl</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>27645</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>27693</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>records_with_usage</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>output_sheets</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>output_nimble_Results, output_nimble_Raw, output_nimble_Summary, output_nimble_Run_info</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="20" min="1" max="1"/>
@@ -3108,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="33" t="n">
-        <v>0.8415755810011986</v>
+        <v>0.7691154479779605</v>
       </c>
       <c r="G2" s="33" t="n">
         <v>0.89</v>
@@ -3150,7 +3984,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>0.8543651811203101</v>
+        <v>0.8195945775641966</v>
       </c>
       <c r="G3" s="33" t="n">
         <v>1</v>
@@ -3188,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="39" t="n">
-        <v>0.2083469223640384</v>
+        <v>0.2861003836327028</v>
       </c>
       <c r="G4" s="39" t="n"/>
       <c r="H4" s="39" t="inlineStr"/>
@@ -3196,158 +4030,144 @@
       <c r="J4" s="39" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="33" t="n">
-        <v>0.4544207116173157</v>
-      </c>
-      <c r="G5" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H5" s="33" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
-      <c r="I5" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="C5" s="39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr"/>
+      <c r="E5" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="39" t="n">
+        <v>0.5252066897339631</v>
+      </c>
+      <c r="G5" s="39" t="n"/>
+      <c r="H5" s="39" t="inlineStr"/>
+      <c r="I5" s="39" t="inlineStr"/>
+      <c r="J5" s="39" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>containment</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>0.9898314939927169</v>
-      </c>
-      <c r="G6" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H6" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I6" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="inlineStr"/>
+      <c r="E6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="39" t="n">
+        <v>0.2688926828193108</v>
+      </c>
+      <c r="G6" s="39" t="n"/>
+      <c r="H6" s="39" t="inlineStr"/>
+      <c r="I6" s="39" t="inlineStr"/>
+      <c r="J6" s="39" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
         <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>0.4356639754842947</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H7" s="33" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="I7" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>failure_mode</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="D7" s="33" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>0.9615497684161856</v>
-      </c>
-      <c r="G7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="39" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D8" s="39" t="inlineStr"/>
-      <c r="E8" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="39" t="n">
-        <v>0.8174736490944896</v>
-      </c>
-      <c r="G8" s="39" t="n"/>
-      <c r="H8" s="39" t="inlineStr"/>
-      <c r="I8" s="39" t="inlineStr"/>
-      <c r="J8" s="39" t="inlineStr"/>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>0.9858959050293358</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I8" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="inlineStr">
@@ -3357,31 +4177,31 @@
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>failure_mode</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="E9" s="33" t="b">
         <v>1</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.9367164107789698</v>
+        <v>0.9707274126385984</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H9" s="33" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="I9" s="33" t="b">
@@ -3394,17 +4214,17 @@
     <row r="10">
       <c r="A10" s="39" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>containment</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D10" s="39" t="inlineStr"/>
@@ -3412,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="39" t="n">
-        <v>0.976902775293818</v>
+        <v>0.8060517778980076</v>
       </c>
       <c r="G10" s="39" t="n"/>
       <c r="H10" s="39" t="inlineStr"/>
@@ -3420,122 +4240,94 @@
       <c r="J10" s="39" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>cross_contamination</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="D11" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E11" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>0.9430803199340453</v>
-      </c>
-      <c r="G11" s="33" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I11" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr"/>
+      <c r="E11" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>0.8107506949544721</v>
+      </c>
+      <c r="G11" s="39" t="n"/>
+      <c r="H11" s="39" t="inlineStr"/>
+      <c r="I11" s="39" t="inlineStr"/>
+      <c r="J11" s="39" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>failure_mode</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="inlineStr">
-        <is>
-          <t>fouling</t>
-        </is>
-      </c>
-      <c r="D12" s="33" t="inlineStr">
-        <is>
-          <t>fouling</t>
-        </is>
-      </c>
-      <c r="E12" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>0.8814499623955965</v>
-      </c>
-      <c r="G12" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>fouling</t>
-        </is>
-      </c>
-      <c r="I12" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr"/>
+      <c r="E12" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>0.6617906884831326</v>
+      </c>
+      <c r="G12" s="39" t="n"/>
+      <c r="H12" s="39" t="inlineStr"/>
+      <c r="I12" s="39" t="inlineStr"/>
+      <c r="J12" s="39" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>urgency</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>routine</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>routine</t>
         </is>
       </c>
       <c r="E13" s="33" t="b">
         <v>1</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.307963612069315</v>
+        <v>0.9057681604539835</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="H13" s="33" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>routine</t>
         </is>
       </c>
       <c r="I13" s="33" t="b">
@@ -3553,12 +4345,12 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>containment</t>
         </is>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>false</t>
         </is>
       </c>
       <c r="D14" s="39" t="inlineStr"/>
@@ -3566,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="39" t="n">
-        <v>0.256700762696308</v>
+        <v>0.9810367320377763</v>
       </c>
       <c r="G14" s="39" t="n"/>
       <c r="H14" s="39" t="inlineStr"/>
@@ -3574,66 +4366,80 @@
       <c r="J14" s="39" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>containment</t>
-        </is>
-      </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>cross_contamination</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="D15" s="39" t="inlineStr"/>
-      <c r="E15" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="39" t="n">
-        <v>0.8028914237863862</v>
-      </c>
-      <c r="G15" s="39" t="n"/>
-      <c r="H15" s="39" t="inlineStr"/>
-      <c r="I15" s="39" t="inlineStr"/>
-      <c r="J15" s="39" t="inlineStr"/>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>0.9600284507335518</v>
+      </c>
+      <c r="G15" s="33" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>cross_contamination</t>
+          <t>failure_mode</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>fouling</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>fouling</t>
         </is>
       </c>
       <c r="E16" s="33" t="b">
         <v>1</v>
       </c>
       <c r="F16" s="33" t="n">
-        <v>0.9932766976597256</v>
+        <v>0.8964189370932257</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H16" s="33" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>fouling</t>
         </is>
       </c>
       <c r="I16" s="33" t="b">
@@ -3646,36 +4452,36 @@
     <row r="17">
       <c r="A17" s="33" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>failure_mode</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>tube_leak</t>
+          <t>degraded</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
         <is>
-          <t>tube_leak</t>
+          <t>degraded</t>
         </is>
       </c>
       <c r="E17" s="33" t="b">
         <v>1</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>0.9837622530540302</v>
+        <v>0.3072345881491388</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
-          <t>tube_leak</t>
+          <t>degraded</t>
         </is>
       </c>
       <c r="I17" s="33" t="b">
@@ -3686,61 +4492,47 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="E18" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="33" t="n">
-        <v>0.3039540830955473</v>
-      </c>
-      <c r="G18" s="33" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H18" s="33" t="inlineStr">
-        <is>
-          <t>severe</t>
-        </is>
-      </c>
-      <c r="I18" s="33" t="b">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr"/>
+      <c r="E18" s="39" t="b">
         <v>0</v>
       </c>
-      <c r="J18" s="33" t="b">
-        <v>0</v>
-      </c>
+      <c r="F18" s="39" t="n">
+        <v>0.5793208854661729</v>
+      </c>
+      <c r="G18" s="39" t="n"/>
+      <c r="H18" s="39" t="inlineStr"/>
+      <c r="I18" s="39" t="inlineStr"/>
+      <c r="J18" s="39" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="39" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>potential_impact</t>
         </is>
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
-          <t>soon</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D19" s="39" t="inlineStr"/>
@@ -3748,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="39" t="n">
-        <v>0.2781025575436905</v>
+        <v>0.2703462680038269</v>
       </c>
       <c r="G19" s="39" t="n"/>
       <c r="H19" s="39" t="inlineStr"/>
@@ -3758,17 +4550,17 @@
     <row r="20">
       <c r="A20" s="39" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>containment</t>
+          <t>urgency</t>
         </is>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>routine</t>
         </is>
       </c>
       <c r="D20" s="39" t="inlineStr"/>
@@ -3776,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="39" t="n">
-        <v>0.9872655920418659</v>
+        <v>0.4559468789770235</v>
       </c>
       <c r="G20" s="39" t="n"/>
       <c r="H20" s="39" t="inlineStr"/>
@@ -3784,108 +4576,108 @@
       <c r="J20" s="39" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>failure_mode</t>
-        </is>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>flooding</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>flooding</t>
-        </is>
-      </c>
-      <c r="E21" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="33" t="n">
-        <v>0.6645757278878761</v>
-      </c>
-      <c r="G21" s="33" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H21" s="33" t="inlineStr">
-        <is>
-          <t>flooding</t>
-        </is>
-      </c>
-      <c r="I21" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr"/>
+      <c r="E21" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="39" t="n">
+        <v>0.8231185626412096</v>
+      </c>
+      <c r="G21" s="39" t="n"/>
+      <c r="H21" s="39" t="inlineStr"/>
+      <c r="I21" s="39" t="inlineStr"/>
+      <c r="J21" s="39" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>severe</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr"/>
-      <c r="E22" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="39" t="n">
-        <v>0.3401207802595729</v>
-      </c>
-      <c r="G22" s="39" t="n"/>
-      <c r="H22" s="39" t="inlineStr"/>
-      <c r="I22" s="39" t="inlineStr"/>
-      <c r="J22" s="39" t="inlineStr"/>
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>cross_contamination</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="33" t="n">
+        <v>0.993523868071281</v>
+      </c>
+      <c r="G22" s="33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H22" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I22" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="33" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>off_spec</t>
+          <t>failure_mode</t>
         </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>tube_leak</t>
         </is>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>tube_leak</t>
         </is>
       </c>
       <c r="E23" s="33" t="b">
         <v>1</v>
       </c>
       <c r="F23" s="33" t="n">
-        <v>0.9970522723523294</v>
+        <v>0.980827621350109</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H23" s="33" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>tube_leak</t>
         </is>
       </c>
       <c r="I23" s="33" t="b">
@@ -3898,59 +4690,59 @@
     <row r="24">
       <c r="A24" s="33" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>upset</t>
+          <t>degraded</t>
         </is>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
-          <t>upset</t>
+          <t>degraded</t>
         </is>
       </c>
       <c r="E24" s="33" t="b">
         <v>1</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>0.8256569376354821</v>
+        <v>0.3120997517953533</v>
       </c>
       <c r="G24" s="33" t="n">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="H24" s="33" t="inlineStr">
         <is>
-          <t>upset</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="I24" s="33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="39" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>load</t>
         </is>
       </c>
       <c r="C25" s="39" t="inlineStr">
         <is>
-          <t>immediate</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D25" s="39" t="inlineStr"/>
@@ -3958,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="39" t="n">
-        <v>0.8252172542970286</v>
+        <v>0.7082652363052141</v>
       </c>
       <c r="G25" s="39" t="n"/>
       <c r="H25" s="39" t="inlineStr"/>
@@ -3968,17 +4760,17 @@
     <row r="26">
       <c r="A26" s="39" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t>containment</t>
+          <t>potential_impact</t>
         </is>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr"/>
@@ -3986,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="39" t="n">
-        <v>0.9974246677596986</v>
+        <v>0.2893414605806364</v>
       </c>
       <c r="G26" s="39" t="n"/>
       <c r="H26" s="39" t="inlineStr"/>
@@ -3994,61 +4786,47 @@
       <c r="J26" s="39" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>failure_mode</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="E27" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="33" t="n">
-        <v>0.9008279495867489</v>
-      </c>
-      <c r="G27" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I27" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>soon</t>
+        </is>
+      </c>
+      <c r="D27" s="39" t="inlineStr"/>
+      <c r="E27" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="39" t="n">
+        <v>0.3004673764848859</v>
+      </c>
+      <c r="G27" s="39" t="n"/>
+      <c r="H27" s="39" t="inlineStr"/>
+      <c r="I27" s="39" t="inlineStr"/>
+      <c r="J27" s="39" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="39" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>containment</t>
         </is>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>false</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr"/>
@@ -4056,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="39" t="n">
-        <v>0.9826158013130231</v>
+        <v>0.9852695044791884</v>
       </c>
       <c r="G28" s="39" t="n"/>
       <c r="H28" s="39" t="inlineStr"/>
@@ -4066,36 +4844,36 @@
     <row r="29">
       <c r="A29" s="33" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>off_spec</t>
+          <t>failure_mode</t>
         </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>flooding</t>
         </is>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>flooding</t>
         </is>
       </c>
       <c r="E29" s="33" t="b">
         <v>1</v>
       </c>
       <c r="F29" s="33" t="n">
-        <v>0.9972445173865104</v>
+        <v>0.6803313388383841</v>
       </c>
       <c r="G29" s="33" t="n">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
       <c r="H29" s="33" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>flooding</t>
         </is>
       </c>
       <c r="I29" s="33" t="b">
@@ -4106,61 +4884,47 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>stability</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-      <c r="E30" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="33" t="n">
-        <v>0.9760509329206121</v>
-      </c>
-      <c r="G30" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="33" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-      <c r="I30" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr"/>
+      <c r="E30" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="39" t="n">
+        <v>0.1934498910234053</v>
+      </c>
+      <c r="G30" s="39" t="n"/>
+      <c r="H30" s="39" t="inlineStr"/>
+      <c r="I30" s="39" t="inlineStr"/>
+      <c r="J30" s="39" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="39" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>load</t>
         </is>
       </c>
       <c r="C31" s="39" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D31" s="39" t="inlineStr"/>
@@ -4168,12 +4932,418 @@
         <v>0</v>
       </c>
       <c r="F31" s="39" t="n">
-        <v>0.9584234273970306</v>
+        <v>0.188075872547421</v>
       </c>
       <c r="G31" s="39" t="n"/>
       <c r="H31" s="39" t="inlineStr"/>
       <c r="I31" s="39" t="inlineStr"/>
       <c r="J31" s="39" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E32" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="33" t="n">
+        <v>0.9972499411450706</v>
+      </c>
+      <c r="G32" s="33" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H32" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I32" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" s="33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="C33" s="39" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="D33" s="39" t="inlineStr"/>
+      <c r="E33" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="39" t="n">
+        <v>0.1714265267610506</v>
+      </c>
+      <c r="G33" s="39" t="n"/>
+      <c r="H33" s="39" t="inlineStr"/>
+      <c r="I33" s="39" t="inlineStr"/>
+      <c r="J33" s="39" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="33" t="n">
+        <v>0.8431627582980868</v>
+      </c>
+      <c r="G34" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="33" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="I34" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" s="33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="C35" s="39" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="D35" s="39" t="inlineStr"/>
+      <c r="E35" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="39" t="n">
+        <v>0.8091260652766668</v>
+      </c>
+      <c r="G35" s="39" t="n"/>
+      <c r="H35" s="39" t="inlineStr"/>
+      <c r="I35" s="39" t="inlineStr"/>
+      <c r="J35" s="39" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr"/>
+      <c r="E36" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="39" t="n">
+        <v>0.9957133755759788</v>
+      </c>
+      <c r="G36" s="39" t="n"/>
+      <c r="H36" s="39" t="inlineStr"/>
+      <c r="I36" s="39" t="inlineStr"/>
+      <c r="J36" s="39" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>failure_mode</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="33" t="n">
+        <v>0.9363398600629796</v>
+      </c>
+      <c r="G37" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I37" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" s="33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="C38" s="39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr"/>
+      <c r="E38" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="39" t="n">
+        <v>0.954014606183754</v>
+      </c>
+      <c r="G38" s="39" t="n"/>
+      <c r="H38" s="39" t="inlineStr"/>
+      <c r="I38" s="39" t="inlineStr"/>
+      <c r="J38" s="39" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="C39" s="39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D39" s="39" t="inlineStr"/>
+      <c r="E39" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="39" t="n">
+        <v>0.9348095470889991</v>
+      </c>
+      <c r="G39" s="39" t="n"/>
+      <c r="H39" s="39" t="inlineStr"/>
+      <c r="I39" s="39" t="inlineStr"/>
+      <c r="J39" s="39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D40" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E40" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="33" t="n">
+        <v>0.9947682918870171</v>
+      </c>
+      <c r="G40" s="33" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H40" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I40" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" s="33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="C41" s="39" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D41" s="39" t="inlineStr"/>
+      <c r="E41" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="39" t="n">
+        <v>0.9293340218130992</v>
+      </c>
+      <c r="G41" s="39" t="n"/>
+      <c r="H41" s="39" t="inlineStr"/>
+      <c r="I41" s="39" t="inlineStr"/>
+      <c r="J41" s="39" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="D42" s="33" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="E42" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="33" t="n">
+        <v>0.9531418933138464</v>
+      </c>
+      <c r="G42" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="33" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="I42" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" s="33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="C43" s="39" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="D43" s="39" t="inlineStr"/>
+      <c r="E43" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="39" t="n">
+        <v>0.9150701099900012</v>
+      </c>
+      <c r="G43" s="39" t="n"/>
+      <c r="H43" s="39" t="inlineStr"/>
+      <c r="I43" s="39" t="inlineStr"/>
+      <c r="J43" s="39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4398,7 +5568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="19" min="1" max="1"/>
@@ -4469,7 +5639,6 @@
           <t>Failure mode</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr"/>
       <c r="D2" s="19" t="inlineStr">
         <is>
           <t>choice</t>
@@ -4505,7 +5674,6 @@
           <t>Containment</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr"/>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>noul</t>
@@ -4533,12 +5701,12 @@
     <row r="4" ht="15" customHeight="1" s="20">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>load</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Urgency</t>
+          <t>Load</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr"/>
@@ -4549,7 +5717,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>How urgent is follow-up?</t>
+          <t>How loaded is the equipment relative to normal/design duty?</t>
         </is>
       </c>
       <c r="F4" s="19" t="inlineStr">
@@ -4569,15 +5737,14 @@
     <row r="5" ht="15" customHeight="1" s="20">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>urgency</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr"/>
+          <t>Urgency</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>score</t>
@@ -4585,7 +5752,7 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>How severe is the performance or operating impact?</t>
+          <t>How urgent is follow-up?</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -4605,27 +5772,22 @@
     <row r="6" ht="15" customHeight="1" s="20">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>cross_contamination</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Cross-contamination</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>noul</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>Does the text suggest mixing of shell-side and tube-side fluids (e.g. from a tube leak)?</t>
+          <t>How severe is the performance or operating impact?</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
@@ -4645,27 +5807,23 @@
     <row r="7" ht="15" customHeight="1" s="20">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>off_spec</t>
+          <t>potential_impact</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Off-spec</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr"/>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>noul</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>Does the text mention off-spec product?</t>
+          <t>If unaddressed, how severe could the consequence become?</t>
         </is>
       </c>
       <c r="F7" s="19" t="inlineStr">
@@ -4685,27 +5843,27 @@
     <row r="8" ht="15" customHeight="1" s="20">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>cross_contamination</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Cross-contamination</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>Distillation Column</t>
+          <t>Heat Exchanger</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>noul</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>How stable is column operation?</t>
+          <t>Does the text suggest mixing of shell-side and tube-side fluids (e.g. from a tube leak)?</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -4722,8 +5880,86 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="20"/>
-    <row r="10" ht="15" customHeight="1" s="20"/>
+    <row r="9" ht="15" customHeight="1" s="20">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>noul</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Does the text mention off-spec product?</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H9" s="19">
+        <f>IF(A9="","",COUNTIF(Labels!$A$2:$A$300,A9))</f>
+        <v/>
+      </c>
+      <c r="I9" s="19">
+        <f>IF(A9="","",IF(COUNTIF($A$2:$A$60,A9)&gt;1,"Duplicate question_id",IF(E9="","Missing instructions",IF(D9="noul",IF(H9=0,"OK","noul takes no labels"),IF(OR(D9="choice",D9="score"),IF(H9&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="20">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>How stable is column operation?</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H10" s="19">
+        <f>IF(A10="","",COUNTIF(Labels!$A$2:$A$300,A10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="19">
+        <f>IF(A10="","",IF(COUNTIF($A$2:$A$60,A10)&gt;1,"Duplicate question_id",IF(E10="","Missing instructions",IF(D10="noul",IF(H10=0,"OK","noul takes no labels"),IF(OR(D10="choice",D10="score"),IF(H10&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
+        <v/>
+      </c>
+    </row>
     <row r="11" ht="15" customHeight="1" s="20"/>
     <row r="12" ht="15" customHeight="1" s="20"/>
     <row r="13" ht="15" customHeight="1" s="20"/>
@@ -4810,7 +6046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="19" min="1" max="1"/>
@@ -5283,7 +6519,6 @@
           <t>urgency</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
       <c r="C19" s="19" t="inlineStr">
         <is>
           <t>routine</t>
@@ -5304,7 +6539,6 @@
           <t>urgency</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
       <c r="C20" s="19" t="inlineStr">
         <is>
           <t>soon</t>
@@ -5325,7 +6559,6 @@
           <t>urgency</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr"/>
       <c r="C21" s="19" t="inlineStr">
         <is>
           <t>immediate</t>
@@ -5346,7 +6579,6 @@
           <t>impact</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr"/>
       <c r="C22" s="19" t="inlineStr">
         <is>
           <t>none</t>
@@ -5367,7 +6599,6 @@
           <t>impact</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr"/>
       <c r="C23" s="19" t="inlineStr">
         <is>
           <t>degraded</t>
@@ -5388,7 +6619,6 @@
           <t>impact</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr"/>
       <c r="C24" s="19" t="inlineStr">
         <is>
           <t>severe</t>
@@ -5409,7 +6639,6 @@
           <t>stability</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr"/>
       <c r="C25" s="19" t="inlineStr">
         <is>
           <t>stable</t>
@@ -5430,7 +6659,6 @@
           <t>stability</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr"/>
       <c r="C26" s="19" t="inlineStr">
         <is>
           <t>marginal</t>
@@ -5451,7 +6679,6 @@
           <t>stability</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr"/>
       <c r="C27" s="19" t="inlineStr">
         <is>
           <t>upset</t>
@@ -5466,12 +6693,132 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="20"/>
-    <row r="29" ht="15" customHeight="1" s="20"/>
-    <row r="30" ht="15" customHeight="1" s="20"/>
-    <row r="31" ht="15" customHeight="1" s="20"/>
-    <row r="32" ht="15" customHeight="1" s="20"/>
-    <row r="33" ht="15" customHeight="1" s="20"/>
+    <row r="28" ht="15" customHeight="1" s="20">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr"/>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Well below normal or design duty</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="20">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Around normal / design duty</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="20">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>At or above design; stressed</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="20">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr"/>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Limited consequence if left alone</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="20">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr"/>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Notable production or reliability risk</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="20">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr"/>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>Serious safety, environmental, or unit risk</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
     <row r="34" ht="15" customHeight="1" s="20"/>
     <row r="35" ht="15" customHeight="1" s="20"/>
     <row r="36" ht="15" customHeight="1" s="20"/>
@@ -5763,7 +7110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="19" min="1" max="1"/>
@@ -5812,25 +7159,35 @@
       </c>
       <c r="H1" s="19" t="inlineStr">
         <is>
+          <t>expected_load</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
           <t>expected_urgency</t>
         </is>
       </c>
-      <c r="I1" s="19" t="inlineStr">
+      <c r="J1" s="19" t="inlineStr">
         <is>
           <t>expected_impact</t>
         </is>
       </c>
-      <c r="J1" s="19" t="inlineStr">
+      <c r="K1" s="19" t="inlineStr">
+        <is>
+          <t>expected_potential_impact</t>
+        </is>
+      </c>
+      <c r="L1" s="19" t="inlineStr">
         <is>
           <t>expected_cross_contamination</t>
         </is>
       </c>
-      <c r="K1" s="19" t="inlineStr">
+      <c r="M1" s="19" t="inlineStr">
         <is>
           <t>expected_off_spec</t>
         </is>
       </c>
-      <c r="L1" s="19" t="inlineStr">
+      <c r="N1" s="19" t="inlineStr">
         <is>
           <t>expected_stability</t>
         </is>
@@ -5867,7 +7224,7 @@
           <t>true</t>
         </is>
       </c>
-      <c r="H2" s="19" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>immediate</t>
         </is>
@@ -5904,7 +7261,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>routine</t>
         </is>
@@ -5936,12 +7293,12 @@
           <t>fouling</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>false</t>
         </is>
@@ -5973,12 +7330,12 @@
           <t>tube_leak</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>severe</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="L5" s="19" t="inlineStr">
         <is>
           <t>true</t>
         </is>
@@ -6010,12 +7367,12 @@
           <t>flooding</t>
         </is>
       </c>
-      <c r="K6" s="19" t="inlineStr">
+      <c r="M6" s="19" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
+      <c r="N6" s="19" t="inlineStr">
         <is>
           <t>upset</t>
         </is>
@@ -6047,12 +7404,12 @@
           <t>other</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="L7" s="19" t="inlineStr">
+      <c r="N7" s="19" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
@@ -6828,10 +8185,10 @@
         </is>
       </c>
       <c r="H2" s="35" t="n">
-        <v>0.8543651811203101</v>
+        <v>1</v>
       </c>
       <c r="I2" s="35" t="n">
-        <v>0.9551397791180488</v>
+        <v>1</v>
       </c>
       <c r="J2" s="33" t="b">
         <v>0</v>
@@ -6876,10 +8233,10 @@
         </is>
       </c>
       <c r="H3" s="35" t="n">
-        <v>0.8415755810011986</v>
+        <v>0.89</v>
       </c>
       <c r="I3" s="35" t="n">
-        <v>0.8415755810011986</v>
+        <v>0.89</v>
       </c>
       <c r="J3" s="33" t="b">
         <v>0</v>
@@ -6888,56 +8245,52 @@
       <c r="L3" s="33" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G4" s="36" t="inlineStr">
+      <c r="G4" s="33" t="inlineStr">
         <is>
           <t>immediate</t>
         </is>
       </c>
-      <c r="H4" s="38" t="n">
-        <v>0.4544207116173157</v>
-      </c>
-      <c r="I4" s="38" t="n">
-        <v>1.752680993235349</v>
-      </c>
-      <c r="J4" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="36" t="inlineStr">
-        <is>
-          <t>urgency: low confidence (0.45)</t>
-        </is>
-      </c>
-      <c r="L4" s="36" t="inlineStr"/>
+      <c r="H4" s="35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J4" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="33" t="inlineStr"/>
+      <c r="L4" s="33" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
@@ -6970,23 +8323,15 @@
           <t>Impact</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="H5" s="38" t="n">
-        <v>0.2083469223640384</v>
-      </c>
-      <c r="I5" s="38" t="n">
-        <v>1.209016256043309</v>
-      </c>
+      <c r="G5" s="36" t="inlineStr"/>
+      <c r="H5" s="36" t="n"/>
+      <c r="I5" s="36" t="n"/>
       <c r="J5" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.21)</t>
+          <t>no answer</t>
         </is>
       </c>
       <c r="L5" s="36" t="inlineStr"/>
@@ -7028,10 +8373,10 @@
         </is>
       </c>
       <c r="H6" s="35" t="n">
-        <v>0.9615497684161856</v>
+        <v>1</v>
       </c>
       <c r="I6" s="35" t="n">
-        <v>0.9907411238692516</v>
+        <v>1</v>
       </c>
       <c r="J6" s="33" t="b">
         <v>0</v>
@@ -7076,10 +8421,10 @@
         </is>
       </c>
       <c r="H7" s="35" t="n">
-        <v>0.9898314939927169</v>
+        <v>0.99</v>
       </c>
       <c r="I7" s="35" t="n">
-        <v>0.0101685060072831</v>
+        <v>0.01</v>
       </c>
       <c r="J7" s="33" t="b">
         <v>0</v>
@@ -7124,10 +8469,10 @@
         </is>
       </c>
       <c r="H8" s="35" t="n">
-        <v>0.9367164107789698</v>
+        <v>0.99</v>
       </c>
       <c r="I8" s="35" t="n">
-        <v>0.01472000131814487</v>
+        <v>0.01</v>
       </c>
       <c r="J8" s="33" t="b">
         <v>0</v>
@@ -7136,52 +8481,48 @@
       <c r="L8" s="33" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>P-114</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>0.8174736490944896</v>
-      </c>
-      <c r="I9" s="35" t="n">
-        <v>0.05067885894075733</v>
-      </c>
-      <c r="J9" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="33" t="inlineStr"/>
-      <c r="L9" s="33" t="inlineStr"/>
+      <c r="G9" s="36" t="inlineStr"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="L9" s="36" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
@@ -7220,10 +8561,10 @@
         </is>
       </c>
       <c r="H10" s="35" t="n">
-        <v>0.8814499623955965</v>
+        <v>1</v>
       </c>
       <c r="I10" s="35" t="n">
-        <v>0.9625561323238369</v>
+        <v>1</v>
       </c>
       <c r="J10" s="33" t="b">
         <v>0</v>
@@ -7232,52 +8573,48 @@
       <c r="L10" s="33" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>E-205</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>Containment</t>
         </is>
       </c>
-      <c r="G11" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H11" s="35" t="n">
-        <v>0.976902775293818</v>
-      </c>
-      <c r="I11" s="35" t="n">
-        <v>0.02309722470618207</v>
-      </c>
-      <c r="J11" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="33" t="inlineStr"/>
-      <c r="L11" s="33" t="inlineStr"/>
+      <c r="G11" s="36" t="inlineStr"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="L11" s="36" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="36" t="inlineStr">
@@ -7310,78 +8647,66 @@
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G12" s="36" t="inlineStr">
-        <is>
-          <t>routine</t>
-        </is>
-      </c>
-      <c r="H12" s="38" t="n">
-        <v>0.256700762696308</v>
-      </c>
-      <c r="I12" s="38" t="n">
-        <v>0.4104402944083502</v>
-      </c>
+      <c r="G12" s="36" t="inlineStr"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
       <c r="J12" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K12" s="36" t="inlineStr">
         <is>
-          <t>urgency: low confidence (0.26)</t>
+          <t>no answer</t>
         </is>
       </c>
       <c r="L12" s="36" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>E-205</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="E13" s="36" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G13" s="36" t="inlineStr">
+      <c r="G13" s="33" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="H13" s="38" t="n">
-        <v>0.307963612069315</v>
-      </c>
-      <c r="I13" s="38" t="n">
-        <v>0.932502515007201</v>
-      </c>
-      <c r="J13" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="36" t="inlineStr">
-        <is>
-          <t>impact: low confidence (0.31)</t>
-        </is>
-      </c>
-      <c r="L13" s="36" t="inlineStr"/>
+      <c r="H13" s="35" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I13" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J13" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="33" t="inlineStr"/>
+      <c r="L13" s="33" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
@@ -7420,10 +8745,10 @@
         </is>
       </c>
       <c r="H14" s="35" t="n">
-        <v>0.9430803199340453</v>
+        <v>0.86</v>
       </c>
       <c r="I14" s="35" t="n">
-        <v>0.05691968006595472</v>
+        <v>0.14</v>
       </c>
       <c r="J14" s="33" t="b">
         <v>0</v>
@@ -7468,10 +8793,10 @@
         </is>
       </c>
       <c r="H15" s="35" t="n">
-        <v>0.9837622530540302</v>
+        <v>1</v>
       </c>
       <c r="I15" s="35" t="n">
-        <v>0.9967058559277659</v>
+        <v>1</v>
       </c>
       <c r="J15" s="33" t="b">
         <v>0</v>
@@ -7480,52 +8805,48 @@
       <c r="L15" s="33" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>E-310</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>Containment</t>
         </is>
       </c>
-      <c r="G16" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H16" s="35" t="n">
-        <v>0.8028914237863862</v>
-      </c>
-      <c r="I16" s="35" t="n">
-        <v>0.1971085762136138</v>
-      </c>
-      <c r="J16" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="33" t="inlineStr"/>
-      <c r="L16" s="33" t="inlineStr"/>
+      <c r="G16" s="36" t="inlineStr"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="L16" s="36" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="36" t="inlineStr">
@@ -7558,23 +8879,15 @@
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G17" s="36" t="inlineStr">
-        <is>
-          <t>soon</t>
-        </is>
-      </c>
-      <c r="H17" s="38" t="n">
-        <v>0.2781025575436905</v>
-      </c>
-      <c r="I17" s="38" t="n">
-        <v>1.367707043608545</v>
-      </c>
+      <c r="G17" s="36" t="inlineStr"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
       <c r="J17" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
-          <t>urgency: low confidence (0.28)</t>
+          <t>no answer</t>
         </is>
       </c>
       <c r="L17" s="36" t="inlineStr"/>
@@ -7616,17 +8929,17 @@
         </is>
       </c>
       <c r="H18" s="38" t="n">
-        <v>0.3039540830955473</v>
+        <v>0.49</v>
       </c>
       <c r="I18" s="38" t="n">
-        <v>1.115588004395997</v>
+        <v>1.25</v>
       </c>
       <c r="J18" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.30)</t>
+          <t>impact: low confidence (0.49)</t>
         </is>
       </c>
       <c r="L18" s="36" t="inlineStr"/>
@@ -7668,10 +8981,10 @@
         </is>
       </c>
       <c r="H19" s="35" t="n">
-        <v>0.9932766976597256</v>
+        <v>0.9</v>
       </c>
       <c r="I19" s="35" t="n">
-        <v>0.9932766976597256</v>
+        <v>0.9</v>
       </c>
       <c r="J19" s="33" t="b">
         <v>0</v>
@@ -7716,10 +9029,10 @@
         </is>
       </c>
       <c r="H20" s="35" t="n">
-        <v>0.6645757278878761</v>
+        <v>0.84</v>
       </c>
       <c r="I20" s="35" t="n">
-        <v>0.7317665088294947</v>
+        <v>0.87</v>
       </c>
       <c r="J20" s="33" t="b">
         <v>0</v>
@@ -7728,100 +9041,92 @@
       <c r="L20" s="33" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C21" s="33" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D21" s="34" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E21" s="33" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="F21" s="33" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>Containment</t>
         </is>
       </c>
-      <c r="G21" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>0.9872655920418659</v>
-      </c>
-      <c r="I21" s="35" t="n">
-        <v>0.01273440795813405</v>
-      </c>
-      <c r="J21" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" s="33" t="inlineStr"/>
-      <c r="L21" s="33" t="inlineStr"/>
+      <c r="G21" s="36" t="inlineStr"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" s="36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="L21" s="36" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B22" s="33" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C22" s="33" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="F22" s="33" t="inlineStr">
+      <c r="F22" s="36" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G22" s="33" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>0.8252172542970286</v>
-      </c>
-      <c r="I22" s="35" t="n">
-        <v>1.940228737306855</v>
-      </c>
-      <c r="J22" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="33" t="inlineStr"/>
-      <c r="L22" s="33" t="inlineStr"/>
+      <c r="G22" s="36" t="inlineStr"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" s="36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="L22" s="36" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="36" t="inlineStr">
@@ -7854,23 +9159,15 @@
           <t>Impact</t>
         </is>
       </c>
-      <c r="G23" s="36" t="inlineStr">
-        <is>
-          <t>severe</t>
-        </is>
-      </c>
-      <c r="H23" s="38" t="n">
-        <v>0.3401207802595729</v>
-      </c>
-      <c r="I23" s="38" t="n">
-        <v>1.670802602896819</v>
-      </c>
+      <c r="G23" s="36" t="inlineStr"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
       <c r="J23" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K23" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.34)</t>
+          <t>no answer</t>
         </is>
       </c>
       <c r="L23" s="36" t="inlineStr"/>
@@ -7912,10 +9209,10 @@
         </is>
       </c>
       <c r="H24" s="35" t="n">
-        <v>0.9970522723523294</v>
+        <v>0.99</v>
       </c>
       <c r="I24" s="35" t="n">
-        <v>0.9970522723523294</v>
+        <v>0.99</v>
       </c>
       <c r="J24" s="33" t="b">
         <v>0</v>
@@ -7960,10 +9257,10 @@
         </is>
       </c>
       <c r="H25" s="35" t="n">
-        <v>0.8256569376354821</v>
+        <v>1</v>
       </c>
       <c r="I25" s="35" t="n">
-        <v>1.930954376914919</v>
+        <v>2</v>
       </c>
       <c r="J25" s="33" t="b">
         <v>0</v>
@@ -8008,10 +9305,10 @@
         </is>
       </c>
       <c r="H26" s="35" t="n">
-        <v>0.9008279495867489</v>
+        <v>1</v>
       </c>
       <c r="I26" s="35" t="n">
-        <v>0.9569117378672546</v>
+        <v>1</v>
       </c>
       <c r="J26" s="33" t="b">
         <v>0</v>
@@ -8020,148 +9317,136 @@
       <c r="L26" s="33" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>C-402</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="F27" s="33" t="inlineStr">
+      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>Containment</t>
         </is>
       </c>
-      <c r="G27" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>0.9974246677596986</v>
-      </c>
-      <c r="I27" s="35" t="n">
-        <v>0.002575332240301419</v>
-      </c>
-      <c r="J27" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" s="33" t="inlineStr"/>
-      <c r="L27" s="33" t="inlineStr"/>
+      <c r="G27" s="36" t="inlineStr"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="36" t="n"/>
+      <c r="J27" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" s="36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="L27" s="36" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>C-402</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="D28" s="37" t="inlineStr">
         <is>
           <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
+      <c r="F28" s="36" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G28" s="33" t="inlineStr">
-        <is>
-          <t>routine</t>
-        </is>
-      </c>
-      <c r="H28" s="35" t="n">
-        <v>0.9584234273970306</v>
-      </c>
-      <c r="I28" s="35" t="n">
-        <v>0.01231830472241001</v>
-      </c>
-      <c r="J28" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" s="33" t="inlineStr"/>
-      <c r="L28" s="33" t="inlineStr"/>
+      <c r="G28" s="36" t="inlineStr"/>
+      <c r="H28" s="36" t="n"/>
+      <c r="I28" s="36" t="n"/>
+      <c r="J28" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" s="36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="L28" s="36" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C29" s="33" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>C-402</t>
         </is>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D29" s="37" t="inlineStr">
         <is>
           <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F29" s="33" t="inlineStr">
+      <c r="F29" s="36" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G29" s="33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>0.9826158013130231</v>
-      </c>
-      <c r="I29" s="35" t="n">
-        <v>0.003729872446792262</v>
-      </c>
-      <c r="J29" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" s="33" t="inlineStr"/>
-      <c r="L29" s="33" t="inlineStr"/>
+      <c r="G29" s="36" t="inlineStr"/>
+      <c r="H29" s="36" t="n"/>
+      <c r="I29" s="36" t="n"/>
+      <c r="J29" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" s="36" t="inlineStr">
+        <is>
+          <t>no answer</t>
+        </is>
+      </c>
+      <c r="L29" s="36" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="33" t="inlineStr">
@@ -8200,10 +9485,10 @@
         </is>
       </c>
       <c r="H30" s="35" t="n">
-        <v>0.9972445173865104</v>
+        <v>0.99</v>
       </c>
       <c r="I30" s="35" t="n">
-        <v>0.002755482613489607</v>
+        <v>0.01</v>
       </c>
       <c r="J30" s="33" t="b">
         <v>0</v>
@@ -8248,10 +9533,10 @@
         </is>
       </c>
       <c r="H31" s="35" t="n">
-        <v>0.9760509329206121</v>
+        <v>1</v>
       </c>
       <c r="I31" s="35" t="n">
-        <v>0.006632824786746479</v>
+        <v>0</v>
       </c>
       <c r="J31" s="33" t="b">
         <v>0</v>
@@ -8303,12 +9588,12 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 1687, "output_tokens": 5}</t>
+          <t>{"input_tokens": 465, "output_tokens": 92}</t>
         </is>
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9551397791180488, "bearing": 0.017744560347897457, "cavitation": 0.019226888125723127, "instrument": 0.002388491844993568, "other": 0.00550028056333722}, "confidence": 0.8543651811203101}, "containment": {"type": "noul", "noul": 0.8415755810011986}, "urgency": {"type": "score", "score": 1.7526809932353493, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.06036041776518882, "1": 0.12659817123427322, "2": 0.8130414110005381}, "confidence": 0.4544207116173157}, "impact": {"type": "score", "score": 1.209016256043309, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.08662081227739292, "1": 0.617742119401905, "2": 0.295637068320702}, "confidence": 0.2083469223640384}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "bearing": 0.0, "instrument": 0.0, "seal": 1.0, "other": 0.0}}, "containment": {"type": "noul", "noul": 0.89}, "urgency": {"type": "score", "score": 1.99, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}}</t>
         </is>
       </c>
     </row>
@@ -8320,12 +9605,12 @@
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 1691, "output_tokens": 5}</t>
+          <t>{"input_tokens": 464, "output_tokens": 92}</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.005957421909585576, "bearing": 0.9907411238692516, "cavitation": 0.0007408557995057459, "instrument": 0.0007257452146151831, "other": 0.0018348532070420252}, "confidence": 0.9615497684161856}, "containment": {"type": "noul", "noul": 0.0101685060072831}, "urgency": {"type": "score", "score": 0.014720001318144868, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9885209687708421, "1": 0.008238061140170954, "2": 0.0032409700889869564}, "confidence": 0.9367164107789698}, "impact": {"type": "score", "score": 0.050678858940757326, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.9550433101512894, "1": 0.03923452075666374, "2": 0.005722169092046795}, "confidence": 0.8174736490944896}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"other": 0.0, "seal": 0.0, "cavitation": 0.0, "bearing": 1.0, "instrument": 0.0}}, "containment": {"type": "noul", "noul": 0.01}, "urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -8337,12 +9622,12 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 2485, "output_tokens": 6}</t>
+          <t>{"input_tokens": 484, "output_tokens": 102}</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9625561323238369, "tube_leak": 0.025102580225401686, "flow_maldistribution": 0.01012357572767959, "control_valve": 0.0009627201007644808, "other": 0.0012549916223175495}, "confidence": 0.8814499623955965}, "containment": {"type": "noul", "noul": 0.023097224706182074}, "urgency": {"type": "score", "score": 0.41044029440835017, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.6838056585579434, "1": 0.22194838847576287, "2": 0.09424595296629364}, "confidence": 0.25670076269630804}, "impact": {"type": "score", "score": 0.932502515007201, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.1682837598839894, "1": 0.73092996522482, "2": 0.10078627489119053}, "confidence": 0.307963612069315}, "cross_contamination": {"type": "noul", "noul": 0.05691968006595472}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "tube_leak": 0.0, "other": 0.0, "flow_maldistribution": 0.0, "fouling": 1.0}}, "cross_contamination": {"type": "noul", "noul": 0.14}, "impact": {"type": "score", "score": 1.1, "confidence": 0.84, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.9, "2": 0.1}}}</t>
         </is>
       </c>
     </row>
@@ -8354,12 +9639,12 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 2480, "output_tokens": 6}</t>
+          <t>{"input_tokens": 487, "output_tokens": 102}</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0011798694219058204, "tube_leak": 0.996705855927766, "flow_maldistribution": 0.0013113580214050814, "control_valve": 0.00021267493790606547, "other": 0.0005902416910171768}, "confidence": 0.9837622530540302}, "containment": {"type": "noul", "noul": 0.1971085762136138}, "urgency": {"type": "score", "score": 1.3677070436085454, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.03054164364731322, "1": 0.5712096690968282, "2": 0.39824868725585866}, "confidence": 0.2781025575436905}, "impact": {"type": "score", "score": 1.115588004395997, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.08285346933139064, "1": 0.718705056941222, "2": 0.1984414737273875}, "confidence": 0.3039540830955473}, "cross_contamination": {"type": "noul", "noul": 0.9932766976597256}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "tube_leak": 1.0, "fouling": 0.0}}, "cross_contamination": {"type": "noul", "noul": 0.9}, "impact": {"type": "score", "score": 1.25, "confidence": 0.49, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.05, "1": 0.65, "2": 0.3}}}</t>
         </is>
       </c>
     </row>
@@ -8371,12 +9656,12 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 3503, "output_tokens": 7}</t>
+          <t>{"input_tokens": 514, "output_tokens": 117}</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.7317665088294947, "weeping": 0.005000078224542254, "foaming": 0.25421878403060466, "fouling": 0.0013624578185003535, "reboiler_condenser": 0.0006427404195924466, "instrument": 0.006772580675485241, "other": 0.00023685000178019802}, "confidence": 0.6645757278878761}, "containment": {"type": "noul", "noul": 0.012734407958134046}, "urgency": {"type": "score", "score": 1.9402287373068552, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.020693983356113145, "1": 0.018383295980918476, "2": 0.9609227206629684}, "confidence": 0.8252172542970286}, "impact": {"type": "score", "score": 1.6708026028968186, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.05576688983379427, "1": 0.21766361743559287, "2": 0.7265694927306129}, "confidence": 0.34012078025957293}, "off_spec": {"type": "noul", "noul": 0.9970522723523294}, "stability": {"type": "score", "score": 1.9309543769149193, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.02902562250345209, "1": 0.010994378078176301, "2": 0.9599799994183715}, "confidence": 0.8256569376354821}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "flooding", "confidence": 0.84, "probabilities": {"instrument": 0.02, "flooding": 0.87, "other": 0.02, "reboiler_condenser": 0.0, "weeping": 0.0, "foaming": 0.09, "fouling": 0.0}}, "off_spec": {"type": "noul", "noul": 0.99}, "stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}}</t>
         </is>
       </c>
     </row>
@@ -8388,12 +9673,12 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 3491, "output_tokens": 7}</t>
+          <t>{"input_tokens": 512, "output_tokens": 115}</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.0399096340750022, "weeping": 0.0007191273733833843, "foaming": 0.0007072333295555924, "fouling": 0.0015257414401928441, "reboiler_condenser": 0.00014483432586719544, "instrument": 8.169158874430721e-05, "other": 0.9569117378672546}, "confidence": 0.9008279495867489}, "containment": {"type": "noul", "noul": 0.002575332240301419}, "urgency": {"type": "score", "score": 0.012318304722410007, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9929855382900995, "1": 0.0017106186973910667, "2": 0.00530384301250947}, "confidence": 0.9584234273970306}, "impact": {"type": "score", "score": 0.0037298724467922616, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.9975164374159761, "1": 0.001237252721255474, "2": 0.0012463098627683938}, "confidence": 0.9826158013130231}, "off_spec": {"type": "noul", "noul": 0.0027554826134896073}, "stability": {"type": "score", "score": 0.0066328247867464794, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.9962986849908512, "1": 0.0007698052315510225, "2": 0.0029315097775977285}, "confidence": 0.9760509329206121}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"fouling": 0.0, "weeping": 0.0, "other": 1.0, "flooding": 0.0, "foaming": 0.0, "reboiler_condenser": 0.0, "instrument": 0.0}}, "off_spec": {"type": "noul", "noul": 0.01}, "stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -8513,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>0.874</v>
+        <v>0.973</v>
       </c>
       <c r="H2" s="33" t="n">
         <v>6</v>
@@ -8525,7 +9810,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>0.874</v>
+        <v>0.973</v>
       </c>
       <c r="L2" s="33" t="inlineStr"/>
     </row>
@@ -8549,13 +9834,13 @@
         <v>6</v>
       </c>
       <c r="E3" s="33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H3" s="33" t="n">
         <v>2</v>
@@ -8567,7 +9852,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>0.916</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L3" s="33" t="inlineStr"/>
     </row>
@@ -8591,13 +9876,13 @@
         <v>6</v>
       </c>
       <c r="E4" s="33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>0.618</v>
+        <v>0.99</v>
       </c>
       <c r="H4" s="33" t="n">
         <v>2</v>
@@ -8609,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="33" t="n">
-        <v>0.696</v>
+        <v>0.99</v>
       </c>
       <c r="L4" s="33" t="inlineStr"/>
     </row>
@@ -8633,13 +9918,13 @@
         <v>6</v>
       </c>
       <c r="E5" s="33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>0.493</v>
+        <v>0.665</v>
       </c>
       <c r="H5" s="33" t="n">
         <v>2</v>
@@ -8651,10 +9936,10 @@
         <v>0.5</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>0.308</v>
+        <v>0.84</v>
       </c>
       <c r="L5" s="33" t="n">
-        <v>0.304</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="6">
@@ -8683,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0.968</v>
+        <v>0.88</v>
       </c>
       <c r="H6" s="33" t="n">
         <v>2</v>
@@ -8695,7 +9980,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="33" t="n">
-        <v>0.968</v>
+        <v>0.88</v>
       </c>
       <c r="L6" s="33" t="inlineStr"/>
     </row>
@@ -8725,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.997</v>
+        <v>0.99</v>
       </c>
       <c r="H7" s="33" t="n">
         <v>2</v>
@@ -8737,7 +10022,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="33" t="n">
-        <v>0.997</v>
+        <v>0.99</v>
       </c>
       <c r="L7" s="33" t="inlineStr"/>
     </row>
@@ -8767,7 +10052,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>0.901</v>
+        <v>1</v>
       </c>
       <c r="H8" s="33" t="n">
         <v>2</v>
@@ -8779,7 +10064,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="33" t="n">
-        <v>0.901</v>
+        <v>1</v>
       </c>
       <c r="L8" s="33" t="inlineStr"/>
     </row>

--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -13,14 +13,14 @@
     <sheet name="Labels" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Records" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Lists" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="output_jev_Results" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="output_jev_Raw" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="output_jev_Summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="output_jev_Run_info" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="output_nimble_Results" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="output_nimble_Raw" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="output_nimble_Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="output_nimble_Run_info" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="output_nimble_Results" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="output_nimble_Raw" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="output_nimble_Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="output_nimble_Run_info" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="output_jev_Results" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="output_jev_Raw" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="output_jev_Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="output_jev_Run_info" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="output_compare" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="20" min="1" max="1"/>
@@ -798,24 +798,228 @@
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
-          <t>engine</t>
+          <t>run_started</t>
         </is>
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>jev</t>
+          <t>20260930_192332</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>remapped to shared ids</t>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>engine</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>nimble</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>nimble</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>base_url</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>http://localhost:11434</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>endpoint_info</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>0.35.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>questions_hash</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>c6060602276b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>api_key_configured</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>records_in_run</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>records_completed</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>failed_records</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>review_threshold_default</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>elapsed_seconds</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_192332.jsonl</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>27645</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>27693</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>records_with_usage</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>output_sheets</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>output_nimble_Results, output_nimble_Raw, output_nimble_Summary, output_nimble_Run_info</t>
         </is>
       </c>
     </row>
@@ -946,10 +1150,10 @@
         </is>
       </c>
       <c r="H2" s="35" t="n">
-        <v>0.8195945775641966</v>
+        <v>1</v>
       </c>
       <c r="I2" s="35" t="n">
-        <v>0.9403764383354369</v>
+        <v>1</v>
       </c>
       <c r="J2" s="33" t="b">
         <v>0</v>
@@ -994,10 +1198,10 @@
         </is>
       </c>
       <c r="H3" s="35" t="n">
-        <v>0.7691154479779605</v>
+        <v>0.88</v>
       </c>
       <c r="I3" s="35" t="n">
-        <v>0.7691154479779605</v>
+        <v>0.88</v>
       </c>
       <c r="J3" s="33" t="b">
         <v>0</v>
@@ -1038,180 +1242,168 @@
       </c>
       <c r="G4" s="36" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H4" s="38" t="n">
-        <v>0.5252066897339631</v>
+        <v>0.26</v>
       </c>
       <c r="I4" s="38" t="n">
-        <v>1.101685927779176</v>
+        <v>1.51</v>
       </c>
       <c r="J4" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="36" t="inlineStr">
         <is>
-          <t>load: low confidence (0.53)</t>
+          <t>load: low confidence (0.26)</t>
         </is>
       </c>
       <c r="L4" s="36" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>immediate</t>
         </is>
       </c>
-      <c r="H5" s="38" t="n">
-        <v>0.4356639754842947</v>
-      </c>
-      <c r="I5" s="38" t="n">
-        <v>1.744118329531175</v>
-      </c>
-      <c r="J5" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="36" t="inlineStr">
-        <is>
-          <t>urgency: low confidence (0.44)</t>
-        </is>
-      </c>
-      <c r="L5" s="36" t="inlineStr"/>
+      <c r="H5" s="35" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J5" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="33" t="inlineStr"/>
+      <c r="L5" s="33" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F6" s="36" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G6" s="36" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="H6" s="38" t="n">
-        <v>0.2861003836327028</v>
-      </c>
-      <c r="I6" s="38" t="n">
-        <v>1.099536415201052</v>
-      </c>
-      <c r="J6" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="36" t="inlineStr">
-        <is>
-          <t>impact: low confidence (0.29)</t>
-        </is>
-      </c>
-      <c r="L6" s="36" t="inlineStr"/>
+      <c r="H6" s="35" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J6" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="33" t="inlineStr"/>
+      <c r="L6" s="33" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="G7" s="36" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="H7" s="38" t="n">
-        <v>0.2688926828193108</v>
-      </c>
-      <c r="I7" s="38" t="n">
-        <v>1.58153004084961</v>
-      </c>
-      <c r="J7" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="36" t="inlineStr">
-        <is>
-          <t>potential_impact: low confidence (0.27)</t>
-        </is>
-      </c>
-      <c r="L7" s="36" t="inlineStr"/>
+      <c r="H7" s="35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J7" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="33" t="inlineStr"/>
+      <c r="L7" s="33" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
@@ -1250,10 +1442,10 @@
         </is>
       </c>
       <c r="H8" s="35" t="n">
-        <v>0.9707274126385984</v>
+        <v>1</v>
       </c>
       <c r="I8" s="35" t="n">
-        <v>0.99356430421049</v>
+        <v>1</v>
       </c>
       <c r="J8" s="33" t="b">
         <v>0</v>
@@ -1298,10 +1490,10 @@
         </is>
       </c>
       <c r="H9" s="35" t="n">
-        <v>0.9858959050293358</v>
+        <v>0.99</v>
       </c>
       <c r="I9" s="35" t="n">
-        <v>0.01410409497066424</v>
+        <v>0.01</v>
       </c>
       <c r="J9" s="33" t="b">
         <v>0</v>
@@ -1346,10 +1538,10 @@
         </is>
       </c>
       <c r="H10" s="35" t="n">
-        <v>0.8107506949544721</v>
+        <v>0.96</v>
       </c>
       <c r="I10" s="35" t="n">
-        <v>0.9830735117434298</v>
+        <v>1.02</v>
       </c>
       <c r="J10" s="33" t="b">
         <v>0</v>
@@ -1394,10 +1586,10 @@
         </is>
       </c>
       <c r="H11" s="35" t="n">
-        <v>0.9057681604539835</v>
+        <v>0.99</v>
       </c>
       <c r="I11" s="35" t="n">
-        <v>0.02394660660151229</v>
+        <v>0.01</v>
       </c>
       <c r="J11" s="33" t="b">
         <v>0</v>
@@ -1442,10 +1634,10 @@
         </is>
       </c>
       <c r="H12" s="35" t="n">
-        <v>0.8060517778980076</v>
+        <v>0.96</v>
       </c>
       <c r="I12" s="35" t="n">
-        <v>0.05461874556361802</v>
+        <v>0.03</v>
       </c>
       <c r="J12" s="33" t="b">
         <v>0</v>
@@ -1490,10 +1682,10 @@
         </is>
       </c>
       <c r="H13" s="35" t="n">
-        <v>0.6617906884831326</v>
+        <v>0.88</v>
       </c>
       <c r="I13" s="35" t="n">
-        <v>0.9272016948488913</v>
+        <v>0.96</v>
       </c>
       <c r="J13" s="33" t="b">
         <v>0</v>
@@ -1538,10 +1730,10 @@
         </is>
       </c>
       <c r="H14" s="35" t="n">
-        <v>0.8964189370932257</v>
+        <v>1</v>
       </c>
       <c r="I14" s="35" t="n">
-        <v>0.9680451306120793</v>
+        <v>1</v>
       </c>
       <c r="J14" s="33" t="b">
         <v>0</v>
@@ -1586,10 +1778,10 @@
         </is>
       </c>
       <c r="H15" s="35" t="n">
-        <v>0.9810367320377763</v>
+        <v>0.97</v>
       </c>
       <c r="I15" s="35" t="n">
-        <v>0.01896326796222373</v>
+        <v>0.03</v>
       </c>
       <c r="J15" s="33" t="b">
         <v>0</v>
@@ -1634,17 +1826,17 @@
         </is>
       </c>
       <c r="H16" s="38" t="n">
-        <v>0.5793208854661729</v>
+        <v>0</v>
       </c>
       <c r="I16" s="38" t="n">
-        <v>0.9234640502322689</v>
+        <v>1.19</v>
       </c>
       <c r="J16" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
-          <t>load: low confidence (0.58)</t>
+          <t>load: low confidence (0.00)</t>
         </is>
       </c>
       <c r="L16" s="36" t="inlineStr"/>
@@ -1682,128 +1874,120 @@
       </c>
       <c r="G17" s="36" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>soon</t>
         </is>
       </c>
       <c r="H17" s="38" t="n">
-        <v>0.4559468789770235</v>
+        <v>0.29</v>
       </c>
       <c r="I17" s="38" t="n">
-        <v>0.2398700214389179</v>
+        <v>0.95</v>
       </c>
       <c r="J17" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
-          <t>urgency: low confidence (0.46)</t>
+          <t>urgency: low confidence (0.29)</t>
         </is>
       </c>
       <c r="L17" s="36" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>E-205</t>
         </is>
       </c>
-      <c r="D18" s="37" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="E18" s="36" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F18" s="36" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G18" s="36" t="inlineStr">
+      <c r="G18" s="33" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="H18" s="38" t="n">
-        <v>0.3072345881491388</v>
-      </c>
-      <c r="I18" s="38" t="n">
-        <v>0.7770780189312785</v>
-      </c>
-      <c r="J18" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="36" t="inlineStr">
-        <is>
-          <t>impact: low confidence (0.31)</t>
-        </is>
-      </c>
-      <c r="L18" s="36" t="inlineStr"/>
+      <c r="H18" s="35" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J18" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="33" t="inlineStr"/>
+      <c r="L18" s="33" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>E-205</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="F19" s="36" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="G19" s="36" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H19" s="38" t="n">
-        <v>0.2703462680038269</v>
-      </c>
-      <c r="I19" s="38" t="n">
-        <v>0.4875360292089463</v>
-      </c>
-      <c r="J19" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="36" t="inlineStr">
-        <is>
-          <t>potential_impact: low confidence (0.27)</t>
-        </is>
-      </c>
-      <c r="L19" s="36" t="inlineStr"/>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J19" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="33" t="inlineStr"/>
+      <c r="L19" s="33" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="33" t="inlineStr">
@@ -1842,10 +2026,10 @@
         </is>
       </c>
       <c r="H20" s="35" t="n">
-        <v>0.9600284507335518</v>
+        <v>0.85</v>
       </c>
       <c r="I20" s="35" t="n">
-        <v>0.0399715492664482</v>
+        <v>0.15</v>
       </c>
       <c r="J20" s="33" t="b">
         <v>0</v>
@@ -1890,10 +2074,10 @@
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>0.980827621350109</v>
+        <v>1</v>
       </c>
       <c r="I21" s="35" t="n">
-        <v>0.9960106591003453</v>
+        <v>1</v>
       </c>
       <c r="J21" s="33" t="b">
         <v>0</v>
@@ -1934,14 +2118,14 @@
       </c>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="H22" s="35" t="n">
-        <v>0.8231185626412096</v>
+        <v>0.67</v>
       </c>
       <c r="I22" s="35" t="n">
-        <v>0.1768814373587904</v>
+        <v>0.67</v>
       </c>
       <c r="J22" s="33" t="b">
         <v>0</v>
@@ -1986,10 +2170,10 @@
         </is>
       </c>
       <c r="H23" s="35" t="n">
-        <v>0.7082652363052141</v>
+        <v>0.84</v>
       </c>
       <c r="I23" s="35" t="n">
-        <v>1.023989710490751</v>
+        <v>1.09</v>
       </c>
       <c r="J23" s="33" t="b">
         <v>0</v>
@@ -1998,56 +2182,52 @@
       <c r="L23" s="33" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>E-310</t>
         </is>
       </c>
-      <c r="D24" s="37" t="inlineStr">
+      <c r="D24" s="34" t="inlineStr">
         <is>
           <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G24" s="36" t="inlineStr">
-        <is>
-          <t>soon</t>
-        </is>
-      </c>
-      <c r="H24" s="38" t="n">
-        <v>0.3004673764848859</v>
-      </c>
-      <c r="I24" s="38" t="n">
-        <v>1.331217847775203</v>
-      </c>
-      <c r="J24" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="36" t="inlineStr">
-        <is>
-          <t>urgency: low confidence (0.30)</t>
-        </is>
-      </c>
-      <c r="L24" s="36" t="inlineStr"/>
+      <c r="G24" s="33" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" s="33" t="inlineStr"/>
+      <c r="L24" s="33" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="36" t="inlineStr">
@@ -2086,72 +2266,68 @@
         </is>
       </c>
       <c r="H25" s="38" t="n">
-        <v>0.3120997517953533</v>
+        <v>0.58</v>
       </c>
       <c r="I25" s="38" t="n">
-        <v>1.139766134713401</v>
+        <v>1.21</v>
       </c>
       <c r="J25" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K25" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.31)</t>
+          <t>impact: low confidence (0.58)</t>
         </is>
       </c>
       <c r="L25" s="36" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C26" s="36" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>E-310</t>
         </is>
       </c>
-      <c r="D26" s="37" t="inlineStr">
+      <c r="D26" s="34" t="inlineStr">
         <is>
           <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
         </is>
       </c>
-      <c r="E26" s="36" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="F26" s="36" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="G26" s="36" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="H26" s="38" t="n">
-        <v>0.2893414605806364</v>
-      </c>
-      <c r="I26" s="38" t="n">
-        <v>1.342348590487079</v>
-      </c>
-      <c r="J26" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="36" t="inlineStr">
-        <is>
-          <t>potential_impact: low confidence (0.29)</t>
-        </is>
-      </c>
-      <c r="L26" s="36" t="inlineStr"/>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J26" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" s="33" t="inlineStr"/>
+      <c r="L26" s="33" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="33" t="inlineStr">
@@ -2190,10 +2366,10 @@
         </is>
       </c>
       <c r="H27" s="35" t="n">
-        <v>0.993523868071281</v>
+        <v>0.95</v>
       </c>
       <c r="I27" s="35" t="n">
-        <v>0.993523868071281</v>
+        <v>0.95</v>
       </c>
       <c r="J27" s="33" t="b">
         <v>0</v>
@@ -2238,10 +2414,10 @@
         </is>
       </c>
       <c r="H28" s="35" t="n">
-        <v>0.6803313388383841</v>
+        <v>0.83</v>
       </c>
       <c r="I28" s="35" t="n">
-        <v>0.7658952561283315</v>
+        <v>0.86</v>
       </c>
       <c r="J28" s="33" t="b">
         <v>0</v>
@@ -2286,10 +2462,10 @@
         </is>
       </c>
       <c r="H29" s="35" t="n">
-        <v>0.9852695044791884</v>
+        <v>0.95</v>
       </c>
       <c r="I29" s="35" t="n">
-        <v>0.01473049552081164</v>
+        <v>0.05</v>
       </c>
       <c r="J29" s="33" t="b">
         <v>0</v>
@@ -2330,21 +2506,21 @@
       </c>
       <c r="G30" s="36" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H30" s="38" t="n">
-        <v>0.188075872547421</v>
+        <v>0.54</v>
       </c>
       <c r="I30" s="38" t="n">
-        <v>1.299708878369453</v>
+        <v>1.69</v>
       </c>
       <c r="J30" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K30" s="36" t="inlineStr">
         <is>
-          <t>load: low confidence (0.19)</t>
+          <t>load: low confidence (0.54)</t>
         </is>
       </c>
       <c r="L30" s="36" t="inlineStr"/>
@@ -2386,10 +2562,10 @@
         </is>
       </c>
       <c r="H31" s="35" t="n">
-        <v>0.8091260652766668</v>
+        <v>1</v>
       </c>
       <c r="I31" s="35" t="n">
-        <v>1.937812200817456</v>
+        <v>2</v>
       </c>
       <c r="J31" s="33" t="b">
         <v>0</v>
@@ -2434,17 +2610,17 @@
         </is>
       </c>
       <c r="H32" s="38" t="n">
-        <v>0.1934498910234053</v>
+        <v>0.52</v>
       </c>
       <c r="I32" s="38" t="n">
-        <v>1.417932638835096</v>
+        <v>1.32</v>
       </c>
       <c r="J32" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K32" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.19)</t>
+          <t>impact: low confidence (0.52)</t>
         </is>
       </c>
       <c r="L32" s="36" t="inlineStr"/>
@@ -2482,21 +2658,21 @@
       </c>
       <c r="G33" s="36" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H33" s="38" t="n">
-        <v>0.1714265267610506</v>
+        <v>0.25</v>
       </c>
       <c r="I33" s="38" t="n">
-        <v>1.337527379063873</v>
+        <v>1.5</v>
       </c>
       <c r="J33" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K33" s="36" t="inlineStr">
         <is>
-          <t>potential_impact: low confidence (0.17)</t>
+          <t>potential_impact: low confidence (0.25)</t>
         </is>
       </c>
       <c r="L33" s="36" t="inlineStr"/>
@@ -2538,10 +2714,10 @@
         </is>
       </c>
       <c r="H34" s="35" t="n">
-        <v>0.9972499411450706</v>
+        <v>0.99</v>
       </c>
       <c r="I34" s="35" t="n">
-        <v>0.9972499411450706</v>
+        <v>0.99</v>
       </c>
       <c r="J34" s="33" t="b">
         <v>0</v>
@@ -2586,10 +2762,10 @@
         </is>
       </c>
       <c r="H35" s="35" t="n">
-        <v>0.8431627582980868</v>
+        <v>1</v>
       </c>
       <c r="I35" s="35" t="n">
-        <v>1.943775069671376</v>
+        <v>2</v>
       </c>
       <c r="J35" s="33" t="b">
         <v>0</v>
@@ -2634,10 +2810,10 @@
         </is>
       </c>
       <c r="H36" s="35" t="n">
-        <v>0.9363398600629796</v>
+        <v>1</v>
       </c>
       <c r="I36" s="35" t="n">
-        <v>0.9784069191734092</v>
+        <v>1</v>
       </c>
       <c r="J36" s="33" t="b">
         <v>0</v>
@@ -2682,10 +2858,10 @@
         </is>
       </c>
       <c r="H37" s="35" t="n">
-        <v>0.9957133755759788</v>
+        <v>0.99</v>
       </c>
       <c r="I37" s="35" t="n">
-        <v>0.004286624424021187</v>
+        <v>0.01</v>
       </c>
       <c r="J37" s="33" t="b">
         <v>0</v>
@@ -2730,10 +2906,10 @@
         </is>
       </c>
       <c r="H38" s="35" t="n">
-        <v>0.9348095470889991</v>
+        <v>1</v>
       </c>
       <c r="I38" s="35" t="n">
-        <v>0.9944437539675687</v>
+        <v>1</v>
       </c>
       <c r="J38" s="33" t="b">
         <v>0</v>
@@ -2778,10 +2954,10 @@
         </is>
       </c>
       <c r="H39" s="35" t="n">
-        <v>0.9150701099900012</v>
+        <v>1</v>
       </c>
       <c r="I39" s="35" t="n">
-        <v>0.02285845930706045</v>
+        <v>0</v>
       </c>
       <c r="J39" s="33" t="b">
         <v>0</v>
@@ -2826,10 +3002,10 @@
         </is>
       </c>
       <c r="H40" s="35" t="n">
-        <v>0.954014606183754</v>
+        <v>1</v>
       </c>
       <c r="I40" s="35" t="n">
-        <v>0.009865682566864381</v>
+        <v>0</v>
       </c>
       <c r="J40" s="33" t="b">
         <v>0</v>
@@ -2874,10 +3050,10 @@
         </is>
       </c>
       <c r="H41" s="35" t="n">
-        <v>0.9293340218130992</v>
+        <v>0.96</v>
       </c>
       <c r="I41" s="35" t="n">
-        <v>0.01860644816057358</v>
+        <v>0.03</v>
       </c>
       <c r="J41" s="33" t="b">
         <v>0</v>
@@ -2922,10 +3098,10 @@
         </is>
       </c>
       <c r="H42" s="35" t="n">
-        <v>0.9947682918870171</v>
+        <v>0.99</v>
       </c>
       <c r="I42" s="35" t="n">
-        <v>0.00523170811298286</v>
+        <v>0.01</v>
       </c>
       <c r="J42" s="33" t="b">
         <v>0</v>
@@ -2970,10 +3146,10 @@
         </is>
       </c>
       <c r="H43" s="35" t="n">
-        <v>0.9531418933138464</v>
+        <v>1</v>
       </c>
       <c r="I43" s="35" t="n">
-        <v>0.01156392735957413</v>
+        <v>0</v>
       </c>
       <c r="J43" s="33" t="b">
         <v>0</v>
@@ -3025,12 +3201,12 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 3431, "output_tokens": 7}</t>
+          <t>{"input_tokens": 643, "output_tokens": 129}</t>
         </is>
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9403764383354369, "bearing": 0.023752584592859, "cavitation": 0.02777636530316554, "instrument": 0.002736962400376868, "other": 0.005357649368161494}, "confidence": 0.8195945775641966}, "containment": {"type": "noul", "noul": 0.7691154479779605}, "load": {"type": "score", "score": 1.1016859277791764, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.03030890919098518, "1": 0.8376962538388533, "2": 0.13199483697016162}, "confidence": 0.5252066897339631}, "urgency": {"type": "score", "score": 1.7441183295311746, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.025617318730848933, "1": 0.20464703300712783, "2": 0.7697356482620233}, "confidence": 0.4356639754842947}, "impact": {"type": "score", "score": 1.0995364152010518, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.09479898270390513, "1": 0.7108656193911379, "2": 0.19433539790495694}, "confidence": 0.28610038363270285}, "potential_impact": {"type": "score", "score": 1.5815300408496102, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.04895136691935876, "1": 0.3205672253116721, "2": 0.6304814077689691}, "confidence": 0.2688926828193108}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "instrument": 0.0, "bearing": 0.0, "other": 0.0, "seal": 1.0}}, "containment": {"type": "noul", "noul": 0.88}, "load": {"type": "score", "score": 1.51, "confidence": 0.26, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.04, "1": 0.41, "2": 0.55}}, "urgency": {"type": "score", "score": 1.99, "confidence": 0.98, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}, "impact": {"type": "score", "score": 1.12, "confidence": 0.82, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.88, "2": 0.12}}, "potential_impact": {"type": "score", "score": 1.78, "confidence": 0.67, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.22, "2": 0.78}}}</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3218,12 @@
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 3437, "output_tokens": 7}</t>
+          <t>{"input_tokens": 642, "output_tokens": 129}</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.00271844877009735, "bearing": 0.99356430421049, "cavitation": 0.0014845156733352789, "instrument": 0.0006423127261355957, "other": 0.0015904186199419271}, "confidence": 0.9707274126385984}, "containment": {"type": "noul", "noul": 0.01410409497066424}, "load": {"type": "score", "score": 0.9830735117434298, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.03050219630445108, "1": 0.9559220956476682, "2": 0.013575708047880834}, "confidence": 0.810750694954472}, "urgency": {"type": "score", "score": 0.023946606601512287, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.981450571740185, "1": 0.013152249918117795, "2": 0.005397178341697247}, "confidence": 0.9057681604539835}, "impact": {"type": "score", "score": 0.054618745563618024, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.9509405327056056, "1": 0.043500189025170735, "2": 0.005559278269223646}, "confidence": 0.8060517778980076}, "potential_impact": {"type": "score", "score": 0.9272016948488913, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.08743343556647779, "1": 0.897931434018153, "2": 0.01463513041536913}, "confidence": 0.6617906884831326}}</t>
+          <t>{"load": {"type": "score", "score": 1.02, "confidence": 0.96, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.0, "1": 0.98, "2": 0.02}}, "urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.99, "1": 0.01, "2": 0.0}}, "impact": {"type": "score", "score": 0.03, "confidence": 0.96, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.97, "1": 0.03, "2": 0.0}}, "potential_impact": {"type": "score", "score": 0.96, "confidence": 0.88, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.06, "1": 0.92, "2": 0.02}}, "failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "instrument": 0.0, "seal": 0.0, "other": 0.0, "bearing": 1.0}}, "containment": {"type": "noul", "noul": 0.01}}</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3235,12 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 4529, "output_tokens": 8}</t>
+          <t>{"input_tokens": 687, "output_tokens": 159}</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9680451306120793, "tube_leak": 0.023515279230748413, "flow_maldistribution": 0.005935079187159576, "control_valve": 0.0009338859656491551, "other": 0.001570625004363632}, "confidence": 0.8964189370932257}, "containment": {"type": "noul", "noul": 0.018963267962223727}, "load": {"type": "score", "score": 0.9234640502322689, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.10501361956542159, "1": 0.8665087106368881, "2": 0.028477669797690393}, "confidence": 0.5793208854661729}, "urgency": {"type": "score", "score": 0.2398700214389179, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.8066961046405768, "1": 0.14673776927992832, "2": 0.04656612607949479}, "confidence": 0.45594687897702346}, "impact": {"type": "score", "score": 0.7770780189312785, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.27090379744411325, "1": 0.681114386180495, "2": 0.04798181637539171}, "confidence": 0.30723458814913884}, "potential_impact": {"type": "score", "score": 0.48753602920894634, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.5430191923742405, "1": 0.4264255860425726, "2": 0.03055522158318688}, "confidence": 0.2703462680038269}, "cross_contamination": {"type": "noul", "noul": 0.0399715492664482}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "tube_leak": 0.0, "fouling": 1.0, "other": 0.0}}, "containment": {"type": "noul", "noul": 0.03}, "load": {"type": "score", "score": 1.19, "confidence": 0.0, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.35, "1": 0.12, "2": 0.53}}, "urgency": {"type": "score", "score": 0.95, "confidence": 0.29, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.26, "1": 0.53, "2": 0.21}}, "impact": {"type": "score", "score": 1.09, "confidence": 0.86, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.91, "2": 0.09}}, "potential_impact": {"type": "score", "score": 1.11, "confidence": 0.82, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.01, "1": 0.87, "2": 0.12}}, "cross_contamination": {"type": "noul", "noul": 0.15}}</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3252,12 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 4522, "output_tokens": 8}</t>
+          <t>{"input_tokens": 690, "output_tokens": 159}</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0012215421919611676, "tube_leak": 0.9960106591003453, "flow_maldistribution": 0.001772688409883248, "control_valve": 0.00026080847162997516, "other": 0.0007343018261804486}, "confidence": 0.980827621350109}, "containment": {"type": "noul", "noul": 0.17688143735879036}, "load": {"type": "score", "score": 1.0239897104907512, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.026435554656885116, "1": 0.9231391801954787, "2": 0.05042526514763627}, "confidence": 0.7082652363052141}, "urgency": {"type": "score", "score": 1.3312178477752035, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.028142554477525075, "1": 0.6124970432697464, "2": 0.3593604022527285}, "confidence": 0.30046737648488586}, "impact": {"type": "score", "score": 1.1397661347134012, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.07158432231093885, "1": 0.7170652206647211, "2": 0.21135045702434}, "confidence": 0.3120997517953533}, "potential_impact": {"type": "score", "score": 1.3423485904870789, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.03001426440708731, "1": 0.5976228806987464, "2": 0.37236285489416626}, "confidence": 0.28934146058063637}, "cross_contamination": {"type": "noul", "noul": 0.993523868071281}}</t>
+          <t>{"containment": {"type": "noul", "noul": 0.67}, "load": {"type": "score", "score": 1.09, "confidence": 0.84, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.01, "1": 0.89, "2": 0.1}}, "urgency": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "impact": {"type": "score", "score": 1.21, "confidence": 0.58, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.03, "1": 0.72, "2": 0.25}}, "potential_impact": {"type": "score", "score": 1.98, "confidence": 0.97, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.02, "2": 0.98}}, "cross_contamination": {"type": "noul", "noul": 0.95}, "failure_mode": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"tube_leak": 1.0, "control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "fouling": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -3093,12 +3269,12 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 5871, "output_tokens": 9}</t>
+          <t>{"input_tokens": 762, "output_tokens": 186}</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.7658952561283315, "weeping": 0.008919577166532836, "foaming": 0.21745773872133595, "fouling": 0.0013342903862147107, "reboiler_condenser": 0.0005000774452204862, "instrument": 0.005652697246225303, "other": 0.0002403629061388724}, "confidence": 0.6803313388383841}, "containment": {"type": "noul", "noul": 0.014730495520811644}, "load": {"type": "score", "score": 1.2997088783694535, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.07551032772657393, "1": 0.5492704661773986, "2": 0.37521920609602744}, "confidence": 0.18807587254742097}, "urgency": {"type": "score", "score": 1.937812200817456, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.018368378254247305, "1": 0.02545104267404942, "2": 0.9561805790717033}, "confidence": 0.8091260652766668}, "impact": {"type": "score", "score": 1.4179326388350961, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.06393700472216769, "1": 0.45419335172056846, "2": 0.4818696435572638}, "confidence": 0.19344989102340526}, "potential_impact": {"type": "score", "score": 1.3375273790638733, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.07889131789555637, "1": 0.5046899851450138, "2": 0.41641869695942973}, "confidence": 0.17142652676105063}, "off_spec": {"type": "noul", "noul": 0.9972499411450706}, "stability": {"type": "score", "score": 1.943775069671376, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.021825125227392647, "1": 0.01257467987383881, "2": 0.9656001948987686}, "confidence": 0.8431627582980868}}</t>
+          <t>{"urgency": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "impact": {"type": "score", "score": 1.32, "confidence": 0.52, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.68, "2": 0.32}}, "potential_impact": {"type": "score", "score": 1.5, "confidence": 0.25, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.49, "2": 0.51}}, "off_spec": {"type": "noul", "noul": 0.99}, "stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "failure_mode": {"type": "choice", "choice": "flooding", "confidence": 0.83, "probabilities": {"other": 0.03, "flooding": 0.86, "instrument": 0.07, "fouling": 0.0, "foaming": 0.04, "weeping": 0.0, "reboiler_condenser": 0.0}}, "containment": {"type": "noul", "noul": 0.05}, "load": {"type": "score", "score": 1.69, "confidence": 0.54, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.01, "1": 0.28, "2": 0.71}}}</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3286,12 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 5855, "output_tokens": 9}</t>
+          <t>{"input_tokens": 760, "output_tokens": 184}</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.015310150196454458, "weeping": 0.003729595689138417, "foaming": 0.0009179110234264862, "fouling": 0.001424967860907713, "reboiler_condenser": 0.00012948811605478457, "instrument": 8.09679406090723e-05, "other": 0.9784069191734092}, "confidence": 0.9363398600629796}, "containment": {"type": "noul", "noul": 0.004286624424021187}, "load": {"type": "score", "score": 0.9944437539675687, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.008743324738875088, "1": 0.988069596554681, "2": 0.003187078706443858}, "confidence": 0.9348095470889991}, "urgency": {"type": "score", "score": 0.02285845930706045, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9839212234793119, "1": 0.009299093734315722, "2": 0.006779682786372365}, "confidence": 0.9150701099900012}, "impact": {"type": "score", "score": 0.00986568256686438, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.992105930482838, "1": 0.005922456467459379, "2": 0.001971613049702501}, "confidence": 0.954014606183754}, "potential_impact": {"type": "score", "score": 0.01860644816057358, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.9871339026939872, "1": 0.0071257464514525295, "2": 0.005740350854560525}, "confidence": 0.9293340218130992}, "off_spec": {"type": "noul", "noul": 0.00523170811298286}, "stability": {"type": "score", "score": 0.011563927359574127, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.9921165372801404, "1": 0.004202998080145225, "2": 0.003680464639714451}, "confidence": 0.9531418933138464}}</t>
+          <t>{"containment": {"type": "noul", "noul": 0.01}, "load": {"type": "score", "score": 1.0, "confidence": 1.0, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.0, "1": 1.0, "2": 0.0}}, "urgency": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "impact": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "potential_impact": {"type": "score", "score": 0.03, "confidence": 0.96, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.98, "1": 0.02, "2": 0.0}}, "off_spec": {"type": "noul", "noul": 0.01}, "stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "failure_mode": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"instrument": 0.0, "other": 1.0, "foaming": 0.0, "fouling": 0.0, "reboiler_condenser": 0.0, "flooding": 0.0, "weeping": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>0.881</v>
+        <v>0.972</v>
       </c>
       <c r="H2" s="33" t="n">
         <v>6</v>
@@ -3247,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>0.881</v>
+        <v>0.972</v>
       </c>
       <c r="L2" s="33" t="inlineStr"/>
     </row>
@@ -3277,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>0.923</v>
+        <v>0.908</v>
       </c>
       <c r="H3" s="33" t="n">
         <v>2</v>
@@ -3289,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>0.878</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="L3" s="33" t="inlineStr"/>
     </row>
@@ -3319,7 +3495,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>0.624</v>
+        <v>0.6</v>
       </c>
       <c r="H4" s="33" t="n">
         <v>0</v>
@@ -3354,10 +3530,10 @@
         <v>6</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>0.637</v>
+        <v>0.877</v>
       </c>
       <c r="H5" s="33" t="n">
         <v>2</v>
@@ -3369,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>0.671</v>
+        <v>0.985</v>
       </c>
       <c r="L5" s="33" t="inlineStr"/>
     </row>
@@ -3396,10 +3572,10 @@
         <v>6</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0.476</v>
+        <v>0.79</v>
       </c>
       <c r="H6" s="33" t="n">
         <v>2</v>
@@ -3411,10 +3587,10 @@
         <v>0.5</v>
       </c>
       <c r="K6" s="33" t="n">
-        <v>0.307</v>
+        <v>0.86</v>
       </c>
       <c r="L6" s="33" t="n">
-        <v>0.312</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="7">
@@ -3440,10 +3616,10 @@
         <v>6</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.432</v>
+        <v>0.758</v>
       </c>
       <c r="H7" s="33" t="n">
         <v>0</v>
@@ -3481,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>0.977</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="33" t="n">
         <v>2</v>
@@ -3493,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="33" t="n">
-        <v>0.977</v>
+        <v>0.9</v>
       </c>
       <c r="L8" s="33" t="inlineStr"/>
     </row>
@@ -3523,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>0.996</v>
+        <v>0.99</v>
       </c>
       <c r="H9" s="33" t="n">
         <v>2</v>
@@ -3535,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="33" t="n">
-        <v>0.996</v>
+        <v>0.99</v>
       </c>
       <c r="L9" s="33" t="inlineStr"/>
     </row>
@@ -3565,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
       <c r="H10" s="33" t="n">
         <v>2</v>
@@ -3577,7 +3753,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="33" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
       <c r="L10" s="33" t="inlineStr"/>
     </row>
@@ -3619,7 +3795,7 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>20260930_192034</t>
+          <t>20260930_192615</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3819,7 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>nimble</t>
+          <t>jev</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3831,7 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>nimble</t>
+          <t>jev-1.13.0</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3843,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>http://localhost:11434</t>
+          <t>https://api.typesafe.ai</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3855,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>0.35.0</t>
+          <t>remote:https://api.typesafe.ai</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3879,7 @@
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3939,7 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3951,7 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_192034.jsonl</t>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_jev_20260930_192615.jsonl</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3963,7 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>4184</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3975,7 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>946</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3987,7 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>5130</t>
         </is>
       </c>
     </row>
@@ -3835,7 +4011,7 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>output_nimble_Results, output_nimble_Raw, output_nimble_Summary, output_nimble_Run_info</t>
+          <t>output_jev_Results, output_jev_Raw, output_jev_Summary, output_jev_Run_info</t>
         </is>
       </c>
     </row>
@@ -3945,7 +4121,7 @@
         <v>0.7691154479779605</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="H2" s="33" t="inlineStr">
         <is>
@@ -4002,32 +4178,38 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr"/>
-      <c r="E4" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="39" t="n">
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="33" t="n">
         <v>0.2861003836327028</v>
       </c>
-      <c r="G4" s="39" t="n"/>
-      <c r="H4" s="39" t="inlineStr"/>
-      <c r="I4" s="39" t="inlineStr"/>
-      <c r="J4" s="39" t="inlineStr"/>
+      <c r="G4" s="33" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H4" s="33" t="inlineStr"/>
+      <c r="I4" s="33" t="inlineStr"/>
+      <c r="J4" s="33" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="39" t="inlineStr">
@@ -4045,45 +4227,57 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="D5" s="39" t="inlineStr"/>
+      <c r="D5" s="39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="E5" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="39" t="n">
         <v>0.5252066897339631</v>
       </c>
-      <c r="G5" s="39" t="n"/>
+      <c r="G5" s="39" t="n">
+        <v>0.26</v>
+      </c>
       <c r="H5" s="39" t="inlineStr"/>
       <c r="I5" s="39" t="inlineStr"/>
       <c r="J5" s="39" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr"/>
-      <c r="E6" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="39" t="n">
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="33" t="n">
         <v>0.2688926828193108</v>
       </c>
-      <c r="G6" s="39" t="n"/>
-      <c r="H6" s="39" t="inlineStr"/>
-      <c r="I6" s="39" t="inlineStr"/>
-      <c r="J6" s="39" t="inlineStr"/>
+      <c r="G6" s="33" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H6" s="33" t="inlineStr"/>
+      <c r="I6" s="33" t="inlineStr"/>
+      <c r="J6" s="33" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
@@ -4113,7 +4307,7 @@
         <v>0.4356639754842947</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="H7" s="33" t="inlineStr">
         <is>
@@ -4212,88 +4406,106 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr"/>
-      <c r="E10" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="39" t="n">
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="33" t="n">
         <v>0.8060517778980076</v>
       </c>
-      <c r="G10" s="39" t="n"/>
-      <c r="H10" s="39" t="inlineStr"/>
-      <c r="I10" s="39" t="inlineStr"/>
-      <c r="J10" s="39" t="inlineStr"/>
+      <c r="G10" s="33" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H10" s="33" t="inlineStr"/>
+      <c r="I10" s="33" t="inlineStr"/>
+      <c r="J10" s="33" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>load</t>
         </is>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="D11" s="39" t="inlineStr"/>
-      <c r="E11" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="39" t="n">
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="33" t="n">
         <v>0.8107506949544721</v>
       </c>
-      <c r="G11" s="39" t="n"/>
-      <c r="H11" s="39" t="inlineStr"/>
-      <c r="I11" s="39" t="inlineStr"/>
-      <c r="J11" s="39" t="inlineStr"/>
+      <c r="G11" s="33" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H11" s="33" t="inlineStr"/>
+      <c r="I11" s="33" t="inlineStr"/>
+      <c r="J11" s="33" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="C12" s="39" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
       </c>
-      <c r="D12" s="39" t="inlineStr"/>
-      <c r="E12" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39" t="n">
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="33" t="n">
         <v>0.6617906884831326</v>
       </c>
-      <c r="G12" s="39" t="n"/>
-      <c r="H12" s="39" t="inlineStr"/>
-      <c r="I12" s="39" t="inlineStr"/>
-      <c r="J12" s="39" t="inlineStr"/>
+      <c r="G12" s="33" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H12" s="33" t="inlineStr"/>
+      <c r="I12" s="33" t="inlineStr"/>
+      <c r="J12" s="33" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
@@ -4338,32 +4550,38 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="D14" s="39" t="inlineStr"/>
-      <c r="E14" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="39" t="n">
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="33" t="n">
         <v>0.9810367320377763</v>
       </c>
-      <c r="G14" s="39" t="n"/>
-      <c r="H14" s="39" t="inlineStr"/>
-      <c r="I14" s="39" t="inlineStr"/>
-      <c r="J14" s="39" t="inlineStr"/>
+      <c r="G14" s="33" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H14" s="33" t="inlineStr"/>
+      <c r="I14" s="33" t="inlineStr"/>
+      <c r="J14" s="33" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
@@ -4393,7 +4611,7 @@
         <v>0.9600284507335518</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="H15" s="33" t="inlineStr">
         <is>
@@ -4477,7 +4695,7 @@
         <v>0.3072345881491388</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
@@ -4492,32 +4710,38 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>load</t>
         </is>
       </c>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="D18" s="39" t="inlineStr"/>
-      <c r="E18" s="39" t="b">
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="33" t="n">
+        <v>0.5793208854661729</v>
+      </c>
+      <c r="G18" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="39" t="n">
-        <v>0.5793208854661729</v>
-      </c>
-      <c r="G18" s="39" t="n"/>
-      <c r="H18" s="39" t="inlineStr"/>
-      <c r="I18" s="39" t="inlineStr"/>
-      <c r="J18" s="39" t="inlineStr"/>
+      <c r="H18" s="33" t="inlineStr"/>
+      <c r="I18" s="33" t="inlineStr"/>
+      <c r="J18" s="33" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="39" t="inlineStr">
@@ -4535,14 +4759,20 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D19" s="39" t="inlineStr"/>
+      <c r="D19" s="39" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
       <c r="E19" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F19" s="39" t="n">
         <v>0.2703462680038269</v>
       </c>
-      <c r="G19" s="39" t="n"/>
+      <c r="G19" s="39" t="n">
+        <v>0.82</v>
+      </c>
       <c r="H19" s="39" t="inlineStr"/>
       <c r="I19" s="39" t="inlineStr"/>
       <c r="J19" s="39" t="inlineStr"/>
@@ -4563,14 +4793,20 @@
           <t>routine</t>
         </is>
       </c>
-      <c r="D20" s="39" t="inlineStr"/>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>soon</t>
+        </is>
+      </c>
       <c r="E20" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F20" s="39" t="n">
         <v>0.4559468789770235</v>
       </c>
-      <c r="G20" s="39" t="n"/>
+      <c r="G20" s="39" t="n">
+        <v>0.29</v>
+      </c>
       <c r="H20" s="39" t="inlineStr"/>
       <c r="I20" s="39" t="inlineStr"/>
       <c r="J20" s="39" t="inlineStr"/>
@@ -4591,14 +4827,20 @@
           <t>false</t>
         </is>
       </c>
-      <c r="D21" s="39" t="inlineStr"/>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="E21" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F21" s="39" t="n">
         <v>0.8231185626412096</v>
       </c>
-      <c r="G21" s="39" t="n"/>
+      <c r="G21" s="39" t="n">
+        <v>0.67</v>
+      </c>
       <c r="H21" s="39" t="inlineStr"/>
       <c r="I21" s="39" t="inlineStr"/>
       <c r="J21" s="39" t="inlineStr"/>
@@ -4631,7 +4873,7 @@
         <v>0.993523868071281</v>
       </c>
       <c r="G22" s="33" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H22" s="33" t="inlineStr">
         <is>
@@ -4715,7 +4957,7 @@
         <v>0.3120997517953533</v>
       </c>
       <c r="G24" s="33" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H24" s="33" t="inlineStr">
         <is>
@@ -4730,32 +4972,38 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>load</t>
         </is>
       </c>
-      <c r="C25" s="39" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="D25" s="39" t="inlineStr"/>
-      <c r="E25" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="39" t="n">
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E25" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="33" t="n">
         <v>0.7082652363052141</v>
       </c>
-      <c r="G25" s="39" t="n"/>
-      <c r="H25" s="39" t="inlineStr"/>
-      <c r="I25" s="39" t="inlineStr"/>
-      <c r="J25" s="39" t="inlineStr"/>
+      <c r="G25" s="33" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H25" s="33" t="inlineStr"/>
+      <c r="I25" s="33" t="inlineStr"/>
+      <c r="J25" s="33" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="39" t="inlineStr">
@@ -4773,14 +5021,20 @@
           <t>moderate</t>
         </is>
       </c>
-      <c r="D26" s="39" t="inlineStr"/>
+      <c r="D26" s="39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="E26" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F26" s="39" t="n">
         <v>0.2893414605806364</v>
       </c>
-      <c r="G26" s="39" t="n"/>
+      <c r="G26" s="39" t="n">
+        <v>0.97</v>
+      </c>
       <c r="H26" s="39" t="inlineStr"/>
       <c r="I26" s="39" t="inlineStr"/>
       <c r="J26" s="39" t="inlineStr"/>
@@ -4801,45 +5055,57 @@
           <t>soon</t>
         </is>
       </c>
-      <c r="D27" s="39" t="inlineStr"/>
+      <c r="D27" s="39" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
       <c r="E27" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F27" s="39" t="n">
         <v>0.3004673764848859</v>
       </c>
-      <c r="G27" s="39" t="n"/>
+      <c r="G27" s="39" t="n">
+        <v>1</v>
+      </c>
       <c r="H27" s="39" t="inlineStr"/>
       <c r="I27" s="39" t="inlineStr"/>
       <c r="J27" s="39" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="C28" s="39" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="D28" s="39" t="inlineStr"/>
-      <c r="E28" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="39" t="n">
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="33" t="n">
         <v>0.9852695044791884</v>
       </c>
-      <c r="G28" s="39" t="n"/>
-      <c r="H28" s="39" t="inlineStr"/>
-      <c r="I28" s="39" t="inlineStr"/>
-      <c r="J28" s="39" t="inlineStr"/>
+      <c r="G28" s="33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H28" s="33" t="inlineStr"/>
+      <c r="I28" s="33" t="inlineStr"/>
+      <c r="J28" s="33" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="33" t="inlineStr">
@@ -4869,7 +5135,7 @@
         <v>0.6803313388383841</v>
       </c>
       <c r="G29" s="33" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="H29" s="33" t="inlineStr">
         <is>
@@ -4884,32 +5150,38 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="C30" s="39" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="D30" s="39" t="inlineStr"/>
-      <c r="E30" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="39" t="n">
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="33" t="n">
         <v>0.1934498910234053</v>
       </c>
-      <c r="G30" s="39" t="n"/>
-      <c r="H30" s="39" t="inlineStr"/>
-      <c r="I30" s="39" t="inlineStr"/>
-      <c r="J30" s="39" t="inlineStr"/>
+      <c r="G30" s="33" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H30" s="33" t="inlineStr"/>
+      <c r="I30" s="33" t="inlineStr"/>
+      <c r="J30" s="33" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="39" t="inlineStr">
@@ -4927,14 +5199,20 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="D31" s="39" t="inlineStr"/>
+      <c r="D31" s="39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="E31" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F31" s="39" t="n">
         <v>0.188075872547421</v>
       </c>
-      <c r="G31" s="39" t="n"/>
+      <c r="G31" s="39" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H31" s="39" t="inlineStr"/>
       <c r="I31" s="39" t="inlineStr"/>
       <c r="J31" s="39" t="inlineStr"/>
@@ -4997,14 +5275,20 @@
           <t>moderate</t>
         </is>
       </c>
-      <c r="D33" s="39" t="inlineStr"/>
+      <c r="D33" s="39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="E33" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F33" s="39" t="n">
         <v>0.1714265267610506</v>
       </c>
-      <c r="G33" s="39" t="n"/>
+      <c r="G33" s="39" t="n">
+        <v>0.25</v>
+      </c>
       <c r="H33" s="39" t="inlineStr"/>
       <c r="I33" s="39" t="inlineStr"/>
       <c r="J33" s="39" t="inlineStr"/>
@@ -5052,60 +5336,72 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B35" s="39" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="C35" s="39" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>immediate</t>
         </is>
       </c>
-      <c r="D35" s="39" t="inlineStr"/>
-      <c r="E35" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" s="39" t="n">
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="E35" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="33" t="n">
         <v>0.8091260652766668</v>
       </c>
-      <c r="G35" s="39" t="n"/>
-      <c r="H35" s="39" t="inlineStr"/>
-      <c r="I35" s="39" t="inlineStr"/>
-      <c r="J35" s="39" t="inlineStr"/>
+      <c r="G35" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="33" t="inlineStr"/>
+      <c r="I35" s="33" t="inlineStr"/>
+      <c r="J35" s="33" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" s="33" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="C36" s="39" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="D36" s="39" t="inlineStr"/>
-      <c r="E36" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" s="39" t="n">
+      <c r="D36" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="33" t="n">
         <v>0.9957133755759788</v>
       </c>
-      <c r="G36" s="39" t="n"/>
-      <c r="H36" s="39" t="inlineStr"/>
-      <c r="I36" s="39" t="inlineStr"/>
-      <c r="J36" s="39" t="inlineStr"/>
+      <c r="G36" s="33" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H36" s="33" t="inlineStr"/>
+      <c r="I36" s="33" t="inlineStr"/>
+      <c r="J36" s="33" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="33" t="inlineStr">
@@ -5150,60 +5446,72 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="33" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="C38" s="39" t="inlineStr">
+      <c r="C38" s="33" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="D38" s="39" t="inlineStr"/>
-      <c r="E38" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" s="39" t="n">
+      <c r="D38" s="33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" s="33" t="n">
         <v>0.954014606183754</v>
       </c>
-      <c r="G38" s="39" t="n"/>
-      <c r="H38" s="39" t="inlineStr"/>
-      <c r="I38" s="39" t="inlineStr"/>
-      <c r="J38" s="39" t="inlineStr"/>
+      <c r="G38" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="33" t="inlineStr"/>
+      <c r="I38" s="33" t="inlineStr"/>
+      <c r="J38" s="33" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>load</t>
         </is>
       </c>
-      <c r="C39" s="39" t="inlineStr">
+      <c r="C39" s="33" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="D39" s="39" t="inlineStr"/>
-      <c r="E39" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="39" t="n">
+      <c r="D39" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="33" t="n">
         <v>0.9348095470889991</v>
       </c>
-      <c r="G39" s="39" t="n"/>
-      <c r="H39" s="39" t="inlineStr"/>
-      <c r="I39" s="39" t="inlineStr"/>
-      <c r="J39" s="39" t="inlineStr"/>
+      <c r="G39" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="33" t="inlineStr"/>
+      <c r="I39" s="33" t="inlineStr"/>
+      <c r="J39" s="33" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="33" t="inlineStr">
@@ -5248,32 +5556,38 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="A41" s="33" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B41" s="39" t="inlineStr">
+      <c r="B41" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="C41" s="39" t="inlineStr">
+      <c r="C41" s="33" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="D41" s="39" t="inlineStr"/>
-      <c r="E41" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="39" t="n">
+      <c r="D41" s="33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E41" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="33" t="n">
         <v>0.9293340218130992</v>
       </c>
-      <c r="G41" s="39" t="n"/>
-      <c r="H41" s="39" t="inlineStr"/>
-      <c r="I41" s="39" t="inlineStr"/>
-      <c r="J41" s="39" t="inlineStr"/>
+      <c r="G41" s="33" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H41" s="33" t="inlineStr"/>
+      <c r="I41" s="33" t="inlineStr"/>
+      <c r="J41" s="33" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
@@ -5318,32 +5632,38 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B43" s="39" t="inlineStr">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="C43" s="39" t="inlineStr">
+      <c r="C43" s="33" t="inlineStr">
         <is>
           <t>routine</t>
         </is>
       </c>
-      <c r="D43" s="39" t="inlineStr"/>
-      <c r="E43" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="39" t="n">
+      <c r="D43" s="33" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="E43" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="33" t="n">
         <v>0.9150701099900012</v>
       </c>
-      <c r="G43" s="39" t="n"/>
-      <c r="H43" s="39" t="inlineStr"/>
-      <c r="I43" s="39" t="inlineStr"/>
-      <c r="J43" s="39" t="inlineStr"/>
+      <c r="G43" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="33" t="inlineStr"/>
+      <c r="I43" s="33" t="inlineStr"/>
+      <c r="J43" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8069,7 +8389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="20" min="1" max="1"/>
@@ -8185,10 +8505,10 @@
         </is>
       </c>
       <c r="H2" s="35" t="n">
-        <v>1</v>
+        <v>0.8195945775641966</v>
       </c>
       <c r="I2" s="35" t="n">
-        <v>1</v>
+        <v>0.9403764383354369</v>
       </c>
       <c r="J2" s="33" t="b">
         <v>0</v>
@@ -8233,10 +8553,10 @@
         </is>
       </c>
       <c r="H3" s="35" t="n">
-        <v>0.89</v>
+        <v>0.7691154479779605</v>
       </c>
       <c r="I3" s="35" t="n">
-        <v>0.89</v>
+        <v>0.7691154479779605</v>
       </c>
       <c r="J3" s="33" t="b">
         <v>0</v>
@@ -8245,52 +8565,56 @@
       <c r="L3" s="33" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="F4" s="33" t="inlineStr">
-        <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="G4" s="33" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
-      <c r="H4" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I4" s="35" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="J4" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="33" t="inlineStr"/>
-      <c r="L4" s="33" t="inlineStr"/>
+      <c r="E4" s="36" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="F4" s="36" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G4" s="36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H4" s="38" t="n">
+        <v>0.5252066897339631</v>
+      </c>
+      <c r="I4" s="38" t="n">
+        <v>1.101685927779176</v>
+      </c>
+      <c r="J4" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="36" t="inlineStr">
+        <is>
+          <t>load: low confidence (0.53)</t>
+        </is>
+      </c>
+      <c r="L4" s="36" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
@@ -8315,122 +8639,138 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="H5" s="38" t="n">
+        <v>0.4356639754842947</v>
+      </c>
+      <c r="I5" s="38" t="n">
+        <v>1.744118329531175</v>
+      </c>
+      <c r="J5" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="36" t="inlineStr">
+        <is>
+          <t>urgency: low confidence (0.44)</t>
+        </is>
+      </c>
+      <c r="L5" s="36" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>P-101A</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr"/>
-      <c r="H5" s="36" t="n"/>
-      <c r="I5" s="36" t="n"/>
-      <c r="J5" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L5" s="36" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>0.2861003836327028</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>1.099536415201052</v>
+      </c>
+      <c r="J6" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="36" t="inlineStr">
+        <is>
+          <t>impact: low confidence (0.29)</t>
+        </is>
+      </c>
+      <c r="L6" s="36" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>P-114</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t>failure_mode</t>
-        </is>
-      </c>
-      <c r="F6" s="33" t="inlineStr">
-        <is>
-          <t>Failure mode</t>
-        </is>
-      </c>
-      <c r="G6" s="33" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="H6" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="33" t="inlineStr"/>
-      <c r="L6" s="33" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>R002</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>Pump</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>P-114</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>containment</t>
-        </is>
-      </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>Containment</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H7" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I7" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J7" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="33" t="inlineStr"/>
-      <c r="L7" s="33" t="inlineStr"/>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>P-101A</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H7" s="38" t="n">
+        <v>0.2688926828193108</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <v>1.58153004084961</v>
+      </c>
+      <c r="J7" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.27)</t>
+        </is>
+      </c>
+      <c r="L7" s="36" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
@@ -8455,24 +8795,24 @@
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>failure_mode</t>
         </is>
       </c>
       <c r="F8" s="33" t="inlineStr">
         <is>
-          <t>Urgency</t>
+          <t>Failure mode</t>
         </is>
       </c>
       <c r="G8" s="33" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="H8" s="35" t="n">
-        <v>0.99</v>
+        <v>0.9707274126385984</v>
       </c>
       <c r="I8" s="35" t="n">
-        <v>0.01</v>
+        <v>0.99356430421049</v>
       </c>
       <c r="J8" s="33" t="b">
         <v>0</v>
@@ -8481,90 +8821,94 @@
       <c r="L8" s="33" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>P-114</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="F9" s="36" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="G9" s="36" t="inlineStr"/>
-      <c r="H9" s="36" t="n"/>
-      <c r="I9" s="36" t="n"/>
-      <c r="J9" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L9" s="36" t="inlineStr"/>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>0.9858959050293358</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>0.01410409497066424</v>
+      </c>
+      <c r="J9" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="33" t="inlineStr"/>
+      <c r="L9" s="33" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>Heat Exchanger</t>
+          <t>Pump</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>E-205</t>
+          <t>P-114</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
         </is>
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
-          <t>failure_mode</t>
+          <t>load</t>
         </is>
       </c>
       <c r="F10" s="33" t="inlineStr">
         <is>
-          <t>Failure mode</t>
+          <t>Load</t>
         </is>
       </c>
       <c r="G10" s="33" t="inlineStr">
         <is>
-          <t>fouling</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="H10" s="35" t="n">
-        <v>1</v>
+        <v>0.8107506949544721</v>
       </c>
       <c r="I10" s="35" t="n">
-        <v>1</v>
+        <v>0.9830735117434298</v>
       </c>
       <c r="J10" s="33" t="b">
         <v>0</v>
@@ -8573,134 +8917,142 @@
       <c r="L10" s="33" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>E-205</t>
-        </is>
-      </c>
-      <c r="D11" s="37" t="inlineStr">
-        <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>containment</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>Containment</t>
-        </is>
-      </c>
-      <c r="G11" s="36" t="inlineStr"/>
-      <c r="H11" s="36" t="n"/>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L11" s="36" t="inlineStr"/>
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>P-114</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>0.9057681604539835</v>
+      </c>
+      <c r="I11" s="35" t="n">
+        <v>0.02394660660151229</v>
+      </c>
+      <c r="J11" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="33" t="inlineStr"/>
+      <c r="L11" s="33" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
-        <is>
-          <t>R003</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>E-205</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="inlineStr">
-        <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="inlineStr">
-        <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="G12" s="36" t="inlineStr"/>
-      <c r="H12" s="36" t="n"/>
-      <c r="I12" s="36" t="n"/>
-      <c r="J12" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L12" s="36" t="inlineStr"/>
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>P-114</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G12" s="33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>0.8060517778980076</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>0.05461874556361802</v>
+      </c>
+      <c r="J12" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="33" t="inlineStr"/>
+      <c r="L12" s="33" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>Heat Exchanger</t>
+          <t>Pump</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>E-205</t>
+          <t>P-114</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+          <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>potential_impact</t>
         </is>
       </c>
       <c r="F13" s="33" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Potential impact</t>
         </is>
       </c>
       <c r="G13" s="33" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="H13" s="35" t="n">
-        <v>0.84</v>
+        <v>0.6617906884831326</v>
       </c>
       <c r="I13" s="35" t="n">
-        <v>1.1</v>
+        <v>0.9272016948488913</v>
       </c>
       <c r="J13" s="33" t="b">
         <v>0</v>
@@ -8731,24 +9083,24 @@
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
-          <t>cross_contamination</t>
+          <t>failure_mode</t>
         </is>
       </c>
       <c r="F14" s="33" t="inlineStr">
         <is>
-          <t>Cross-contamination</t>
+          <t>Failure mode</t>
         </is>
       </c>
       <c r="G14" s="33" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>fouling</t>
         </is>
       </c>
       <c r="H14" s="35" t="n">
-        <v>0.86</v>
+        <v>0.8964189370932257</v>
       </c>
       <c r="I14" s="35" t="n">
-        <v>0.14</v>
+        <v>0.9680451306120793</v>
       </c>
       <c r="J14" s="33" t="b">
         <v>0</v>
@@ -8759,7 +9111,7 @@
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
@@ -8769,34 +9121,34 @@
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>E-310</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
-          <t>failure_mode</t>
+          <t>containment</t>
         </is>
       </c>
       <c r="F15" s="33" t="inlineStr">
         <is>
-          <t>Failure mode</t>
+          <t>Containment</t>
         </is>
       </c>
       <c r="G15" s="33" t="inlineStr">
         <is>
-          <t>tube_leak</t>
+          <t>false</t>
         </is>
       </c>
       <c r="H15" s="35" t="n">
-        <v>1</v>
+        <v>0.9810367320377763</v>
       </c>
       <c r="I15" s="35" t="n">
-        <v>1</v>
+        <v>0.01896326796222373</v>
       </c>
       <c r="J15" s="33" t="b">
         <v>0</v>
@@ -8807,7 +9159,7 @@
     <row r="16">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B16" s="36" t="inlineStr">
@@ -8817,33 +9169,41 @@
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>E-310</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D16" s="37" t="inlineStr">
         <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E16" s="36" t="inlineStr">
         <is>
-          <t>containment</t>
+          <t>load</t>
         </is>
       </c>
       <c r="F16" s="36" t="inlineStr">
         <is>
-          <t>Containment</t>
-        </is>
-      </c>
-      <c r="G16" s="36" t="inlineStr"/>
-      <c r="H16" s="36" t="n"/>
-      <c r="I16" s="36" t="n"/>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G16" s="36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>0.5793208854661729</v>
+      </c>
+      <c r="I16" s="38" t="n">
+        <v>0.9234640502322689</v>
+      </c>
       <c r="J16" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
-          <t>no answer</t>
+          <t>load: low confidence (0.58)</t>
         </is>
       </c>
       <c r="L16" s="36" t="inlineStr"/>
@@ -8851,7 +9211,7 @@
     <row r="17">
       <c r="A17" s="36" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B17" s="36" t="inlineStr">
@@ -8861,12 +9221,12 @@
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>E-310</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D17" s="37" t="inlineStr">
         <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E17" s="36" t="inlineStr">
@@ -8879,15 +9239,23 @@
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G17" s="36" t="inlineStr"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
+      <c r="G17" s="36" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="H17" s="38" t="n">
+        <v>0.4559468789770235</v>
+      </c>
+      <c r="I17" s="38" t="n">
+        <v>0.2398700214389179</v>
+      </c>
       <c r="J17" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
-          <t>no answer</t>
+          <t>urgency: low confidence (0.46)</t>
         </is>
       </c>
       <c r="L17" s="36" t="inlineStr"/>
@@ -8895,7 +9263,7 @@
     <row r="18">
       <c r="A18" s="36" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B18" s="36" t="inlineStr">
@@ -8905,12 +9273,12 @@
       </c>
       <c r="C18" s="36" t="inlineStr">
         <is>
-          <t>E-310</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D18" s="37" t="inlineStr">
         <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E18" s="36" t="inlineStr">
@@ -8929,110 +9297,114 @@
         </is>
       </c>
       <c r="H18" s="38" t="n">
-        <v>0.49</v>
+        <v>0.3072345881491388</v>
       </c>
       <c r="I18" s="38" t="n">
-        <v>1.25</v>
+        <v>0.7770780189312785</v>
       </c>
       <c r="J18" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.49)</t>
+          <t>impact: low confidence (0.31)</t>
         </is>
       </c>
       <c r="L18" s="36" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C19" s="33" t="inlineStr">
-        <is>
-          <t>E-310</t>
-        </is>
-      </c>
-      <c r="D19" s="34" t="inlineStr">
-        <is>
-          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
-        </is>
-      </c>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>cross_contamination</t>
-        </is>
-      </c>
-      <c r="F19" s="33" t="inlineStr">
-        <is>
-          <t>Cross-contamination</t>
-        </is>
-      </c>
-      <c r="G19" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I19" s="35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J19" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="33" t="inlineStr"/>
-      <c r="L19" s="33" t="inlineStr"/>
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>E-205</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F19" s="36" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H19" s="38" t="n">
+        <v>0.2703462680038269</v>
+      </c>
+      <c r="I19" s="38" t="n">
+        <v>0.4875360292089463</v>
+      </c>
+      <c r="J19" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.27)</t>
+        </is>
+      </c>
+      <c r="L19" s="36" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="33" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>Distillation Column</t>
+          <t>Heat Exchanger</t>
         </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>C-301</t>
+          <t>E-205</t>
         </is>
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+          <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
-          <t>failure_mode</t>
+          <t>cross_contamination</t>
         </is>
       </c>
       <c r="F20" s="33" t="inlineStr">
         <is>
-          <t>Failure mode</t>
+          <t>Cross-contamination</t>
         </is>
       </c>
       <c r="G20" s="33" t="inlineStr">
         <is>
-          <t>flooding</t>
+          <t>false</t>
         </is>
       </c>
       <c r="H20" s="35" t="n">
-        <v>0.84</v>
+        <v>0.9600284507335518</v>
       </c>
       <c r="I20" s="35" t="n">
-        <v>0.87</v>
+        <v>0.0399715492664482</v>
       </c>
       <c r="J20" s="33" t="b">
         <v>0</v>
@@ -9041,465 +9413,505 @@
       <c r="L20" s="33" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>failure_mode</t>
+        </is>
+      </c>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="inlineStr">
+        <is>
+          <t>tube_leak</t>
+        </is>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>0.980827621350109</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>0.9960106591003453</v>
+      </c>
+      <c r="J21" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="33" t="inlineStr"/>
+      <c r="L21" s="33" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>0.8231185626412096</v>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>0.1768814373587904</v>
+      </c>
+      <c r="J22" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="33" t="inlineStr"/>
+      <c r="L22" s="33" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G23" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>0.7082652363052141</v>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>1.023989710490751</v>
+      </c>
+      <c r="J23" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="33" t="inlineStr"/>
+      <c r="L23" s="33" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="F24" s="36" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G24" s="36" t="inlineStr">
+        <is>
+          <t>soon</t>
+        </is>
+      </c>
+      <c r="H24" s="38" t="n">
+        <v>0.3004673764848859</v>
+      </c>
+      <c r="I24" s="38" t="n">
+        <v>1.331217847775203</v>
+      </c>
+      <c r="J24" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" s="36" t="inlineStr">
+        <is>
+          <t>urgency: low confidence (0.30)</t>
+        </is>
+      </c>
+      <c r="L24" s="36" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E25" s="36" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="F25" s="36" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="H25" s="38" t="n">
+        <v>0.3120997517953533</v>
+      </c>
+      <c r="I25" s="38" t="n">
+        <v>1.139766134713401</v>
+      </c>
+      <c r="J25" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" s="36" t="inlineStr">
+        <is>
+          <t>impact: low confidence (0.31)</t>
+        </is>
+      </c>
+      <c r="L25" s="36" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E26" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F26" s="36" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G26" s="36" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="H26" s="38" t="n">
+        <v>0.2893414605806364</v>
+      </c>
+      <c r="I26" s="38" t="n">
+        <v>1.342348590487079</v>
+      </c>
+      <c r="J26" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.29)</t>
+        </is>
+      </c>
+      <c r="L26" s="36" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>Heat Exchanger</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>E-310</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>cross_contamination</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>Cross-contamination</t>
+        </is>
+      </c>
+      <c r="G27" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>0.993523868071281</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>0.993523868071281</v>
+      </c>
+      <c r="J27" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="33" t="inlineStr"/>
+      <c r="L27" s="33" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D21" s="37" t="inlineStr">
+      <c r="D28" s="34" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
+        <is>
+          <t>failure_mode</t>
+        </is>
+      </c>
+      <c r="F28" s="33" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="G28" s="33" t="inlineStr">
+        <is>
+          <t>flooding</t>
+        </is>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>0.6803313388383841</v>
+      </c>
+      <c r="I28" s="35" t="n">
+        <v>0.7658952561283315</v>
+      </c>
+      <c r="J28" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" s="33" t="inlineStr"/>
+      <c r="L28" s="33" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>containment</t>
         </is>
       </c>
-      <c r="F21" s="36" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>Containment</t>
         </is>
       </c>
-      <c r="G21" s="36" t="inlineStr"/>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L21" s="36" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>0.9852695044791884</v>
+      </c>
+      <c r="I29" s="35" t="n">
+        <v>0.01473049552081164</v>
+      </c>
+      <c r="J29" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" s="33" t="inlineStr"/>
+      <c r="L29" s="33" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C22" s="36" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D22" s="37" t="inlineStr">
+      <c r="D30" s="37" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E22" s="36" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="F22" s="36" t="inlineStr">
-        <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="G22" s="36" t="inlineStr"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L22" s="36" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="36" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="inlineStr">
-        <is>
-          <t>C-301</t>
-        </is>
-      </c>
-      <c r="D23" s="37" t="inlineStr">
-        <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
-        </is>
-      </c>
-      <c r="E23" s="36" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="F23" s="36" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="G23" s="36" t="inlineStr"/>
-      <c r="H23" s="36" t="n"/>
-      <c r="I23" s="36" t="n"/>
-      <c r="J23" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L23" s="36" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="inlineStr">
-        <is>
-          <t>C-301</t>
-        </is>
-      </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>off_spec</t>
-        </is>
-      </c>
-      <c r="F24" s="33" t="inlineStr">
-        <is>
-          <t>Off-spec</t>
-        </is>
-      </c>
-      <c r="G24" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H24" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I24" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J24" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" s="33" t="inlineStr"/>
-      <c r="L24" s="33" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>C-301</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
-        </is>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>stability</t>
-        </is>
-      </c>
-      <c r="F25" s="33" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="G25" s="33" t="inlineStr">
-        <is>
-          <t>upset</t>
-        </is>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" s="33" t="inlineStr"/>
-      <c r="L25" s="33" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C26" s="33" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E26" s="33" t="inlineStr">
-        <is>
-          <t>failure_mode</t>
-        </is>
-      </c>
-      <c r="F26" s="33" t="inlineStr">
-        <is>
-          <t>Failure mode</t>
-        </is>
-      </c>
-      <c r="G26" s="33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="H26" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" s="33" t="inlineStr"/>
-      <c r="L26" s="33" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="36" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B27" s="36" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C27" s="36" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D27" s="37" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E27" s="36" t="inlineStr">
-        <is>
-          <t>containment</t>
-        </is>
-      </c>
-      <c r="F27" s="36" t="inlineStr">
-        <is>
-          <t>Containment</t>
-        </is>
-      </c>
-      <c r="G27" s="36" t="inlineStr"/>
-      <c r="H27" s="36" t="n"/>
-      <c r="I27" s="36" t="n"/>
-      <c r="J27" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L27" s="36" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D28" s="37" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E28" s="36" t="inlineStr">
-        <is>
-          <t>urgency</t>
-        </is>
-      </c>
-      <c r="F28" s="36" t="inlineStr">
-        <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="G28" s="36" t="inlineStr"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L28" s="36" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="36" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B29" s="36" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D29" s="37" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E29" s="36" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="F29" s="36" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="G29" s="36" t="inlineStr"/>
-      <c r="H29" s="36" t="n"/>
-      <c r="I29" s="36" t="n"/>
-      <c r="J29" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" s="36" t="inlineStr">
-        <is>
-          <t>no answer</t>
-        </is>
-      </c>
-      <c r="L29" s="36" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>R006</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>C-402</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="E30" s="33" t="inlineStr">
-        <is>
-          <t>off_spec</t>
-        </is>
-      </c>
-      <c r="F30" s="33" t="inlineStr">
-        <is>
-          <t>Off-spec</t>
-        </is>
-      </c>
-      <c r="G30" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H30" s="35" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I30" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J30" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" s="33" t="inlineStr"/>
-      <c r="L30" s="33" t="inlineStr"/>
+      <c r="E30" s="36" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="F30" s="36" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H30" s="38" t="n">
+        <v>0.188075872547421</v>
+      </c>
+      <c r="I30" s="38" t="n">
+        <v>1.299708878369453</v>
+      </c>
+      <c r="J30" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" s="36" t="inlineStr">
+        <is>
+          <t>load: low confidence (0.19)</t>
+        </is>
+      </c>
+      <c r="L30" s="36" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="B31" s="33" t="inlineStr">
@@ -9509,40 +9921,624 @@
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>C-402</t>
+          <t>C-301</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
       <c r="E31" s="33" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>urgency</t>
         </is>
       </c>
       <c r="F31" s="33" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Urgency</t>
         </is>
       </c>
       <c r="G31" s="33" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>immediate</t>
         </is>
       </c>
       <c r="H31" s="35" t="n">
-        <v>1</v>
+        <v>0.8091260652766668</v>
       </c>
       <c r="I31" s="35" t="n">
-        <v>0</v>
+        <v>1.937812200817456</v>
       </c>
       <c r="J31" s="33" t="b">
         <v>0</v>
       </c>
       <c r="K31" s="33" t="inlineStr"/>
       <c r="L31" s="33" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="36" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C32" s="36" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D32" s="37" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E32" s="36" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="F32" s="36" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G32" s="36" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="H32" s="38" t="n">
+        <v>0.1934498910234053</v>
+      </c>
+      <c r="I32" s="38" t="n">
+        <v>1.417932638835096</v>
+      </c>
+      <c r="J32" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" s="36" t="inlineStr">
+        <is>
+          <t>impact: low confidence (0.19)</t>
+        </is>
+      </c>
+      <c r="L32" s="36" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D33" s="37" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E33" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F33" s="36" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G33" s="36" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="H33" s="38" t="n">
+        <v>0.1714265267610506</v>
+      </c>
+      <c r="I33" s="38" t="n">
+        <v>1.337527379063873</v>
+      </c>
+      <c r="J33" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.17)</t>
+        </is>
+      </c>
+      <c r="L33" s="36" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="F34" s="33" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="G34" s="33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H34" s="35" t="n">
+        <v>0.9972499411450706</v>
+      </c>
+      <c r="I34" s="35" t="n">
+        <v>0.9972499411450706</v>
+      </c>
+      <c r="J34" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" s="33" t="inlineStr"/>
+      <c r="L34" s="33" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>C-301</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
+        </is>
+      </c>
+      <c r="E35" s="33" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="F35" s="33" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="G35" s="33" t="inlineStr">
+        <is>
+          <t>upset</t>
+        </is>
+      </c>
+      <c r="H35" s="35" t="n">
+        <v>0.8431627582980868</v>
+      </c>
+      <c r="I35" s="35" t="n">
+        <v>1.943775069671376</v>
+      </c>
+      <c r="J35" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" s="33" t="inlineStr"/>
+      <c r="L35" s="33" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E36" s="33" t="inlineStr">
+        <is>
+          <t>failure_mode</t>
+        </is>
+      </c>
+      <c r="F36" s="33" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="G36" s="33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>0.9363398600629796</v>
+      </c>
+      <c r="I36" s="35" t="n">
+        <v>0.9784069191734092</v>
+      </c>
+      <c r="J36" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" s="33" t="inlineStr"/>
+      <c r="L36" s="33" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="inlineStr">
+        <is>
+          <t>containment</t>
+        </is>
+      </c>
+      <c r="F37" s="33" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+      <c r="G37" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H37" s="35" t="n">
+        <v>0.9957133755759788</v>
+      </c>
+      <c r="I37" s="35" t="n">
+        <v>0.004286624424021187</v>
+      </c>
+      <c r="J37" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="33" t="inlineStr"/>
+      <c r="L37" s="33" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="G38" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H38" s="35" t="n">
+        <v>0.9348095470889991</v>
+      </c>
+      <c r="I38" s="35" t="n">
+        <v>0.9944437539675687</v>
+      </c>
+      <c r="J38" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" s="33" t="inlineStr"/>
+      <c r="L38" s="33" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="G39" s="33" t="inlineStr">
+        <is>
+          <t>routine</t>
+        </is>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>0.9150701099900012</v>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>0.02285845930706045</v>
+      </c>
+      <c r="J39" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" s="33" t="inlineStr"/>
+      <c r="L39" s="33" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E40" s="33" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+      <c r="F40" s="33" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="G40" s="33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>0.954014606183754</v>
+      </c>
+      <c r="I40" s="35" t="n">
+        <v>0.009865682566864381</v>
+      </c>
+      <c r="J40" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" s="33" t="inlineStr"/>
+      <c r="L40" s="33" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E41" s="33" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="F41" s="33" t="inlineStr">
+        <is>
+          <t>Potential impact</t>
+        </is>
+      </c>
+      <c r="G41" s="33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>0.9293340218130992</v>
+      </c>
+      <c r="I41" s="35" t="n">
+        <v>0.01860644816057358</v>
+      </c>
+      <c r="J41" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" s="33" t="inlineStr"/>
+      <c r="L41" s="33" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E42" s="33" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="F42" s="33" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="G42" s="33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H42" s="35" t="n">
+        <v>0.9947682918870171</v>
+      </c>
+      <c r="I42" s="35" t="n">
+        <v>0.00523170811298286</v>
+      </c>
+      <c r="J42" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" s="33" t="inlineStr"/>
+      <c r="L42" s="33" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>C-402</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
+        </is>
+      </c>
+      <c r="E43" s="33" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="F43" s="33" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="G43" s="33" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="H43" s="35" t="n">
+        <v>0.9531418933138464</v>
+      </c>
+      <c r="I43" s="35" t="n">
+        <v>0.01156392735957413</v>
+      </c>
+      <c r="J43" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" s="33" t="inlineStr"/>
+      <c r="L43" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9588,12 +10584,12 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 465, "output_tokens": 92}</t>
+          <t>{"input_tokens": 3431, "output_tokens": 7}</t>
         </is>
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "bearing": 0.0, "instrument": 0.0, "seal": 1.0, "other": 0.0}}, "containment": {"type": "noul", "noul": 0.89}, "urgency": {"type": "score", "score": 1.99, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9403764383354369, "bearing": 0.023752584592859, "cavitation": 0.02777636530316554, "instrument": 0.002736962400376868, "other": 0.005357649368161494}, "confidence": 0.8195945775641966}, "containment": {"type": "noul", "noul": 0.7691154479779605}, "load": {"type": "score", "score": 1.1016859277791764, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.03030890919098518, "1": 0.8376962538388533, "2": 0.13199483697016162}, "confidence": 0.5252066897339631}, "urgency": {"type": "score", "score": 1.7441183295311746, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.025617318730848933, "1": 0.20464703300712783, "2": 0.7697356482620233}, "confidence": 0.4356639754842947}, "impact": {"type": "score", "score": 1.0995364152010518, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.09479898270390513, "1": 0.7108656193911379, "2": 0.19433539790495694}, "confidence": 0.28610038363270285}, "potential_impact": {"type": "score", "score": 1.5815300408496102, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.04895136691935876, "1": 0.3205672253116721, "2": 0.6304814077689691}, "confidence": 0.2688926828193108}}</t>
         </is>
       </c>
     </row>
@@ -9605,12 +10601,12 @@
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 464, "output_tokens": 92}</t>
+          <t>{"input_tokens": 3437, "output_tokens": 7}</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"other": 0.0, "seal": 0.0, "cavitation": 0.0, "bearing": 1.0, "instrument": 0.0}}, "containment": {"type": "noul", "noul": 0.01}, "urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.00271844877009735, "bearing": 0.99356430421049, "cavitation": 0.0014845156733352789, "instrument": 0.0006423127261355957, "other": 0.0015904186199419271}, "confidence": 0.9707274126385984}, "containment": {"type": "noul", "noul": 0.01410409497066424}, "load": {"type": "score", "score": 0.9830735117434298, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.03050219630445108, "1": 0.9559220956476682, "2": 0.013575708047880834}, "confidence": 0.810750694954472}, "urgency": {"type": "score", "score": 0.023946606601512287, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.981450571740185, "1": 0.013152249918117795, "2": 0.005397178341697247}, "confidence": 0.9057681604539835}, "impact": {"type": "score", "score": 0.054618745563618024, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.9509405327056056, "1": 0.043500189025170735, "2": 0.005559278269223646}, "confidence": 0.8060517778980076}, "potential_impact": {"type": "score", "score": 0.9272016948488913, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.08743343556647779, "1": 0.897931434018153, "2": 0.01463513041536913}, "confidence": 0.6617906884831326}}</t>
         </is>
       </c>
     </row>
@@ -9622,12 +10618,12 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 484, "output_tokens": 102}</t>
+          <t>{"input_tokens": 4529, "output_tokens": 8}</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "tube_leak": 0.0, "other": 0.0, "flow_maldistribution": 0.0, "fouling": 1.0}}, "cross_contamination": {"type": "noul", "noul": 0.14}, "impact": {"type": "score", "score": 1.1, "confidence": 0.84, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.9, "2": 0.1}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9680451306120793, "tube_leak": 0.023515279230748413, "flow_maldistribution": 0.005935079187159576, "control_valve": 0.0009338859656491551, "other": 0.001570625004363632}, "confidence": 0.8964189370932257}, "containment": {"type": "noul", "noul": 0.018963267962223727}, "load": {"type": "score", "score": 0.9234640502322689, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.10501361956542159, "1": 0.8665087106368881, "2": 0.028477669797690393}, "confidence": 0.5793208854661729}, "urgency": {"type": "score", "score": 0.2398700214389179, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.8066961046405768, "1": 0.14673776927992832, "2": 0.04656612607949479}, "confidence": 0.45594687897702346}, "impact": {"type": "score", "score": 0.7770780189312785, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.27090379744411325, "1": 0.681114386180495, "2": 0.04798181637539171}, "confidence": 0.30723458814913884}, "potential_impact": {"type": "score", "score": 0.48753602920894634, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.5430191923742405, "1": 0.4264255860425726, "2": 0.03055522158318688}, "confidence": 0.2703462680038269}, "cross_contamination": {"type": "noul", "noul": 0.0399715492664482}}</t>
         </is>
       </c>
     </row>
@@ -9639,12 +10635,12 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 487, "output_tokens": 102}</t>
+          <t>{"input_tokens": 4522, "output_tokens": 8}</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "tube_leak": 1.0, "fouling": 0.0}}, "cross_contamination": {"type": "noul", "noul": 0.9}, "impact": {"type": "score", "score": 1.25, "confidence": 0.49, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.05, "1": 0.65, "2": 0.3}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0012215421919611676, "tube_leak": 0.9960106591003453, "flow_maldistribution": 0.001772688409883248, "control_valve": 0.00026080847162997516, "other": 0.0007343018261804486}, "confidence": 0.980827621350109}, "containment": {"type": "noul", "noul": 0.17688143735879036}, "load": {"type": "score", "score": 1.0239897104907512, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.026435554656885116, "1": 0.9231391801954787, "2": 0.05042526514763627}, "confidence": 0.7082652363052141}, "urgency": {"type": "score", "score": 1.3312178477752035, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.028142554477525075, "1": 0.6124970432697464, "2": 0.3593604022527285}, "confidence": 0.30046737648488586}, "impact": {"type": "score", "score": 1.1397661347134012, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.07158432231093885, "1": 0.7170652206647211, "2": 0.21135045702434}, "confidence": 0.3120997517953533}, "potential_impact": {"type": "score", "score": 1.3423485904870789, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.03001426440708731, "1": 0.5976228806987464, "2": 0.37236285489416626}, "confidence": 0.28934146058063637}, "cross_contamination": {"type": "noul", "noul": 0.993523868071281}}</t>
         </is>
       </c>
     </row>
@@ -9656,12 +10652,12 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 514, "output_tokens": 117}</t>
+          <t>{"input_tokens": 5871, "output_tokens": 9}</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "flooding", "confidence": 0.84, "probabilities": {"instrument": 0.02, "flooding": 0.87, "other": 0.02, "reboiler_condenser": 0.0, "weeping": 0.0, "foaming": 0.09, "fouling": 0.0}}, "off_spec": {"type": "noul", "noul": 0.99}, "stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.7658952561283315, "weeping": 0.008919577166532836, "foaming": 0.21745773872133595, "fouling": 0.0013342903862147107, "reboiler_condenser": 0.0005000774452204862, "instrument": 0.005652697246225303, "other": 0.0002403629061388724}, "confidence": 0.6803313388383841}, "containment": {"type": "noul", "noul": 0.014730495520811644}, "load": {"type": "score", "score": 1.2997088783694535, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.07551032772657393, "1": 0.5492704661773986, "2": 0.37521920609602744}, "confidence": 0.18807587254742097}, "urgency": {"type": "score", "score": 1.937812200817456, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.018368378254247305, "1": 0.02545104267404942, "2": 0.9561805790717033}, "confidence": 0.8091260652766668}, "impact": {"type": "score", "score": 1.4179326388350961, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.06393700472216769, "1": 0.45419335172056846, "2": 0.4818696435572638}, "confidence": 0.19344989102340526}, "potential_impact": {"type": "score", "score": 1.3375273790638733, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.07889131789555637, "1": 0.5046899851450138, "2": 0.41641869695942973}, "confidence": 0.17142652676105063}, "off_spec": {"type": "noul", "noul": 0.9972499411450706}, "stability": {"type": "score", "score": 1.943775069671376, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.021825125227392647, "1": 0.01257467987383881, "2": 0.9656001948987686}, "confidence": 0.8431627582980868}}</t>
         </is>
       </c>
     </row>
@@ -9673,12 +10669,12 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 512, "output_tokens": 115}</t>
+          <t>{"input_tokens": 5855, "output_tokens": 9}</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"fouling": 0.0, "weeping": 0.0, "other": 1.0, "flooding": 0.0, "foaming": 0.0, "reboiler_condenser": 0.0, "instrument": 0.0}}, "off_spec": {"type": "noul", "noul": 0.01}, "stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.015310150196454458, "weeping": 0.003729595689138417, "foaming": 0.0009179110234264862, "fouling": 0.001424967860907713, "reboiler_condenser": 0.00012948811605478457, "instrument": 8.09679406090723e-05, "other": 0.9784069191734092}, "confidence": 0.9363398600629796}, "containment": {"type": "noul", "noul": 0.004286624424021187}, "load": {"type": "score", "score": 0.9944437539675687, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.008743324738875088, "1": 0.988069596554681, "2": 0.003187078706443858}, "confidence": 0.9348095470889991}, "urgency": {"type": "score", "score": 0.02285845930706045, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9839212234793119, "1": 0.009299093734315722, "2": 0.006779682786372365}, "confidence": 0.9150701099900012}, "impact": {"type": "score", "score": 0.00986568256686438, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.992105930482838, "1": 0.005922456467459379, "2": 0.001971613049702501}, "confidence": 0.954014606183754}, "potential_impact": {"type": "score", "score": 0.01860644816057358, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.9871339026939872, "1": 0.0071257464514525295, "2": 0.005740350854560525}, "confidence": 0.9293340218130992}, "off_spec": {"type": "noul", "noul": 0.00523170811298286}, "stability": {"type": "score", "score": 0.011563927359574127, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.9921165372801404, "1": 0.004202998080145225, "2": 0.003680464639714451}, "confidence": 0.9531418933138464}}</t>
         </is>
       </c>
     </row>
@@ -9693,7 +10689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="20" min="1" max="1"/>
@@ -9798,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>0.973</v>
+        <v>0.881</v>
       </c>
       <c r="H2" s="33" t="n">
         <v>6</v>
@@ -9810,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>0.973</v>
+        <v>0.881</v>
       </c>
       <c r="L2" s="33" t="inlineStr"/>
     </row>
@@ -9834,13 +10830,13 @@
         <v>6</v>
       </c>
       <c r="E3" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.923</v>
       </c>
       <c r="H3" s="33" t="n">
         <v>2</v>
@@ -9852,19 +10848,19 @@
         <v>1</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.878</v>
       </c>
       <c r="L3" s="33" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="33" t="inlineStr">
         <is>
-          <t>urgency</t>
+          <t>load</t>
         </is>
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>Urgency</t>
+          <t>Load</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
@@ -9876,37 +10872,33 @@
         <v>6</v>
       </c>
       <c r="E4" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>0.99</v>
+        <v>0.624</v>
       </c>
       <c r="H4" s="33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="33" t="n">
-        <v>0.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J4" s="33" t="inlineStr"/>
+      <c r="K4" s="33" t="inlineStr"/>
       <c r="L4" s="33" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>urgency</t>
         </is>
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Urgency</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
@@ -9918,128 +10910,124 @@
         <v>6</v>
       </c>
       <c r="E5" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>0.665</v>
+        <v>0.637</v>
       </c>
       <c r="H5" s="33" t="n">
         <v>2</v>
       </c>
       <c r="I5" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L5" s="33" t="n">
-        <v>0.49</v>
-      </c>
+        <v>0.671</v>
+      </c>
+      <c r="L5" s="33" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
         <is>
-          <t>cross_contamination</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>Cross-contamination</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>noul</t>
+          <t>score</t>
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0.88</v>
+        <v>0.476</v>
       </c>
       <c r="H6" s="33" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="33" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L6" s="33" t="inlineStr"/>
+        <v>0.307</v>
+      </c>
+      <c r="L6" s="33" t="n">
+        <v>0.312</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
         <is>
-          <t>off_spec</t>
+          <t>potential_impact</t>
         </is>
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>Off-spec</t>
+          <t>Potential impact</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>noul</t>
+          <t>score</t>
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F7" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="H7" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>2</v>
-      </c>
       <c r="I7" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="33" t="n">
-        <v>0.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J7" s="33" t="inlineStr"/>
+      <c r="K7" s="33" t="inlineStr"/>
       <c r="L7" s="33" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>cross_contamination</t>
         </is>
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Cross-contamination</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>noul</t>
         </is>
       </c>
       <c r="D8" s="33" t="n">
@@ -10052,7 +11040,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="H8" s="33" t="n">
         <v>2</v>
@@ -10064,9 +11052,93 @@
         <v>1</v>
       </c>
       <c r="K8" s="33" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="L8" s="33" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>off_spec</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>Off-spec</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>noul</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="33" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="L9" s="33" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="33" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nimble_classifier_workbook.xlsx
+++ b/nimble_classifier_workbook.xlsx
@@ -12,16 +12,15 @@
     <sheet name="Questions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Labels" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Records" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Lists" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="output_nimble_Results" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="output_nimble_Raw" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="output_nimble_Summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="output_nimble_Run_info" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="output_jev_Results" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="output_jev_Raw" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="output_jev_Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="output_jev_Run_info" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="output_compare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="output_jev_Results" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="output_jev_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="output_jev_Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="output_jev_Run_info" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="output_jevk5_Results" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="output_jevk5_Raw" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="output_jevk5_Summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="output_jevk5_Run_info" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="output_compare" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -573,14 +572,14 @@
     <row r="1" ht="17.25" customHeight="1" s="20">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>Nimble and Jev — control workbook</t>
+          <t>Nimble, Jev, and JevK5 — control workbook</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="20">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Classify plant statements with Nimble (local) or Jev (cloud). Edit this file; run from the terminal (see repo README).</t>
+          <t>Classify plant statements with Nimble (Ollama), Jev (TypeSafe), or JevK5 (local open-weight). Edit this file; run from the terminal (see repo README).</t>
         </is>
       </c>
     </row>
@@ -600,7 +599,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Records.text is the statement to classify.</t>
+          <t>Records.statement is the statement to classify.</t>
         </is>
       </c>
     </row>
@@ -675,7 +674,7 @@
     <row r="13" ht="15" customHeight="1" s="20">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Questions / Labels / Records / Lists</t>
+          <t>Questions / Labels / Records</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
@@ -687,12 +686,12 @@
     <row r="14" ht="45" customHeight="1" s="20">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>output_nimble_* / output_jev_*</t>
+          <t>output_&lt;engine&gt;_*</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Results (one row per answer), Raw, Summary, Run_info.</t>
+          <t>Results (one row per answer), Raw, Summary, Run_info for nimble / jev / jevk5.</t>
         </is>
       </c>
     </row>
@@ -704,7 +703,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Nimble vs Jev when both have been run.</t>
+          <t>Side-by-side when two or more engines have been run.</t>
         </is>
       </c>
     </row>
@@ -736,7 +735,7 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>For Jev: export TYPESAFE_API_KEY=... Leave Config api_key blank.</t>
+          <t>For cloud Jev only: export TYPESAFE_API_KEY=... Leave Config api_key blank. Nimble/JevK5 need no key.</t>
         </is>
       </c>
     </row>
@@ -776,264 +775,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" style="20" min="1" max="1"/>
-    <col width="70" customWidth="1" style="20" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="32" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="33" t="inlineStr">
-        <is>
-          <t>run_started</t>
-        </is>
-      </c>
-      <c r="B2" s="33" t="inlineStr">
-        <is>
-          <t>20260930_192332</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="33" t="inlineStr">
-        <is>
-          <t>workbook</t>
-        </is>
-      </c>
-      <c r="B3" s="33" t="inlineStr">
-        <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="33" t="inlineStr">
-        <is>
-          <t>engine</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="inlineStr">
-        <is>
-          <t>nimble</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="33" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>nimble</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>base_url</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>http://localhost:11434</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>endpoint_info</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>0.35.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="33" t="inlineStr">
-        <is>
-          <t>questions_hash</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>c6060602276b</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>api_key_configured</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>records_in_run</t>
-        </is>
-      </c>
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>records_completed</t>
-        </is>
-      </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>failed_records</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>review_threshold_default</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>elapsed_seconds</t>
-        </is>
-      </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>checkpoint</t>
-        </is>
-      </c>
-      <c r="B15" s="33" t="inlineStr">
-        <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_nimble_20260930_192332.jsonl</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>input_tokens</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>27645</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="33" t="inlineStr">
-        <is>
-          <t>total_tokens</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>27693</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>records_with_usage</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>output_sheets</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>output_nimble_Results, output_nimble_Raw, output_nimble_Summary, output_nimble_Run_info</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1069,7 +810,7 @@
       </c>
       <c r="D1" s="32" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E1" s="32" t="inlineStr">
@@ -1150,10 +891,10 @@
         </is>
       </c>
       <c r="H2" s="35" t="n">
-        <v>1</v>
+        <v>0.9824340738888386</v>
       </c>
       <c r="I2" s="35" t="n">
-        <v>1</v>
+        <v>0.9824340738888386</v>
       </c>
       <c r="J2" s="33" t="b">
         <v>0</v>
@@ -1198,10 +939,10 @@
         </is>
       </c>
       <c r="H3" s="35" t="n">
-        <v>0.88</v>
+        <v>0.7065507973266721</v>
       </c>
       <c r="I3" s="35" t="n">
-        <v>0.88</v>
+        <v>0.7065507973266721</v>
       </c>
       <c r="J3" s="33" t="b">
         <v>0</v>
@@ -1242,21 +983,21 @@
       </c>
       <c r="G4" s="36" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="H4" s="38" t="n">
-        <v>0.26</v>
+        <v>0.5508631005132343</v>
       </c>
       <c r="I4" s="38" t="n">
-        <v>1.51</v>
+        <v>0.6577839987135929</v>
       </c>
       <c r="J4" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="36" t="inlineStr">
         <is>
-          <t>load: low confidence (0.26)</t>
+          <t>load: low confidence (0.55)</t>
         </is>
       </c>
       <c r="L4" s="36" t="inlineStr"/>
@@ -1298,10 +1039,10 @@
         </is>
       </c>
       <c r="H5" s="35" t="n">
-        <v>0.98</v>
+        <v>0.90947554364201</v>
       </c>
       <c r="I5" s="35" t="n">
-        <v>1.99</v>
+        <v>1.894700467376794</v>
       </c>
       <c r="J5" s="33" t="b">
         <v>0</v>
@@ -1310,52 +1051,56 @@
       <c r="L5" s="33" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G6" s="33" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="H6" s="35" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I6" s="35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="J6" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="33" t="inlineStr"/>
-      <c r="L6" s="33" t="inlineStr"/>
+      <c r="H6" s="38" t="n">
+        <v>0.5483561966627606</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>1.330091546292686</v>
+      </c>
+      <c r="J6" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="36" t="inlineStr">
+        <is>
+          <t>impact: low confidence (0.55)</t>
+        </is>
+      </c>
+      <c r="L6" s="36" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
@@ -1394,10 +1139,10 @@
         </is>
       </c>
       <c r="H7" s="35" t="n">
-        <v>0.67</v>
+        <v>0.8992780191968657</v>
       </c>
       <c r="I7" s="35" t="n">
-        <v>1.78</v>
+        <v>1.888143082543135</v>
       </c>
       <c r="J7" s="33" t="b">
         <v>0</v>
@@ -1442,10 +1187,10 @@
         </is>
       </c>
       <c r="H8" s="35" t="n">
-        <v>1</v>
+        <v>0.9610943867016385</v>
       </c>
       <c r="I8" s="35" t="n">
-        <v>1</v>
+        <v>0.9610943867016385</v>
       </c>
       <c r="J8" s="33" t="b">
         <v>0</v>
@@ -1490,10 +1235,10 @@
         </is>
       </c>
       <c r="H9" s="35" t="n">
-        <v>0.99</v>
+        <v>0.9781857449061092</v>
       </c>
       <c r="I9" s="35" t="n">
-        <v>0.01</v>
+        <v>0.02181425509389075</v>
       </c>
       <c r="J9" s="33" t="b">
         <v>0</v>
@@ -1538,10 +1283,10 @@
         </is>
       </c>
       <c r="H10" s="35" t="n">
-        <v>0.96</v>
+        <v>0.8084353234082341</v>
       </c>
       <c r="I10" s="35" t="n">
-        <v>1.02</v>
+        <v>1.043975643496921</v>
       </c>
       <c r="J10" s="33" t="b">
         <v>0</v>
@@ -1586,10 +1331,10 @@
         </is>
       </c>
       <c r="H11" s="35" t="n">
-        <v>0.99</v>
+        <v>0.9029075553748133</v>
       </c>
       <c r="I11" s="35" t="n">
-        <v>0.01</v>
+        <v>0.1091994976994665</v>
       </c>
       <c r="J11" s="33" t="b">
         <v>0</v>
@@ -1634,10 +1379,10 @@
         </is>
       </c>
       <c r="H12" s="35" t="n">
-        <v>0.96</v>
+        <v>0.7321666759484706</v>
       </c>
       <c r="I12" s="35" t="n">
-        <v>0.03</v>
+        <v>0.2786306304512531</v>
       </c>
       <c r="J12" s="33" t="b">
         <v>0</v>
@@ -1682,10 +1427,10 @@
         </is>
       </c>
       <c r="H13" s="35" t="n">
-        <v>0.88</v>
+        <v>0.6134537990255072</v>
       </c>
       <c r="I13" s="35" t="n">
-        <v>0.96</v>
+        <v>1.165712902776003</v>
       </c>
       <c r="J13" s="33" t="b">
         <v>0</v>
@@ -1730,10 +1475,10 @@
         </is>
       </c>
       <c r="H14" s="35" t="n">
-        <v>1</v>
+        <v>0.9801978339182461</v>
       </c>
       <c r="I14" s="35" t="n">
-        <v>1</v>
+        <v>0.9801978339182461</v>
       </c>
       <c r="J14" s="33" t="b">
         <v>0</v>
@@ -1778,10 +1523,10 @@
         </is>
       </c>
       <c r="H15" s="35" t="n">
-        <v>0.97</v>
+        <v>0.8297088427074472</v>
       </c>
       <c r="I15" s="35" t="n">
-        <v>0.03</v>
+        <v>0.1702911572925529</v>
       </c>
       <c r="J15" s="33" t="b">
         <v>0</v>
@@ -1826,17 +1571,17 @@
         </is>
       </c>
       <c r="H16" s="38" t="n">
-        <v>0</v>
+        <v>0.5098955077545156</v>
       </c>
       <c r="I16" s="38" t="n">
-        <v>1.19</v>
+        <v>1.192779827896732</v>
       </c>
       <c r="J16" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
-          <t>load: low confidence (0.00)</t>
+          <t>load: low confidence (0.51)</t>
         </is>
       </c>
       <c r="L16" s="36" t="inlineStr"/>
@@ -1878,17 +1623,17 @@
         </is>
       </c>
       <c r="H17" s="38" t="n">
-        <v>0.29</v>
+        <v>0.5198005205954765</v>
       </c>
       <c r="I17" s="38" t="n">
-        <v>0.95</v>
+        <v>1.23864302750015</v>
       </c>
       <c r="J17" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
-          <t>urgency: low confidence (0.29)</t>
+          <t>urgency: low confidence (0.52)</t>
         </is>
       </c>
       <c r="L17" s="36" t="inlineStr"/>
@@ -1930,10 +1675,10 @@
         </is>
       </c>
       <c r="H18" s="35" t="n">
-        <v>0.86</v>
+        <v>0.6286301802274425</v>
       </c>
       <c r="I18" s="35" t="n">
-        <v>1.09</v>
+        <v>1.127319182522956</v>
       </c>
       <c r="J18" s="33" t="b">
         <v>0</v>
@@ -1942,52 +1687,56 @@
       <c r="L18" s="33" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C19" s="33" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>E-205</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="G19" s="33" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
       </c>
-      <c r="H19" s="35" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I19" s="35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="J19" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="33" t="inlineStr"/>
-      <c r="L19" s="33" t="inlineStr"/>
+      <c r="H19" s="38" t="n">
+        <v>0.503374419114064</v>
+      </c>
+      <c r="I19" s="38" t="n">
+        <v>1.467436699793837</v>
+      </c>
+      <c r="J19" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="36" t="inlineStr">
+        <is>
+          <t>potential_impact: low confidence (0.50)</t>
+        </is>
+      </c>
+      <c r="L19" s="36" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="33" t="inlineStr">
@@ -2026,10 +1775,10 @@
         </is>
       </c>
       <c r="H20" s="35" t="n">
-        <v>0.85</v>
+        <v>0.734098606902861</v>
       </c>
       <c r="I20" s="35" t="n">
-        <v>0.15</v>
+        <v>0.265901393097139</v>
       </c>
       <c r="J20" s="33" t="b">
         <v>0</v>
@@ -2074,10 +1823,10 @@
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>1</v>
+        <v>0.97878383278065</v>
       </c>
       <c r="I21" s="35" t="n">
-        <v>1</v>
+        <v>0.97878383278065</v>
       </c>
       <c r="J21" s="33" t="b">
         <v>0</v>
@@ -2118,14 +1867,14 @@
       </c>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="H22" s="35" t="n">
-        <v>0.67</v>
+        <v>0.6847134664950006</v>
       </c>
       <c r="I22" s="35" t="n">
-        <v>0.67</v>
+        <v>0.3152865335049994</v>
       </c>
       <c r="J22" s="33" t="b">
         <v>0</v>
@@ -2134,52 +1883,56 @@
       <c r="L22" s="33" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C23" s="33" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>E-310</t>
         </is>
       </c>
-      <c r="D23" s="34" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
         </is>
       </c>
-      <c r="E23" s="33" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>load</t>
         </is>
       </c>
-      <c r="F23" s="33" t="inlineStr">
+      <c r="F23" s="36" t="inlineStr">
         <is>
           <t>Load</t>
         </is>
       </c>
-      <c r="G23" s="33" t="inlineStr">
+      <c r="G23" s="36" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="H23" s="35" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I23" s="35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="J23" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="33" t="inlineStr"/>
-      <c r="L23" s="33" t="inlineStr"/>
+      <c r="H23" s="38" t="n">
+        <v>0.5742634787665343</v>
+      </c>
+      <c r="I23" s="38" t="n">
+        <v>1.018681279462452</v>
+      </c>
+      <c r="J23" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" s="36" t="inlineStr">
+        <is>
+          <t>load: low confidence (0.57)</t>
+        </is>
+      </c>
+      <c r="L23" s="36" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="33" t="inlineStr">
@@ -2218,10 +1971,10 @@
         </is>
       </c>
       <c r="H24" s="35" t="n">
-        <v>1</v>
+        <v>0.8346517779922784</v>
       </c>
       <c r="I24" s="35" t="n">
-        <v>2</v>
+        <v>1.822521317526802</v>
       </c>
       <c r="J24" s="33" t="b">
         <v>0</v>
@@ -2230,56 +1983,52 @@
       <c r="L24" s="33" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>E-310</t>
         </is>
       </c>
-      <c r="D25" s="37" t="inlineStr">
+      <c r="D25" s="34" t="inlineStr">
         <is>
           <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
         </is>
       </c>
-      <c r="E25" s="36" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F25" s="36" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G25" s="36" t="inlineStr">
+      <c r="G25" s="33" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="H25" s="38" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I25" s="38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J25" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="36" t="inlineStr">
-        <is>
-          <t>impact: low confidence (0.58)</t>
-        </is>
-      </c>
-      <c r="L25" s="36" t="inlineStr"/>
+      <c r="H25" s="35" t="n">
+        <v>0.6365532188860706</v>
+      </c>
+      <c r="I25" s="35" t="n">
+        <v>1.064216789479891</v>
+      </c>
+      <c r="J25" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" s="33" t="inlineStr"/>
+      <c r="L25" s="33" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="33" t="inlineStr">
@@ -2318,10 +2067,10 @@
         </is>
       </c>
       <c r="H26" s="35" t="n">
-        <v>0.97</v>
+        <v>0.9035722899097612</v>
       </c>
       <c r="I26" s="35" t="n">
-        <v>1.98</v>
+        <v>1.892514651537182</v>
       </c>
       <c r="J26" s="33" t="b">
         <v>0</v>
@@ -2366,10 +2115,10 @@
         </is>
       </c>
       <c r="H27" s="35" t="n">
-        <v>0.95</v>
+        <v>0.9040281719700221</v>
       </c>
       <c r="I27" s="35" t="n">
-        <v>0.95</v>
+        <v>0.9040281719700221</v>
       </c>
       <c r="J27" s="33" t="b">
         <v>0</v>
@@ -2414,10 +2163,10 @@
         </is>
       </c>
       <c r="H28" s="35" t="n">
-        <v>0.83</v>
+        <v>0.6564551974427104</v>
       </c>
       <c r="I28" s="35" t="n">
-        <v>0.86</v>
+        <v>0.6564551974427104</v>
       </c>
       <c r="J28" s="33" t="b">
         <v>0</v>
@@ -2462,10 +2211,10 @@
         </is>
       </c>
       <c r="H29" s="35" t="n">
-        <v>0.95</v>
+        <v>0.9338403184871535</v>
       </c>
       <c r="I29" s="35" t="n">
-        <v>0.05</v>
+        <v>0.06615968151284642</v>
       </c>
       <c r="J29" s="33" t="b">
         <v>0</v>
@@ -2474,56 +2223,52 @@
       <c r="L29" s="33" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C30" s="36" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D30" s="37" t="inlineStr">
+      <c r="D30" s="34" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E30" s="36" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>load</t>
         </is>
       </c>
-      <c r="F30" s="36" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>Load</t>
         </is>
       </c>
-      <c r="G30" s="36" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H30" s="38" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I30" s="38" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J30" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" s="36" t="inlineStr">
-        <is>
-          <t>load: low confidence (0.54)</t>
-        </is>
-      </c>
-      <c r="L30" s="36" t="inlineStr"/>
+      <c r="G30" s="33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H30" s="35" t="n">
+        <v>0.6137554280557379</v>
+      </c>
+      <c r="I30" s="35" t="n">
+        <v>1.467252363041319</v>
+      </c>
+      <c r="J30" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" s="33" t="inlineStr"/>
+      <c r="L30" s="33" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="33" t="inlineStr">
@@ -2562,10 +2307,10 @@
         </is>
       </c>
       <c r="H31" s="35" t="n">
-        <v>1</v>
+        <v>0.9751721173161316</v>
       </c>
       <c r="I31" s="35" t="n">
-        <v>2</v>
+        <v>1.960784315097702</v>
       </c>
       <c r="J31" s="33" t="b">
         <v>0</v>
@@ -2574,108 +2319,100 @@
       <c r="L31" s="33" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C32" s="36" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D32" s="37" t="inlineStr">
+      <c r="D32" s="34" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E32" s="36" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F32" s="36" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G32" s="36" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="H32" s="38" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I32" s="38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J32" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" s="36" t="inlineStr">
-        <is>
-          <t>impact: low confidence (0.52)</t>
-        </is>
-      </c>
-      <c r="L32" s="36" t="inlineStr"/>
+      <c r="G32" s="33" t="inlineStr">
+        <is>
+          <t>severe</t>
+        </is>
+      </c>
+      <c r="H32" s="35" t="n">
+        <v>0.8433683442914435</v>
+      </c>
+      <c r="I32" s="35" t="n">
+        <v>1.818289743065716</v>
+      </c>
+      <c r="J32" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" s="33" t="inlineStr"/>
+      <c r="L32" s="33" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B33" s="36" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Distillation Column</t>
         </is>
       </c>
-      <c r="C33" s="36" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
       </c>
-      <c r="D33" s="37" t="inlineStr">
+      <c r="D33" s="34" t="inlineStr">
         <is>
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="E33" s="36" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="F33" s="36" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="G33" s="36" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="H33" s="38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I33" s="38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J33" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" s="36" t="inlineStr">
-        <is>
-          <t>potential_impact: low confidence (0.25)</t>
-        </is>
-      </c>
-      <c r="L33" s="36" t="inlineStr"/>
+      <c r="H33" s="35" t="n">
+        <v>0.7537415277615147</v>
+      </c>
+      <c r="I33" s="35" t="n">
+        <v>1.738873547266182</v>
+      </c>
+      <c r="J33" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" s="33" t="inlineStr"/>
+      <c r="L33" s="33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="33" t="inlineStr">
@@ -2714,10 +2451,10 @@
         </is>
       </c>
       <c r="H34" s="35" t="n">
-        <v>0.99</v>
+        <v>0.9562932354335837</v>
       </c>
       <c r="I34" s="35" t="n">
-        <v>0.99</v>
+        <v>0.9562932354335837</v>
       </c>
       <c r="J34" s="33" t="b">
         <v>0</v>
@@ -2762,10 +2499,10 @@
         </is>
       </c>
       <c r="H35" s="35" t="n">
-        <v>1</v>
+        <v>0.891040773520861</v>
       </c>
       <c r="I35" s="35" t="n">
-        <v>2</v>
+        <v>1.861764998681898</v>
       </c>
       <c r="J35" s="33" t="b">
         <v>0</v>
@@ -2810,10 +2547,10 @@
         </is>
       </c>
       <c r="H36" s="35" t="n">
-        <v>1</v>
+        <v>0.9466925860999985</v>
       </c>
       <c r="I36" s="35" t="n">
-        <v>1</v>
+        <v>0.9466925860999985</v>
       </c>
       <c r="J36" s="33" t="b">
         <v>0</v>
@@ -2858,10 +2595,10 @@
         </is>
       </c>
       <c r="H37" s="35" t="n">
-        <v>0.99</v>
+        <v>0.9492659532500998</v>
       </c>
       <c r="I37" s="35" t="n">
-        <v>0.01</v>
+        <v>0.05073404674990022</v>
       </c>
       <c r="J37" s="33" t="b">
         <v>0</v>
@@ -2906,10 +2643,10 @@
         </is>
       </c>
       <c r="H38" s="35" t="n">
-        <v>1</v>
+        <v>0.9367838391403669</v>
       </c>
       <c r="I38" s="35" t="n">
-        <v>1</v>
+        <v>1.019265482746454</v>
       </c>
       <c r="J38" s="33" t="b">
         <v>0</v>
@@ -2954,10 +2691,10 @@
         </is>
       </c>
       <c r="H39" s="35" t="n">
-        <v>1</v>
+        <v>0.8947989958986674</v>
       </c>
       <c r="I39" s="35" t="n">
-        <v>0</v>
+        <v>0.1374592171098581</v>
       </c>
       <c r="J39" s="33" t="b">
         <v>0</v>
@@ -3002,10 +2739,10 @@
         </is>
       </c>
       <c r="H40" s="35" t="n">
-        <v>1</v>
+        <v>0.9703695663705273</v>
       </c>
       <c r="I40" s="35" t="n">
-        <v>0</v>
+        <v>0.03782822664221772</v>
       </c>
       <c r="J40" s="33" t="b">
         <v>0</v>
@@ -3046,14 +2783,14 @@
       </c>
       <c r="G41" s="33" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="H41" s="35" t="n">
-        <v>0.96</v>
+        <v>0.6036773309179262</v>
       </c>
       <c r="I41" s="35" t="n">
-        <v>0.03</v>
+        <v>0.5136285965754814</v>
       </c>
       <c r="J41" s="33" t="b">
         <v>0</v>
@@ -3098,10 +2835,10 @@
         </is>
       </c>
       <c r="H42" s="35" t="n">
-        <v>0.99</v>
+        <v>0.950423993422423</v>
       </c>
       <c r="I42" s="35" t="n">
-        <v>0.01</v>
+        <v>0.04957600657757703</v>
       </c>
       <c r="J42" s="33" t="b">
         <v>0</v>
@@ -3146,10 +2883,10 @@
         </is>
       </c>
       <c r="H43" s="35" t="n">
-        <v>1</v>
+        <v>0.9800865084202343</v>
       </c>
       <c r="I43" s="35" t="n">
-        <v>0</v>
+        <v>0.02475723940192736</v>
       </c>
       <c r="J43" s="33" t="b">
         <v>0</v>
@@ -3162,7 +2899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3201,12 +2938,12 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 643, "output_tokens": 129}</t>
+          <t>{"input_tokens": 890, "output_tokens": 0}</t>
         </is>
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "instrument": 0.0, "bearing": 0.0, "other": 0.0, "seal": 1.0}}, "containment": {"type": "noul", "noul": 0.88}, "load": {"type": "score", "score": 1.51, "confidence": 0.26, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.04, "1": 0.41, "2": 0.55}}, "urgency": {"type": "score", "score": 1.99, "confidence": 0.98, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}, "impact": {"type": "score", "score": 1.12, "confidence": 0.82, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.88, "2": 0.12}}, "potential_impact": {"type": "score", "score": 1.78, "confidence": 0.67, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.22, "2": 0.78}}}</t>
+          <t>{"failure_mode": {"type": "choice", "confidence": 0.9824340738888386, "choice": "seal", "probabilities": {"seal": 0.9824340738888386, "bearing": 0.003831670114733441, "cavitation": 0.00377594886684965, "instrument": 0.002831547600483606, "other": 0.007126759529094709}}, "containment": {"type": "noul", "confidence": 0.7065507973266721, "noul": 0.7065507973266721}, "load": {"type": "score", "confidence": 0.5508631005132343, "score": 0.6577839987135929, "probabilities": {"0": 0.5508631005132343, "1": 0.2404898002599384, "2": 0.20864709922682728}}, "urgency": {"type": "score", "confidence": 0.90947554364201, "score": 1.894700467376794, "probabilities": {"0": 0.014775076265215917, "1": 0.07574938009277409, "2": 0.90947554364201}}, "impact": {"type": "score", "confidence": 0.5483561966627606, "score": 1.330091546292686, "probabilities": {"0": 0.0607761285222767, "1": 0.5483561966627606, "2": 0.39086767481496265}}, "potential_impact": {"type": "score", "confidence": 0.8992780191968657, "score": 1.8881430825431347, "probabilities": {"0": 0.011134936653731121, "1": 0.08958704414940327, "2": 0.8992780191968657}}}</t>
         </is>
       </c>
     </row>
@@ -3218,12 +2955,12 @@
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 642, "output_tokens": 129}</t>
+          <t>{"input_tokens": 896, "output_tokens": 0}</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>{"load": {"type": "score", "score": 1.02, "confidence": 0.96, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.0, "1": 0.98, "2": 0.02}}, "urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.99, "1": 0.01, "2": 0.0}}, "impact": {"type": "score", "score": 0.03, "confidence": 0.96, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.97, "1": 0.03, "2": 0.0}}, "potential_impact": {"type": "score", "score": 0.96, "confidence": 0.88, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.06, "1": 0.92, "2": 0.02}}, "failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "instrument": 0.0, "seal": 0.0, "other": 0.0, "bearing": 1.0}}, "containment": {"type": "noul", "noul": 0.01}}</t>
+          <t>{"failure_mode": {"type": "choice", "confidence": 0.9610943867016385, "choice": "bearing", "probabilities": {"seal": 0.0057394968181944585, "bearing": 0.9610943867016385, "cavitation": 0.0019366442489334326, "instrument": 0.00877948661088984, "other": 0.022449985620343754}}, "containment": {"type": "noul", "confidence": 0.9781857449061092, "noul": 0.02181425509389075}, "load": {"type": "score", "confidence": 0.8084353234082341, "score": 1.0439756434969214, "probabilities": {"0": 0.07379451654742221, "1": 0.8084353234082341, "2": 0.11777016004434367}}, "urgency": {"type": "score", "confidence": 0.9029075553748133, "score": 0.10919949769946653, "probabilities": {"0": 0.9029075553748133, "1": 0.08498539155090704, "2": 0.012107053074279747}}, "impact": {"type": "score", "confidence": 0.7321666759484706, "score": 0.27863063045125314, "probabilities": {"0": 0.7321666759484706, "1": 0.2570360176518058, "2": 0.010797306399723686}}, "potential_impact": {"type": "score", "confidence": 0.6134537990255072, "score": 1.1657129027760027, "probabilities": {"0": 0.11041664909924502, "1": 0.6134537990255072, "2": 0.27612955187524774}}}</t>
         </is>
       </c>
     </row>
@@ -3235,12 +2972,12 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 687, "output_tokens": 159}</t>
+          <t>{"input_tokens": 1079, "output_tokens": 0}</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "tube_leak": 0.0, "fouling": 1.0, "other": 0.0}}, "containment": {"type": "noul", "noul": 0.03}, "load": {"type": "score", "score": 1.19, "confidence": 0.0, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.35, "1": 0.12, "2": 0.53}}, "urgency": {"type": "score", "score": 0.95, "confidence": 0.29, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.26, "1": 0.53, "2": 0.21}}, "impact": {"type": "score", "score": 1.09, "confidence": 0.86, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.91, "2": 0.09}}, "potential_impact": {"type": "score", "score": 1.11, "confidence": 0.82, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.01, "1": 0.87, "2": 0.12}}, "cross_contamination": {"type": "noul", "noul": 0.15}}</t>
+          <t>{"failure_mode": {"type": "choice", "confidence": 0.9801978339182461, "choice": "fouling", "probabilities": {"fouling": 0.9801978339182461, "tube_leak": 0.013412876664608706, "flow_maldistribution": 0.0036256895715309945, "control_valve": 0.0007628618486180945, "other": 0.002000737996996189}}, "containment": {"type": "noul", "confidence": 0.8297088427074472, "noul": 0.17029115729255292}, "load": {"type": "score", "confidence": 0.5098955077545156, "score": 1.1927798278967316, "probabilities": {"0": 0.3171156798577839, "1": 0.17298881238770045, "2": 0.5098955077545156}}, "urgency": {"type": "score", "confidence": 0.5198005205954765, "score": 1.2386430275001499, "probabilities": {"0": 0.12077822595218683, "1": 0.5198005205954765, "2": 0.3594212534523366}}, "impact": {"type": "score", "confidence": 0.6286301802274425, "score": 1.127319182522956, "probabilities": {"0": 0.12202531862480066, "1": 0.6286301802274425, "2": 0.24934450114775678}}, "potential_impact": {"type": "score", "confidence": 0.503374419114064, "score": 1.4674366997938366, "probabilities": {"0": 0.035937719320227476, "1": 0.46068786156570857, "2": 0.503374419114064}}, "cross_contamination": {"type": "noul", "confidence": 0.734098606902861, "noul": 0.265901393097139}}</t>
         </is>
       </c>
     </row>
@@ -3252,12 +2989,12 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 690, "output_tokens": 159}</t>
+          <t>{"input_tokens": 1072, "output_tokens": 0}</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>{"containment": {"type": "noul", "noul": 0.67}, "load": {"type": "score", "score": 1.09, "confidence": 0.84, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.01, "1": 0.89, "2": 0.1}}, "urgency": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "impact": {"type": "score", "score": 1.21, "confidence": 0.58, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.03, "1": 0.72, "2": 0.25}}, "potential_impact": {"type": "score", "score": 1.98, "confidence": 0.97, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.02, "2": 0.98}}, "cross_contamination": {"type": "noul", "noul": 0.95}, "failure_mode": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"tube_leak": 1.0, "control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "fouling": 0.0}}}</t>
+          <t>{"failure_mode": {"type": "choice", "confidence": 0.97878383278065, "choice": "tube_leak", "probabilities": {"fouling": 0.0017846624761990017, "tube_leak": 0.97878383278065, "flow_maldistribution": 0.0023308037594201377, "control_valve": 0.0021150075451381745, "other": 0.014985693438592707}}, "containment": {"type": "noul", "confidence": 0.6847134664950006, "noul": 0.3152865335049994}, "load": {"type": "score", "confidence": 0.5742634787665343, "score": 1.0186812794624522, "probabilities": {"0": 0.20352762088550677, "1": 0.5742634787665343, "2": 0.22220890034795893}}, "urgency": {"type": "score", "confidence": 0.8346517779922784, "score": 1.8225213175268022, "probabilities": {"0": 0.012130460465476018, "1": 0.15321776154224553, "2": 0.8346517779922784}}, "impact": {"type": "score", "confidence": 0.6365532188860706, "score": 1.0642167894798906, "probabilities": {"0": 0.1496149958170193, "1": 0.6365532188860706, "2": 0.21383178529691}}, "potential_impact": {"type": "score", "confidence": 0.9035722899097612, "score": 1.8925146515371818, "probabilities": {"0": 0.011057638372579455, "1": 0.08537007171765933, "2": 0.9035722899097612}}, "cross_contamination": {"type": "noul", "confidence": 0.904028171970022, "noul": 0.904028171970022}}</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3006,12 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 762, "output_tokens": 186}</t>
+          <t>{"input_tokens": 1253, "output_tokens": 0}</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>{"urgency": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "impact": {"type": "score", "score": 1.32, "confidence": 0.52, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.68, "2": 0.32}}, "potential_impact": {"type": "score", "score": 1.5, "confidence": 0.25, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.49, "2": 0.51}}, "off_spec": {"type": "noul", "noul": 0.99}, "stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "failure_mode": {"type": "choice", "choice": "flooding", "confidence": 0.83, "probabilities": {"other": 0.03, "flooding": 0.86, "instrument": 0.07, "fouling": 0.0, "foaming": 0.04, "weeping": 0.0, "reboiler_condenser": 0.0}}, "containment": {"type": "noul", "noul": 0.05}, "load": {"type": "score", "score": 1.69, "confidence": 0.54, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.01, "1": 0.28, "2": 0.71}}}</t>
+          <t>{"failure_mode": {"type": "choice", "confidence": 0.6564551974427104, "choice": "flooding", "probabilities": {"flooding": 0.6564551974427104, "weeping": 0.013207449650020771, "foaming": 0.3055821752680637, "fouling": 0.004574747910430328, "reboiler_condenser": 0.004074720321028966, "instrument": 0.00389611920465889, "other": 0.012209590203086975}}, "containment": {"type": "noul", "confidence": 0.9338403184871535, "noul": 0.06615968151284642}, "load": {"type": "score", "confidence": 0.6137554280557379, "score": 1.4672523630413188, "probabilities": {"0": 0.14650306501441915, "1": 0.23974150692984292, "2": 0.6137554280557379}}, "urgency": {"type": "score", "confidence": 0.9751721173161316, "score": 1.9607843150977025, "probabilities": {"0": 0.014387802218429196, "1": 0.010440080465439186, "2": 0.9751721173161316}}, "impact": {"type": "score", "confidence": 0.8433683442914435, "score": 1.8182897430657157, "probabilities": {"0": 0.02507860122572771, "1": 0.13155305448282884, "2": 0.8433683442914435}}, "potential_impact": {"type": "score", "confidence": 0.7537415277615147, "score": 1.738873547266182, "probabilities": {"0": 0.014867980495332804, "1": 0.23139049174315252, "2": 0.7537415277615147}}, "off_spec": {"type": "noul", "confidence": 0.9562932354335837, "noul": 0.9562932354335837}, "stability": {"type": "score", "confidence": 0.891040773520861, "score": 1.8617649986818978, "probabilities": {"0": 0.029275774838962952, "1": 0.07968345164017597, "2": 0.891040773520861}}}</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3023,12 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 760, "output_tokens": 184}</t>
+          <t>{"input_tokens": 1237, "output_tokens": 0}</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>{"containment": {"type": "noul", "noul": 0.01}, "load": {"type": "score", "score": 1.0, "confidence": 1.0, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.0, "1": 1.0, "2": 0.0}}, "urgency": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "impact": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "potential_impact": {"type": "score", "score": 0.03, "confidence": 0.96, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.98, "1": 0.02, "2": 0.0}}, "off_spec": {"type": "noul", "noul": 0.01}, "stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "failure_mode": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"instrument": 0.0, "other": 1.0, "foaming": 0.0, "fouling": 0.0, "reboiler_condenser": 0.0, "flooding": 0.0, "weeping": 0.0}}}</t>
+          <t>{"failure_mode": {"type": "choice", "confidence": 0.9466925860999985, "choice": "other", "probabilities": {"flooding": 0.00659046658003055, "weeping": 0.013650097586510236, "foaming": 0.0040722866090719114, "fouling": 0.011932895527116853, "reboiler_condenser": 0.014694204851308752, "instrument": 0.0023674627459631973, "other": 0.9466925860999985}}, "containment": {"type": "noul", "confidence": 0.9492659532500998, "noul": 0.05073404674990022}, "load": {"type": "score", "confidence": 0.9367838391403669, "score": 1.0192654827464538, "probabilities": {"0": 0.02197533905658961, "1": 0.9367838391403669, "2": 0.041240821803043504}}, "urgency": {"type": "score", "confidence": 0.8947989958986674, "score": 0.13745921710985815, "probabilities": {"0": 0.8947989958986674, "1": 0.07294279109280712, "2": 0.03225821300852551}}, "impact": {"type": "score", "confidence": 0.9703695663705273, "score": 0.037828226642217716, "probabilities": {"0": 0.9703695663705273, "1": 0.021432640616727876, "2": 0.008197793012744918}}, "potential_impact": {"type": "score", "confidence": 0.6036773309179262, "score": 0.5136285965754814, "probabilities": {"0": 0.6036773309179262, "1": 0.2790167415886663, "2": 0.1173059274934076}}, "off_spec": {"type": "noul", "confidence": 0.950423993422423, "noul": 0.04957600657757703}, "stability": {"type": "score", "confidence": 0.9800865084202343, "score": 0.02475723940192736, "probabilities": {"0": 0.9800865084202343, "1": 0.015069743757604144, "2": 0.004843747822161609}}}</t>
         </is>
       </c>
     </row>
@@ -3300,13 +3037,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="20" min="1" max="1"/>
@@ -3316,11 +3053,6 @@
     <col width="10" customWidth="1" style="20" min="5" max="5"/>
     <col width="18" customWidth="1" style="20" min="6" max="6"/>
     <col width="16" customWidth="1" style="20" min="7" max="7"/>
-    <col width="14" customWidth="1" style="20" min="8" max="8"/>
-    <col width="9" customWidth="1" style="20" min="9" max="9"/>
-    <col width="10" customWidth="1" style="20" min="10" max="10"/>
-    <col width="20" customWidth="1" style="20" min="11" max="11"/>
-    <col width="20" customWidth="1" style="20" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3359,31 +3091,6 @@
           <t>mean_confidence</t>
         </is>
       </c>
-      <c r="H1" s="32" t="inlineStr">
-        <is>
-          <t>with_expected</t>
-        </is>
-      </c>
-      <c r="I1" s="32" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="J1" s="32" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="K1" s="32" t="inlineStr">
-        <is>
-          <t>mean_conf_when_correct</t>
-        </is>
-      </c>
-      <c r="L1" s="32" t="inlineStr">
-        <is>
-          <t>mean_conf_when_wrong</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
@@ -3411,21 +3118,8 @@
         <v>0</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="H2" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="33" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="L2" s="33" t="inlineStr"/>
+        <v>0.918</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
@@ -3453,21 +3147,8 @@
         <v>0</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="H3" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="33" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="L3" s="33" t="inlineStr"/>
+        <v>0.847</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="inlineStr">
@@ -3495,17 +3176,8 @@
         <v>3</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H4" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="33" t="inlineStr"/>
-      <c r="K4" s="33" t="inlineStr"/>
-      <c r="L4" s="33" t="inlineStr"/>
+        <v>0.666</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
@@ -3533,21 +3205,8 @@
         <v>1</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="H5" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="33" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="L5" s="33" t="inlineStr"/>
+        <v>0.839</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
@@ -3572,25 +3231,10 @@
         <v>6</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="H6" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K6" s="33" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L6" s="33" t="n">
-        <v>0.58</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="7">
@@ -3619,17 +3263,8 @@
         <v>1</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="33" t="inlineStr"/>
-      <c r="K7" s="33" t="inlineStr"/>
-      <c r="L7" s="33" t="inlineStr"/>
+        <v>0.713</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
@@ -3657,21 +3292,8 @@
         <v>0</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L8" s="33" t="inlineStr"/>
+        <v>0.819</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="inlineStr">
@@ -3699,21 +3321,8 @@
         <v>0</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H9" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="L9" s="33" t="inlineStr"/>
+        <v>0.953</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
@@ -3741,28 +3350,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="33" t="inlineStr"/>
+        <v>0.9360000000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3795,7 +3391,7 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>20260930_192615</t>
+          <t>20261026_103600</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3415,7 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>jev</t>
+          <t>jevk5</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3427,7 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>jev-1.13.0</t>
+          <t>alibiserikbay/JevK5</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3439,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>https://api.typesafe.ai</t>
+          <t>http://localhost:8090</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3451,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>remote:https://api.typesafe.ai</t>
+          <t>local:http://localhost:8090</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3463,7 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>c6060602276b</t>
+          <t>20bd4549a071</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3475,7 @@
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3535,7 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>3.5</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3547,7 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_jev_20260930_192615.jsonl</t>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_jevk5_20261026_103600.jsonl</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3559,7 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>6427</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3571,7 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3583,7 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>6427</t>
         </is>
       </c>
     </row>
@@ -4011,7 +3607,7 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>output_jev_Results, output_jev_Raw, output_jev_Summary, output_jev_Run_info</t>
+          <t>output_jevk5_Results, output_jevk5_Raw, output_jevk5_Summary, output_jevk5_Run_info</t>
         </is>
       </c>
     </row>
@@ -4020,25 +3616,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="20" min="1" max="1"/>
     <col width="22" customWidth="1" style="20" min="2" max="2"/>
     <col width="14" customWidth="1" style="20" min="3" max="3"/>
     <col width="14" customWidth="1" style="20" min="4" max="4"/>
-    <col width="8" customWidth="1" style="20" min="5" max="5"/>
+    <col width="10" customWidth="1" style="20" min="5" max="5"/>
     <col width="14" customWidth="1" style="20" min="6" max="6"/>
     <col width="14" customWidth="1" style="20" min="7" max="7"/>
-    <col width="12" customWidth="1" style="20" min="8" max="8"/>
-    <col width="12" customWidth="1" style="20" min="9" max="9"/>
-    <col width="12" customWidth="1" style="20" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4054,42 +3647,27 @@
       </c>
       <c r="C1" s="32" t="inlineStr">
         <is>
-          <t>nimble_answer</t>
+          <t>jev_answer</t>
         </is>
       </c>
       <c r="D1" s="32" t="inlineStr">
         <is>
-          <t>jev_answer</t>
+          <t>jevk5_answer</t>
         </is>
       </c>
       <c r="E1" s="32" t="inlineStr">
         <is>
-          <t>agree</t>
+          <t>all_agree</t>
         </is>
       </c>
       <c r="F1" s="32" t="inlineStr">
         <is>
-          <t>nimble_confidence</t>
+          <t>jev_confidence</t>
         </is>
       </c>
       <c r="G1" s="32" t="inlineStr">
         <is>
-          <t>jev_confidence</t>
-        </is>
-      </c>
-      <c r="H1" s="32" t="inlineStr">
-        <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="I1" s="32" t="inlineStr">
-        <is>
-          <t>nimble_correct</t>
-        </is>
-      </c>
-      <c r="J1" s="32" t="inlineStr">
-        <is>
-          <t>jev_correct</t>
+          <t>jevk5_confidence</t>
         </is>
       </c>
     </row>
@@ -4118,21 +3696,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="33" t="n">
-        <v>0.7691154479779605</v>
+        <v>0.88</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="H2" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I2" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" s="33" t="b">
-        <v>1</v>
+        <v>0.7065507973266721</v>
       </c>
     </row>
     <row r="3">
@@ -4160,21 +3727,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>0.8195945775641966</v>
+        <v>1</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>seal</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" s="33" t="b">
-        <v>1</v>
+        <v>0.9824340738888386</v>
       </c>
     </row>
     <row r="4">
@@ -4202,14 +3758,11 @@
         <v>1</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>0.2861003836327028</v>
+        <v>0.82</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="H4" s="33" t="inlineStr"/>
-      <c r="I4" s="33" t="inlineStr"/>
-      <c r="J4" s="33" t="inlineStr"/>
+        <v>0.5483561966627606</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="39" t="inlineStr">
@@ -4224,26 +3777,23 @@
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr">
+        <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="D5" s="39" t="inlineStr">
-        <is>
-          <t>high</t>
         </is>
       </c>
       <c r="E5" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="39" t="n">
-        <v>0.5252066897339631</v>
+        <v>0.26</v>
       </c>
       <c r="G5" s="39" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H5" s="39" t="inlineStr"/>
-      <c r="I5" s="39" t="inlineStr"/>
-      <c r="J5" s="39" t="inlineStr"/>
+        <v>0.5508631005132343</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
@@ -4270,14 +3820,11 @@
         <v>1</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.2688926828193108</v>
+        <v>0.67</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H6" s="33" t="inlineStr"/>
-      <c r="I6" s="33" t="inlineStr"/>
-      <c r="J6" s="33" t="inlineStr"/>
+        <v>0.8992780191968657</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
@@ -4304,21 +3851,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.4356639754842947</v>
+        <v>0.98</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="33" t="b">
-        <v>1</v>
+        <v>0.90947554364201</v>
       </c>
     </row>
     <row r="8">
@@ -4346,21 +3882,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>0.9858959050293358</v>
+        <v>0.99</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="33" t="b">
-        <v>1</v>
+        <v>0.9781857449061092</v>
       </c>
     </row>
     <row r="9">
@@ -4388,21 +3913,10 @@
         <v>1</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.9707274126385984</v>
+        <v>1</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="33" t="b">
-        <v>1</v>
+        <v>0.9610943867016385</v>
       </c>
     </row>
     <row r="10">
@@ -4430,14 +3944,11 @@
         <v>1</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.8060517778980076</v>
+        <v>0.96</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="H10" s="33" t="inlineStr"/>
-      <c r="I10" s="33" t="inlineStr"/>
-      <c r="J10" s="33" t="inlineStr"/>
+        <v>0.7321666759484706</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="inlineStr">
@@ -4464,14 +3975,11 @@
         <v>1</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.8107506949544721</v>
+        <v>0.96</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="H11" s="33" t="inlineStr"/>
-      <c r="I11" s="33" t="inlineStr"/>
-      <c r="J11" s="33" t="inlineStr"/>
+        <v>0.8084353234082341</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="inlineStr">
@@ -4498,14 +4006,11 @@
         <v>1</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.6617906884831326</v>
+        <v>0.88</v>
       </c>
       <c r="G12" s="33" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="H12" s="33" t="inlineStr"/>
-      <c r="I12" s="33" t="inlineStr"/>
-      <c r="J12" s="33" t="inlineStr"/>
+        <v>0.6134537990255072</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
@@ -4532,21 +4037,10 @@
         <v>1</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.9057681604539835</v>
+        <v>0.99</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H13" s="33" t="inlineStr">
-        <is>
-          <t>routine</t>
-        </is>
-      </c>
-      <c r="I13" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="33" t="b">
-        <v>1</v>
+        <v>0.9029075553748133</v>
       </c>
     </row>
     <row r="14">
@@ -4574,14 +4068,11 @@
         <v>1</v>
       </c>
       <c r="F14" s="33" t="n">
-        <v>0.9810367320377763</v>
+        <v>0.97</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="H14" s="33" t="inlineStr"/>
-      <c r="I14" s="33" t="inlineStr"/>
-      <c r="J14" s="33" t="inlineStr"/>
+        <v>0.8297088427074472</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
@@ -4608,21 +4099,10 @@
         <v>1</v>
       </c>
       <c r="F15" s="33" t="n">
-        <v>0.9600284507335518</v>
+        <v>0.85</v>
       </c>
       <c r="G15" s="33" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H15" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I15" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="33" t="b">
-        <v>1</v>
+        <v>0.734098606902861</v>
       </c>
     </row>
     <row r="16">
@@ -4650,21 +4130,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="33" t="n">
-        <v>0.8964189370932257</v>
+        <v>1</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="33" t="inlineStr">
-        <is>
-          <t>fouling</t>
-        </is>
-      </c>
-      <c r="I16" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" s="33" t="b">
-        <v>1</v>
+        <v>0.9801978339182461</v>
       </c>
     </row>
     <row r="17">
@@ -4692,21 +4161,10 @@
         <v>1</v>
       </c>
       <c r="F17" s="33" t="n">
-        <v>0.3072345881491388</v>
+        <v>0.86</v>
       </c>
       <c r="G17" s="33" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H17" s="33" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="I17" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="33" t="b">
-        <v>1</v>
+        <v>0.6286301802274425</v>
       </c>
     </row>
     <row r="18">
@@ -4734,82 +4192,73 @@
         <v>1</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>0.5793208854661729</v>
+        <v>0</v>
       </c>
       <c r="G18" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="33" t="inlineStr"/>
-      <c r="I18" s="33" t="inlineStr"/>
-      <c r="J18" s="33" t="inlineStr"/>
+        <v>0.5098955077545156</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="C19" s="39" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D19" s="39" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
       </c>
-      <c r="E19" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="39" t="n">
-        <v>0.2703462680038269</v>
-      </c>
-      <c r="G19" s="39" t="n">
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="33" t="n">
         <v>0.82</v>
       </c>
-      <c r="H19" s="39" t="inlineStr"/>
-      <c r="I19" s="39" t="inlineStr"/>
-      <c r="J19" s="39" t="inlineStr"/>
+      <c r="G19" s="33" t="n">
+        <v>0.503374419114064</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>routine</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>soon</t>
         </is>
       </c>
-      <c r="E20" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="39" t="n">
-        <v>0.4559468789770235</v>
-      </c>
-      <c r="G20" s="39" t="n">
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>soon</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="33" t="n">
         <v>0.29</v>
       </c>
-      <c r="H20" s="39" t="inlineStr"/>
-      <c r="I20" s="39" t="inlineStr"/>
-      <c r="J20" s="39" t="inlineStr"/>
+      <c r="G20" s="33" t="n">
+        <v>0.5198005205954765</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="39" t="inlineStr">
@@ -4824,26 +4273,23 @@
       </c>
       <c r="C21" s="39" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D21" s="39" t="inlineStr">
+        <is>
           <t>false</t>
-        </is>
-      </c>
-      <c r="D21" s="39" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
       <c r="E21" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F21" s="39" t="n">
-        <v>0.8231185626412096</v>
+        <v>0.67</v>
       </c>
       <c r="G21" s="39" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H21" s="39" t="inlineStr"/>
-      <c r="I21" s="39" t="inlineStr"/>
-      <c r="J21" s="39" t="inlineStr"/>
+        <v>0.6847134664950006</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="33" t="inlineStr">
@@ -4870,21 +4316,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="33" t="n">
-        <v>0.993523868071281</v>
+        <v>0.95</v>
       </c>
       <c r="G22" s="33" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H22" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I22" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" s="33" t="b">
-        <v>1</v>
+        <v>0.9040281719700221</v>
       </c>
     </row>
     <row r="23">
@@ -4912,21 +4347,10 @@
         <v>1</v>
       </c>
       <c r="F23" s="33" t="n">
-        <v>0.980827621350109</v>
+        <v>1</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="33" t="inlineStr">
-        <is>
-          <t>tube_leak</t>
-        </is>
-      </c>
-      <c r="I23" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" s="33" t="b">
-        <v>1</v>
+        <v>0.97878383278065</v>
       </c>
     </row>
     <row r="24">
@@ -4954,21 +4378,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>0.3120997517953533</v>
+        <v>0.58</v>
       </c>
       <c r="G24" s="33" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H24" s="33" t="inlineStr">
-        <is>
-          <t>severe</t>
-        </is>
-      </c>
-      <c r="I24" s="33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" s="33" t="b">
-        <v>0</v>
+        <v>0.6365532188860706</v>
       </c>
     </row>
     <row r="25">
@@ -4996,82 +4409,73 @@
         <v>1</v>
       </c>
       <c r="F25" s="33" t="n">
-        <v>0.7082652363052141</v>
+        <v>0.84</v>
       </c>
       <c r="G25" s="33" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H25" s="33" t="inlineStr"/>
-      <c r="I25" s="33" t="inlineStr"/>
-      <c r="J25" s="33" t="inlineStr"/>
+        <v>0.5742634787665343</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="C26" s="39" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="D26" s="39" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E26" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="39" t="n">
-        <v>0.2893414605806364</v>
-      </c>
-      <c r="G26" s="39" t="n">
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="33" t="n">
         <v>0.97</v>
       </c>
-      <c r="H26" s="39" t="inlineStr"/>
-      <c r="I26" s="39" t="inlineStr"/>
-      <c r="J26" s="39" t="inlineStr"/>
+      <c r="G26" s="33" t="n">
+        <v>0.9035722899097612</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="C27" s="39" t="inlineStr">
-        <is>
-          <t>soon</t>
-        </is>
-      </c>
-      <c r="D27" s="39" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>immediate</t>
         </is>
       </c>
-      <c r="E27" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="39" t="n">
-        <v>0.3004673764848859</v>
-      </c>
-      <c r="G27" s="39" t="n">
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="H27" s="39" t="inlineStr"/>
-      <c r="I27" s="39" t="inlineStr"/>
-      <c r="J27" s="39" t="inlineStr"/>
+      <c r="F27" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="33" t="n">
+        <v>0.8346517779922784</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="33" t="inlineStr">
@@ -5098,14 +4502,11 @@
         <v>1</v>
       </c>
       <c r="F28" s="33" t="n">
-        <v>0.9852695044791884</v>
+        <v>0.95</v>
       </c>
       <c r="G28" s="33" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H28" s="33" t="inlineStr"/>
-      <c r="I28" s="33" t="inlineStr"/>
-      <c r="J28" s="33" t="inlineStr"/>
+        <v>0.9338403184871535</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="33" t="inlineStr">
@@ -5132,56 +4533,42 @@
         <v>1</v>
       </c>
       <c r="F29" s="33" t="n">
-        <v>0.6803313388383841</v>
+        <v>0.83</v>
       </c>
       <c r="G29" s="33" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H29" s="33" t="inlineStr">
-        <is>
-          <t>flooding</t>
-        </is>
-      </c>
-      <c r="I29" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" s="33" t="b">
-        <v>1</v>
+        <v>0.6564551974427104</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C30" s="39" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="E30" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" s="33" t="n">
-        <v>0.1934498910234053</v>
-      </c>
-      <c r="G30" s="33" t="n">
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>severe</t>
+        </is>
+      </c>
+      <c r="E30" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="39" t="n">
         <v>0.52</v>
       </c>
-      <c r="H30" s="33" t="inlineStr"/>
-      <c r="I30" s="33" t="inlineStr"/>
-      <c r="J30" s="33" t="inlineStr"/>
+      <c r="G30" s="39" t="n">
+        <v>0.8433683442914435</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="39" t="inlineStr">
@@ -5196,26 +4583,23 @@
       </c>
       <c r="C31" s="39" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D31" s="39" t="inlineStr">
+        <is>
           <t>normal</t>
-        </is>
-      </c>
-      <c r="D31" s="39" t="inlineStr">
-        <is>
-          <t>high</t>
         </is>
       </c>
       <c r="E31" s="39" t="b">
         <v>0</v>
       </c>
       <c r="F31" s="39" t="n">
-        <v>0.188075872547421</v>
+        <v>0.54</v>
       </c>
       <c r="G31" s="39" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H31" s="39" t="inlineStr"/>
-      <c r="I31" s="39" t="inlineStr"/>
-      <c r="J31" s="39" t="inlineStr"/>
+        <v>0.6137554280557379</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="33" t="inlineStr">
@@ -5242,56 +4626,42 @@
         <v>1</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>0.9972499411450706</v>
+        <v>0.99</v>
       </c>
       <c r="G32" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H32" s="33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I32" s="33" t="b">
+        <v>0.9562932354335837</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>potential_impact</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="J32" s="33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="39" t="inlineStr">
-        <is>
-          <t>R005</t>
-        </is>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>potential_impact</t>
-        </is>
-      </c>
-      <c r="C33" s="39" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="D33" s="39" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E33" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="39" t="n">
-        <v>0.1714265267610506</v>
-      </c>
-      <c r="G33" s="39" t="n">
+      <c r="F33" s="33" t="n">
         <v>0.25</v>
       </c>
-      <c r="H33" s="39" t="inlineStr"/>
-      <c r="I33" s="39" t="inlineStr"/>
-      <c r="J33" s="39" t="inlineStr"/>
+      <c r="G33" s="33" t="n">
+        <v>0.7537415277615147</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="33" t="inlineStr">
@@ -5318,21 +4688,10 @@
         <v>1</v>
       </c>
       <c r="F34" s="33" t="n">
-        <v>0.8431627582980868</v>
+        <v>1</v>
       </c>
       <c r="G34" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="33" t="inlineStr">
-        <is>
-          <t>upset</t>
-        </is>
-      </c>
-      <c r="I34" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" s="33" t="b">
-        <v>1</v>
+        <v>0.891040773520861</v>
       </c>
     </row>
     <row r="35">
@@ -5360,14 +4719,11 @@
         <v>1</v>
       </c>
       <c r="F35" s="33" t="n">
-        <v>0.8091260652766668</v>
+        <v>1</v>
       </c>
       <c r="G35" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="33" t="inlineStr"/>
-      <c r="I35" s="33" t="inlineStr"/>
-      <c r="J35" s="33" t="inlineStr"/>
+        <v>0.9751721173161316</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="33" t="inlineStr">
@@ -5394,14 +4750,11 @@
         <v>1</v>
       </c>
       <c r="F36" s="33" t="n">
-        <v>0.9957133755759788</v>
+        <v>0.99</v>
       </c>
       <c r="G36" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H36" s="33" t="inlineStr"/>
-      <c r="I36" s="33" t="inlineStr"/>
-      <c r="J36" s="33" t="inlineStr"/>
+        <v>0.9492659532500998</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="33" t="inlineStr">
@@ -5428,21 +4781,10 @@
         <v>1</v>
       </c>
       <c r="F37" s="33" t="n">
-        <v>0.9363398600629796</v>
+        <v>1</v>
       </c>
       <c r="G37" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I37" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" s="33" t="b">
-        <v>1</v>
+        <v>0.9466925860999985</v>
       </c>
     </row>
     <row r="38">
@@ -5470,14 +4812,11 @@
         <v>1</v>
       </c>
       <c r="F38" s="33" t="n">
-        <v>0.954014606183754</v>
+        <v>1</v>
       </c>
       <c r="G38" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="33" t="inlineStr"/>
-      <c r="I38" s="33" t="inlineStr"/>
-      <c r="J38" s="33" t="inlineStr"/>
+        <v>0.9703695663705273</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="33" t="inlineStr">
@@ -5504,14 +4843,11 @@
         <v>1</v>
       </c>
       <c r="F39" s="33" t="n">
-        <v>0.9348095470889991</v>
+        <v>1</v>
       </c>
       <c r="G39" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="33" t="inlineStr"/>
-      <c r="I39" s="33" t="inlineStr"/>
-      <c r="J39" s="33" t="inlineStr"/>
+        <v>0.9367838391403669</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="33" t="inlineStr">
@@ -5538,56 +4874,42 @@
         <v>1</v>
       </c>
       <c r="F40" s="33" t="n">
-        <v>0.9947682918870171</v>
+        <v>0.99</v>
       </c>
       <c r="G40" s="33" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H40" s="33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I40" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" s="33" t="b">
-        <v>1</v>
+        <v>0.950423993422423</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="inlineStr">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="C41" s="33" t="inlineStr">
+      <c r="C41" s="39" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="D41" s="33" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="E41" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" s="33" t="n">
-        <v>0.9293340218130992</v>
-      </c>
-      <c r="G41" s="33" t="n">
+      <c r="D41" s="39" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="E41" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="39" t="n">
         <v>0.96</v>
       </c>
-      <c r="H41" s="33" t="inlineStr"/>
-      <c r="I41" s="33" t="inlineStr"/>
-      <c r="J41" s="33" t="inlineStr"/>
+      <c r="G41" s="39" t="n">
+        <v>0.6036773309179262</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
@@ -5614,21 +4936,10 @@
         <v>1</v>
       </c>
       <c r="F42" s="33" t="n">
-        <v>0.9531418933138464</v>
+        <v>1</v>
       </c>
       <c r="G42" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="33" t="inlineStr">
-        <is>
-          <t>stable</t>
-        </is>
-      </c>
-      <c r="I42" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" s="33" t="b">
-        <v>1</v>
+        <v>0.9800865084202343</v>
       </c>
     </row>
     <row r="43">
@@ -5656,14 +4967,11 @@
         <v>1</v>
       </c>
       <c r="F43" s="33" t="n">
-        <v>0.9150701099900012</v>
+        <v>1</v>
       </c>
       <c r="G43" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="33" t="inlineStr"/>
-      <c r="I43" s="33" t="inlineStr"/>
-      <c r="J43" s="33" t="inlineStr"/>
+        <v>0.8947989958986674</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5714,7 +5022,7 @@
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>nimble (local Ollama) or jev (TypeSafe). CLI --engine overrides this. Preset sets model/base_url/endpoint.</t>
+          <t>nimble | jev | jevk5. CLI --engine overrides. Preset sets model/base_url/endpoint.</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5039,7 @@
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>Overridden by engine preset at runtime (nimble or jev-1.13.0). Kept for reference.</t>
+          <t>Overridden by engine preset (nimble, jev-1.13.0, or alibiserikbay/JevK5).</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5056,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>Overridden by engine preset (localhost:11434 or https://api.typesafe.ai).</t>
+          <t>Overridden by preset (Ollama :11434, TypeSafe cloud, or JevK5 :8090).</t>
         </is>
       </c>
     </row>
@@ -5832,12 +5140,12 @@
     <row r="10" ht="15" customHeight="1" s="20">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>record_text_column</t>
+          <t>record_statement_column</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -5888,7 +5196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="19" min="1" max="1"/>
@@ -5932,21 +5240,6 @@
           <t>active</t>
         </is>
       </c>
-      <c r="G1" s="19" t="inlineStr">
-        <is>
-          <t>review_below</t>
-        </is>
-      </c>
-      <c r="H1" s="19" t="inlineStr">
-        <is>
-          <t>label_count</t>
-        </is>
-      </c>
-      <c r="I1" s="19" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="20">
       <c r="A2" s="19" t="inlineStr">
@@ -5974,14 +5267,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H2" s="19">
-        <f>IF(A2="","",COUNTIF(Labels!$A$2:$A$300,A2))</f>
-        <v/>
-      </c>
-      <c r="I2" s="19">
-        <f>IF(A2="","",IF(COUNTIF($A$2:$A$60,A2)&gt;1,"Duplicate question_id",IF(E2="","Missing instructions",IF(D2="noul",IF(H2=0,"OK","noul takes no labels"),IF(OR(D2="choice",D2="score"),IF(H2&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
-      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="20">
       <c r="A3" s="19" t="inlineStr">
@@ -6001,21 +5286,13 @@
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>Does the text describe process fluid leaking out of the equipment to the surroundings?</t>
+          <t>Does the statement describe process fluid leaking out of the equipment to the surroundings?</t>
         </is>
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
-      </c>
-      <c r="H3" s="19">
-        <f>IF(A3="","",COUNTIF(Labels!$A$2:$A$300,A3))</f>
-        <v/>
-      </c>
-      <c r="I3" s="19">
-        <f>IF(A3="","",IF(COUNTIF($A$2:$A$60,A3)&gt;1,"Duplicate question_id",IF(E3="","Missing instructions",IF(D3="noul",IF(H3=0,"OK","noul takes no labels"),IF(OR(D3="choice",D3="score"),IF(H3&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="20">
@@ -6029,7 +5306,6 @@
           <t>Load</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr"/>
       <c r="D4" s="19" t="inlineStr">
         <is>
           <t>score</t>
@@ -6044,14 +5320,6 @@
         <is>
           <t>Y</t>
         </is>
-      </c>
-      <c r="H4" s="19">
-        <f>IF(A4="","",COUNTIF(Labels!$A$2:$A$300,A4))</f>
-        <v/>
-      </c>
-      <c r="I4" s="19">
-        <f>IF(A4="","",IF(COUNTIF($A$2:$A$60,A4)&gt;1,"Duplicate question_id",IF(E4="","Missing instructions",IF(D4="noul",IF(H4=0,"OK","noul takes no labels"),IF(OR(D4="choice",D4="score"),IF(H4&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="20">
@@ -6080,14 +5348,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H5" s="19">
-        <f>IF(A5="","",COUNTIF(Labels!$A$2:$A$300,A5))</f>
-        <v/>
-      </c>
-      <c r="I5" s="19">
-        <f>IF(A5="","",IF(COUNTIF($A$2:$A$60,A5)&gt;1,"Duplicate question_id",IF(E5="","Missing instructions",IF(D5="noul",IF(H5=0,"OK","noul takes no labels"),IF(OR(D5="choice",D5="score"),IF(H5&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
-      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
       <c r="A6" s="19" t="inlineStr">
@@ -6115,14 +5375,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H6" s="19">
-        <f>IF(A6="","",COUNTIF(Labels!$A$2:$A$300,A6))</f>
-        <v/>
-      </c>
-      <c r="I6" s="19">
-        <f>IF(A6="","",IF(COUNTIF($A$2:$A$60,A6)&gt;1,"Duplicate question_id",IF(E6="","Missing instructions",IF(D6="noul",IF(H6=0,"OK","noul takes no labels"),IF(OR(D6="choice",D6="score"),IF(H6&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
-      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
       <c r="A7" s="19" t="inlineStr">
@@ -6135,7 +5387,6 @@
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr"/>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>score</t>
@@ -6150,14 +5401,6 @@
         <is>
           <t>Y</t>
         </is>
-      </c>
-      <c r="H7" s="19">
-        <f>IF(A7="","",COUNTIF(Labels!$A$2:$A$300,A7))</f>
-        <v/>
-      </c>
-      <c r="I7" s="19">
-        <f>IF(A7="","",IF(COUNTIF($A$2:$A$60,A7)&gt;1,"Duplicate question_id",IF(E7="","Missing instructions",IF(D7="noul",IF(H7=0,"OK","noul takes no labels"),IF(OR(D7="choice",D7="score"),IF(H7&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
@@ -6183,21 +5426,13 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>Does the text suggest mixing of shell-side and tube-side fluids (e.g. from a tube leak)?</t>
+          <t>Does the statement suggest mixing of shell-side and tube-side fluids (e.g. from a tube leak)?</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
-      </c>
-      <c r="H8" s="19">
-        <f>IF(A8="","",COUNTIF(Labels!$A$2:$A$300,A8))</f>
-        <v/>
-      </c>
-      <c r="I8" s="19">
-        <f>IF(A8="","",IF(COUNTIF($A$2:$A$60,A8)&gt;1,"Duplicate question_id",IF(E8="","Missing instructions",IF(D8="noul",IF(H8=0,"OK","noul takes no labels"),IF(OR(D8="choice",D8="score"),IF(H8&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="20">
@@ -6223,21 +5458,13 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>Does the text mention off-spec product?</t>
+          <t>Does the statement mention off-spec product?</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
-      </c>
-      <c r="H9" s="19">
-        <f>IF(A9="","",COUNTIF(Labels!$A$2:$A$300,A9))</f>
-        <v/>
-      </c>
-      <c r="I9" s="19">
-        <f>IF(A9="","",IF(COUNTIF($A$2:$A$60,A9)&gt;1,"Duplicate question_id",IF(E9="","Missing instructions",IF(D9="noul",IF(H9=0,"OK","noul takes no labels"),IF(OR(D9="choice",D9="score"),IF(H9&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
@@ -6270,14 +5497,6 @@
         <is>
           <t>Y</t>
         </is>
-      </c>
-      <c r="H10" s="19">
-        <f>IF(A10="","",COUNTIF(Labels!$A$2:$A$300,A10))</f>
-        <v/>
-      </c>
-      <c r="I10" s="19">
-        <f>IF(A10="","",IF(COUNTIF($A$2:$A$60,A10)&gt;1,"Duplicate question_id",IF(E10="","Missing instructions",IF(D10="noul",IF(H10=0,"OK","noul takes no labels"),IF(OR(D10="choice",D10="score"),IF(H10&gt;=2,"OK","Needs 2+ labels"),"Type must be choice, noul or score")))))</f>
-        <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="20"/>
@@ -6336,22 +5555,15 @@
       <formula>AND(H2&lt;&gt;"",LEFT(H2,2)&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation sqref="C2:C60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pump,Heat Exchanger,Distillation Column"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"choice,noul,score"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="E2:E60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Y,N"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>Lists!$A$2:$A$30</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Enter a value between 0 and 1" type="decimal" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -6366,7 +5578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="19" min="1" max="1"/>
@@ -6402,11 +5614,6 @@
           <t>order</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="20">
       <c r="A2" s="19" t="inlineStr">
@@ -7019,7 +6226,6 @@
           <t>load</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr"/>
       <c r="C28" s="19" t="inlineStr">
         <is>
           <t>low</t>
@@ -7040,7 +6246,6 @@
           <t>load</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
       <c r="C29" s="19" t="inlineStr">
         <is>
           <t>normal</t>
@@ -7061,7 +6266,6 @@
           <t>load</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
       <c r="C30" s="19" t="inlineStr">
         <is>
           <t>high</t>
@@ -7082,7 +6286,6 @@
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr"/>
       <c r="C31" s="19" t="inlineStr">
         <is>
           <t>low</t>
@@ -7103,7 +6306,6 @@
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr"/>
       <c r="C32" s="19" t="inlineStr">
         <is>
           <t>moderate</t>
@@ -7124,7 +6326,6 @@
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr"/>
       <c r="C33" s="19" t="inlineStr">
         <is>
           <t>high</t>
@@ -7412,10 +6613,12 @@
       <formula>AND(E2&lt;&gt;"",LEFT(E2,2)&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pump,Heat Exchanger,Distillation Column"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A2:A300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Questions!$A$2:$A$60</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -7430,7 +6633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="19" min="1" max="1"/>
@@ -7459,57 +6662,7 @@
       </c>
       <c r="D1" s="19" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E1" s="19" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t>expected_failure_mode</t>
-        </is>
-      </c>
-      <c r="G1" s="19" t="inlineStr">
-        <is>
-          <t>expected_containment</t>
-        </is>
-      </c>
-      <c r="H1" s="19" t="inlineStr">
-        <is>
-          <t>expected_load</t>
-        </is>
-      </c>
-      <c r="I1" s="19" t="inlineStr">
-        <is>
-          <t>expected_urgency</t>
-        </is>
-      </c>
-      <c r="J1" s="19" t="inlineStr">
-        <is>
-          <t>expected_impact</t>
-        </is>
-      </c>
-      <c r="K1" s="19" t="inlineStr">
-        <is>
-          <t>expected_potential_impact</t>
-        </is>
-      </c>
-      <c r="L1" s="19" t="inlineStr">
-        <is>
-          <t>expected_cross_contamination</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="inlineStr">
-        <is>
-          <t>expected_off_spec</t>
-        </is>
-      </c>
-      <c r="N1" s="19" t="inlineStr">
-        <is>
-          <t>expected_stability</t>
+          <t>statement</t>
         </is>
       </c>
     </row>
@@ -7534,21 +6687,6 @@
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
-        <is>
-          <t>seal</t>
-        </is>
-      </c>
-      <c r="G2" s="19" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I2" s="19" t="inlineStr">
-        <is>
-          <t>immediate</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="23.25" customHeight="1" s="20">
       <c r="A3" s="19" t="inlineStr">
@@ -7571,21 +6709,6 @@
           <t>Routine check on P-114 shows slightly elevated bearing temperature. Watch at next planned PM.</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I3" s="19" t="inlineStr">
-        <is>
-          <t>routine</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="23.25" customHeight="1" s="20">
       <c r="A4" s="19" t="inlineStr">
@@ -7608,21 +6731,6 @@
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
-        <is>
-          <t>fouling</t>
-        </is>
-      </c>
-      <c r="J4" s="19" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="20">
       <c r="A5" s="19" t="inlineStr">
@@ -7645,21 +6753,6 @@
           <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>tube_leak</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
-        <is>
-          <t>severe</t>
-        </is>
-      </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
       <c r="A6" s="19" t="inlineStr">
@@ -7682,21 +6775,6 @@
           <t>C-301 dP spiking, bottoms level unstable, overhead product off-spec since 14:20.</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>flooding</t>
-        </is>
-      </c>
-      <c r="M6" s="19" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="N6" s="19" t="inlineStr">
-        <is>
-          <t>upset</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
       <c r="A7" s="19" t="inlineStr">
@@ -7717,21 +6795,6 @@
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>C-402 running steady at rate. Reflux and reboiler duty normal, no alarms this shift.</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="M7" s="19" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="N7" s="19" t="inlineStr">
-        <is>
-          <t>stable</t>
         </is>
       </c>
     </row>
@@ -8234,22 +7297,9 @@
       <formula>AND(E2&lt;&gt;"",LEFT(E2,2)&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>Lists!$A$2:$A$30</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"true,false"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"true,false"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"true,false"</formula1>
-      <formula2>0</formula2>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pump,Heat Exchanger,Distillation Column"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -8259,131 +7309,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:A30"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="26" customWidth="1" style="19" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" s="20">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>equipment_types</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="20">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Pump</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="20">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>Heat Exchanger</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="20">
-      <c r="A4" s="24" t="inlineStr">
-        <is>
-          <t>Distillation Column</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="20">
-      <c r="A5" s="24" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="20">
-      <c r="A6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="20">
-      <c r="A7" s="24" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="20">
-      <c r="A8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="20">
-      <c r="A9" s="24" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="20">
-      <c r="A10" s="24" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="20">
-      <c r="A11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="20">
-      <c r="A12" s="24" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="20">
-      <c r="A13" s="24" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="20">
-      <c r="A14" s="24" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="20">
-      <c r="A15" s="24" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="20">
-      <c r="A16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="20">
-      <c r="A17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="20">
-      <c r="A18" s="24" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="20">
-      <c r="A19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="20">
-      <c r="A20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="20">
-      <c r="A21" s="24" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="20">
-      <c r="A22" s="24" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="20">
-      <c r="A23" s="24" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="20">
-      <c r="A24" s="24" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="20">
-      <c r="A25" s="24" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="20">
-      <c r="A26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="20">
-      <c r="A27" s="24" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="20">
-      <c r="A28" s="24" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="20">
-      <c r="A29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="20">
-      <c r="A30" s="24" t="n"/>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8424,7 +7349,7 @@
       </c>
       <c r="D1" s="32" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E1" s="32" t="inlineStr">
@@ -8505,10 +7430,10 @@
         </is>
       </c>
       <c r="H2" s="35" t="n">
-        <v>0.8195945775641966</v>
+        <v>1</v>
       </c>
       <c r="I2" s="35" t="n">
-        <v>0.9403764383354369</v>
+        <v>1</v>
       </c>
       <c r="J2" s="33" t="b">
         <v>0</v>
@@ -8553,10 +7478,10 @@
         </is>
       </c>
       <c r="H3" s="35" t="n">
-        <v>0.7691154479779605</v>
+        <v>0.88</v>
       </c>
       <c r="I3" s="35" t="n">
-        <v>0.7691154479779605</v>
+        <v>0.88</v>
       </c>
       <c r="J3" s="33" t="b">
         <v>0</v>
@@ -8597,180 +7522,168 @@
       </c>
       <c r="G4" s="36" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H4" s="38" t="n">
-        <v>0.5252066897339631</v>
+        <v>0.26</v>
       </c>
       <c r="I4" s="38" t="n">
-        <v>1.101685927779176</v>
+        <v>1.51</v>
       </c>
       <c r="J4" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="36" t="inlineStr">
         <is>
-          <t>load: low confidence (0.53)</t>
+          <t>load: low confidence (0.26)</t>
         </is>
       </c>
       <c r="L4" s="36" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>immediate</t>
         </is>
       </c>
-      <c r="H5" s="38" t="n">
-        <v>0.4356639754842947</v>
-      </c>
-      <c r="I5" s="38" t="n">
-        <v>1.744118329531175</v>
-      </c>
-      <c r="J5" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="36" t="inlineStr">
-        <is>
-          <t>urgency: low confidence (0.44)</t>
-        </is>
-      </c>
-      <c r="L5" s="36" t="inlineStr"/>
+      <c r="H5" s="35" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J5" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="33" t="inlineStr"/>
+      <c r="L5" s="33" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F6" s="36" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G6" s="36" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="H6" s="38" t="n">
-        <v>0.2861003836327028</v>
-      </c>
-      <c r="I6" s="38" t="n">
-        <v>1.099536415201052</v>
-      </c>
-      <c r="J6" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="36" t="inlineStr">
-        <is>
-          <t>impact: low confidence (0.29)</t>
-        </is>
-      </c>
-      <c r="L6" s="36" t="inlineStr"/>
+      <c r="H6" s="35" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J6" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="33" t="inlineStr"/>
+      <c r="L6" s="33" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>P-101A</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>P-101A discharge pressure fluctuating, seal leak observed, standby pump started.</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="G7" s="36" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="H7" s="38" t="n">
-        <v>0.2688926828193108</v>
-      </c>
-      <c r="I7" s="38" t="n">
-        <v>1.58153004084961</v>
-      </c>
-      <c r="J7" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="36" t="inlineStr">
-        <is>
-          <t>potential_impact: low confidence (0.27)</t>
-        </is>
-      </c>
-      <c r="L7" s="36" t="inlineStr"/>
+      <c r="H7" s="35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J7" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="33" t="inlineStr"/>
+      <c r="L7" s="33" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
@@ -8809,10 +7722,10 @@
         </is>
       </c>
       <c r="H8" s="35" t="n">
-        <v>0.9707274126385984</v>
+        <v>1</v>
       </c>
       <c r="I8" s="35" t="n">
-        <v>0.99356430421049</v>
+        <v>1</v>
       </c>
       <c r="J8" s="33" t="b">
         <v>0</v>
@@ -8857,10 +7770,10 @@
         </is>
       </c>
       <c r="H9" s="35" t="n">
-        <v>0.9858959050293358</v>
+        <v>0.99</v>
       </c>
       <c r="I9" s="35" t="n">
-        <v>0.01410409497066424</v>
+        <v>0.01</v>
       </c>
       <c r="J9" s="33" t="b">
         <v>0</v>
@@ -8905,10 +7818,10 @@
         </is>
       </c>
       <c r="H10" s="35" t="n">
-        <v>0.8107506949544721</v>
+        <v>0.96</v>
       </c>
       <c r="I10" s="35" t="n">
-        <v>0.9830735117434298</v>
+        <v>1.02</v>
       </c>
       <c r="J10" s="33" t="b">
         <v>0</v>
@@ -8953,10 +7866,10 @@
         </is>
       </c>
       <c r="H11" s="35" t="n">
-        <v>0.9057681604539835</v>
+        <v>0.99</v>
       </c>
       <c r="I11" s="35" t="n">
-        <v>0.02394660660151229</v>
+        <v>0.01</v>
       </c>
       <c r="J11" s="33" t="b">
         <v>0</v>
@@ -9001,10 +7914,10 @@
         </is>
       </c>
       <c r="H12" s="35" t="n">
-        <v>0.8060517778980076</v>
+        <v>0.96</v>
       </c>
       <c r="I12" s="35" t="n">
-        <v>0.05461874556361802</v>
+        <v>0.03</v>
       </c>
       <c r="J12" s="33" t="b">
         <v>0</v>
@@ -9049,10 +7962,10 @@
         </is>
       </c>
       <c r="H13" s="35" t="n">
-        <v>0.6617906884831326</v>
+        <v>0.88</v>
       </c>
       <c r="I13" s="35" t="n">
-        <v>0.9272016948488913</v>
+        <v>0.96</v>
       </c>
       <c r="J13" s="33" t="b">
         <v>0</v>
@@ -9097,10 +8010,10 @@
         </is>
       </c>
       <c r="H14" s="35" t="n">
-        <v>0.8964189370932257</v>
+        <v>1</v>
       </c>
       <c r="I14" s="35" t="n">
-        <v>0.9680451306120793</v>
+        <v>1</v>
       </c>
       <c r="J14" s="33" t="b">
         <v>0</v>
@@ -9145,10 +8058,10 @@
         </is>
       </c>
       <c r="H15" s="35" t="n">
-        <v>0.9810367320377763</v>
+        <v>0.97</v>
       </c>
       <c r="I15" s="35" t="n">
-        <v>0.01896326796222373</v>
+        <v>0.03</v>
       </c>
       <c r="J15" s="33" t="b">
         <v>0</v>
@@ -9193,17 +8106,17 @@
         </is>
       </c>
       <c r="H16" s="38" t="n">
-        <v>0.5793208854661729</v>
+        <v>0</v>
       </c>
       <c r="I16" s="38" t="n">
-        <v>0.9234640502322689</v>
+        <v>1.19</v>
       </c>
       <c r="J16" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
-          <t>load: low confidence (0.58)</t>
+          <t>load: low confidence (0.00)</t>
         </is>
       </c>
       <c r="L16" s="36" t="inlineStr"/>
@@ -9241,128 +8154,120 @@
       </c>
       <c r="G17" s="36" t="inlineStr">
         <is>
-          <t>routine</t>
+          <t>soon</t>
         </is>
       </c>
       <c r="H17" s="38" t="n">
-        <v>0.4559468789770235</v>
+        <v>0.29</v>
       </c>
       <c r="I17" s="38" t="n">
-        <v>0.2398700214389179</v>
+        <v>0.95</v>
       </c>
       <c r="J17" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
-          <t>urgency: low confidence (0.46)</t>
+          <t>urgency: low confidence (0.29)</t>
         </is>
       </c>
       <c r="L17" s="36" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>E-205</t>
         </is>
       </c>
-      <c r="D18" s="37" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="E18" s="36" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="F18" s="36" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="G18" s="36" t="inlineStr">
+      <c r="G18" s="33" t="inlineStr">
         <is>
           <t>degraded</t>
         </is>
       </c>
-      <c r="H18" s="38" t="n">
-        <v>0.3072345881491388</v>
-      </c>
-      <c r="I18" s="38" t="n">
-        <v>0.7770780189312785</v>
-      </c>
-      <c r="J18" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="36" t="inlineStr">
-        <is>
-          <t>impact: low confidence (0.31)</t>
-        </is>
-      </c>
-      <c r="L18" s="36" t="inlineStr"/>
+      <c r="H18" s="35" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J18" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="33" t="inlineStr"/>
+      <c r="L18" s="33" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>E-205</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>E-205 outlet temperature 15 C below normal, dP up over last two weeks, cleaning scheduled.</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="F19" s="36" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="G19" s="36" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H19" s="38" t="n">
-        <v>0.2703462680038269</v>
-      </c>
-      <c r="I19" s="38" t="n">
-        <v>0.4875360292089463</v>
-      </c>
-      <c r="J19" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="36" t="inlineStr">
-        <is>
-          <t>potential_impact: low confidence (0.27)</t>
-        </is>
-      </c>
-      <c r="L19" s="36" t="inlineStr"/>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J19" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="33" t="inlineStr"/>
+      <c r="L19" s="33" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="33" t="inlineStr">
@@ -9401,10 +8306,10 @@
         </is>
       </c>
       <c r="H20" s="35" t="n">
-        <v>0.9600284507335518</v>
+        <v>0.85</v>
       </c>
       <c r="I20" s="35" t="n">
-        <v>0.0399715492664482</v>
+        <v>0.15</v>
       </c>
       <c r="J20" s="33" t="b">
         <v>0</v>
@@ -9449,10 +8354,10 @@
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>0.980827621350109</v>
+        <v>1</v>
       </c>
       <c r="I21" s="35" t="n">
-        <v>0.9960106591003453</v>
+        <v>1</v>
       </c>
       <c r="J21" s="33" t="b">
         <v>0</v>
@@ -9493,14 +8398,14 @@
       </c>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="H22" s="35" t="n">
-        <v>0.8231185626412096</v>
+        <v>0.67</v>
       </c>
       <c r="I22" s="35" t="n">
-        <v>0.1768814373587904</v>
+        <v>0.67</v>
       </c>
       <c r="J22" s="33" t="b">
         <v>0</v>
@@ -9545,10 +8450,10 @@
         </is>
       </c>
       <c r="H23" s="35" t="n">
-        <v>0.7082652363052141</v>
+        <v>0.84</v>
       </c>
       <c r="I23" s="35" t="n">
-        <v>1.023989710490751</v>
+        <v>1.09</v>
       </c>
       <c r="J23" s="33" t="b">
         <v>0</v>
@@ -9557,56 +8462,52 @@
       <c r="L23" s="33" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>E-310</t>
         </is>
       </c>
-      <c r="D24" s="37" t="inlineStr">
+      <c r="D24" s="34" t="inlineStr">
         <is>
           <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>urgency</t>
         </is>
       </c>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="G24" s="36" t="inlineStr">
-        <is>
-          <t>soon</t>
-        </is>
-      </c>
-      <c r="H24" s="38" t="n">
-        <v>0.3004673764848859</v>
-      </c>
-      <c r="I24" s="38" t="n">
-        <v>1.331217847775203</v>
-      </c>
-      <c r="J24" s="36" t="b">
+      <c r="G24" s="33" t="inlineStr">
+        <is>
+          <t>immediate</t>
+        </is>
+      </c>
+      <c r="H24" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="K24" s="36" t="inlineStr">
-        <is>
-          <t>urgency: low confidence (0.30)</t>
-        </is>
-      </c>
-      <c r="L24" s="36" t="inlineStr"/>
+      <c r="I24" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" s="33" t="inlineStr"/>
+      <c r="L24" s="33" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="36" t="inlineStr">
@@ -9645,72 +8546,68 @@
         </is>
       </c>
       <c r="H25" s="38" t="n">
-        <v>0.3120997517953533</v>
+        <v>0.58</v>
       </c>
       <c r="I25" s="38" t="n">
-        <v>1.139766134713401</v>
+        <v>1.21</v>
       </c>
       <c r="J25" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K25" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.31)</t>
+          <t>impact: low confidence (0.58)</t>
         </is>
       </c>
       <c r="L25" s="36" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Heat Exchanger</t>
         </is>
       </c>
-      <c r="C26" s="36" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>E-310</t>
         </is>
       </c>
-      <c r="D26" s="37" t="inlineStr">
+      <c r="D26" s="34" t="inlineStr">
         <is>
           <t>Cooling water pH dropped and hydrocarbon detected in E-310 cooling water return. Suspect tube leak.</t>
         </is>
       </c>
-      <c r="E26" s="36" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>potential_impact</t>
         </is>
       </c>
-      <c r="F26" s="36" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>Potential impact</t>
         </is>
       </c>
-      <c r="G26" s="36" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="H26" s="38" t="n">
-        <v>0.2893414605806364</v>
-      </c>
-      <c r="I26" s="38" t="n">
-        <v>1.342348590487079</v>
-      </c>
-      <c r="J26" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="36" t="inlineStr">
-        <is>
-          <t>potential_impact: low confidence (0.29)</t>
-        </is>
-      </c>
-      <c r="L26" s="36" t="inlineStr"/>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J26" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" s="33" t="inlineStr"/>
+      <c r="L26" s="33" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="33" t="inlineStr">
@@ -9749,10 +8646,10 @@
         </is>
       </c>
       <c r="H27" s="35" t="n">
-        <v>0.993523868071281</v>
+        <v>0.95</v>
       </c>
       <c r="I27" s="35" t="n">
-        <v>0.993523868071281</v>
+        <v>0.95</v>
       </c>
       <c r="J27" s="33" t="b">
         <v>0</v>
@@ -9797,10 +8694,10 @@
         </is>
       </c>
       <c r="H28" s="35" t="n">
-        <v>0.6803313388383841</v>
+        <v>0.83</v>
       </c>
       <c r="I28" s="35" t="n">
-        <v>0.7658952561283315</v>
+        <v>0.86</v>
       </c>
       <c r="J28" s="33" t="b">
         <v>0</v>
@@ -9845,10 +8742,10 @@
         </is>
       </c>
       <c r="H29" s="35" t="n">
-        <v>0.9852695044791884</v>
+        <v>0.95</v>
       </c>
       <c r="I29" s="35" t="n">
-        <v>0.01473049552081164</v>
+        <v>0.05</v>
       </c>
       <c r="J29" s="33" t="b">
         <v>0</v>
@@ -9889,21 +8786,21 @@
       </c>
       <c r="G30" s="36" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H30" s="38" t="n">
-        <v>0.188075872547421</v>
+        <v>0.54</v>
       </c>
       <c r="I30" s="38" t="n">
-        <v>1.299708878369453</v>
+        <v>1.69</v>
       </c>
       <c r="J30" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K30" s="36" t="inlineStr">
         <is>
-          <t>load: low confidence (0.19)</t>
+          <t>load: low confidence (0.54)</t>
         </is>
       </c>
       <c r="L30" s="36" t="inlineStr"/>
@@ -9945,10 +8842,10 @@
         </is>
       </c>
       <c r="H31" s="35" t="n">
-        <v>0.8091260652766668</v>
+        <v>1</v>
       </c>
       <c r="I31" s="35" t="n">
-        <v>1.937812200817456</v>
+        <v>2</v>
       </c>
       <c r="J31" s="33" t="b">
         <v>0</v>
@@ -9993,17 +8890,17 @@
         </is>
       </c>
       <c r="H32" s="38" t="n">
-        <v>0.1934498910234053</v>
+        <v>0.52</v>
       </c>
       <c r="I32" s="38" t="n">
-        <v>1.417932638835096</v>
+        <v>1.32</v>
       </c>
       <c r="J32" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K32" s="36" t="inlineStr">
         <is>
-          <t>impact: low confidence (0.19)</t>
+          <t>impact: low confidence (0.52)</t>
         </is>
       </c>
       <c r="L32" s="36" t="inlineStr"/>
@@ -10041,21 +8938,21 @@
       </c>
       <c r="G33" s="36" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H33" s="38" t="n">
-        <v>0.1714265267610506</v>
+        <v>0.25</v>
       </c>
       <c r="I33" s="38" t="n">
-        <v>1.337527379063873</v>
+        <v>1.5</v>
       </c>
       <c r="J33" s="36" t="b">
         <v>1</v>
       </c>
       <c r="K33" s="36" t="inlineStr">
         <is>
-          <t>potential_impact: low confidence (0.17)</t>
+          <t>potential_impact: low confidence (0.25)</t>
         </is>
       </c>
       <c r="L33" s="36" t="inlineStr"/>
@@ -10097,10 +8994,10 @@
         </is>
       </c>
       <c r="H34" s="35" t="n">
-        <v>0.9972499411450706</v>
+        <v>0.99</v>
       </c>
       <c r="I34" s="35" t="n">
-        <v>0.9972499411450706</v>
+        <v>0.99</v>
       </c>
       <c r="J34" s="33" t="b">
         <v>0</v>
@@ -10145,10 +9042,10 @@
         </is>
       </c>
       <c r="H35" s="35" t="n">
-        <v>0.8431627582980868</v>
+        <v>1</v>
       </c>
       <c r="I35" s="35" t="n">
-        <v>1.943775069671376</v>
+        <v>2</v>
       </c>
       <c r="J35" s="33" t="b">
         <v>0</v>
@@ -10193,10 +9090,10 @@
         </is>
       </c>
       <c r="H36" s="35" t="n">
-        <v>0.9363398600629796</v>
+        <v>1</v>
       </c>
       <c r="I36" s="35" t="n">
-        <v>0.9784069191734092</v>
+        <v>1</v>
       </c>
       <c r="J36" s="33" t="b">
         <v>0</v>
@@ -10241,10 +9138,10 @@
         </is>
       </c>
       <c r="H37" s="35" t="n">
-        <v>0.9957133755759788</v>
+        <v>0.99</v>
       </c>
       <c r="I37" s="35" t="n">
-        <v>0.004286624424021187</v>
+        <v>0.01</v>
       </c>
       <c r="J37" s="33" t="b">
         <v>0</v>
@@ -10289,10 +9186,10 @@
         </is>
       </c>
       <c r="H38" s="35" t="n">
-        <v>0.9348095470889991</v>
+        <v>1</v>
       </c>
       <c r="I38" s="35" t="n">
-        <v>0.9944437539675687</v>
+        <v>1</v>
       </c>
       <c r="J38" s="33" t="b">
         <v>0</v>
@@ -10337,10 +9234,10 @@
         </is>
       </c>
       <c r="H39" s="35" t="n">
-        <v>0.9150701099900012</v>
+        <v>1</v>
       </c>
       <c r="I39" s="35" t="n">
-        <v>0.02285845930706045</v>
+        <v>0</v>
       </c>
       <c r="J39" s="33" t="b">
         <v>0</v>
@@ -10385,10 +9282,10 @@
         </is>
       </c>
       <c r="H40" s="35" t="n">
-        <v>0.954014606183754</v>
+        <v>1</v>
       </c>
       <c r="I40" s="35" t="n">
-        <v>0.009865682566864381</v>
+        <v>0</v>
       </c>
       <c r="J40" s="33" t="b">
         <v>0</v>
@@ -10433,10 +9330,10 @@
         </is>
       </c>
       <c r="H41" s="35" t="n">
-        <v>0.9293340218130992</v>
+        <v>0.96</v>
       </c>
       <c r="I41" s="35" t="n">
-        <v>0.01860644816057358</v>
+        <v>0.03</v>
       </c>
       <c r="J41" s="33" t="b">
         <v>0</v>
@@ -10481,10 +9378,10 @@
         </is>
       </c>
       <c r="H42" s="35" t="n">
-        <v>0.9947682918870171</v>
+        <v>0.99</v>
       </c>
       <c r="I42" s="35" t="n">
-        <v>0.00523170811298286</v>
+        <v>0.01</v>
       </c>
       <c r="J42" s="33" t="b">
         <v>0</v>
@@ -10529,10 +9426,10 @@
         </is>
       </c>
       <c r="H43" s="35" t="n">
-        <v>0.9531418933138464</v>
+        <v>1</v>
       </c>
       <c r="I43" s="35" t="n">
-        <v>0.01156392735957413</v>
+        <v>0</v>
       </c>
       <c r="J43" s="33" t="b">
         <v>0</v>
@@ -10545,7 +9442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10584,12 +9481,12 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 3431, "output_tokens": 7}</t>
+          <t>{"input_tokens": 643, "output_tokens": 129}</t>
         </is>
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "seal", "probabilities": {"seal": 0.9403764383354369, "bearing": 0.023752584592859, "cavitation": 0.02777636530316554, "instrument": 0.002736962400376868, "other": 0.005357649368161494}, "confidence": 0.8195945775641966}, "containment": {"type": "noul", "noul": 0.7691154479779605}, "load": {"type": "score", "score": 1.1016859277791764, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.03030890919098518, "1": 0.8376962538388533, "2": 0.13199483697016162}, "confidence": 0.5252066897339631}, "urgency": {"type": "score", "score": 1.7441183295311746, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.025617318730848933, "1": 0.20464703300712783, "2": 0.7697356482620233}, "confidence": 0.4356639754842947}, "impact": {"type": "score", "score": 1.0995364152010518, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.09479898270390513, "1": 0.7108656193911379, "2": 0.19433539790495694}, "confidence": 0.28610038363270285}, "potential_impact": {"type": "score", "score": 1.5815300408496102, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.04895136691935876, "1": 0.3205672253116721, "2": 0.6304814077689691}, "confidence": 0.2688926828193108}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "seal", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "instrument": 0.0, "bearing": 0.0, "other": 0.0, "seal": 1.0}}, "containment": {"type": "noul", "noul": 0.88}, "load": {"type": "score", "score": 1.51, "confidence": 0.26, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.04, "1": 0.41, "2": 0.55}}, "urgency": {"type": "score", "score": 1.99, "confidence": 0.98, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.01, "2": 0.99}}, "impact": {"type": "score", "score": 1.12, "confidence": 0.82, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.88, "2": 0.12}}, "potential_impact": {"type": "score", "score": 1.78, "confidence": 0.67, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.22, "2": 0.78}}}</t>
         </is>
       </c>
     </row>
@@ -10601,12 +9498,12 @@
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 3437, "output_tokens": 7}</t>
+          <t>{"input_tokens": 642, "output_tokens": 129}</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "bearing", "probabilities": {"seal": 0.00271844877009735, "bearing": 0.99356430421049, "cavitation": 0.0014845156733352789, "instrument": 0.0006423127261355957, "other": 0.0015904186199419271}, "confidence": 0.9707274126385984}, "containment": {"type": "noul", "noul": 0.01410409497066424}, "load": {"type": "score", "score": 0.9830735117434298, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.03050219630445108, "1": 0.9559220956476682, "2": 0.013575708047880834}, "confidence": 0.810750694954472}, "urgency": {"type": "score", "score": 0.023946606601512287, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.981450571740185, "1": 0.013152249918117795, "2": 0.005397178341697247}, "confidence": 0.9057681604539835}, "impact": {"type": "score", "score": 0.054618745563618024, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.9509405327056056, "1": 0.043500189025170735, "2": 0.005559278269223646}, "confidence": 0.8060517778980076}, "potential_impact": {"type": "score", "score": 0.9272016948488913, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.08743343556647779, "1": 0.897931434018153, "2": 0.01463513041536913}, "confidence": 0.6617906884831326}}</t>
+          <t>{"load": {"type": "score", "score": 1.02, "confidence": 0.96, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.0, "1": 0.98, "2": 0.02}}, "urgency": {"type": "score", "score": 0.01, "confidence": 0.99, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.99, "1": 0.01, "2": 0.0}}, "impact": {"type": "score", "score": 0.03, "confidence": 0.96, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.97, "1": 0.03, "2": 0.0}}, "potential_impact": {"type": "score", "score": 0.96, "confidence": 0.88, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.06, "1": 0.92, "2": 0.02}}, "failure_mode": {"type": "choice", "choice": "bearing", "confidence": 1.0, "probabilities": {"cavitation": 0.0, "instrument": 0.0, "seal": 0.0, "other": 0.0, "bearing": 1.0}}, "containment": {"type": "noul", "noul": 0.01}}</t>
         </is>
       </c>
     </row>
@@ -10618,12 +9515,12 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 4529, "output_tokens": 8}</t>
+          <t>{"input_tokens": 687, "output_tokens": 159}</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "probabilities": {"fouling": 0.9680451306120793, "tube_leak": 0.023515279230748413, "flow_maldistribution": 0.005935079187159576, "control_valve": 0.0009338859656491551, "other": 0.001570625004363632}, "confidence": 0.8964189370932257}, "containment": {"type": "noul", "noul": 0.018963267962223727}, "load": {"type": "score", "score": 0.9234640502322689, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.10501361956542159, "1": 0.8665087106368881, "2": 0.028477669797690393}, "confidence": 0.5793208854661729}, "urgency": {"type": "score", "score": 0.2398700214389179, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.8066961046405768, "1": 0.14673776927992832, "2": 0.04656612607949479}, "confidence": 0.45594687897702346}, "impact": {"type": "score", "score": 0.7770780189312785, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.27090379744411325, "1": 0.681114386180495, "2": 0.04798181637539171}, "confidence": 0.30723458814913884}, "potential_impact": {"type": "score", "score": 0.48753602920894634, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.5430191923742405, "1": 0.4264255860425726, "2": 0.03055522158318688}, "confidence": 0.2703462680038269}, "cross_contamination": {"type": "noul", "noul": 0.0399715492664482}}</t>
+          <t>{"failure_mode": {"type": "choice", "choice": "fouling", "confidence": 1.0, "probabilities": {"control_valve": 0.0, "flow_maldistribution": 0.0, "tube_leak": 0.0, "fouling": 1.0, "other": 0.0}}, "containment": {"type": "noul", "noul": 0.03}, "load": {"type": "score", "score": 1.19, "confidence": 0.0, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.35, "1": 0.12, "2": 0.53}}, "urgency": {"type": "score", "score": 0.95, "confidence": 0.29, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.26, "1": 0.53, "2": 0.21}}, "impact": {"type": "score", "score": 1.09, "confidence": 0.86, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.91, "2": 0.09}}, "potential_impact": {"type": "score", "score": 1.11, "confidence": 0.82, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.01, "1": 0.87, "2": 0.12}}, "cross_contamination": {"type": "noul", "noul": 0.15}}</t>
         </is>
       </c>
     </row>
@@ -10635,12 +9532,12 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 4522, "output_tokens": 8}</t>
+          <t>{"input_tokens": 690, "output_tokens": 159}</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "tube_leak", "probabilities": {"fouling": 0.0012215421919611676, "tube_leak": 0.9960106591003453, "flow_maldistribution": 0.001772688409883248, "control_valve": 0.00026080847162997516, "other": 0.0007343018261804486}, "confidence": 0.980827621350109}, "containment": {"type": "noul", "noul": 0.17688143735879036}, "load": {"type": "score", "score": 1.0239897104907512, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.026435554656885116, "1": 0.9231391801954787, "2": 0.05042526514763627}, "confidence": 0.7082652363052141}, "urgency": {"type": "score", "score": 1.3312178477752035, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.028142554477525075, "1": 0.6124970432697464, "2": 0.3593604022527285}, "confidence": 0.30046737648488586}, "impact": {"type": "score", "score": 1.1397661347134012, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.07158432231093885, "1": 0.7170652206647211, "2": 0.21135045702434}, "confidence": 0.3120997517953533}, "potential_impact": {"type": "score", "score": 1.3423485904870789, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.03001426440708731, "1": 0.5976228806987464, "2": 0.37236285489416626}, "confidence": 0.28934146058063637}, "cross_contamination": {"type": "noul", "noul": 0.993523868071281}}</t>
+          <t>{"containment": {"type": "noul", "noul": 0.67}, "load": {"type": "score", "score": 1.09, "confidence": 0.84, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.01, "1": 0.89, "2": 0.1}}, "urgency": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "impact": {"type": "score", "score": 1.21, "confidence": 0.58, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.03, "1": 0.72, "2": 0.25}}, "potential_impact": {"type": "score", "score": 1.98, "confidence": 0.97, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.02, "2": 0.98}}, "cross_contamination": {"type": "noul", "noul": 0.95}, "failure_mode": {"type": "choice", "choice": "tube_leak", "confidence": 1.0, "probabilities": {"tube_leak": 1.0, "control_valve": 0.0, "flow_maldistribution": 0.0, "other": 0.0, "fouling": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -10652,12 +9549,12 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 5871, "output_tokens": 9}</t>
+          <t>{"input_tokens": 762, "output_tokens": 186}</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "flooding", "probabilities": {"flooding": 0.7658952561283315, "weeping": 0.008919577166532836, "foaming": 0.21745773872133595, "fouling": 0.0013342903862147107, "reboiler_condenser": 0.0005000774452204862, "instrument": 0.005652697246225303, "other": 0.0002403629061388724}, "confidence": 0.6803313388383841}, "containment": {"type": "noul", "noul": 0.014730495520811644}, "load": {"type": "score", "score": 1.2997088783694535, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.07551032772657393, "1": 0.5492704661773986, "2": 0.37521920609602744}, "confidence": 0.18807587254742097}, "urgency": {"type": "score", "score": 1.937812200817456, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.018368378254247305, "1": 0.02545104267404942, "2": 0.9561805790717033}, "confidence": 0.8091260652766668}, "impact": {"type": "score", "score": 1.4179326388350961, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.06393700472216769, "1": 0.45419335172056846, "2": 0.4818696435572638}, "confidence": 0.19344989102340526}, "potential_impact": {"type": "score", "score": 1.3375273790638733, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.07889131789555637, "1": 0.5046899851450138, "2": 0.41641869695942973}, "confidence": 0.17142652676105063}, "off_spec": {"type": "noul", "noul": 0.9972499411450706}, "stability": {"type": "score", "score": 1.943775069671376, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.021825125227392647, "1": 0.01257467987383881, "2": 0.9656001948987686}, "confidence": 0.8431627582980868}}</t>
+          <t>{"urgency": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "impact": {"type": "score", "score": 1.32, "confidence": 0.52, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.0, "1": 0.68, "2": 0.32}}, "potential_impact": {"type": "score", "score": 1.5, "confidence": 0.25, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.0, "1": 0.49, "2": 0.51}}, "off_spec": {"type": "noul", "noul": 0.99}, "stability": {"type": "score", "score": 2.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.0, "1": 0.0, "2": 1.0}}, "failure_mode": {"type": "choice", "choice": "flooding", "confidence": 0.83, "probabilities": {"other": 0.03, "flooding": 0.86, "instrument": 0.07, "fouling": 0.0, "foaming": 0.04, "weeping": 0.0, "reboiler_condenser": 0.0}}, "containment": {"type": "noul", "noul": 0.05}, "load": {"type": "score", "score": 1.69, "confidence": 0.54, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.01, "1": 0.28, "2": 0.71}}}</t>
         </is>
       </c>
     </row>
@@ -10669,12 +9566,12 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>{"input_tokens": 5855, "output_tokens": 9}</t>
+          <t>{"input_tokens": 760, "output_tokens": 184}</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>{"failure_mode": {"type": "choice", "choice": "other", "probabilities": {"flooding": 0.015310150196454458, "weeping": 0.003729595689138417, "foaming": 0.0009179110234264862, "fouling": 0.001424967860907713, "reboiler_condenser": 0.00012948811605478457, "instrument": 8.09679406090723e-05, "other": 0.9784069191734092}, "confidence": 0.9363398600629796}, "containment": {"type": "noul", "noul": 0.004286624424021187}, "load": {"type": "score", "score": 0.9944437539675687, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.008743324738875088, "1": 0.988069596554681, "2": 0.003187078706443858}, "confidence": 0.9348095470889991}, "urgency": {"type": "score", "score": 0.02285845930706045, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 0.9839212234793119, "1": 0.009299093734315722, "2": 0.006779682786372365}, "confidence": 0.9150701099900012}, "impact": {"type": "score", "score": 0.00986568256686438, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 0.992105930482838, "1": 0.005922456467459379, "2": 0.001971613049702501}, "confidence": 0.954014606183754}, "potential_impact": {"type": "score", "score": 0.01860644816057358, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.9871339026939872, "1": 0.0071257464514525295, "2": 0.005740350854560525}, "confidence": 0.9293340218130992}, "off_spec": {"type": "noul", "noul": 0.00523170811298286}, "stability": {"type": "score", "score": 0.011563927359574127, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 0.9921165372801404, "1": 0.004202998080145225, "2": 0.003680464639714451}, "confidence": 0.9531418933138464}}</t>
+          <t>{"containment": {"type": "noul", "noul": 0.01}, "load": {"type": "score", "score": 1.0, "confidence": 1.0, "legend": {"0": "Well below normal or design duty", "1": "Around normal / design duty", "2": "At or above design; stressed"}, "probabilities": {"0": 0.0, "1": 1.0, "2": 0.0}}, "urgency": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Can wait for the next planned window", "1": "Should be handled within days", "2": "Needs attention now"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "impact": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "No noticeable impact", "1": "Reduced duty but operating", "2": "Major loss of duty or unit unusable"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "potential_impact": {"type": "score", "score": 0.03, "confidence": 0.96, "legend": {"0": "Limited consequence if left alone", "1": "Notable production or reliability risk", "2": "Serious safety, environmental, or unit risk"}, "probabilities": {"0": 0.98, "1": 0.02, "2": 0.0}}, "off_spec": {"type": "noul", "noul": 0.01}, "stability": {"type": "score", "score": 0.0, "confidence": 1.0, "legend": {"0": "Steady operation", "1": "Drifting or minor swings", "2": "Significant upset"}, "probabilities": {"0": 1.0, "1": 0.0, "2": 0.0}}, "failure_mode": {"type": "choice", "choice": "other", "confidence": 1.0, "probabilities": {"instrument": 0.0, "other": 1.0, "foaming": 0.0, "fouling": 0.0, "reboiler_condenser": 0.0, "flooding": 0.0, "weeping": 0.0}}}</t>
         </is>
       </c>
     </row>
@@ -10683,7 +9580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10794,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="33" t="n">
-        <v>0.881</v>
+        <v>0.972</v>
       </c>
       <c r="H2" s="33" t="n">
         <v>6</v>
@@ -10806,7 +9703,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="33" t="n">
-        <v>0.881</v>
+        <v>0.972</v>
       </c>
       <c r="L2" s="33" t="inlineStr"/>
     </row>
@@ -10836,7 +9733,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>0.923</v>
+        <v>0.908</v>
       </c>
       <c r="H3" s="33" t="n">
         <v>2</v>
@@ -10848,7 +9745,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="33" t="n">
-        <v>0.878</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="L3" s="33" t="inlineStr"/>
     </row>
@@ -10878,7 +9775,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>0.624</v>
+        <v>0.6</v>
       </c>
       <c r="H4" s="33" t="n">
         <v>0</v>
@@ -10913,10 +9810,10 @@
         <v>6</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>0.637</v>
+        <v>0.877</v>
       </c>
       <c r="H5" s="33" t="n">
         <v>2</v>
@@ -10928,7 +9825,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="33" t="n">
-        <v>0.671</v>
+        <v>0.985</v>
       </c>
       <c r="L5" s="33" t="inlineStr"/>
     </row>
@@ -10955,10 +9852,10 @@
         <v>6</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0.476</v>
+        <v>0.79</v>
       </c>
       <c r="H6" s="33" t="n">
         <v>2</v>
@@ -10970,10 +9867,10 @@
         <v>0.5</v>
       </c>
       <c r="K6" s="33" t="n">
-        <v>0.307</v>
+        <v>0.86</v>
       </c>
       <c r="L6" s="33" t="n">
-        <v>0.312</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="7">
@@ -10999,10 +9896,10 @@
         <v>6</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>0.432</v>
+        <v>0.758</v>
       </c>
       <c r="H7" s="33" t="n">
         <v>0</v>
@@ -11040,7 +9937,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>0.977</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="33" t="n">
         <v>2</v>
@@ -11052,7 +9949,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="33" t="n">
-        <v>0.977</v>
+        <v>0.9</v>
       </c>
       <c r="L8" s="33" t="inlineStr"/>
     </row>
@@ -11082,7 +9979,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>0.996</v>
+        <v>0.99</v>
       </c>
       <c r="H9" s="33" t="n">
         <v>2</v>
@@ -11094,7 +9991,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="33" t="n">
-        <v>0.996</v>
+        <v>0.99</v>
       </c>
       <c r="L9" s="33" t="inlineStr"/>
     </row>
@@ -11124,7 +10021,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
       <c r="H10" s="33" t="n">
         <v>2</v>
@@ -11136,9 +10033,267 @@
         <v>1</v>
       </c>
       <c r="K10" s="33" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
       <c r="L10" s="33" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" style="20" min="1" max="1"/>
+    <col width="70" customWidth="1" style="20" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="32" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>run_started</t>
+        </is>
+      </c>
+      <c r="B2" s="33" t="inlineStr">
+        <is>
+          <t>20260930_192615</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>engine</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>jev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>jev-1.13.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>base_url</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>https://api.typesafe.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>endpoint_info</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>remote:https://api.typesafe.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>questions_hash</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>c6060602276b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>api_key_configured</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>records_in_run</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>records_completed</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>failed_records</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>review_threshold_default</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>elapsed_seconds</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>/mnt/d/dev/nimble_plant/nimble_classifier_workbook_jev_20260930_192615.jsonl</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>4184</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>5130</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>records_with_usage</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>output_sheets</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>output_jev_Results, output_jev_Raw, output_jev_Summary, output_jev_Run_info</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
